--- a/files/NRL_upcoming_projections.xlsx
+++ b/files/NRL_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -86,43 +86,40 @@
     <t xml:space="preserve">Rain Total Adj</t>
   </si>
   <si>
+    <t xml:space="preserve">16:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accor Stadium, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Rain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">same_city_different_ground</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1H</t>
+  </si>
+  <si>
     <t xml:space="preserve">19:50</t>
   </si>
   <si>
-    <t xml:space="preserve">manly-warringah sea eagles</t>
-  </si>
-  <si>
     <t xml:space="preserve">south sydney rabbitohs</t>
   </si>
   <si>
-    <t xml:space="preserve">4 Pines Park, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Rain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">same_city_different_ground</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">melbourne storm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">newcastle knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AAMI Park, Melbourne</t>
+    <t xml:space="preserve">brisbane broncos</t>
   </si>
   <si>
     <t xml:space="preserve">diff_city</t>
@@ -131,73 +128,46 @@
     <t xml:space="preserve">20:00</t>
   </si>
   <si>
+    <t xml:space="preserve">dolphins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suncorp Stadium, Brisbane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Go Media Stadium, Auckland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:35</t>
+  </si>
+  <si>
     <t xml:space="preserve">canberra raiders</t>
   </si>
   <si>
-    <t xml:space="preserve">sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GIO Stadium, Canberra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north queensland cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Queensland Country Bank Stadium, Townsville</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
+    <t xml:space="preserve">CommBank Stadium, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wests tigers</t>
   </si>
   <si>
     <t xml:space="preserve">gold coast titans</t>
   </si>
   <si>
-    <t xml:space="preserve">Suncorp Stadium, Brisbane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wests tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penrith panthers</t>
-  </si>
-  <si>
     <t xml:space="preserve">Leichhardt Oval, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st george-illawarra dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sharks Stadium, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accor Stadium, Sydney</t>
   </si>
 </sst>
 </file>
@@ -548,9 +518,9 @@
     <col min="1" max="1" width="4.9975" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="4.9975" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="25.5775" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="23.8625" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="23.005" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="14.43" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="37.5825" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="23.005" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="11.8575" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="14.43" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="14.43" hidden="0" customWidth="1"/>
@@ -647,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>24</v>
@@ -659,7 +629,7 @@
         <v>26</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>27</v>
@@ -671,28 +641,28 @@
         <v>29</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>-3.5</v>
+        <v>-6</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>50.5</v>
+        <v>51</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>-2.08</v>
+        <v>-2.95</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>47.44</v>
+        <v>49.84</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>-2.13</v>
+        <v>0.6</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>47.7</v>
+        <v>48.48</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>30</v>
@@ -701,19 +671,19 @@
         <v>1</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>-0.14</v>
+        <v>-0.15</v>
       </c>
       <c r="T2" s="4" t="n">
-        <v>-1.83</v>
+        <v>-2.01</v>
       </c>
       <c r="U2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>-0.21</v>
+        <v>1.96</v>
       </c>
       <c r="W2" s="4" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="X2" s="4" t="n">
         <v>0</v>
@@ -721,7 +691,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>24</v>
@@ -733,7 +703,7 @@
         <v>26</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>27</v>
@@ -745,28 +715,28 @@
         <v>31</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-3.5</v>
+        <v>-6</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>50.5</v>
+        <v>51</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>-2.08</v>
+        <v>-2.9</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>47.44</v>
+        <v>48.19</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>-2.13</v>
+        <v>0.6</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>47.7</v>
+        <v>48.48</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>30</v>
@@ -775,27 +745,27 @@
         <v>1</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>-0.14</v>
+        <v>-0.15</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>-1.83</v>
+        <v>-2.01</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>-0.21</v>
+        <v>1.96</v>
       </c>
       <c r="W3" s="4" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="X3" s="4" t="n">
-        <v>0</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>24</v>
@@ -807,7 +777,7 @@
         <v>26</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>27</v>
@@ -819,28 +789,28 @@
         <v>29</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-3.5</v>
+        <v>-6</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>50.5</v>
+        <v>51</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>-1.04</v>
+        <v>-1.48</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>23.72</v>
+        <v>24.92</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>-1.06</v>
+        <v>0.3</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>23.85</v>
+        <v>24.24</v>
       </c>
       <c r="Q4" s="3" t="s">
         <v>30</v>
@@ -849,16 +819,16 @@
         <v>0.5</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>-0.07</v>
+        <v>-0.08</v>
       </c>
       <c r="T4" s="4" t="n">
-        <v>-0.91</v>
+        <v>-1</v>
       </c>
       <c r="U4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>-0.1</v>
+        <v>0.98</v>
       </c>
       <c r="W4" s="4" t="n">
         <v>2.04</v>
@@ -869,7 +839,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>24</v>
@@ -881,7 +851,7 @@
         <v>26</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>27</v>
@@ -893,28 +863,28 @@
         <v>31</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-3.5</v>
+        <v>-6</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>50.5</v>
+        <v>51</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>-1.04</v>
+        <v>-1.45</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>23.72</v>
+        <v>24.1</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>-1.06</v>
+        <v>0.3</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>23.85</v>
+        <v>24.24</v>
       </c>
       <c r="Q5" s="3" t="s">
         <v>30</v>
@@ -923,27 +893,27 @@
         <v>0.5</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>-0.07</v>
+        <v>-0.08</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>-0.91</v>
+        <v>-1</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>-0.1</v>
+        <v>0.98</v>
       </c>
       <c r="W5" s="4" t="n">
         <v>2.04</v>
       </c>
       <c r="X5" s="4" t="n">
-        <v>0</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46178</v>
+        <v>46184</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>33</v>
@@ -955,10 +925,10 @@
         <v>35</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>28</v>
@@ -973,43 +943,43 @@
         <v>1</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-4</v>
+        <v>-3.5</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>49</v>
+        <v>50.5</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-5.38</v>
+        <v>-9.86</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>47.66</v>
+        <v>47.13</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-1.34</v>
+        <v>-0.73</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>44.79</v>
+        <v>48.29</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R6" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-1.83</v>
+        <v>-2.01</v>
       </c>
       <c r="U6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="X6" s="4" t="n">
         <v>0</v>
@@ -1017,7 +987,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46178</v>
+        <v>46184</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>33</v>
@@ -1029,10 +999,10 @@
         <v>35</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>28</v>
@@ -1047,51 +1017,51 @@
         <v>1</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-4</v>
+        <v>-3.5</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>49</v>
+        <v>50.5</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-5.2</v>
+        <v>-9.86</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>44.65</v>
+        <v>47.13</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-1.34</v>
+        <v>-0.73</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>44.79</v>
+        <v>48.29</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R7" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-1.83</v>
+        <v>-2.01</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.19</v>
+        <v>0</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-3.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46178</v>
+        <v>46184</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>33</v>
@@ -1103,10 +1073,10 @@
         <v>35</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>32</v>
@@ -1121,40 +1091,40 @@
         <v>1</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-4</v>
+        <v>-3.5</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>49</v>
+        <v>50.5</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-2.69</v>
+        <v>-4.93</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>23.83</v>
+        <v>23.57</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.67</v>
+        <v>-0.37</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>22.4</v>
+        <v>24.15</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R8" s="4" t="n">
         <v>1.25</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.91</v>
+        <v>-1</v>
       </c>
       <c r="U8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="W8" s="4" t="n">
         <v>2.04</v>
@@ -1165,7 +1135,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46178</v>
+        <v>46184</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>33</v>
@@ -1177,10 +1147,10 @@
         <v>35</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>32</v>
@@ -1195,66 +1165,66 @@
         <v>1</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-4</v>
+        <v>-3.5</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>49</v>
+        <v>50.5</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-2.6</v>
+        <v>-4.93</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>22.32</v>
+        <v>23.57</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.67</v>
+        <v>-0.37</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>22.4</v>
+        <v>24.15</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R9" s="4" t="n">
         <v>1.25</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.91</v>
+        <v>-1</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="W9" s="4" t="n">
         <v>2.04</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46178</v>
+        <v>46185</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="E10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>28</v>
@@ -1269,43 +1239,43 @@
         <v>1</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2.5</v>
+        <v>-2.5</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>49.5</v>
+        <v>51.5</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-3.86</v>
+        <v>-6.14</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>46.83</v>
+        <v>46.05</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-5</v>
+        <v>-1.95</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>47.1</v>
+        <v>46.71</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R10" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.29</v>
+        <v>-0.03</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-1.83</v>
+        <v>-2.01</v>
       </c>
       <c r="U10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.41</v>
+        <v>-0.59</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="X10" s="4" t="n">
         <v>0</v>
@@ -1313,22 +1283,22 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46178</v>
+        <v>46185</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>28</v>
@@ -1343,66 +1313,66 @@
         <v>1</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.5</v>
+        <v>-2.5</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>49.5</v>
+        <v>51.5</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-3.85</v>
+        <v>-6.14</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>46.64</v>
+        <v>46.05</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-5</v>
+        <v>-1.95</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>47.1</v>
+        <v>46.71</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R11" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.29</v>
+        <v>-0.03</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-1.83</v>
+        <v>-2.01</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.41</v>
+        <v>-0.59</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46178</v>
+        <v>46185</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>32</v>
@@ -1417,40 +1387,40 @@
         <v>1</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.5</v>
+        <v>-2.5</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>49.5</v>
+        <v>51.5</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.93</v>
+        <v>-3.07</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>23.42</v>
+        <v>23.03</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.5</v>
+        <v>-0.97</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>23.55</v>
+        <v>23.36</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R12" s="4" t="n">
         <v>1.25</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.14</v>
+        <v>-0.02</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.91</v>
+        <v>-1</v>
       </c>
       <c r="U12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.2</v>
+        <v>-0.29</v>
       </c>
       <c r="W12" s="4" t="n">
         <v>2.04</v>
@@ -1461,22 +1431,22 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46178</v>
+        <v>46185</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="E13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>32</v>
@@ -1491,66 +1461,66 @@
         <v>1</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>2.5</v>
+        <v>-2.5</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>49.5</v>
+        <v>51.5</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.93</v>
+        <v>-3.07</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>23.32</v>
+        <v>23.03</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.5</v>
+        <v>-0.97</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>23.55</v>
+        <v>23.36</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R13" s="4" t="n">
         <v>1.25</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.14</v>
+        <v>-0.02</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.91</v>
+        <v>-1</v>
       </c>
       <c r="U13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.2</v>
+        <v>-0.29</v>
       </c>
       <c r="W13" s="4" t="n">
         <v>2.04</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46179</v>
+        <v>46186</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="E14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>28</v>
@@ -1565,43 +1535,43 @@
         <v>1</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>4.5</v>
+        <v>-8.5</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>55</v>
+        <v>49.5</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-8.97</v>
+        <v>2.15</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>49.87</v>
+        <v>46.63</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-10.77</v>
+        <v>2.52</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>50.55</v>
+        <v>47.24</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R14" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.36</v>
+        <v>-0.01</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-1.83</v>
+        <v>-2.01</v>
       </c>
       <c r="U14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>1.91</v>
+        <v>-0.3</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="X14" s="4" t="n">
         <v>0</v>
@@ -1609,22 +1579,22 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46179</v>
+        <v>46186</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>28</v>
@@ -1639,43 +1609,43 @@
         <v>1</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>4.5</v>
+        <v>-8.5</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>55</v>
+        <v>49.5</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-8.97</v>
+        <v>2.15</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>49.87</v>
+        <v>46.63</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-10.77</v>
+        <v>2.52</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>50.55</v>
+        <v>47.24</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R15" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.36</v>
+        <v>-0.01</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-1.83</v>
+        <v>-2.01</v>
       </c>
       <c r="U15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>1.91</v>
+        <v>-0.3</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="X15" s="4" t="n">
         <v>0</v>
@@ -1683,22 +1653,22 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46179</v>
+        <v>46186</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>32</v>
@@ -1713,40 +1683,40 @@
         <v>1</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>4.5</v>
+        <v>-8.5</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>55</v>
+        <v>49.5</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-4.48</v>
+        <v>1.08</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>24.94</v>
+        <v>23.31</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-5.39</v>
+        <v>1.26</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>25.28</v>
+        <v>23.62</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R16" s="4" t="n">
         <v>1.25</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.18</v>
+        <v>-0.01</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.91</v>
+        <v>-1</v>
       </c>
       <c r="U16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.95</v>
+        <v>-0.15</v>
       </c>
       <c r="W16" s="4" t="n">
         <v>2.04</v>
@@ -1757,22 +1727,22 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46179</v>
+        <v>46186</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="E17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>32</v>
@@ -1787,40 +1757,40 @@
         <v>1</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>4.5</v>
+        <v>-8.5</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>55</v>
+        <v>49.5</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-4.48</v>
+        <v>1.08</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>24.94</v>
+        <v>23.31</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-5.39</v>
+        <v>1.26</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>25.28</v>
+        <v>23.62</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R17" s="4" t="n">
         <v>1.25</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.18</v>
+        <v>-0.01</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.91</v>
+        <v>-1</v>
       </c>
       <c r="U17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.95</v>
+        <v>-0.15</v>
       </c>
       <c r="W17" s="4" t="n">
         <v>2.04</v>
@@ -1831,22 +1801,22 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46179</v>
+        <v>46186</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="E18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>28</v>
@@ -1861,43 +1831,43 @@
         <v>1</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-8.5</v>
+        <v>3.5</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>51</v>
+        <v>50.5</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.76</v>
+        <v>-2.56</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>47.16</v>
+        <v>47.18</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-5.96</v>
+        <v>-0.72</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>48.03</v>
+        <v>47.89</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R18" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.15</v>
+        <v>-0.01</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-1.83</v>
+        <v>-2.01</v>
       </c>
       <c r="U18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="X18" s="4" t="n">
         <v>0</v>
@@ -1905,22 +1875,22 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46179</v>
+        <v>46186</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="E19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>28</v>
@@ -1935,43 +1905,43 @@
         <v>1</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-8.5</v>
+        <v>3.5</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>51</v>
+        <v>50.5</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.76</v>
+        <v>-2.56</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>47.16</v>
+        <v>47.18</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-5.96</v>
+        <v>-0.72</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>48.03</v>
+        <v>47.89</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R19" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.15</v>
+        <v>-0.01</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-1.83</v>
+        <v>-2.01</v>
       </c>
       <c r="U19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="X19" s="4" t="n">
         <v>0</v>
@@ -1979,22 +1949,22 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46179</v>
+        <v>46186</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="E20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>32</v>
@@ -2009,40 +1979,40 @@
         <v>1</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-8.5</v>
+        <v>3.5</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>51</v>
+        <v>50.5</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.88</v>
+        <v>-1.28</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>23.58</v>
+        <v>23.59</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-2.98</v>
+        <v>-0.36</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>24.02</v>
+        <v>23.95</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R20" s="4" t="n">
         <v>1.25</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.07</v>
+        <v>-0.01</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.91</v>
+        <v>-1</v>
       </c>
       <c r="U20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.1</v>
+        <v>-0.15</v>
       </c>
       <c r="W20" s="4" t="n">
         <v>2.04</v>
@@ -2053,22 +2023,22 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46179</v>
+        <v>46186</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="E21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>32</v>
@@ -2083,40 +2053,40 @@
         <v>1</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-8.5</v>
+        <v>3.5</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>51</v>
+        <v>50.5</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.88</v>
+        <v>-1.28</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>23.58</v>
+        <v>23.59</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-2.98</v>
+        <v>-0.36</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>24.02</v>
+        <v>23.95</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R21" s="4" t="n">
         <v>1.25</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.07</v>
+        <v>-0.01</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.91</v>
+        <v>-1</v>
       </c>
       <c r="U21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.1</v>
+        <v>-0.15</v>
       </c>
       <c r="W21" s="4" t="n">
         <v>2.04</v>
@@ -2127,22 +2097,22 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46180</v>
+        <v>46187</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="E22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>28</v>
@@ -2157,43 +2127,43 @@
         <v>1</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>13.5</v>
+        <v>-9.5</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>49</v>
+        <v>50.5</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.31</v>
+        <v>-2.77</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>50.59</v>
+        <v>49.49</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.73</v>
+        <v>-2.99</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>49.68</v>
+        <v>50.61</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.07</v>
+        <v>-0.15</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-1.83</v>
+        <v>-2.01</v>
       </c>
       <c r="U22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>2.54</v>
+        <v>1.99</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="X22" s="4" t="n">
         <v>0</v>
@@ -2201,22 +2171,22 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46180</v>
+        <v>46187</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="E23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>28</v>
@@ -2231,66 +2201,66 @@
         <v>1</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>13.5</v>
+        <v>-9.5</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>49</v>
+        <v>50.5</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.35</v>
+        <v>-2.77</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>49.62</v>
+        <v>49.49</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.73</v>
+        <v>-2.99</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>49.68</v>
+        <v>50.61</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.07</v>
+        <v>-0.15</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-1.83</v>
+        <v>-2.01</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>2.54</v>
+        <v>1.99</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46180</v>
+        <v>46187</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="E24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>32</v>
@@ -2305,40 +2275,40 @@
         <v>1</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>13.5</v>
+        <v>-9.5</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>49</v>
+        <v>50.5</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.16</v>
+        <v>-1.39</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>25.29</v>
+        <v>24.75</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.37</v>
+        <v>-1.5</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>24.84</v>
+        <v>25.31</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.91</v>
+        <v>-1</v>
       </c>
       <c r="U24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>1.27</v>
+        <v>0.99</v>
       </c>
       <c r="W24" s="4" t="n">
         <v>2.04</v>
@@ -2349,22 +2319,22 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46180</v>
+        <v>46187</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="E25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>32</v>
@@ -2379,638 +2349,46 @@
         <v>1</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>13.5</v>
+        <v>-9.5</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>49</v>
+        <v>50.5</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.17</v>
+        <v>-1.39</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>24.81</v>
+        <v>24.75</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.37</v>
+        <v>-1.5</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>24.84</v>
+        <v>25.31</v>
       </c>
       <c r="Q25" s="3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.91</v>
+        <v>-1</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>1.27</v>
+        <v>0.99</v>
       </c>
       <c r="W25" s="4" t="n">
         <v>2.04</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.48</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>46180</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I26" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" s="4" t="n">
-        <v>-11</v>
-      </c>
-      <c r="L26" s="4" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="M26" s="4" t="n">
-        <v>-4.19</v>
-      </c>
-      <c r="N26" s="4" t="n">
-        <v>49.24</v>
-      </c>
-      <c r="O26" s="4" t="n">
-        <v>-9.84</v>
-      </c>
-      <c r="P26" s="4" t="n">
-        <v>48.82</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="R26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S26" s="4" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="T26" s="4" t="n">
-        <v>-1.83</v>
-      </c>
-      <c r="U26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="4" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="W26" s="4" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="X26" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>46180</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" s="4" t="n">
-        <v>-11</v>
-      </c>
-      <c r="L27" s="4" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="M27" s="4" t="n">
-        <v>-4.16</v>
-      </c>
-      <c r="N27" s="4" t="n">
-        <v>48.53</v>
-      </c>
-      <c r="O27" s="4" t="n">
-        <v>-9.84</v>
-      </c>
-      <c r="P27" s="4" t="n">
-        <v>48.82</v>
-      </c>
-      <c r="Q27" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="R27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S27" s="4" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="T27" s="4" t="n">
-        <v>-1.83</v>
-      </c>
-      <c r="U27" s="4" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="V27" s="4" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="W27" s="4" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="X27" s="4" t="n">
-        <v>-0.71</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>46180</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I28" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" s="4" t="n">
-        <v>-11</v>
-      </c>
-      <c r="L28" s="4" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="M28" s="4" t="n">
-        <v>-2.09</v>
-      </c>
-      <c r="N28" s="4" t="n">
-        <v>24.62</v>
-      </c>
-      <c r="O28" s="4" t="n">
-        <v>-4.92</v>
-      </c>
-      <c r="P28" s="4" t="n">
-        <v>24.41</v>
-      </c>
-      <c r="Q28" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="R28" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S28" s="4" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="T28" s="4" t="n">
-        <v>-0.91</v>
-      </c>
-      <c r="U28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" s="4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W28" s="4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="X28" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>46180</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I29" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" s="4" t="n">
-        <v>-11</v>
-      </c>
-      <c r="L29" s="4" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="M29" s="4" t="n">
-        <v>-2.08</v>
-      </c>
-      <c r="N29" s="4" t="n">
-        <v>24.27</v>
-      </c>
-      <c r="O29" s="4" t="n">
-        <v>-4.92</v>
-      </c>
-      <c r="P29" s="4" t="n">
-        <v>24.41</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="R29" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S29" s="4" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="T29" s="4" t="n">
-        <v>-0.91</v>
-      </c>
-      <c r="U29" s="4" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="V29" s="4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W29" s="4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="X29" s="4" t="n">
-        <v>-0.35</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>46181</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I30" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L30" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="M30" s="4" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="N30" s="4" t="n">
-        <v>49.46</v>
-      </c>
-      <c r="O30" s="4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="P30" s="4" t="n">
-        <v>48.27</v>
-      </c>
-      <c r="Q30" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="R30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S30" s="4" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="T30" s="4" t="n">
-        <v>-1.83</v>
-      </c>
-      <c r="U30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" s="4" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="W30" s="4" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="X30" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>46181</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K31" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L31" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="M31" s="4" t="n">
-        <v>-2.63</v>
-      </c>
-      <c r="N31" s="4" t="n">
-        <v>47.81</v>
-      </c>
-      <c r="O31" s="4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="P31" s="4" t="n">
-        <v>48.27</v>
-      </c>
-      <c r="Q31" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="R31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S31" s="4" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="T31" s="4" t="n">
-        <v>-1.83</v>
-      </c>
-      <c r="U31" s="4" t="n">
-        <v>-0.07</v>
-      </c>
-      <c r="V31" s="4" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="W31" s="4" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="X31" s="4" t="n">
-        <v>-1.65</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>46181</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I32" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L32" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="M32" s="4" t="n">
-        <v>-1.35</v>
-      </c>
-      <c r="N32" s="4" t="n">
-        <v>24.73</v>
-      </c>
-      <c r="O32" s="4" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="P32" s="4" t="n">
-        <v>24.14</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="R32" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S32" s="4" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="T32" s="4" t="n">
-        <v>-0.91</v>
-      </c>
-      <c r="U32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W32" s="4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="X32" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>46181</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I33" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L33" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="M33" s="4" t="n">
-        <v>-1.32</v>
-      </c>
-      <c r="N33" s="4" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="O33" s="4" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="P33" s="4" t="n">
-        <v>24.14</v>
-      </c>
-      <c r="Q33" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="R33" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S33" s="4" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="T33" s="4" t="n">
-        <v>-0.91</v>
-      </c>
-      <c r="U33" s="4" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="V33" s="4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W33" s="4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="X33" s="4" t="n">
-        <v>-0.82</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_upcoming_projections.xlsx
+++ b/files/NRL_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -86,70 +86,61 @@
     <t xml:space="preserve">Rain Total Adj</t>
   </si>
   <si>
-    <t xml:space="preserve">16:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
+    <t xml:space="preserve">19:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">south sydney rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accor Stadium, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Rain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">diff_city</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dolphins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suncorp Stadium, Brisbane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Go Media Stadium, Auckland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:35</t>
   </si>
   <si>
     <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accor Stadium, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Rain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">same_city_different_ground</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">south sydney rabbitohs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">diff_city</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suncorp Stadium, Brisbane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Go Media Stadium, Auckland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:35</t>
   </si>
   <si>
     <t xml:space="preserve">canberra raiders</t>
@@ -517,7 +508,7 @@
   <cols>
     <col min="1" max="1" width="4.9975" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="4.9975" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="25.5775" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="19.575" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="23.005" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="14.43" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="23.005" hidden="0" customWidth="1"/>
@@ -531,7 +522,7 @@
     <col min="14" max="14" width="14.43" hidden="0" customWidth="1"/>
     <col min="15" max="15" width="16.145" hidden="0" customWidth="1"/>
     <col min="16" max="16" width="12.715" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="23.005" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="8.4275" hidden="0" customWidth="1"/>
     <col min="18" max="18" width="8.4275" hidden="0" customWidth="1"/>
     <col min="19" max="19" width="17.0025" hidden="0" customWidth="1"/>
     <col min="20" max="20" width="17.0025" hidden="0" customWidth="1"/>
@@ -617,7 +608,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46181</v>
+        <v>46184</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>24</v>
@@ -629,7 +620,7 @@
         <v>26</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>27</v>
@@ -641,37 +632,37 @@
         <v>29</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>-6</v>
+        <v>-5.5</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>51</v>
+        <v>49.5</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>-2.95</v>
+        <v>-9.86</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>49.84</v>
+        <v>47.12</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>0.6</v>
+        <v>-0.7</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>48.48</v>
+        <v>47.33</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>30</v>
       </c>
       <c r="R2" s="4" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>-0.15</v>
+        <v>-0.02</v>
       </c>
       <c r="T2" s="4" t="n">
         <v>-2.01</v>
@@ -680,7 +671,7 @@
         <v>0</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>1.96</v>
+        <v>-0.29</v>
       </c>
       <c r="W2" s="4" t="n">
         <v>4.07</v>
@@ -691,7 +682,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46181</v>
+        <v>46184</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>24</v>
@@ -703,7 +694,7 @@
         <v>26</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>27</v>
@@ -715,57 +706,57 @@
         <v>31</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-6</v>
+        <v>-5.5</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>51</v>
+        <v>49.5</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>-2.9</v>
+        <v>-9.83</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>48.19</v>
+        <v>46.2</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>0.6</v>
+        <v>-0.7</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>48.48</v>
+        <v>47.33</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>30</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>-0.15</v>
+        <v>-0.02</v>
       </c>
       <c r="T3" s="4" t="n">
         <v>-2.01</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>1.96</v>
+        <v>-0.29</v>
       </c>
       <c r="W3" s="4" t="n">
         <v>4.07</v>
       </c>
       <c r="X3" s="4" t="n">
-        <v>-1.65</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46181</v>
+        <v>46184</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>24</v>
@@ -777,7 +768,7 @@
         <v>26</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>27</v>
@@ -789,37 +780,37 @@
         <v>29</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-6</v>
+        <v>-5.5</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>51</v>
+        <v>49.5</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>-1.48</v>
+        <v>-4.93</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>24.92</v>
+        <v>23.56</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>0.3</v>
+        <v>-0.35</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>24.24</v>
+        <v>23.67</v>
       </c>
       <c r="Q4" s="3" t="s">
         <v>30</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>-0.08</v>
+        <v>-0.01</v>
       </c>
       <c r="T4" s="4" t="n">
         <v>-1</v>
@@ -828,7 +819,7 @@
         <v>0</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>0.98</v>
+        <v>-0.15</v>
       </c>
       <c r="W4" s="4" t="n">
         <v>2.04</v>
@@ -839,7 +830,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46181</v>
+        <v>46184</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>24</v>
@@ -851,7 +842,7 @@
         <v>26</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>27</v>
@@ -863,57 +854,57 @@
         <v>31</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-6</v>
+        <v>-5.5</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>51</v>
+        <v>49.5</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>-1.45</v>
+        <v>-4.92</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>24.1</v>
+        <v>23.1</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>0.3</v>
+        <v>-0.35</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>24.24</v>
+        <v>23.67</v>
       </c>
       <c r="Q5" s="3" t="s">
         <v>30</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>-0.08</v>
+        <v>-0.01</v>
       </c>
       <c r="T5" s="4" t="n">
         <v>-1</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>0.98</v>
+        <v>-0.15</v>
       </c>
       <c r="W5" s="4" t="n">
         <v>2.04</v>
       </c>
       <c r="X5" s="4" t="n">
-        <v>-0.82</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>33</v>
@@ -925,10 +916,10 @@
         <v>35</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>28</v>
@@ -943,31 +934,31 @@
         <v>1</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-3.5</v>
+        <v>-5.5</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>50.5</v>
+        <v>51</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-9.86</v>
+        <v>-6.14</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>47.13</v>
+        <v>46.03</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.73</v>
+        <v>-1.86</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>48.29</v>
+        <v>44.59</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="R6" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="T6" s="4" t="n">
         <v>-2.01</v>
@@ -976,7 +967,7 @@
         <v>0</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.3</v>
+        <v>-0.56</v>
       </c>
       <c r="W6" s="4" t="n">
         <v>4.07</v>
@@ -987,7 +978,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>33</v>
@@ -999,10 +990,10 @@
         <v>35</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>28</v>
@@ -1017,51 +1008,51 @@
         <v>1</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-3.5</v>
+        <v>-5.5</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>50.5</v>
+        <v>51</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-9.86</v>
+        <v>-6.05</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>47.13</v>
+        <v>43.96</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.73</v>
+        <v>-1.86</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>48.29</v>
+        <v>44.59</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="R7" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="T7" s="4" t="n">
         <v>-2.01</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.3</v>
+        <v>-0.56</v>
       </c>
       <c r="W7" s="4" t="n">
         <v>4.07</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>0</v>
+        <v>-2.07</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>33</v>
@@ -1073,10 +1064,10 @@
         <v>35</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>32</v>
@@ -1091,31 +1082,31 @@
         <v>1</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-3.5</v>
+        <v>-5.5</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>50.5</v>
+        <v>51</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-4.93</v>
+        <v>-3.07</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>23.57</v>
+        <v>23.02</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.37</v>
+        <v>-0.93</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>24.15</v>
+        <v>22.3</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="R8" s="4" t="n">
         <v>1.25</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="T8" s="4" t="n">
         <v>-1</v>
@@ -1124,7 +1115,7 @@
         <v>0</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.15</v>
+        <v>-0.28</v>
       </c>
       <c r="W8" s="4" t="n">
         <v>2.04</v>
@@ -1135,7 +1126,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>33</v>
@@ -1147,10 +1138,10 @@
         <v>35</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>32</v>
@@ -1165,51 +1156,51 @@
         <v>1</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-3.5</v>
+        <v>-5.5</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>50.5</v>
+        <v>51</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-4.93</v>
+        <v>-3.03</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>23.57</v>
+        <v>21.98</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.37</v>
+        <v>-0.93</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>24.15</v>
+        <v>22.3</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="R9" s="4" t="n">
         <v>1.25</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="T9" s="4" t="n">
         <v>-1</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.15</v>
+        <v>-0.28</v>
       </c>
       <c r="W9" s="4" t="n">
         <v>2.04</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>0</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>37</v>
@@ -1239,31 +1230,31 @@
         <v>1</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-2.5</v>
+        <v>-9</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>51.5</v>
+        <v>49</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-6.14</v>
+        <v>2.16</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>46.05</v>
+        <v>46.61</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.95</v>
+        <v>2.52</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>46.71</v>
+        <v>47.22</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="R10" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="T10" s="4" t="n">
         <v>-2.01</v>
@@ -1272,7 +1263,7 @@
         <v>0</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.59</v>
+        <v>-0.3</v>
       </c>
       <c r="W10" s="4" t="n">
         <v>4.07</v>
@@ -1283,7 +1274,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>37</v>
@@ -1313,31 +1304,31 @@
         <v>1</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-2.5</v>
+        <v>-9</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>51.5</v>
+        <v>49</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-6.14</v>
+        <v>2.16</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>46.05</v>
+        <v>46.61</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.95</v>
+        <v>2.52</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>46.71</v>
+        <v>47.22</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="R11" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="T11" s="4" t="n">
         <v>-2.01</v>
@@ -1346,7 +1337,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.59</v>
+        <v>-0.3</v>
       </c>
       <c r="W11" s="4" t="n">
         <v>4.07</v>
@@ -1357,7 +1348,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>37</v>
@@ -1387,31 +1378,31 @@
         <v>1</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-2.5</v>
+        <v>-9</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>51.5</v>
+        <v>49</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-3.07</v>
+        <v>1.08</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>23.03</v>
+        <v>23.31</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.97</v>
+        <v>1.26</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>23.36</v>
+        <v>23.61</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="R12" s="4" t="n">
         <v>1.25</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="T12" s="4" t="n">
         <v>-1</v>
@@ -1420,7 +1411,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.29</v>
+        <v>-0.15</v>
       </c>
       <c r="W12" s="4" t="n">
         <v>2.04</v>
@@ -1431,7 +1422,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>37</v>
@@ -1461,31 +1452,31 @@
         <v>1</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-2.5</v>
+        <v>-9</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>51.5</v>
+        <v>49</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-3.07</v>
+        <v>1.08</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>23.03</v>
+        <v>23.31</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.97</v>
+        <v>1.26</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>23.36</v>
+        <v>23.61</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="R13" s="4" t="n">
         <v>1.25</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="T13" s="4" t="n">
         <v>-1</v>
@@ -1494,7 +1485,7 @@
         <v>0</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.29</v>
+        <v>-0.15</v>
       </c>
       <c r="W13" s="4" t="n">
         <v>2.04</v>
@@ -1535,31 +1526,31 @@
         <v>1</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-8.5</v>
+        <v>3.5</v>
       </c>
       <c r="L14" s="4" t="n">
         <v>49.5</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>2.15</v>
+        <v>-2.56</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>46.63</v>
+        <v>47.17</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>2.52</v>
+        <v>-0.72</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>47.24</v>
+        <v>47.88</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="R14" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="T14" s="4" t="n">
         <v>-2.01</v>
@@ -1609,31 +1600,31 @@
         <v>1</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-8.5</v>
+        <v>3.5</v>
       </c>
       <c r="L15" s="4" t="n">
         <v>49.5</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>2.15</v>
+        <v>-2.56</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>46.63</v>
+        <v>47.17</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>2.52</v>
+        <v>-0.72</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>47.24</v>
+        <v>47.88</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="R15" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="T15" s="4" t="n">
         <v>-2.01</v>
@@ -1683,25 +1674,25 @@
         <v>1</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-8.5</v>
+        <v>3.5</v>
       </c>
       <c r="L16" s="4" t="n">
         <v>49.5</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.08</v>
+        <v>-1.28</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>23.31</v>
+        <v>23.58</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.26</v>
+        <v>-0.36</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>23.62</v>
+        <v>23.94</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="R16" s="4" t="n">
         <v>1.25</v>
@@ -1757,25 +1748,25 @@
         <v>1</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-8.5</v>
+        <v>3.5</v>
       </c>
       <c r="L17" s="4" t="n">
         <v>49.5</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.08</v>
+        <v>-1.28</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>23.31</v>
+        <v>23.58</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.26</v>
+        <v>-0.36</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>23.62</v>
+        <v>23.94</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="R17" s="4" t="n">
         <v>1.25</v>
@@ -1801,22 +1792,22 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>45</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>28</v>
@@ -1831,31 +1822,31 @@
         <v>1</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>3.5</v>
+        <v>-5.5</v>
       </c>
       <c r="L18" s="4" t="n">
         <v>50.5</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.56</v>
+        <v>-2.77</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>47.18</v>
+        <v>49.47</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.72</v>
+        <v>-2.97</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>47.89</v>
+        <v>49.87</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="R18" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.01</v>
+        <v>-0.15</v>
       </c>
       <c r="T18" s="4" t="n">
         <v>-2.01</v>
@@ -1864,7 +1855,7 @@
         <v>0</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.3</v>
+        <v>1.95</v>
       </c>
       <c r="W18" s="4" t="n">
         <v>4.07</v>
@@ -1875,22 +1866,22 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>45</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>28</v>
@@ -1905,66 +1896,66 @@
         <v>1</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>3.5</v>
+        <v>-5.5</v>
       </c>
       <c r="L19" s="4" t="n">
         <v>50.5</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.56</v>
+        <v>-2.75</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>47.18</v>
+        <v>48.77</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.72</v>
+        <v>-2.97</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>47.89</v>
+        <v>49.87</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="R19" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.01</v>
+        <v>-0.15</v>
       </c>
       <c r="T19" s="4" t="n">
         <v>-2.01</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.3</v>
+        <v>1.95</v>
       </c>
       <c r="W19" s="4" t="n">
         <v>4.07</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>45</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>32</v>
@@ -1979,31 +1970,31 @@
         <v>1</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>3.5</v>
+        <v>-5.5</v>
       </c>
       <c r="L20" s="4" t="n">
         <v>50.5</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.28</v>
+        <v>-1.38</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>23.59</v>
+        <v>24.73</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.36</v>
+        <v>-1.49</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>23.95</v>
+        <v>24.94</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="R20" s="4" t="n">
         <v>1.25</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="T20" s="4" t="n">
         <v>-1</v>
@@ -2012,7 +2003,7 @@
         <v>0</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.15</v>
+        <v>0.97</v>
       </c>
       <c r="W20" s="4" t="n">
         <v>2.04</v>
@@ -2023,22 +2014,22 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>45</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>32</v>
@@ -2053,342 +2044,46 @@
         <v>1</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>3.5</v>
+        <v>-5.5</v>
       </c>
       <c r="L21" s="4" t="n">
         <v>50.5</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.28</v>
+        <v>-1.38</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>23.59</v>
+        <v>24.39</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.36</v>
+        <v>-1.49</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>23.95</v>
+        <v>24.94</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="R21" s="4" t="n">
         <v>1.25</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="T21" s="4" t="n">
         <v>-1</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.15</v>
+        <v>0.97</v>
       </c>
       <c r="W21" s="4" t="n">
         <v>2.04</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I22" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" s="4" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="L22" s="4" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="M22" s="4" t="n">
-        <v>-2.77</v>
-      </c>
-      <c r="N22" s="4" t="n">
-        <v>49.49</v>
-      </c>
-      <c r="O22" s="4" t="n">
-        <v>-2.99</v>
-      </c>
-      <c r="P22" s="4" t="n">
-        <v>50.61</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="R22" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S22" s="4" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="T22" s="4" t="n">
-        <v>-2.01</v>
-      </c>
-      <c r="U22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="4" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="W22" s="4" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="X22" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I23" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" s="4" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="L23" s="4" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="M23" s="4" t="n">
-        <v>-2.77</v>
-      </c>
-      <c r="N23" s="4" t="n">
-        <v>49.49</v>
-      </c>
-      <c r="O23" s="4" t="n">
-        <v>-2.99</v>
-      </c>
-      <c r="P23" s="4" t="n">
-        <v>50.61</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="R23" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S23" s="4" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="T23" s="4" t="n">
-        <v>-2.01</v>
-      </c>
-      <c r="U23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="4" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="W23" s="4" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="X23" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I24" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" s="4" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="L24" s="4" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="M24" s="4" t="n">
-        <v>-1.39</v>
-      </c>
-      <c r="N24" s="4" t="n">
-        <v>24.75</v>
-      </c>
-      <c r="O24" s="4" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="P24" s="4" t="n">
-        <v>25.31</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="R24" s="4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S24" s="4" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="T24" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="4" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="W24" s="4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="X24" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" s="4" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="L25" s="4" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="M25" s="4" t="n">
-        <v>-1.39</v>
-      </c>
-      <c r="N25" s="4" t="n">
-        <v>24.75</v>
-      </c>
-      <c r="O25" s="4" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="P25" s="4" t="n">
-        <v>25.31</v>
-      </c>
-      <c r="Q25" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="R25" s="4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S25" s="4" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="T25" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="4" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="W25" s="4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="X25" s="4" t="n">
-        <v>0</v>
+        <v>-0.35</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_upcoming_projections.xlsx
+++ b/files/NRL_upcoming_projections.xlsx
@@ -644,16 +644,16 @@
         <v>49.5</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>-9.86</v>
+        <v>-6.49</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>47.12</v>
+        <v>50.72</v>
       </c>
       <c r="O2" s="4" t="n">
         <v>-0.7</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>47.33</v>
+        <v>50.61</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>30</v>
@@ -671,7 +671,7 @@
         <v>0</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>-0.29</v>
+        <v>-0.3</v>
       </c>
       <c r="W2" s="4" t="n">
         <v>4.07</v>
@@ -718,16 +718,16 @@
         <v>49.5</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>-9.83</v>
+        <v>-6.47</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>46.2</v>
+        <v>49.79</v>
       </c>
       <c r="O3" s="4" t="n">
         <v>-0.7</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>47.33</v>
+        <v>50.61</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>30</v>
@@ -745,13 +745,13 @@
         <v>-0.02</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>-0.29</v>
+        <v>-0.3</v>
       </c>
       <c r="W3" s="4" t="n">
         <v>4.07</v>
       </c>
       <c r="X3" s="4" t="n">
-        <v>-0.92</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="4">
@@ -792,16 +792,16 @@
         <v>49.5</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>-4.93</v>
+        <v>-3.25</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>23.56</v>
+        <v>25.36</v>
       </c>
       <c r="O4" s="4" t="n">
         <v>-0.35</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>23.67</v>
+        <v>25.3</v>
       </c>
       <c r="Q4" s="3" t="s">
         <v>30</v>
@@ -866,16 +866,16 @@
         <v>49.5</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>-4.92</v>
+        <v>-3.23</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>23.1</v>
+        <v>24.9</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>-0.35</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>23.67</v>
+        <v>25.3</v>
       </c>
       <c r="Q5" s="3" t="s">
         <v>30</v>
@@ -940,16 +940,16 @@
         <v>51</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-6.14</v>
+        <v>-0.21</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>46.03</v>
+        <v>49.67</v>
       </c>
       <c r="O6" s="4" t="n">
         <v>-1.86</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>44.59</v>
+        <v>47.87</v>
       </c>
       <c r="Q6" s="3" t="s">
         <v>30</v>
@@ -967,7 +967,7 @@
         <v>0</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.56</v>
+        <v>-0.57</v>
       </c>
       <c r="W6" s="4" t="n">
         <v>4.07</v>
@@ -1014,16 +1014,16 @@
         <v>51</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-6.05</v>
+        <v>-0.13</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>43.96</v>
+        <v>47.58</v>
       </c>
       <c r="O7" s="4" t="n">
         <v>-1.86</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>44.59</v>
+        <v>47.87</v>
       </c>
       <c r="Q7" s="3" t="s">
         <v>30</v>
@@ -1041,13 +1041,13 @@
         <v>-0.08</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.56</v>
+        <v>-0.57</v>
       </c>
       <c r="W7" s="4" t="n">
         <v>4.07</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-2.07</v>
+        <v>-2.09</v>
       </c>
     </row>
     <row r="8">
@@ -1088,16 +1088,16 @@
         <v>51</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-3.07</v>
+        <v>-0.11</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>23.02</v>
+        <v>24.84</v>
       </c>
       <c r="O8" s="4" t="n">
         <v>-0.93</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>22.3</v>
+        <v>23.94</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>30</v>
@@ -1162,16 +1162,16 @@
         <v>51</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-3.03</v>
+        <v>-0.06</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>21.98</v>
+        <v>23.79</v>
       </c>
       <c r="O9" s="4" t="n">
         <v>-0.93</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>22.3</v>
+        <v>23.94</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>30</v>
@@ -1224,7 +1224,7 @@
         <v>29</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>1</v>
@@ -1236,16 +1236,16 @@
         <v>49</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.16</v>
+        <v>-1.89</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>46.61</v>
+        <v>50.2</v>
       </c>
       <c r="O10" s="4" t="n">
         <v>2.52</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>47.22</v>
+        <v>50.5</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>30</v>
@@ -1298,7 +1298,7 @@
         <v>31</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" s="5" t="n">
         <v>1</v>
@@ -1310,16 +1310,16 @@
         <v>49</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>2.16</v>
+        <v>-1.89</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>46.61</v>
+        <v>50.2</v>
       </c>
       <c r="O11" s="4" t="n">
         <v>2.52</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>47.22</v>
+        <v>50.5</v>
       </c>
       <c r="Q11" s="3" t="s">
         <v>30</v>
@@ -1372,7 +1372,7 @@
         <v>29</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" s="5" t="n">
         <v>1</v>
@@ -1384,16 +1384,16 @@
         <v>49</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.08</v>
+        <v>-0.95</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>23.31</v>
+        <v>25.1</v>
       </c>
       <c r="O12" s="4" t="n">
         <v>1.26</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>23.61</v>
+        <v>25.25</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>30</v>
@@ -1446,7 +1446,7 @@
         <v>31</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" s="5" t="n">
         <v>1</v>
@@ -1458,16 +1458,16 @@
         <v>49</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>1.08</v>
+        <v>-0.95</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>23.31</v>
+        <v>25.1</v>
       </c>
       <c r="O13" s="4" t="n">
         <v>1.26</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>23.61</v>
+        <v>25.25</v>
       </c>
       <c r="Q13" s="3" t="s">
         <v>30</v>
@@ -1532,16 +1532,16 @@
         <v>49.5</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.56</v>
+        <v>-0.18</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>47.17</v>
+        <v>50.62</v>
       </c>
       <c r="O14" s="4" t="n">
         <v>-0.72</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>47.88</v>
+        <v>51.15</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>30</v>
@@ -1606,16 +1606,16 @@
         <v>49.5</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.56</v>
+        <v>-0.18</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>47.17</v>
+        <v>50.62</v>
       </c>
       <c r="O15" s="4" t="n">
         <v>-0.72</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>47.88</v>
+        <v>51.15</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>30</v>
@@ -1680,16 +1680,16 @@
         <v>49.5</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.28</v>
+        <v>-0.09</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>23.58</v>
+        <v>25.31</v>
       </c>
       <c r="O16" s="4" t="n">
         <v>-0.36</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>23.94</v>
+        <v>25.58</v>
       </c>
       <c r="Q16" s="3" t="s">
         <v>30</v>
@@ -1754,16 +1754,16 @@
         <v>49.5</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.28</v>
+        <v>-0.09</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>23.58</v>
+        <v>25.31</v>
       </c>
       <c r="O17" s="4" t="n">
         <v>-0.36</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>23.94</v>
+        <v>25.58</v>
       </c>
       <c r="Q17" s="3" t="s">
         <v>30</v>
@@ -1828,16 +1828,16 @@
         <v>50.5</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.77</v>
+        <v>-4.44</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>49.47</v>
+        <v>53.18</v>
       </c>
       <c r="O18" s="4" t="n">
         <v>-2.97</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>49.87</v>
+        <v>53.15</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>30</v>
@@ -1855,7 +1855,7 @@
         <v>0</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="W18" s="4" t="n">
         <v>4.07</v>
@@ -1902,16 +1902,16 @@
         <v>50.5</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.75</v>
+        <v>-4.42</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>48.77</v>
+        <v>52.47</v>
       </c>
       <c r="O19" s="4" t="n">
         <v>-2.97</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>49.87</v>
+        <v>53.15</v>
       </c>
       <c r="Q19" s="3" t="s">
         <v>30</v>
@@ -1929,7 +1929,7 @@
         <v>-0.02</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="W19" s="4" t="n">
         <v>4.07</v>
@@ -1976,16 +1976,16 @@
         <v>50.5</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.38</v>
+        <v>-2.22</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>24.73</v>
+        <v>26.59</v>
       </c>
       <c r="O20" s="4" t="n">
         <v>-1.49</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>24.94</v>
+        <v>26.57</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>30</v>
@@ -2003,7 +2003,7 @@
         <v>0</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="W20" s="4" t="n">
         <v>2.04</v>
@@ -2050,16 +2050,16 @@
         <v>50.5</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.38</v>
+        <v>-2.21</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>24.39</v>
+        <v>26.24</v>
       </c>
       <c r="O21" s="4" t="n">
         <v>-1.49</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>24.94</v>
+        <v>26.57</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>30</v>
@@ -2077,7 +2077,7 @@
         <v>-0.01</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="W21" s="4" t="n">
         <v>2.04</v>

--- a/files/NRL_upcoming_projections.xlsx
+++ b/files/NRL_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -86,79 +86,118 @@
     <t xml:space="preserve">Rain Total Adj</t>
   </si>
   <si>
+    <t xml:space="preserve">20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st george-illawarra dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">McDonald Jones Stadium, Newcastle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Rain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">diff_city</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wests tigers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dolphins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campbelltown Sports Stadium, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penrith panthers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cbus Super Stadium, Gold Coast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manly-warringah sea eagles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accor Stadium, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">same_city_different_ground</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north queensland cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One NZ Stadium, Christchurch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melbourne storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AAMI Park, Melbourne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allianz Stadium, Sydney</t>
+  </si>
+  <si>
     <t xml:space="preserve">19:50</t>
   </si>
   <si>
+    <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
     <t xml:space="preserve">south sydney rabbitohs</t>
   </si>
   <si>
-    <t xml:space="preserve">brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accor Stadium, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Rain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">diff_city</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suncorp Stadium, Brisbane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Go Media Stadium, Auckland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberra raiders</t>
-  </si>
-  <si>
     <t xml:space="preserve">CommBank Stadium, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wests tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leichhardt Oval, Sydney</t>
   </si>
 </sst>
 </file>
@@ -508,10 +547,10 @@
   <cols>
     <col min="1" max="1" width="4.9975" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="4.9975" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="19.575" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="23.005" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="25.5775" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="23.8625" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="14.43" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="23.005" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="30.7225" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="11.8575" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="14.43" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="14.43" hidden="0" customWidth="1"/>
@@ -522,7 +561,7 @@
     <col min="14" max="14" width="14.43" hidden="0" customWidth="1"/>
     <col min="15" max="15" width="16.145" hidden="0" customWidth="1"/>
     <col min="16" max="16" width="12.715" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="8.4275" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="23.005" hidden="0" customWidth="1"/>
     <col min="18" max="18" width="8.4275" hidden="0" customWidth="1"/>
     <col min="19" max="19" width="17.0025" hidden="0" customWidth="1"/>
     <col min="20" max="20" width="17.0025" hidden="0" customWidth="1"/>
@@ -608,7 +647,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46184</v>
+        <v>46192</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>24</v>
@@ -620,7 +659,7 @@
         <v>26</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>27</v>
@@ -638,22 +677,22 @@
         <v>1</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>-5.5</v>
+        <v>-10.5</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>49.5</v>
+        <v>49</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>-6.49</v>
+        <v>-6.72</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>50.72</v>
+        <v>49.69</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>-0.7</v>
+        <v>-11.85</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>50.61</v>
+        <v>50.01</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>30</v>
@@ -662,19 +701,19 @@
         <v>2.5</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>-0.02</v>
+        <v>0.07</v>
       </c>
       <c r="T2" s="4" t="n">
-        <v>-2.01</v>
+        <v>-1.92</v>
       </c>
       <c r="U2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>-0.3</v>
+        <v>-0.63</v>
       </c>
       <c r="W2" s="4" t="n">
-        <v>4.07</v>
+        <v>4.02</v>
       </c>
       <c r="X2" s="4" t="n">
         <v>0</v>
@@ -682,7 +721,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46184</v>
+        <v>46192</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>24</v>
@@ -694,7 +733,7 @@
         <v>26</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>27</v>
@@ -712,22 +751,22 @@
         <v>1</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-5.5</v>
+        <v>-10.5</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>49.5</v>
+        <v>49</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>-6.47</v>
+        <v>-6.72</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>49.79</v>
+        <v>49.69</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>-0.7</v>
+        <v>-11.85</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>50.61</v>
+        <v>50.01</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>30</v>
@@ -736,27 +775,27 @@
         <v>2.5</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>-0.02</v>
+        <v>0.07</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>-2.01</v>
+        <v>-1.92</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>-0.3</v>
+        <v>-0.63</v>
       </c>
       <c r="W3" s="4" t="n">
-        <v>4.07</v>
+        <v>4.02</v>
       </c>
       <c r="X3" s="4" t="n">
-        <v>-0.93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46184</v>
+        <v>46192</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>24</v>
@@ -768,7 +807,7 @@
         <v>26</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>27</v>
@@ -786,22 +825,22 @@
         <v>1</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-5.5</v>
+        <v>-10.5</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>49.5</v>
+        <v>49</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>-3.25</v>
+        <v>-3.36</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>25.36</v>
+        <v>24.84</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>-0.35</v>
+        <v>-5.93</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>25.3</v>
+        <v>25</v>
       </c>
       <c r="Q4" s="3" t="s">
         <v>30</v>
@@ -810,19 +849,19 @@
         <v>1.25</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>-0.01</v>
+        <v>0.04</v>
       </c>
       <c r="T4" s="4" t="n">
-        <v>-1</v>
+        <v>-0.96</v>
       </c>
       <c r="U4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>-0.15</v>
+        <v>-0.31</v>
       </c>
       <c r="W4" s="4" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="X4" s="4" t="n">
         <v>0</v>
@@ -830,7 +869,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46184</v>
+        <v>46192</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>24</v>
@@ -842,7 +881,7 @@
         <v>26</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>27</v>
@@ -860,22 +899,22 @@
         <v>1</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-5.5</v>
+        <v>-10.5</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>49.5</v>
+        <v>49</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>-3.23</v>
+        <v>-3.36</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>24.9</v>
+        <v>24.84</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>-0.35</v>
+        <v>-5.93</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>25.3</v>
+        <v>25</v>
       </c>
       <c r="Q5" s="3" t="s">
         <v>30</v>
@@ -884,27 +923,27 @@
         <v>1.25</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>-0.01</v>
+        <v>0.04</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>-1</v>
+        <v>-0.96</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>-0.15</v>
+        <v>-0.31</v>
       </c>
       <c r="W5" s="4" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="X5" s="4" t="n">
-        <v>-0.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46185</v>
+        <v>46193</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>33</v>
@@ -916,7 +955,7 @@
         <v>35</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>36</v>
@@ -934,22 +973,22 @@
         <v>1</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-5.5</v>
+        <v>8.5</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.21</v>
+        <v>-5.4</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>49.67</v>
+        <v>53.13</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-1.86</v>
+        <v>-4.52</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>47.87</v>
+        <v>53.45</v>
       </c>
       <c r="Q6" s="3" t="s">
         <v>30</v>
@@ -958,19 +997,19 @@
         <v>2.5</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.03</v>
+        <v>-0.25</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-2.01</v>
+        <v>-1.92</v>
       </c>
       <c r="U6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.57</v>
+        <v>2.31</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>4.07</v>
+        <v>4.02</v>
       </c>
       <c r="X6" s="4" t="n">
         <v>0</v>
@@ -978,7 +1017,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46185</v>
+        <v>46193</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>33</v>
@@ -990,7 +1029,7 @@
         <v>35</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>36</v>
@@ -1008,22 +1047,22 @@
         <v>1</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-5.5</v>
+        <v>8.5</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.13</v>
+        <v>-5.4</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>47.58</v>
+        <v>53.13</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-1.86</v>
+        <v>-4.52</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>47.87</v>
+        <v>53.45</v>
       </c>
       <c r="Q7" s="3" t="s">
         <v>30</v>
@@ -1032,27 +1071,27 @@
         <v>2.5</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.03</v>
+        <v>-0.25</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-2.01</v>
+        <v>-1.92</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.57</v>
+        <v>2.31</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>4.07</v>
+        <v>4.02</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-2.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46185</v>
+        <v>46193</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>33</v>
@@ -1064,7 +1103,7 @@
         <v>35</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>36</v>
@@ -1082,22 +1121,22 @@
         <v>1</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-5.5</v>
+        <v>8.5</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.11</v>
+        <v>-2.7</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>24.84</v>
+        <v>26.57</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.93</v>
+        <v>-2.26</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>23.94</v>
+        <v>26.72</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>30</v>
@@ -1106,19 +1145,19 @@
         <v>1.25</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.02</v>
+        <v>-0.12</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-1</v>
+        <v>-0.96</v>
       </c>
       <c r="U8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.28</v>
+        <v>1.16</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="X8" s="4" t="n">
         <v>0</v>
@@ -1126,7 +1165,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46185</v>
+        <v>46193</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>33</v>
@@ -1138,7 +1177,7 @@
         <v>35</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>36</v>
@@ -1156,22 +1195,22 @@
         <v>1</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-5.5</v>
+        <v>8.5</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.06</v>
+        <v>-2.7</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>23.79</v>
+        <v>26.57</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.93</v>
+        <v>-2.26</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>23.94</v>
+        <v>26.72</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>30</v>
@@ -1180,27 +1219,27 @@
         <v>1.25</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.02</v>
+        <v>-0.12</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-1</v>
+        <v>-0.96</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.28</v>
+        <v>1.16</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-1.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>37</v>
@@ -1224,28 +1263,28 @@
         <v>29</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-9</v>
+        <v>12.5</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>49</v>
+        <v>49.5</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.89</v>
+        <v>-1.79</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>50.2</v>
+        <v>52.78</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.52</v>
+        <v>-1.58</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>50.5</v>
+        <v>53.06</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>30</v>
@@ -1254,19 +1293,19 @@
         <v>2.5</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.02</v>
+        <v>-0.18</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-2.01</v>
+        <v>-1.92</v>
       </c>
       <c r="U10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.3</v>
+        <v>1.65</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>4.07</v>
+        <v>4.02</v>
       </c>
       <c r="X10" s="4" t="n">
         <v>0</v>
@@ -1274,7 +1313,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>37</v>
@@ -1298,28 +1337,28 @@
         <v>31</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-9</v>
+        <v>12.5</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>49</v>
+        <v>49.5</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.89</v>
+        <v>-1.79</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>50.2</v>
+        <v>52.78</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>2.52</v>
+        <v>-1.58</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>50.5</v>
+        <v>53.06</v>
       </c>
       <c r="Q11" s="3" t="s">
         <v>30</v>
@@ -1328,19 +1367,19 @@
         <v>2.5</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.02</v>
+        <v>-0.18</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-2.01</v>
+        <v>-1.92</v>
       </c>
       <c r="U11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.3</v>
+        <v>1.65</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>4.07</v>
+        <v>4.02</v>
       </c>
       <c r="X11" s="4" t="n">
         <v>0</v>
@@ -1348,7 +1387,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>37</v>
@@ -1372,28 +1411,28 @@
         <v>29</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-9</v>
+        <v>12.5</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>49</v>
+        <v>49.5</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.95</v>
+        <v>-0.9</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>25.1</v>
+        <v>26.39</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>1.26</v>
+        <v>-0.79</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>25.25</v>
+        <v>26.53</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>30</v>
@@ -1402,19 +1441,19 @@
         <v>1.25</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.01</v>
+        <v>-0.09</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-1</v>
+        <v>-0.96</v>
       </c>
       <c r="U12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.15</v>
+        <v>0.83</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="X12" s="4" t="n">
         <v>0</v>
@@ -1422,7 +1461,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>37</v>
@@ -1446,28 +1485,28 @@
         <v>31</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-9</v>
+        <v>12.5</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>49</v>
+        <v>49.5</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.95</v>
+        <v>-0.9</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>25.1</v>
+        <v>26.39</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.26</v>
+        <v>-0.79</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>25.25</v>
+        <v>26.53</v>
       </c>
       <c r="Q13" s="3" t="s">
         <v>30</v>
@@ -1476,19 +1515,19 @@
         <v>1.25</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.01</v>
+        <v>-0.09</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-1</v>
+        <v>-0.96</v>
       </c>
       <c r="U13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.15</v>
+        <v>0.83</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="X13" s="4" t="n">
         <v>0</v>
@@ -1496,7 +1535,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>41</v>
@@ -1526,43 +1565,43 @@
         <v>1</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>49.5</v>
+        <v>48.5</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.18</v>
+        <v>0.4</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>50.62</v>
+        <v>50.42</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.72</v>
+        <v>1.88</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>51.15</v>
+        <v>50.59</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.02</v>
+        <v>0.04</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-2.01</v>
+        <v>-1.92</v>
       </c>
       <c r="U14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.3</v>
+        <v>-0.32</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>4.07</v>
+        <v>4.02</v>
       </c>
       <c r="X14" s="4" t="n">
         <v>0</v>
@@ -1570,7 +1609,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>41</v>
@@ -1600,43 +1639,43 @@
         <v>1</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>49.5</v>
+        <v>48.5</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.18</v>
+        <v>0.4</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>50.62</v>
+        <v>50.42</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.72</v>
+        <v>1.88</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>51.15</v>
+        <v>50.59</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.02</v>
+        <v>0.04</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-2.01</v>
+        <v>-1.92</v>
       </c>
       <c r="U15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.3</v>
+        <v>-0.32</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>4.07</v>
+        <v>4.02</v>
       </c>
       <c r="X15" s="4" t="n">
         <v>0</v>
@@ -1644,7 +1683,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>41</v>
@@ -1674,43 +1713,43 @@
         <v>1</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>49.5</v>
+        <v>48.5</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.09</v>
+        <v>0.2</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>25.31</v>
+        <v>25.21</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.36</v>
+        <v>0.94</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>25.58</v>
+        <v>25.3</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-1</v>
+        <v>-0.96</v>
       </c>
       <c r="U16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.15</v>
+        <v>-0.16</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="X16" s="4" t="n">
         <v>0</v>
@@ -1718,7 +1757,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>41</v>
@@ -1748,43 +1787,43 @@
         <v>1</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>49.5</v>
+        <v>48.5</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.09</v>
+        <v>0.2</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>25.31</v>
+        <v>25.21</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.36</v>
+        <v>0.94</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>25.58</v>
+        <v>25.3</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-1</v>
+        <v>-0.96</v>
       </c>
       <c r="U17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.15</v>
+        <v>-0.16</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="X17" s="4" t="n">
         <v>0</v>
@@ -1792,22 +1831,22 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46187</v>
+        <v>46194</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>28</v>
@@ -1822,22 +1861,22 @@
         <v>1</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-5.5</v>
+        <v>-10</v>
       </c>
       <c r="L18" s="4" t="n">
         <v>50.5</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-4.44</v>
+        <v>9.87</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>53.18</v>
+        <v>53.84</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.97</v>
+        <v>6.99</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>53.15</v>
+        <v>53.45</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>30</v>
@@ -1846,19 +1885,19 @@
         <v>2.5</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.15</v>
+        <v>-0.28</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-2.01</v>
+        <v>-1.92</v>
       </c>
       <c r="U18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>1.98</v>
+        <v>2.59</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>4.07</v>
+        <v>4.02</v>
       </c>
       <c r="X18" s="4" t="n">
         <v>0</v>
@@ -1866,22 +1905,22 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46187</v>
+        <v>46194</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>28</v>
@@ -1896,22 +1935,22 @@
         <v>1</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-5.5</v>
+        <v>-10</v>
       </c>
       <c r="L19" s="4" t="n">
         <v>50.5</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-4.42</v>
+        <v>9.9</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>52.47</v>
+        <v>52.76</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.97</v>
+        <v>6.99</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>53.15</v>
+        <v>53.45</v>
       </c>
       <c r="Q19" s="3" t="s">
         <v>30</v>
@@ -1920,42 +1959,42 @@
         <v>2.5</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.15</v>
+        <v>-0.28</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-2.01</v>
+        <v>-1.92</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>1.98</v>
+        <v>2.59</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>4.07</v>
+        <v>4.02</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.7</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46187</v>
+        <v>46194</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>32</v>
@@ -1970,22 +2009,22 @@
         <v>1</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-5.5</v>
+        <v>-10</v>
       </c>
       <c r="L20" s="4" t="n">
         <v>50.5</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.22</v>
+        <v>4.94</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>26.59</v>
+        <v>26.92</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.49</v>
+        <v>3.49</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>26.57</v>
+        <v>26.72</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>30</v>
@@ -1994,19 +2033,19 @@
         <v>1.25</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.08</v>
+        <v>-0.14</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-1</v>
+        <v>-0.96</v>
       </c>
       <c r="U20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.99</v>
+        <v>1.29</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="X20" s="4" t="n">
         <v>0</v>
@@ -2014,22 +2053,22 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46187</v>
+        <v>46194</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>32</v>
@@ -2044,22 +2083,22 @@
         <v>1</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-5.5</v>
+        <v>-10</v>
       </c>
       <c r="L21" s="4" t="n">
         <v>50.5</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.21</v>
+        <v>4.95</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>26.24</v>
+        <v>26.38</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.49</v>
+        <v>3.49</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>26.57</v>
+        <v>26.72</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>30</v>
@@ -2068,22 +2107,894 @@
         <v>1.25</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.08</v>
+        <v>-0.14</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-1</v>
+        <v>-0.96</v>
       </c>
       <c r="U21" s="4" t="n">
         <v>-0.01</v>
       </c>
       <c r="V21" s="4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W21" s="4" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="X21" s="4" t="n">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" s="4" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="M22" s="4" t="n">
+        <v>-6.41</v>
+      </c>
+      <c r="N22" s="4" t="n">
+        <v>53.21</v>
+      </c>
+      <c r="O22" s="4" t="n">
+        <v>-1.88</v>
+      </c>
+      <c r="P22" s="4" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="R22" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S22" s="4" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="T22" s="4" t="n">
+        <v>-1.92</v>
+      </c>
+      <c r="U22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="W22" s="4" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="X22" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="M23" s="4" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="N23" s="4" t="n">
+        <v>52.58</v>
+      </c>
+      <c r="O23" s="4" t="n">
+        <v>-1.88</v>
+      </c>
+      <c r="P23" s="4" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="R23" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S23" s="4" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="T23" s="4" t="n">
+        <v>-1.92</v>
+      </c>
+      <c r="U23" s="4" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V23" s="4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="W23" s="4" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="X23" s="4" t="n">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" s="4" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="M24" s="4" t="n">
+        <v>-3.21</v>
+      </c>
+      <c r="N24" s="4" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="O24" s="4" t="n">
+        <v>-0.94</v>
+      </c>
+      <c r="P24" s="4" t="n">
+        <v>26.35</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="R24" s="4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S24" s="4" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="T24" s="4" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="U24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="W21" s="4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="X21" s="4" t="n">
-        <v>-0.35</v>
+      <c r="W24" s="4" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="X24" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" s="4" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="L25" s="4" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="M25" s="4" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="N25" s="4" t="n">
+        <v>26.29</v>
+      </c>
+      <c r="O25" s="4" t="n">
+        <v>-0.94</v>
+      </c>
+      <c r="P25" s="4" t="n">
+        <v>26.35</v>
+      </c>
+      <c r="Q25" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="R25" s="4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S25" s="4" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="T25" s="4" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="U25" s="4" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V25" s="4" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="W25" s="4" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="X25" s="4" t="n">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" s="4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="M26" s="4" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="N26" s="4" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="O26" s="4" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="P26" s="4" t="n">
+        <v>49.15</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="R26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="4" t="n">
+        <v>-1.92</v>
+      </c>
+      <c r="U26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" s="4" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="X26" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" s="4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L27" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="M27" s="4" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="N27" s="4" t="n">
+        <v>48.76</v>
+      </c>
+      <c r="O27" s="4" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="P27" s="4" t="n">
+        <v>49.15</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="R27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="4" t="n">
+        <v>-1.92</v>
+      </c>
+      <c r="U27" s="4" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="V27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" s="4" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="X27" s="4" t="n">
+        <v>-1.93</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" s="4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L28" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="M28" s="4" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="N28" s="4" t="n">
+        <v>25.35</v>
+      </c>
+      <c r="O28" s="4" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="P28" s="4" t="n">
+        <v>24.58</v>
+      </c>
+      <c r="Q28" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="R28" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="4" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="U28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" s="4" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="X28" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" s="4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="M29" s="4" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="N29" s="4" t="n">
+        <v>24.38</v>
+      </c>
+      <c r="O29" s="4" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="P29" s="4" t="n">
+        <v>24.58</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="R29" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="4" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="U29" s="4" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="V29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" s="4" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="X29" s="4" t="n">
+        <v>-0.97</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>50.91</v>
+      </c>
+      <c r="O30" s="4" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="P30" s="4" t="n">
+        <v>50.91</v>
+      </c>
+      <c r="Q30" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="R30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S30" s="4" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="T30" s="4" t="n">
+        <v>-1.92</v>
+      </c>
+      <c r="U30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="4" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="W30" s="4" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="X30" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="4" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="N31" s="4" t="n">
+        <v>50.91</v>
+      </c>
+      <c r="O31" s="4" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="P31" s="4" t="n">
+        <v>50.91</v>
+      </c>
+      <c r="Q31" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="R31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S31" s="4" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="T31" s="4" t="n">
+        <v>-1.92</v>
+      </c>
+      <c r="U31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="4" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="W31" s="4" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="X31" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="4" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="N32" s="4" t="n">
+        <v>25.46</v>
+      </c>
+      <c r="O32" s="4" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="P32" s="4" t="n">
+        <v>25.46</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="R32" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S32" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="T32" s="4" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="U32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="4" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="W32" s="4" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="X32" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="4" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="N33" s="4" t="n">
+        <v>25.46</v>
+      </c>
+      <c r="O33" s="4" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="P33" s="4" t="n">
+        <v>25.46</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="R33" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S33" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="T33" s="4" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="U33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="4" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="W33" s="4" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="X33" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_upcoming_projections.xlsx
+++ b/files/NRL_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -86,118 +86,124 @@
     <t xml:space="preserve">Rain Total Adj</t>
   </si>
   <si>
+    <t xml:space="preserve">Home Raw Form</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Away Raw Form</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net Uncapped Form</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">south sydney rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CommBank Stadium, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Rain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">same_city_different_ground</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cbus Super Stadium, Gold Coast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">diff_city</t>
+  </si>
+  <si>
     <t xml:space="preserve">20:00</t>
   </si>
   <si>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suncorp Stadium, Brisbane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dolphins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north queensland cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penrith panthers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Queensland Country Bank Stadium, Townsville</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manly-warringah sea eagles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melbourne storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Pines Park, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st george-illawarra dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GIO Stadium, Canberra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:05</t>
+  </si>
+  <si>
     <t xml:space="preserve">newcastle knights</t>
   </si>
   <si>
-    <t xml:space="preserve">st george-illawarra dragons</t>
+    <t xml:space="preserve">wests tigers</t>
   </si>
   <si>
     <t xml:space="preserve">McDonald Jones Stadium, Newcastle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Rain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">diff_city</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wests tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campbelltown Sports Stadium, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penrith panthers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cbus Super Stadium, Gold Coast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manly-warringah sea eagles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accor Stadium, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">same_city_different_ground</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north queensland cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One NZ Stadium, Christchurch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">melbourne storm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberra raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AAMI Park, Melbourne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allianz Stadium, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">south sydney rabbitohs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CommBank Stadium, Sydney</t>
   </si>
 </sst>
 </file>
@@ -547,10 +553,10 @@
   <cols>
     <col min="1" max="1" width="4.9975" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="4.9975" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="25.5775" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="23.8625" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="23.005" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="25.5775" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="14.43" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="30.7225" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="37.5825" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="11.8575" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="14.43" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="14.43" hidden="0" customWidth="1"/>
@@ -569,6 +575,9 @@
     <col min="22" max="22" width="16.145" hidden="0" customWidth="1"/>
     <col min="23" max="23" width="16.145" hidden="0" customWidth="1"/>
     <col min="24" max="24" width="12.715" hidden="0" customWidth="1"/>
+    <col min="25" max="25" width="11.8575" hidden="0" customWidth="1"/>
+    <col min="26" max="26" width="11.8575" hidden="0" customWidth="1"/>
+    <col min="27" max="27" width="15.2875" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -644,31 +653,40 @@
       <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I2" s="5" t="n">
         <v>1</v>
@@ -677,72 +695,81 @@
         <v>1</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>-10.5</v>
+        <v>6.5</v>
       </c>
       <c r="L2" s="4" t="n">
         <v>49</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>-6.72</v>
+        <v>1.06</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>49.69</v>
+        <v>50.41</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>-11.85</v>
+        <v>0.1</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>50.01</v>
+        <v>47.46</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="R2" s="4" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.07</v>
+        <v>-0.01</v>
       </c>
       <c r="T2" s="4" t="n">
-        <v>-1.92</v>
+        <v>-1.87</v>
       </c>
       <c r="U2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>-0.63</v>
+        <v>-0.3</v>
       </c>
       <c r="W2" s="4" t="n">
         <v>4.02</v>
       </c>
       <c r="X2" s="4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y2" s="4" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Z2" s="4" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AA2" s="4" t="n">
+        <v>2.03</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I3" s="5" t="n">
         <v>1</v>
@@ -751,73 +778,82 @@
         <v>1</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-10.5</v>
+        <v>6.5</v>
       </c>
       <c r="L3" s="4" t="n">
         <v>49</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>-6.72</v>
+        <v>1.3</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>49.69</v>
+        <v>47.09</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>-11.85</v>
+        <v>0.1</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>50.01</v>
+        <v>47.46</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.07</v>
+        <v>-0.01</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>-1.92</v>
+        <v>-1.87</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>0</v>
+        <v>-0.24</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>-0.63</v>
+        <v>-0.3</v>
       </c>
       <c r="W3" s="4" t="n">
         <v>4.02</v>
       </c>
       <c r="X3" s="4" t="n">
-        <v>0</v>
+        <v>-3.32</v>
+      </c>
+      <c r="Y3" s="4" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Z3" s="4" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AA3" s="4" t="n">
+        <v>2.03</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>29</v>
-      </c>
       <c r="I4" s="5" t="n">
         <v>1</v>
       </c>
@@ -825,72 +861,81 @@
         <v>1</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-10.5</v>
+        <v>6.5</v>
       </c>
       <c r="L4" s="4" t="n">
         <v>49</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>-3.36</v>
+        <v>0.53</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>24.84</v>
+        <v>25.2</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>-5.93</v>
+        <v>0.05</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>25</v>
+        <v>23.73</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="T4" s="4" t="n">
-        <v>-0.96</v>
+        <v>-0.94</v>
       </c>
       <c r="U4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>-0.31</v>
+        <v>-0.15</v>
       </c>
       <c r="W4" s="4" t="n">
         <v>2.01</v>
       </c>
       <c r="X4" s="4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y4" s="4" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Z4" s="4" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AA4" s="4" t="n">
+        <v>2.03</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>1</v>
@@ -899,72 +944,81 @@
         <v>1</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-10.5</v>
+        <v>6.5</v>
       </c>
       <c r="L5" s="4" t="n">
         <v>49</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>-3.36</v>
+        <v>0.65</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>24.84</v>
+        <v>23.54</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>-5.93</v>
+        <v>0.05</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>25</v>
+        <v>23.73</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>-0.96</v>
+        <v>-0.94</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>-0.31</v>
+        <v>-0.15</v>
       </c>
       <c r="W5" s="4" t="n">
         <v>2.01</v>
       </c>
       <c r="X5" s="4" t="n">
-        <v>0</v>
+        <v>-1.66</v>
+      </c>
+      <c r="Y5" s="4" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Z5" s="4" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AA5" s="4" t="n">
+        <v>2.03</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>1</v>
@@ -973,73 +1027,82 @@
         <v>1</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>8.5</v>
+        <v>1</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>52</v>
+        <v>46.5</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-5.4</v>
+        <v>-4.98</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>53.13</v>
+        <v>50.6</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-4.52</v>
+        <v>-7.44</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>53.45</v>
+        <v>48.03</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="R6" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.25</v>
+        <v>0.01</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-1.92</v>
+        <v>-1.87</v>
       </c>
       <c r="U6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="W6" s="4" t="n">
         <v>4.02</v>
       </c>
       <c r="X6" s="4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y6" s="4" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="Z6" s="4" t="n">
+        <v>-4.43</v>
+      </c>
+      <c r="AA6" s="4" t="n">
+        <v>2.81</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="I7" s="5" t="n">
         <v>1</v>
       </c>
@@ -1047,73 +1110,82 @@
         <v>1</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>8.5</v>
+        <v>1</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>52</v>
+        <v>46.5</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-5.4</v>
+        <v>-4.81</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>53.13</v>
+        <v>47.67</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-4.52</v>
+        <v>-7.44</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>53.45</v>
+        <v>48.03</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="R7" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.25</v>
+        <v>0.01</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-1.92</v>
+        <v>-1.87</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="W7" s="4" t="n">
         <v>4.02</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>0</v>
+        <v>-2.93</v>
+      </c>
+      <c r="Y7" s="4" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="Z7" s="4" t="n">
+        <v>-4.43</v>
+      </c>
+      <c r="AA7" s="4" t="n">
+        <v>2.81</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>29</v>
-      </c>
       <c r="I8" s="5" t="n">
         <v>1</v>
       </c>
@@ -1121,73 +1193,82 @@
         <v>1</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>8.5</v>
+        <v>1</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>52</v>
+        <v>46.5</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-2.7</v>
+        <v>-2.49</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>26.57</v>
+        <v>25.3</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-2.26</v>
+        <v>-3.72</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>26.72</v>
+        <v>24.01</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="R8" s="4" t="n">
         <v>1.25</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.12</v>
+        <v>0.01</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.96</v>
+        <v>-0.94</v>
       </c>
       <c r="U8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W8" s="4" t="n">
         <v>2.01</v>
       </c>
       <c r="X8" s="4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y8" s="4" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="Z8" s="4" t="n">
+        <v>-4.43</v>
+      </c>
+      <c r="AA8" s="4" t="n">
+        <v>2.81</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="I9" s="5" t="n">
         <v>1</v>
       </c>
@@ -1195,72 +1276,81 @@
         <v>1</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>8.5</v>
+        <v>1</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>52</v>
+        <v>46.5</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-2.7</v>
+        <v>-2.4</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>26.57</v>
+        <v>23.84</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-2.26</v>
+        <v>-3.72</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>26.72</v>
+        <v>24.01</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="R9" s="4" t="n">
         <v>1.25</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.12</v>
+        <v>0.01</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.96</v>
+        <v>-0.94</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W9" s="4" t="n">
         <v>2.01</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>0</v>
+        <v>-1.46</v>
+      </c>
+      <c r="Y9" s="4" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="Z9" s="4" t="n">
+        <v>-4.43</v>
+      </c>
+      <c r="AA9" s="4" t="n">
+        <v>2.81</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>1</v>
@@ -1269,72 +1359,81 @@
         <v>1</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>12.5</v>
+        <v>3.5</v>
       </c>
       <c r="L10" s="4" t="n">
         <v>49.5</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.79</v>
+        <v>-0.95</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>52.78</v>
+        <v>49.84</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.58</v>
+        <v>-6.73</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>53.06</v>
+        <v>49.48</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="R10" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.18</v>
+        <v>-0.02</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-1.92</v>
+        <v>-1.87</v>
       </c>
       <c r="U10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>1.65</v>
+        <v>-0.63</v>
       </c>
       <c r="W10" s="4" t="n">
         <v>4.02</v>
       </c>
       <c r="X10" s="4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y10" s="4" t="n">
+        <v>-28.11</v>
+      </c>
+      <c r="Z10" s="4" t="n">
+        <v>-14.26</v>
+      </c>
+      <c r="AA10" s="4" t="n">
+        <v>-11.08</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I11" s="5" t="n">
         <v>1</v>
@@ -1343,73 +1442,82 @@
         <v>1</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>12.5</v>
+        <v>3.5</v>
       </c>
       <c r="L11" s="4" t="n">
         <v>49.5</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.79</v>
+        <v>-0.93</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>52.78</v>
+        <v>48.87</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.58</v>
+        <v>-6.73</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>53.06</v>
+        <v>49.48</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="R11" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.18</v>
+        <v>-0.02</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-1.92</v>
+        <v>-1.87</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>1.65</v>
+        <v>-0.63</v>
       </c>
       <c r="W11" s="4" t="n">
         <v>4.02</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>0</v>
+        <v>-0.98</v>
+      </c>
+      <c r="Y11" s="4" t="n">
+        <v>-28.11</v>
+      </c>
+      <c r="Z11" s="4" t="n">
+        <v>-14.26</v>
+      </c>
+      <c r="AA11" s="4" t="n">
+        <v>-11.08</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>29</v>
-      </c>
       <c r="I12" s="5" t="n">
         <v>1</v>
       </c>
@@ -1417,72 +1525,81 @@
         <v>1</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>12.5</v>
+        <v>3.5</v>
       </c>
       <c r="L12" s="4" t="n">
         <v>49.5</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.9</v>
+        <v>-0.48</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>26.39</v>
+        <v>24.92</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.79</v>
+        <v>-3.36</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>26.53</v>
+        <v>24.74</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="R12" s="4" t="n">
         <v>1.25</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.09</v>
+        <v>-0.01</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.96</v>
+        <v>-0.94</v>
       </c>
       <c r="U12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.83</v>
+        <v>-0.31</v>
       </c>
       <c r="W12" s="4" t="n">
         <v>2.01</v>
       </c>
       <c r="X12" s="4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y12" s="4" t="n">
+        <v>-28.11</v>
+      </c>
+      <c r="Z12" s="4" t="n">
+        <v>-14.26</v>
+      </c>
+      <c r="AA12" s="4" t="n">
+        <v>-11.08</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I13" s="5" t="n">
         <v>1</v>
@@ -1491,72 +1608,81 @@
         <v>1</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>12.5</v>
+        <v>3.5</v>
       </c>
       <c r="L13" s="4" t="n">
         <v>49.5</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.9</v>
+        <v>-0.47</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>26.39</v>
+        <v>24.43</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.79</v>
+        <v>-3.36</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>26.53</v>
+        <v>24.74</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="R13" s="4" t="n">
         <v>1.25</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.09</v>
+        <v>-0.01</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.96</v>
+        <v>-0.94</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>0.83</v>
+        <v>-0.31</v>
       </c>
       <c r="W13" s="4" t="n">
         <v>2.01</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>0</v>
+        <v>-0.49</v>
+      </c>
+      <c r="Y13" s="4" t="n">
+        <v>-28.11</v>
+      </c>
+      <c r="Z13" s="4" t="n">
+        <v>-14.26</v>
+      </c>
+      <c r="AA13" s="4" t="n">
+        <v>-11.08</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>44</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I14" s="5" t="n">
         <v>1</v>
@@ -1565,72 +1691,81 @@
         <v>1</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>7.5</v>
+        <v>-4</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>48.5</v>
+        <v>50.5</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.4</v>
+        <v>-7.17</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>50.42</v>
+        <v>52.55</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.88</v>
+        <v>-4.51</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>50.59</v>
+        <v>51.48</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.04</v>
+        <v>-0.12</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-1.92</v>
+        <v>-1.87</v>
       </c>
       <c r="U14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.32</v>
+        <v>2.29</v>
       </c>
       <c r="W14" s="4" t="n">
         <v>4.02</v>
       </c>
       <c r="X14" s="4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y14" s="4" t="n">
+        <v>21.73</v>
+      </c>
+      <c r="Z14" s="4" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="AA14" s="4" t="n">
+        <v>8.27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>44</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I15" s="5" t="n">
         <v>1</v>
@@ -1639,73 +1774,82 @@
         <v>1</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>7.5</v>
+        <v>-4</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>48.5</v>
+        <v>50.5</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.4</v>
+        <v>-7.12</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>50.42</v>
+        <v>51.08</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.88</v>
+        <v>-4.51</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>50.59</v>
+        <v>51.48</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.04</v>
+        <v>-0.12</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-1.92</v>
+        <v>-1.87</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.32</v>
+        <v>2.29</v>
       </c>
       <c r="W15" s="4" t="n">
         <v>4.02</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>0</v>
+        <v>-1.47</v>
+      </c>
+      <c r="Y15" s="4" t="n">
+        <v>21.73</v>
+      </c>
+      <c r="Z15" s="4" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="AA15" s="4" t="n">
+        <v>8.27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>44</v>
       </c>
       <c r="G16" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>29</v>
-      </c>
       <c r="I16" s="5" t="n">
         <v>1</v>
       </c>
@@ -1713,72 +1857,81 @@
         <v>1</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>7.5</v>
+        <v>-4</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>48.5</v>
+        <v>50.5</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.2</v>
+        <v>-3.58</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>25.21</v>
+        <v>26.28</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.94</v>
+        <v>-2.25</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>25.3</v>
+        <v>25.74</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.96</v>
+        <v>-0.94</v>
       </c>
       <c r="U16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.16</v>
+        <v>1.14</v>
       </c>
       <c r="W16" s="4" t="n">
         <v>2.01</v>
       </c>
       <c r="X16" s="4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y16" s="4" t="n">
+        <v>21.73</v>
+      </c>
+      <c r="Z16" s="4" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="AA16" s="4" t="n">
+        <v>8.27</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>44</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I17" s="5" t="n">
         <v>1</v>
@@ -1787,72 +1940,81 @@
         <v>1</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>7.5</v>
+        <v>-4</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>48.5</v>
+        <v>50.5</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.2</v>
+        <v>-3.56</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>25.21</v>
+        <v>25.54</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.94</v>
+        <v>-2.25</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>25.3</v>
+        <v>25.74</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.96</v>
+        <v>-0.94</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.16</v>
+        <v>1.14</v>
       </c>
       <c r="W17" s="4" t="n">
         <v>2.01</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>0</v>
+        <v>-0.74</v>
+      </c>
+      <c r="Y17" s="4" t="n">
+        <v>21.73</v>
+      </c>
+      <c r="Z17" s="4" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="AA17" s="4" t="n">
+        <v>8.27</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I18" s="5" t="n">
         <v>1</v>
@@ -1861,72 +2023,81 @@
         <v>1</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-10</v>
+        <v>11.5</v>
       </c>
       <c r="L18" s="4" t="n">
         <v>50.5</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>9.87</v>
+        <v>-3.11</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>53.84</v>
+        <v>53.67</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>6.99</v>
+        <v>-7.2</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>53.45</v>
+        <v>52.87</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="R18" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.28</v>
+        <v>-0.16</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-1.92</v>
+        <v>-1.87</v>
       </c>
       <c r="U18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>2.59</v>
+        <v>1.73</v>
       </c>
       <c r="W18" s="4" t="n">
         <v>4.02</v>
       </c>
       <c r="X18" s="4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y18" s="4" t="n">
+        <v>-4.02</v>
+      </c>
+      <c r="Z18" s="4" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="AA18" s="4" t="n">
+        <v>-11.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I19" s="5" t="n">
         <v>1</v>
@@ -1935,73 +2106,82 @@
         <v>1</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-10</v>
+        <v>11.5</v>
       </c>
       <c r="L19" s="4" t="n">
         <v>50.5</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>9.9</v>
+        <v>-3.1</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>52.76</v>
+        <v>52.73</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>6.99</v>
+        <v>-7.2</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>53.45</v>
+        <v>52.87</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="R19" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.28</v>
+        <v>-0.16</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-1.92</v>
+        <v>-1.87</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>2.59</v>
+        <v>1.73</v>
       </c>
       <c r="W19" s="4" t="n">
         <v>4.02</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-1.08</v>
+        <v>-0.94</v>
+      </c>
+      <c r="Y19" s="4" t="n">
+        <v>-4.02</v>
+      </c>
+      <c r="Z19" s="4" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="AA19" s="4" t="n">
+        <v>-11.1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H20" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>29</v>
-      </c>
       <c r="I20" s="5" t="n">
         <v>1</v>
       </c>
@@ -2009,72 +2189,81 @@
         <v>1</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-10</v>
+        <v>11.5</v>
       </c>
       <c r="L20" s="4" t="n">
         <v>50.5</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>4.94</v>
+        <v>-1.56</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>26.92</v>
+        <v>26.84</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>3.49</v>
+        <v>-3.6</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>26.72</v>
+        <v>26.44</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="R20" s="4" t="n">
         <v>1.25</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.14</v>
+        <v>-0.08</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.96</v>
+        <v>-0.94</v>
       </c>
       <c r="U20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>1.29</v>
+        <v>0.87</v>
       </c>
       <c r="W20" s="4" t="n">
         <v>2.01</v>
       </c>
       <c r="X20" s="4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y20" s="4" t="n">
+        <v>-4.02</v>
+      </c>
+      <c r="Z20" s="4" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="AA20" s="4" t="n">
+        <v>-11.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I21" s="5" t="n">
         <v>1</v>
@@ -2083,72 +2272,81 @@
         <v>1</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-10</v>
+        <v>11.5</v>
       </c>
       <c r="L21" s="4" t="n">
         <v>50.5</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>4.95</v>
+        <v>-1.55</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>26.38</v>
+        <v>26.36</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>3.49</v>
+        <v>-3.6</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>26.72</v>
+        <v>26.44</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="R21" s="4" t="n">
         <v>1.25</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.14</v>
+        <v>-0.08</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.96</v>
+        <v>-0.94</v>
       </c>
       <c r="U21" s="4" t="n">
         <v>-0.01</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>1.29</v>
+        <v>0.87</v>
       </c>
       <c r="W21" s="4" t="n">
         <v>2.01</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.54</v>
+        <v>-0.47</v>
+      </c>
+      <c r="Y21" s="4" t="n">
+        <v>-4.02</v>
+      </c>
+      <c r="Z21" s="4" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="AA21" s="4" t="n">
+        <v>-11.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.37</v>
+        <v>1.47</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I22" s="5" t="n">
         <v>1</v>
@@ -2157,72 +2355,81 @@
         <v>1</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-9.5</v>
+        <v>-4.5</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>50.5</v>
+        <v>48</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-6.41</v>
+        <v>-3.01</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>53.21</v>
+        <v>50.54</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.88</v>
+        <v>-3.84</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>52.7</v>
+        <v>48.98</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="R22" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-0.22</v>
+        <v>-0.01</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-1.92</v>
+        <v>-1.87</v>
       </c>
       <c r="U22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>1.97</v>
+        <v>-0.32</v>
       </c>
       <c r="W22" s="4" t="n">
         <v>4.02</v>
       </c>
       <c r="X22" s="4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y22" s="4" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="Z22" s="4" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="AA22" s="4" t="n">
+        <v>3.35</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.37</v>
+        <v>1.47</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I23" s="5" t="n">
         <v>1</v>
@@ -2231,73 +2438,82 @@
         <v>1</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-9.5</v>
+        <v>-4.5</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>50.5</v>
+        <v>48</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-6.4</v>
+        <v>-2.95</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>52.58</v>
+        <v>48.87</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.88</v>
+        <v>-3.84</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>52.7</v>
+        <v>48.98</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="R23" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-0.22</v>
+        <v>-0.01</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-1.92</v>
+        <v>-1.87</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>1.97</v>
+        <v>-0.32</v>
       </c>
       <c r="W23" s="4" t="n">
         <v>4.02</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.63</v>
+        <v>-1.67</v>
+      </c>
+      <c r="Y23" s="4" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="Z23" s="4" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="AA23" s="4" t="n">
+        <v>3.35</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.37</v>
+        <v>1.47</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G24" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>29</v>
-      </c>
       <c r="I24" s="5" t="n">
         <v>1</v>
       </c>
@@ -2305,72 +2521,81 @@
         <v>1</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-9.5</v>
+        <v>-4.5</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>50.5</v>
+        <v>48</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-3.21</v>
+        <v>-1.51</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>26.6</v>
+        <v>25.27</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.94</v>
+        <v>-1.92</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>26.35</v>
+        <v>24.49</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="R24" s="4" t="n">
         <v>1.25</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.11</v>
+        <v>0</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.96</v>
+        <v>-0.94</v>
       </c>
       <c r="U24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.99</v>
+        <v>-0.16</v>
       </c>
       <c r="W24" s="4" t="n">
         <v>2.01</v>
       </c>
       <c r="X24" s="4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y24" s="4" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="Z24" s="4" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="AA24" s="4" t="n">
+        <v>3.35</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.37</v>
+        <v>1.47</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I25" s="5" t="n">
         <v>1</v>
@@ -2379,72 +2604,81 @@
         <v>1</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-9.5</v>
+        <v>-4.5</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>50.5</v>
+        <v>48</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-3.2</v>
+        <v>-1.48</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>26.29</v>
+        <v>24.44</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.94</v>
+        <v>-1.92</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>26.35</v>
+        <v>24.49</v>
       </c>
       <c r="Q25" s="3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="R25" s="4" t="n">
         <v>1.25</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.11</v>
+        <v>0</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.96</v>
+        <v>-0.94</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>0.99</v>
+        <v>-0.16</v>
       </c>
       <c r="W25" s="4" t="n">
         <v>2.01</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.32</v>
+        <v>-0.84</v>
+      </c>
+      <c r="Y25" s="4" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="Z25" s="4" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="AA25" s="4" t="n">
+        <v>3.35</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I26" s="5" t="n">
         <v>1</v>
@@ -2453,72 +2687,81 @@
         <v>1</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-6</v>
+        <v>-11</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>50</v>
+        <v>52.5</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-2.4</v>
+        <v>-5.43</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>50.7</v>
+        <v>53.2</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.23</v>
+        <v>-10.37</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>49.15</v>
+        <v>51.72</v>
       </c>
       <c r="Q26" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-1.92</v>
+        <v>-1.87</v>
       </c>
       <c r="U26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="W26" s="4" t="n">
         <v>4.02</v>
       </c>
       <c r="X26" s="4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y26" s="4" t="n">
+        <v>-4.29</v>
+      </c>
+      <c r="Z26" s="4" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AA26" s="4" t="n">
+        <v>-5.48</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I27" s="5" t="n">
         <v>1</v>
@@ -2527,73 +2770,82 @@
         <v>1</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-6</v>
+        <v>-11</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>50</v>
+        <v>52.5</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-2.32</v>
+        <v>-5.38</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>48.76</v>
+        <v>51.54</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.23</v>
+        <v>-10.37</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>49.15</v>
+        <v>51.72</v>
       </c>
       <c r="Q27" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-1.92</v>
+        <v>-1.87</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="W27" s="4" t="n">
         <v>4.02</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-1.93</v>
+        <v>-1.67</v>
+      </c>
+      <c r="Y27" s="4" t="n">
+        <v>-4.29</v>
+      </c>
+      <c r="Z27" s="4" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AA27" s="4" t="n">
+        <v>-5.48</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G28" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H28" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H28" s="3" t="s">
-        <v>29</v>
-      </c>
       <c r="I28" s="5" t="n">
         <v>1</v>
       </c>
@@ -2601,72 +2853,81 @@
         <v>1</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-6</v>
+        <v>-11</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>50</v>
+        <v>52.5</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.2</v>
+        <v>-2.72</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>25.35</v>
+        <v>26.6</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.11</v>
+        <v>-5.19</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>24.58</v>
+        <v>25.86</v>
       </c>
       <c r="Q28" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.96</v>
+        <v>-0.94</v>
       </c>
       <c r="U28" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W28" s="4" t="n">
         <v>2.01</v>
       </c>
       <c r="X28" s="4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y28" s="4" t="n">
+        <v>-4.29</v>
+      </c>
+      <c r="Z28" s="4" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AA28" s="4" t="n">
+        <v>-5.48</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I29" s="5" t="n">
         <v>1</v>
@@ -2675,326 +2936,387 @@
         <v>1</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-6</v>
+        <v>-11</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>50</v>
+        <v>52.5</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.16</v>
+        <v>-2.69</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>24.38</v>
+        <v>25.77</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.11</v>
+        <v>-5.19</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>24.58</v>
+        <v>25.86</v>
       </c>
       <c r="Q29" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.96</v>
+        <v>-0.94</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W29" s="4" t="n">
         <v>2.01</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.97</v>
+        <v>-0.83</v>
+      </c>
+      <c r="Y29" s="4" t="n">
+        <v>-4.29</v>
+      </c>
+      <c r="Z29" s="4" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AA29" s="4" t="n">
+        <v>-5.48</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46198</v>
+        <v>46201</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="4"/>
-      <c r="L30" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>52</v>
+      </c>
       <c r="M30" s="4" t="n">
-        <v>-0.08</v>
+        <v>-3.29</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>50.91</v>
+        <v>53.32</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.09</v>
+        <v>-4.78</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>50.91</v>
+        <v>52.98</v>
       </c>
       <c r="Q30" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.04</v>
+        <v>-0.14</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-1.92</v>
+        <v>-1.87</v>
       </c>
       <c r="U30" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.32</v>
+        <v>2.04</v>
       </c>
       <c r="W30" s="4" t="n">
         <v>4.02</v>
       </c>
       <c r="X30" s="4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y30" s="4" t="n">
+        <v>13.92</v>
+      </c>
+      <c r="Z30" s="4" t="n">
+        <v>-19.15</v>
+      </c>
+      <c r="AA30" s="4" t="n">
+        <v>26.46</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46198</v>
+        <v>46201</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="4"/>
-      <c r="L31" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="K31" s="4" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>52</v>
+      </c>
       <c r="M31" s="4" t="n">
-        <v>-0.08</v>
+        <v>-3.28</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>50.91</v>
+        <v>52.51</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.09</v>
+        <v>-4.78</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>50.91</v>
+        <v>52.98</v>
       </c>
       <c r="Q31" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.04</v>
+        <v>-0.14</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-1.92</v>
+        <v>-1.87</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.32</v>
+        <v>2.04</v>
       </c>
       <c r="W31" s="4" t="n">
         <v>4.02</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>0</v>
+        <v>-0.81</v>
+      </c>
+      <c r="Y31" s="4" t="n">
+        <v>13.92</v>
+      </c>
+      <c r="Z31" s="4" t="n">
+        <v>-19.15</v>
+      </c>
+      <c r="AA31" s="4" t="n">
+        <v>26.46</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46198</v>
+        <v>46201</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G32" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H32" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>29</v>
-      </c>
       <c r="I32" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="4"/>
-      <c r="L32" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>52</v>
+      </c>
       <c r="M32" s="4" t="n">
-        <v>-0.04</v>
+        <v>-1.65</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>25.46</v>
+        <v>26.66</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.04</v>
+        <v>-2.39</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>25.46</v>
+        <v>26.49</v>
       </c>
       <c r="Q32" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>0.02</v>
+        <v>-0.07</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.96</v>
+        <v>-0.94</v>
       </c>
       <c r="U32" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.16</v>
+        <v>1.02</v>
       </c>
       <c r="W32" s="4" t="n">
         <v>2.01</v>
       </c>
       <c r="X32" s="4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y32" s="4" t="n">
+        <v>13.92</v>
+      </c>
+      <c r="Z32" s="4" t="n">
+        <v>-19.15</v>
+      </c>
+      <c r="AA32" s="4" t="n">
+        <v>26.46</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>46198</v>
+        <v>46201</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="4"/>
-      <c r="L33" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="K33" s="4" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="L33" s="4" t="n">
+        <v>52</v>
+      </c>
       <c r="M33" s="4" t="n">
-        <v>-0.04</v>
+        <v>-1.64</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>25.46</v>
+        <v>26.26</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.04</v>
+        <v>-2.39</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>25.46</v>
+        <v>26.49</v>
       </c>
       <c r="Q33" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>0.02</v>
+        <v>-0.07</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.96</v>
+        <v>-0.94</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.16</v>
+        <v>1.02</v>
       </c>
       <c r="W33" s="4" t="n">
         <v>2.01</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>0</v>
+        <v>-0.4</v>
+      </c>
+      <c r="Y33" s="4" t="n">
+        <v>13.92</v>
+      </c>
+      <c r="Z33" s="4" t="n">
+        <v>-19.15</v>
+      </c>
+      <c r="AA33" s="4" t="n">
+        <v>26.46</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_upcoming_projections.xlsx
+++ b/files/NRL_upcoming_projections.xlsx
@@ -701,10 +701,10 @@
         <v>49</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>50.41</v>
+        <v>50.43</v>
       </c>
       <c r="O2" s="4" t="n">
         <v>0.1</v>
@@ -784,10 +784,10 @@
         <v>49</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>47.09</v>
+        <v>47.1</v>
       </c>
       <c r="O3" s="4" t="n">
         <v>0.1</v>
@@ -870,7 +870,7 @@
         <v>0.53</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>25.2</v>
+        <v>25.21</v>
       </c>
       <c r="O4" s="4" t="n">
         <v>0.05</v>
@@ -950,10 +950,10 @@
         <v>49</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>23.54</v>
+        <v>23.55</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>0.05</v>

--- a/files/NRL_upcoming_projections.xlsx
+++ b/files/NRL_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -95,112 +95,79 @@
     <t xml:space="preserve">Net Uncapped Form</t>
   </si>
   <si>
-    <t xml:space="preserve">19:50</t>
+    <t xml:space="preserve">20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penrith panthers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">south sydney rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlueBet Stadium, Penrith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Rain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">same_city_different_ground</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st george-illawarra dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wests tigers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jubilee Oval, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suncorp Stadium, Brisbane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">diff_city</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:00</t>
   </si>
   <si>
     <t xml:space="preserve">parramatta eels</t>
   </si>
   <si>
-    <t xml:space="preserve">south sydney rabbitohs</t>
+    <t xml:space="preserve">manly-warringah sea eagles</t>
   </si>
   <si>
     <t xml:space="preserve">CommBank Stadium, Sydney</t>
   </si>
   <si>
-    <t xml:space="preserve">FT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Rain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">same_city_different_ground</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cbus Super Stadium, Gold Coast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">diff_city</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suncorp Stadium, Brisbane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:00</t>
+    <t xml:space="preserve">16:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">newcastle knights</t>
   </si>
   <si>
     <t xml:space="preserve">dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north queensland cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penrith panthers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Queensland Country Bank Stadium, Townsville</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manly-warringah sea eagles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">melbourne storm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 Pines Park, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberra raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st george-illawarra dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GIO Stadium, Canberra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">newcastle knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wests tigers</t>
   </si>
   <si>
     <t xml:space="preserve">McDonald Jones Stadium, Newcastle</t>
@@ -553,10 +520,10 @@
   <cols>
     <col min="1" max="1" width="4.9975" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="4.9975" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="23.005" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="25.5775" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="23.8625" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="23.005" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="14.43" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="37.5825" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="29.0075" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="11.8575" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="14.43" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="14.43" hidden="0" customWidth="1"/>
@@ -665,7 +632,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46198</v>
+        <v>46206</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>27</v>
@@ -677,7 +644,7 @@
         <v>29</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>30</v>
@@ -695,22 +662,22 @@
         <v>1</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>6.5</v>
+        <v>-4</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>1.05</v>
+        <v>-4.95</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>50.43</v>
+        <v>50.17</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>0.1</v>
+        <v>-2.95</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>47.46</v>
+        <v>50.21</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>33</v>
@@ -719,36 +686,36 @@
         <v>1</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="T2" s="4" t="n">
-        <v>-1.87</v>
+        <v>-1.91</v>
       </c>
       <c r="U2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>-0.3</v>
+        <v>-0.73</v>
       </c>
       <c r="W2" s="4" t="n">
-        <v>4.02</v>
+        <v>3.87</v>
       </c>
       <c r="X2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Y2" s="4" t="n">
-        <v>2.66</v>
+        <v>7.55</v>
       </c>
       <c r="Z2" s="4" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>2.03</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46198</v>
+        <v>46206</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>27</v>
@@ -760,7 +727,7 @@
         <v>29</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>30</v>
@@ -778,22 +745,22 @@
         <v>1</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>6.5</v>
+        <v>-4</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>1.29</v>
+        <v>-4.95</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>47.1</v>
+        <v>50.17</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>0.1</v>
+        <v>-2.95</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>47.46</v>
+        <v>50.21</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>33</v>
@@ -802,36 +769,36 @@
         <v>1</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>-1.87</v>
+        <v>-1.91</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>-0.24</v>
+        <v>0</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>-0.3</v>
+        <v>-0.73</v>
       </c>
       <c r="W3" s="4" t="n">
-        <v>4.02</v>
+        <v>3.87</v>
       </c>
       <c r="X3" s="4" t="n">
-        <v>-3.32</v>
+        <v>0</v>
       </c>
       <c r="Y3" s="4" t="n">
-        <v>2.66</v>
+        <v>7.55</v>
       </c>
       <c r="Z3" s="4" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>2.03</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46198</v>
+        <v>46206</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>27</v>
@@ -843,7 +810,7 @@
         <v>29</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>30</v>
@@ -861,22 +828,22 @@
         <v>1</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>6.5</v>
+        <v>-4</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.53</v>
+        <v>-2.47</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>25.21</v>
+        <v>25.09</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>0.05</v>
+        <v>-1.48</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>23.73</v>
+        <v>25.11</v>
       </c>
       <c r="Q4" s="3" t="s">
         <v>33</v>
@@ -888,33 +855,33 @@
         <v>0</v>
       </c>
       <c r="T4" s="4" t="n">
-        <v>-0.94</v>
+        <v>-0.96</v>
       </c>
       <c r="U4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>-0.15</v>
+        <v>-0.37</v>
       </c>
       <c r="W4" s="4" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="X4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="4" t="n">
-        <v>2.66</v>
+        <v>7.55</v>
       </c>
       <c r="Z4" s="4" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>2.03</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46198</v>
+        <v>46206</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>27</v>
@@ -926,7 +893,7 @@
         <v>29</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>30</v>
@@ -944,22 +911,22 @@
         <v>1</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>6.5</v>
+        <v>-4</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>0.64</v>
+        <v>-2.47</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>23.55</v>
+        <v>25.09</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>0.05</v>
+        <v>-1.48</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>23.73</v>
+        <v>25.11</v>
       </c>
       <c r="Q5" s="3" t="s">
         <v>33</v>
@@ -971,33 +938,33 @@
         <v>0</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>-0.94</v>
+        <v>-0.96</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>-0.15</v>
+        <v>-0.37</v>
       </c>
       <c r="W5" s="4" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="X5" s="4" t="n">
-        <v>-1.66</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="4" t="n">
-        <v>2.66</v>
+        <v>7.55</v>
       </c>
       <c r="Z5" s="4" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>2.03</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46199</v>
+        <v>46207</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>36</v>
@@ -1009,7 +976,7 @@
         <v>38</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>39</v>
@@ -1027,60 +994,60 @@
         <v>1</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>46.5</v>
+        <v>48.5</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-4.98</v>
+        <v>1.48</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>50.6</v>
+        <v>51.97</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-7.44</v>
+        <v>4.78</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>48.03</v>
+        <v>52.04</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.01</v>
+        <v>-0.1</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-1.87</v>
+        <v>-1.91</v>
       </c>
       <c r="U6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>4.02</v>
+        <v>3.87</v>
       </c>
       <c r="X6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.91</v>
+        <v>3.92</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-4.43</v>
+        <v>-17.44</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>2.81</v>
+        <v>17.09</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46199</v>
+        <v>46207</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>36</v>
@@ -1092,7 +1059,7 @@
         <v>38</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>39</v>
@@ -1110,60 +1077,60 @@
         <v>1</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>46.5</v>
+        <v>48.5</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-4.81</v>
+        <v>1.48</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>47.67</v>
+        <v>51.97</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-7.44</v>
+        <v>4.78</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>48.03</v>
+        <v>52.04</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.01</v>
+        <v>-0.1</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-1.87</v>
+        <v>-1.91</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>4.02</v>
+        <v>3.87</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-2.93</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.91</v>
+        <v>3.92</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-4.43</v>
+        <v>-17.44</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>2.81</v>
+        <v>17.09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46199</v>
+        <v>46207</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>36</v>
@@ -1175,7 +1142,7 @@
         <v>38</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>39</v>
@@ -1193,60 +1160,60 @@
         <v>1</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>46.5</v>
+        <v>48.5</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-2.49</v>
+        <v>0.74</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>25.3</v>
+        <v>25.98</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-3.72</v>
+        <v>2.39</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>24.01</v>
+        <v>26.02</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.94</v>
+        <v>-0.96</v>
       </c>
       <c r="U8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="X8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.91</v>
+        <v>3.92</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-4.43</v>
+        <v>-17.44</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>2.81</v>
+        <v>17.09</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46199</v>
+        <v>46207</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>36</v>
@@ -1258,7 +1225,7 @@
         <v>38</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>39</v>
@@ -1276,75 +1243,75 @@
         <v>1</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>46.5</v>
+        <v>48.5</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-2.4</v>
+        <v>0.74</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>23.84</v>
+        <v>25.98</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-3.72</v>
+        <v>2.39</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>24.01</v>
+        <v>26.02</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.94</v>
+        <v>-0.96</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-1.46</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.91</v>
+        <v>3.92</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-4.43</v>
+        <v>-17.44</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>2.81</v>
+        <v>17.09</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46199</v>
+        <v>46207</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="E10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>31</v>
@@ -1356,78 +1323,78 @@
         <v>1</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>49.5</v>
+        <v>48.5</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.95</v>
+        <v>1.59</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>49.84</v>
+        <v>50.3</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-6.73</v>
+        <v>-4.74</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>49.48</v>
+        <v>50.73</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="R10" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-1.87</v>
+        <v>-1.91</v>
       </c>
       <c r="U10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.63</v>
+        <v>-0.36</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>4.02</v>
+        <v>3.87</v>
       </c>
       <c r="X10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-28.11</v>
+        <v>-28.09</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-14.26</v>
+        <v>0.19</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>-11.08</v>
+        <v>-22.63</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46199</v>
+        <v>46207</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>31</v>
@@ -1439,78 +1406,78 @@
         <v>1</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>49.5</v>
+        <v>48.5</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.93</v>
+        <v>1.59</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>48.87</v>
+        <v>50.3</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-6.73</v>
+        <v>-4.74</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>49.48</v>
+        <v>50.73</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="R11" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-1.87</v>
+        <v>-1.91</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.63</v>
+        <v>-0.36</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>4.02</v>
+        <v>3.87</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.98</v>
+        <v>0</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-28.11</v>
+        <v>-28.09</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-14.26</v>
+        <v>0.19</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>-11.08</v>
+        <v>-22.63</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46199</v>
+        <v>46207</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>35</v>
@@ -1522,78 +1489,78 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>49.5</v>
+        <v>48.5</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.48</v>
+        <v>0.79</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>24.92</v>
+        <v>25.15</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-3.36</v>
+        <v>-2.37</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>24.74</v>
+        <v>25.37</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="R12" s="4" t="n">
         <v>1.25</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.94</v>
+        <v>-0.96</v>
       </c>
       <c r="U12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.31</v>
+        <v>-0.18</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="X12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-28.11</v>
+        <v>-28.09</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-14.26</v>
+        <v>0.19</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>-11.08</v>
+        <v>-22.63</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46199</v>
+        <v>46207</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="E13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>35</v>
@@ -1605,63 +1572,63 @@
         <v>1</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>49.5</v>
+        <v>48.5</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.47</v>
+        <v>0.79</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>24.43</v>
+        <v>25.15</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-3.36</v>
+        <v>-2.37</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>24.74</v>
+        <v>25.37</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="R13" s="4" t="n">
         <v>1.25</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.94</v>
+        <v>-0.96</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.31</v>
+        <v>-0.18</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.49</v>
+        <v>0</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-28.11</v>
+        <v>-28.09</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-14.26</v>
+        <v>0.19</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>-11.08</v>
+        <v>-22.63</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46200</v>
+        <v>46208</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>45</v>
@@ -1673,10 +1640,10 @@
         <v>47</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.13</v>
+        <v>0.67</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>31</v>
@@ -1691,60 +1658,60 @@
         <v>1</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-4</v>
+        <v>8.5</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>50.5</v>
+        <v>50</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-7.17</v>
+        <v>1.41</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>52.55</v>
+        <v>53.54</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-4.51</v>
+        <v>-0.3</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>51.48</v>
+        <v>52.73</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="S14" s="4" t="n">
         <v>-0.12</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-1.87</v>
+        <v>-1.91</v>
       </c>
       <c r="U14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>2.29</v>
+        <v>2.65</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>4.02</v>
+        <v>3.87</v>
       </c>
       <c r="X14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>21.73</v>
+        <v>2.65</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>11.4</v>
+        <v>-0.46</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>8.27</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46200</v>
+        <v>46208</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>45</v>
@@ -1756,10 +1723,10 @@
         <v>47</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.13</v>
+        <v>0.67</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>31</v>
@@ -1774,60 +1741,60 @@
         <v>1</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-4</v>
+        <v>8.5</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>50.5</v>
+        <v>50</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-7.12</v>
+        <v>1.44</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>51.08</v>
+        <v>52.5</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-4.51</v>
+        <v>-0.3</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>51.48</v>
+        <v>52.73</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="S15" s="4" t="n">
         <v>-0.12</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-1.87</v>
+        <v>-1.91</v>
       </c>
       <c r="U15" s="4" t="n">
         <v>-0.04</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>2.29</v>
+        <v>2.65</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>4.02</v>
+        <v>3.87</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-1.47</v>
+        <v>-1.04</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>21.73</v>
+        <v>2.65</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>11.4</v>
+        <v>-0.46</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>8.27</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46200</v>
+        <v>46208</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>45</v>
@@ -1839,10 +1806,10 @@
         <v>47</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.13</v>
+        <v>0.67</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>35</v>
@@ -1857,60 +1824,60 @@
         <v>1</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-4</v>
+        <v>8.5</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>50.5</v>
+        <v>50</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-3.58</v>
+        <v>0.7</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>26.28</v>
+        <v>26.77</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.25</v>
+        <v>-0.15</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>25.74</v>
+        <v>26.36</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="S16" s="4" t="n">
         <v>-0.06</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.94</v>
+        <v>-0.96</v>
       </c>
       <c r="U16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="X16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>21.73</v>
+        <v>2.65</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>11.4</v>
+        <v>-0.46</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>8.27</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46200</v>
+        <v>46208</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>45</v>
@@ -1922,10 +1889,10 @@
         <v>47</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.13</v>
+        <v>0.67</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>35</v>
@@ -1940,75 +1907,75 @@
         <v>1</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-4</v>
+        <v>8.5</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>50.5</v>
+        <v>50</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.56</v>
+        <v>0.72</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>25.54</v>
+        <v>26.25</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.25</v>
+        <v>-0.15</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>25.74</v>
+        <v>26.36</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="S17" s="4" t="n">
         <v>-0.06</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.94</v>
+        <v>-0.96</v>
       </c>
       <c r="U17" s="4" t="n">
         <v>-0.02</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.74</v>
+        <v>-0.52</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>21.73</v>
+        <v>2.65</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>11.4</v>
+        <v>-0.46</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>8.27</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46200</v>
+        <v>46208</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.6</v>
+        <v>5.03</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>31</v>
@@ -2023,75 +1990,75 @@
         <v>1</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="L18" s="4" t="n">
         <v>50.5</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-3.11</v>
+        <v>-5.72</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>53.67</v>
+        <v>52.7</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-7.2</v>
+        <v>-6.07</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>52.87</v>
+        <v>49.41</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="R18" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.16</v>
+        <v>-0.11</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-1.87</v>
+        <v>-1.91</v>
       </c>
       <c r="U18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>4.02</v>
+        <v>3.87</v>
       </c>
       <c r="X18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-4.02</v>
+        <v>3.66</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>9.85</v>
+        <v>22.46</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>-11.1</v>
+        <v>-15.04</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46200</v>
+        <v>46208</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.6</v>
+        <v>5.03</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>31</v>
@@ -2106,75 +2073,75 @@
         <v>1</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="L19" s="4" t="n">
         <v>50.5</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-3.1</v>
+        <v>-5.47</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>52.73</v>
+        <v>49.19</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-7.2</v>
+        <v>-6.07</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>52.87</v>
+        <v>49.41</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="R19" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.16</v>
+        <v>-0.11</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-1.87</v>
+        <v>-1.91</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.02</v>
+        <v>-0.25</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>4.02</v>
+        <v>3.87</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.94</v>
+        <v>-3.51</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-4.02</v>
+        <v>3.66</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>9.85</v>
+        <v>22.46</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>-11.1</v>
+        <v>-15.04</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46200</v>
+        <v>46208</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.6</v>
+        <v>5.03</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>35</v>
@@ -2189,75 +2156,75 @@
         <v>1</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="L20" s="4" t="n">
         <v>50.5</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.56</v>
+        <v>-2.86</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>26.84</v>
+        <v>26.35</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-3.6</v>
+        <v>-3.03</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>26.44</v>
+        <v>24.7</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="R20" s="4" t="n">
         <v>1.25</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.94</v>
+        <v>-0.96</v>
       </c>
       <c r="U20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.87</v>
+        <v>0.89</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="X20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-4.02</v>
+        <v>3.66</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>9.85</v>
+        <v>22.46</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>-11.1</v>
+        <v>-15.04</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46200</v>
+        <v>46208</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.6</v>
+        <v>5.03</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>35</v>
@@ -2272,1051 +2239,55 @@
         <v>1</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="L21" s="4" t="n">
         <v>50.5</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.55</v>
+        <v>-2.73</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>26.36</v>
+        <v>24.6</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-3.6</v>
+        <v>-3.03</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>26.44</v>
+        <v>24.7</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="R21" s="4" t="n">
         <v>1.25</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.94</v>
+        <v>-0.96</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.01</v>
+        <v>-0.12</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.87</v>
+        <v>0.89</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.47</v>
+        <v>-1.75</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-4.02</v>
+        <v>3.66</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>9.85</v>
+        <v>22.46</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>-11.1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>46200</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" s="4" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="L22" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="M22" s="4" t="n">
-        <v>-3.01</v>
-      </c>
-      <c r="N22" s="4" t="n">
-        <v>50.54</v>
-      </c>
-      <c r="O22" s="4" t="n">
-        <v>-3.84</v>
-      </c>
-      <c r="P22" s="4" t="n">
-        <v>48.98</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="R22" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S22" s="4" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="T22" s="4" t="n">
-        <v>-1.87</v>
-      </c>
-      <c r="U22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="4" t="n">
-        <v>-0.32</v>
-      </c>
-      <c r="W22" s="4" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="X22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="4" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="Z22" s="4" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="AA22" s="4" t="n">
-        <v>3.35</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>46200</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I23" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" s="4" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="L23" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="M23" s="4" t="n">
-        <v>-2.95</v>
-      </c>
-      <c r="N23" s="4" t="n">
-        <v>48.87</v>
-      </c>
-      <c r="O23" s="4" t="n">
-        <v>-3.84</v>
-      </c>
-      <c r="P23" s="4" t="n">
-        <v>48.98</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="R23" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S23" s="4" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="T23" s="4" t="n">
-        <v>-1.87</v>
-      </c>
-      <c r="U23" s="4" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="V23" s="4" t="n">
-        <v>-0.32</v>
-      </c>
-      <c r="W23" s="4" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="X23" s="4" t="n">
-        <v>-1.67</v>
-      </c>
-      <c r="Y23" s="4" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="Z23" s="4" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="AA23" s="4" t="n">
-        <v>3.35</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>46200</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I24" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" s="4" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="L24" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="M24" s="4" t="n">
-        <v>-1.51</v>
-      </c>
-      <c r="N24" s="4" t="n">
-        <v>25.27</v>
-      </c>
-      <c r="O24" s="4" t="n">
-        <v>-1.92</v>
-      </c>
-      <c r="P24" s="4" t="n">
-        <v>24.49</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="R24" s="4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" s="4" t="n">
-        <v>-0.94</v>
-      </c>
-      <c r="U24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="4" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="W24" s="4" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="X24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="4" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="Z24" s="4" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="AA24" s="4" t="n">
-        <v>3.35</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>46200</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" s="4" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="L25" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="M25" s="4" t="n">
-        <v>-1.48</v>
-      </c>
-      <c r="N25" s="4" t="n">
-        <v>24.44</v>
-      </c>
-      <c r="O25" s="4" t="n">
-        <v>-1.92</v>
-      </c>
-      <c r="P25" s="4" t="n">
-        <v>24.49</v>
-      </c>
-      <c r="Q25" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="R25" s="4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" s="4" t="n">
-        <v>-0.94</v>
-      </c>
-      <c r="U25" s="4" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="V25" s="4" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="W25" s="4" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="X25" s="4" t="n">
-        <v>-0.84</v>
-      </c>
-      <c r="Y25" s="4" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="Z25" s="4" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="AA25" s="4" t="n">
-        <v>3.35</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>46201</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" s="4" t="n">
-        <v>-11</v>
-      </c>
-      <c r="L26" s="4" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="M26" s="4" t="n">
-        <v>-5.43</v>
-      </c>
-      <c r="N26" s="4" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="O26" s="4" t="n">
-        <v>-10.37</v>
-      </c>
-      <c r="P26" s="4" t="n">
-        <v>51.72</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="R26" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S26" s="4" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="T26" s="4" t="n">
-        <v>-1.87</v>
-      </c>
-      <c r="U26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="4" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="W26" s="4" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="X26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" s="4" t="n">
-        <v>-4.29</v>
-      </c>
-      <c r="Z26" s="4" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AA26" s="4" t="n">
-        <v>-5.48</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>46201</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" s="4" t="n">
-        <v>-11</v>
-      </c>
-      <c r="L27" s="4" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="M27" s="4" t="n">
-        <v>-5.38</v>
-      </c>
-      <c r="N27" s="4" t="n">
-        <v>51.54</v>
-      </c>
-      <c r="O27" s="4" t="n">
-        <v>-10.37</v>
-      </c>
-      <c r="P27" s="4" t="n">
-        <v>51.72</v>
-      </c>
-      <c r="Q27" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="R27" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S27" s="4" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="T27" s="4" t="n">
-        <v>-1.87</v>
-      </c>
-      <c r="U27" s="4" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="V27" s="4" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="W27" s="4" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="X27" s="4" t="n">
-        <v>-1.67</v>
-      </c>
-      <c r="Y27" s="4" t="n">
-        <v>-4.29</v>
-      </c>
-      <c r="Z27" s="4" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AA27" s="4" t="n">
-        <v>-5.48</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>46201</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I28" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" s="4" t="n">
-        <v>-11</v>
-      </c>
-      <c r="L28" s="4" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="M28" s="4" t="n">
-        <v>-2.72</v>
-      </c>
-      <c r="N28" s="4" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="O28" s="4" t="n">
-        <v>-5.19</v>
-      </c>
-      <c r="P28" s="4" t="n">
-        <v>25.86</v>
-      </c>
-      <c r="Q28" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="R28" s="4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S28" s="4" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="T28" s="4" t="n">
-        <v>-0.94</v>
-      </c>
-      <c r="U28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" s="4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W28" s="4" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="X28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" s="4" t="n">
-        <v>-4.29</v>
-      </c>
-      <c r="Z28" s="4" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AA28" s="4" t="n">
-        <v>-5.48</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>46201</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I29" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" s="4" t="n">
-        <v>-11</v>
-      </c>
-      <c r="L29" s="4" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="M29" s="4" t="n">
-        <v>-2.69</v>
-      </c>
-      <c r="N29" s="4" t="n">
-        <v>25.77</v>
-      </c>
-      <c r="O29" s="4" t="n">
-        <v>-5.19</v>
-      </c>
-      <c r="P29" s="4" t="n">
-        <v>25.86</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="R29" s="4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S29" s="4" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="T29" s="4" t="n">
-        <v>-0.94</v>
-      </c>
-      <c r="U29" s="4" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="V29" s="4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W29" s="4" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="X29" s="4" t="n">
-        <v>-0.83</v>
-      </c>
-      <c r="Y29" s="4" t="n">
-        <v>-4.29</v>
-      </c>
-      <c r="Z29" s="4" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AA29" s="4" t="n">
-        <v>-5.48</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>46201</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I30" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" s="4" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="L30" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="M30" s="4" t="n">
-        <v>-3.29</v>
-      </c>
-      <c r="N30" s="4" t="n">
-        <v>53.32</v>
-      </c>
-      <c r="O30" s="4" t="n">
-        <v>-4.78</v>
-      </c>
-      <c r="P30" s="4" t="n">
-        <v>52.98</v>
-      </c>
-      <c r="Q30" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="R30" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S30" s="4" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="T30" s="4" t="n">
-        <v>-1.87</v>
-      </c>
-      <c r="U30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" s="4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="W30" s="4" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="X30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" s="4" t="n">
-        <v>13.92</v>
-      </c>
-      <c r="Z30" s="4" t="n">
-        <v>-19.15</v>
-      </c>
-      <c r="AA30" s="4" t="n">
-        <v>26.46</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>46201</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K31" s="4" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="L31" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="M31" s="4" t="n">
-        <v>-3.28</v>
-      </c>
-      <c r="N31" s="4" t="n">
-        <v>52.51</v>
-      </c>
-      <c r="O31" s="4" t="n">
-        <v>-4.78</v>
-      </c>
-      <c r="P31" s="4" t="n">
-        <v>52.98</v>
-      </c>
-      <c r="Q31" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="R31" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S31" s="4" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="T31" s="4" t="n">
-        <v>-1.87</v>
-      </c>
-      <c r="U31" s="4" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="V31" s="4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="W31" s="4" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="X31" s="4" t="n">
-        <v>-0.81</v>
-      </c>
-      <c r="Y31" s="4" t="n">
-        <v>13.92</v>
-      </c>
-      <c r="Z31" s="4" t="n">
-        <v>-19.15</v>
-      </c>
-      <c r="AA31" s="4" t="n">
-        <v>26.46</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>46201</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I32" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" s="4" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="L32" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="M32" s="4" t="n">
-        <v>-1.65</v>
-      </c>
-      <c r="N32" s="4" t="n">
-        <v>26.66</v>
-      </c>
-      <c r="O32" s="4" t="n">
-        <v>-2.39</v>
-      </c>
-      <c r="P32" s="4" t="n">
-        <v>26.49</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="R32" s="4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S32" s="4" t="n">
-        <v>-0.07</v>
-      </c>
-      <c r="T32" s="4" t="n">
-        <v>-0.94</v>
-      </c>
-      <c r="U32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W32" s="4" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="X32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="4" t="n">
-        <v>13.92</v>
-      </c>
-      <c r="Z32" s="4" t="n">
-        <v>-19.15</v>
-      </c>
-      <c r="AA32" s="4" t="n">
-        <v>26.46</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>46201</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I33" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" s="4" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="L33" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="M33" s="4" t="n">
-        <v>-1.64</v>
-      </c>
-      <c r="N33" s="4" t="n">
-        <v>26.26</v>
-      </c>
-      <c r="O33" s="4" t="n">
-        <v>-2.39</v>
-      </c>
-      <c r="P33" s="4" t="n">
-        <v>26.49</v>
-      </c>
-      <c r="Q33" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="R33" s="4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S33" s="4" t="n">
-        <v>-0.07</v>
-      </c>
-      <c r="T33" s="4" t="n">
-        <v>-0.94</v>
-      </c>
-      <c r="U33" s="4" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="V33" s="4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W33" s="4" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="X33" s="4" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="Y33" s="4" t="n">
-        <v>13.92</v>
-      </c>
-      <c r="Z33" s="4" t="n">
-        <v>-19.15</v>
-      </c>
-      <c r="AA33" s="4" t="n">
-        <v>26.46</v>
+        <v>-15.04</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_upcoming_projections.xlsx
+++ b/files/NRL_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -98,79 +98,100 @@
     <t xml:space="preserve">20:00</t>
   </si>
   <si>
-    <t xml:space="preserve">penrith panthers</t>
+    <t xml:space="preserve">wests tigers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leichhardt Oval, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Rain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">diff_city</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dolphins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suncorp Stadium, Brisbane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accor Stadium, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allianz Stadium, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">same_city_different_ground</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:00</t>
   </si>
   <si>
     <t xml:space="preserve">south sydney rabbitohs</t>
   </si>
   <si>
-    <t xml:space="preserve">BlueBet Stadium, Penrith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Rain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">same_city_different_ground</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st george-illawarra dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wests tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jubilee Oval, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suncorp Stadium, Brisbane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">diff_city</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
+    <t xml:space="preserve">newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:05</t>
   </si>
   <si>
     <t xml:space="preserve">manly-warringah sea eagles</t>
   </si>
   <si>
-    <t xml:space="preserve">CommBank Stadium, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">newcastle knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">McDonald Jones Stadium, Newcastle</t>
+    <t xml:space="preserve">north queensland cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Pines Park, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melbourne storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AAMI Park, Melbourne</t>
   </si>
 </sst>
 </file>
@@ -520,10 +541,10 @@
   <cols>
     <col min="1" max="1" width="4.9975" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="4.9975" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="23.8625" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="25.5775" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="23.005" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="14.43" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="29.0075" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="22.1475" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="11.8575" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="14.43" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="14.43" hidden="0" customWidth="1"/>
@@ -632,7 +653,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>27</v>
@@ -644,7 +665,7 @@
         <v>29</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>30</v>
@@ -662,60 +683,60 @@
         <v>1</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>-4</v>
+        <v>9</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>46</v>
+        <v>45.5</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>-4.95</v>
+        <v>-6.12</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>50.17</v>
+        <v>49.28</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>-2.95</v>
+        <v>-5.66</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>50.21</v>
+        <v>48.73</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>33</v>
       </c>
       <c r="R2" s="4" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.01</v>
+        <v>0.13</v>
       </c>
       <c r="T2" s="4" t="n">
-        <v>-1.91</v>
+        <v>-1.84</v>
       </c>
       <c r="U2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>-0.73</v>
+        <v>-0.69</v>
       </c>
       <c r="W2" s="4" t="n">
-        <v>3.87</v>
+        <v>3.79</v>
       </c>
       <c r="X2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Y2" s="4" t="n">
-        <v>7.55</v>
+        <v>-6.7</v>
       </c>
       <c r="Z2" s="4" t="n">
-        <v>0.12</v>
+        <v>7.16</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>5.95</v>
+        <v>-11.08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>27</v>
@@ -727,7 +748,7 @@
         <v>29</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>30</v>
@@ -745,60 +766,60 @@
         <v>1</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-4</v>
+        <v>9</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>46</v>
+        <v>45.5</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>-4.95</v>
+        <v>-6.09</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>50.17</v>
+        <v>48.19</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>-2.95</v>
+        <v>-5.66</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>50.21</v>
+        <v>48.73</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>33</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.01</v>
+        <v>0.13</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>-1.91</v>
+        <v>-1.84</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>-0.73</v>
+        <v>-0.69</v>
       </c>
       <c r="W3" s="4" t="n">
-        <v>3.87</v>
+        <v>3.79</v>
       </c>
       <c r="X3" s="4" t="n">
-        <v>0</v>
+        <v>-1.1</v>
       </c>
       <c r="Y3" s="4" t="n">
-        <v>7.55</v>
+        <v>-6.7</v>
       </c>
       <c r="Z3" s="4" t="n">
-        <v>0.12</v>
+        <v>7.16</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>5.95</v>
+        <v>-11.08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>27</v>
@@ -810,7 +831,7 @@
         <v>29</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>30</v>
@@ -828,60 +849,60 @@
         <v>1</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-4</v>
+        <v>9</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>46</v>
+        <v>45.5</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>-2.47</v>
+        <v>-3.06</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>25.09</v>
+        <v>24.64</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>-1.48</v>
+        <v>-2.83</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>25.11</v>
+        <v>24.37</v>
       </c>
       <c r="Q4" s="3" t="s">
         <v>33</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0</v>
+        <v>0.07</v>
       </c>
       <c r="T4" s="4" t="n">
-        <v>-0.96</v>
+        <v>-0.92</v>
       </c>
       <c r="U4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>-0.37</v>
+        <v>-0.35</v>
       </c>
       <c r="W4" s="4" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="X4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="4" t="n">
-        <v>7.55</v>
+        <v>-6.7</v>
       </c>
       <c r="Z4" s="4" t="n">
-        <v>0.12</v>
+        <v>7.16</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>5.95</v>
+        <v>-11.08</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>27</v>
@@ -893,7 +914,7 @@
         <v>29</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>30</v>
@@ -911,60 +932,60 @@
         <v>1</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-4</v>
+        <v>9</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>46</v>
+        <v>45.5</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>-2.47</v>
+        <v>-3.04</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>25.09</v>
+        <v>24.09</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>-1.48</v>
+        <v>-2.83</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>25.11</v>
+        <v>24.37</v>
       </c>
       <c r="Q5" s="3" t="s">
         <v>33</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>0</v>
+        <v>0.07</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>-0.96</v>
+        <v>-0.92</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>-0.37</v>
+        <v>-0.35</v>
       </c>
       <c r="W5" s="4" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="X5" s="4" t="n">
-        <v>0</v>
+        <v>-0.55</v>
       </c>
       <c r="Y5" s="4" t="n">
-        <v>7.55</v>
+        <v>-6.7</v>
       </c>
       <c r="Z5" s="4" t="n">
-        <v>0.12</v>
+        <v>7.16</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>5.95</v>
+        <v>-11.08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>36</v>
@@ -976,7 +997,7 @@
         <v>38</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>39</v>
@@ -994,60 +1015,60 @@
         <v>1</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>5</v>
+        <v>-4.5</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>48.5</v>
+        <v>49.5</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>1.48</v>
+        <v>-0.46</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>51.97</v>
+        <v>52.44</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>4.78</v>
+        <v>-1.55</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>52.04</v>
+        <v>52.4</v>
       </c>
       <c r="Q6" s="3" t="s">
         <v>33</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.1</v>
+        <v>-0.12</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-1.91</v>
+        <v>-1.84</v>
       </c>
       <c r="U6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>1.54</v>
+        <v>2.18</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>3.87</v>
+        <v>3.79</v>
       </c>
       <c r="X6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>3.92</v>
+        <v>14.01</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-17.44</v>
+        <v>3.05</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>17.09</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>36</v>
@@ -1059,7 +1080,7 @@
         <v>38</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>39</v>
@@ -1077,60 +1098,60 @@
         <v>1</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>5</v>
+        <v>-4.5</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>48.5</v>
+        <v>49.5</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>1.48</v>
+        <v>-0.46</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>51.97</v>
+        <v>52.01</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>4.78</v>
+        <v>-1.55</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>52.04</v>
+        <v>52.4</v>
       </c>
       <c r="Q7" s="3" t="s">
         <v>33</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.1</v>
+        <v>-0.12</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-1.91</v>
+        <v>-1.84</v>
       </c>
       <c r="U7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>1.54</v>
+        <v>2.18</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>3.87</v>
+        <v>3.79</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>0</v>
+        <v>-0.42</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>3.92</v>
+        <v>14.01</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-17.44</v>
+        <v>3.05</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>17.09</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>36</v>
@@ -1142,7 +1163,7 @@
         <v>38</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>39</v>
@@ -1160,60 +1181,60 @@
         <v>1</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>5</v>
+        <v>-4.5</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>48.5</v>
+        <v>49.5</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.74</v>
+        <v>-0.23</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>25.98</v>
+        <v>26.22</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>2.39</v>
+        <v>-0.78</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>26.02</v>
+        <v>26.2</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>33</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.96</v>
+        <v>-0.92</v>
       </c>
       <c r="U8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.77</v>
+        <v>1.09</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="X8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>3.92</v>
+        <v>14.01</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-17.44</v>
+        <v>3.05</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>17.09</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>36</v>
@@ -1225,7 +1246,7 @@
         <v>38</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>39</v>
@@ -1243,60 +1264,60 @@
         <v>1</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>5</v>
+        <v>-4.5</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>48.5</v>
+        <v>49.5</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.74</v>
+        <v>-0.23</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>25.98</v>
+        <v>26.01</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>2.39</v>
+        <v>-0.78</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>26.02</v>
+        <v>26.2</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>33</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.96</v>
+        <v>-0.92</v>
       </c>
       <c r="U9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.77</v>
+        <v>1.09</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>0</v>
+        <v>-0.21</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>3.92</v>
+        <v>14.01</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-17.44</v>
+        <v>3.05</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>17.09</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>40</v>
@@ -1323,63 +1344,63 @@
         <v>1</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>7</v>
+        <v>-4.5</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>48.5</v>
+        <v>45.5</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.59</v>
+        <v>-4.63</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>50.3</v>
+        <v>51.73</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-4.74</v>
+        <v>0.28</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>50.73</v>
+        <v>52.14</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="R10" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-1.91</v>
+        <v>-1.84</v>
       </c>
       <c r="U10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.36</v>
+        <v>1.44</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>3.87</v>
+        <v>3.79</v>
       </c>
       <c r="X10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-28.09</v>
+        <v>2.21</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>0.19</v>
+        <v>-10.06</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>-22.63</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>40</v>
@@ -1406,63 +1427,63 @@
         <v>1</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>7</v>
+        <v>-4.5</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>48.5</v>
+        <v>45.5</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.59</v>
+        <v>-4.63</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>50.3</v>
+        <v>51.73</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-4.74</v>
+        <v>0.28</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>50.73</v>
+        <v>52.14</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="R11" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-1.91</v>
+        <v>-1.84</v>
       </c>
       <c r="U11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.36</v>
+        <v>1.44</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>3.87</v>
+        <v>3.79</v>
       </c>
       <c r="X11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-28.09</v>
+        <v>2.21</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>0.19</v>
+        <v>-10.06</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>-22.63</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>40</v>
@@ -1489,28 +1510,28 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>7</v>
+        <v>-4.5</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>48.5</v>
+        <v>45.5</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.79</v>
+        <v>-2.32</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>25.15</v>
+        <v>25.86</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.37</v>
+        <v>0.14</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>25.37</v>
+        <v>26.07</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="R12" s="4" t="n">
         <v>1.25</v>
@@ -1519,33 +1540,33 @@
         <v>0</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.96</v>
+        <v>-0.92</v>
       </c>
       <c r="U12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.18</v>
+        <v>0.72</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="X12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-28.09</v>
+        <v>2.21</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>0.19</v>
+        <v>-10.06</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>-22.63</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>40</v>
@@ -1572,28 +1593,28 @@
         <v>1</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>7</v>
+        <v>-4.5</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>48.5</v>
+        <v>45.5</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.79</v>
+        <v>-2.32</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>25.15</v>
+        <v>25.86</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.37</v>
+        <v>0.14</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>25.37</v>
+        <v>26.07</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="R13" s="4" t="n">
         <v>1.25</v>
@@ -1602,48 +1623,48 @@
         <v>0</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.96</v>
+        <v>-0.92</v>
       </c>
       <c r="U13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.18</v>
+        <v>0.72</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="X13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-28.09</v>
+        <v>2.21</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>0.19</v>
+        <v>-10.06</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>-22.63</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="E14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>31</v>
@@ -1658,75 +1679,75 @@
         <v>1</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>8.5</v>
+        <v>-13.5</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.41</v>
+        <v>-2.3</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>53.54</v>
+        <v>49.93</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.3</v>
+        <v>-1.95</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>52.73</v>
+        <v>50.21</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="R14" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.12</v>
+        <v>0.07</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-1.91</v>
+        <v>-1.84</v>
       </c>
       <c r="U14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>2.65</v>
+        <v>-0.36</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>3.87</v>
+        <v>3.79</v>
       </c>
       <c r="X14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>2.65</v>
+        <v>0.33</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.46</v>
+        <v>9.27</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>2.48</v>
+        <v>-7.15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>31</v>
@@ -1741,75 +1762,75 @@
         <v>1</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>8.5</v>
+        <v>-13.5</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.44</v>
+        <v>-2.3</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>52.5</v>
+        <v>49.93</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.3</v>
+        <v>-1.95</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>52.73</v>
+        <v>50.21</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="R15" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.12</v>
+        <v>0.07</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-1.91</v>
+        <v>-1.84</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>2.65</v>
+        <v>-0.36</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>3.87</v>
+        <v>3.79</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-1.04</v>
+        <v>0</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>2.65</v>
+        <v>0.33</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.46</v>
+        <v>9.27</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>2.48</v>
+        <v>-7.15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>35</v>
@@ -1824,75 +1845,75 @@
         <v>1</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>8.5</v>
+        <v>-13.5</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.7</v>
+        <v>-1.15</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>26.77</v>
+        <v>24.96</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.15</v>
+        <v>-0.98</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>26.36</v>
+        <v>25.11</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="R16" s="4" t="n">
         <v>0.5</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.06</v>
+        <v>0.04</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.96</v>
+        <v>-0.92</v>
       </c>
       <c r="U16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>1.32</v>
+        <v>-0.18</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="X16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>2.65</v>
+        <v>0.33</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.46</v>
+        <v>9.27</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>2.48</v>
+        <v>-7.15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="E17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>35</v>
@@ -1907,60 +1928,60 @@
         <v>1</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>8.5</v>
+        <v>-13.5</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.72</v>
+        <v>-1.15</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>26.25</v>
+        <v>24.96</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.15</v>
+        <v>-0.98</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>26.36</v>
+        <v>25.11</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="R17" s="4" t="n">
         <v>0.5</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.06</v>
+        <v>0.04</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.96</v>
+        <v>-0.92</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>1.32</v>
+        <v>-0.18</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.52</v>
+        <v>0</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>2.65</v>
+        <v>0.33</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.46</v>
+        <v>9.27</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>2.48</v>
+        <v>-7.15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46208</v>
+        <v>46215</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>49</v>
@@ -1972,10 +1993,10 @@
         <v>51</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>5.03</v>
+        <v>1.5</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>31</v>
@@ -1993,57 +2014,57 @@
         <v>1.5</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>50.5</v>
+        <v>49</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-5.72</v>
+        <v>-1.96</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>52.7</v>
+        <v>53.5</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-6.07</v>
+        <v>-2.6</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>49.41</v>
+        <v>52</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="R18" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.11</v>
+        <v>-0.18</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-1.91</v>
+        <v>-1.84</v>
       </c>
       <c r="U18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>1.78</v>
+        <v>2.51</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>3.87</v>
+        <v>3.79</v>
       </c>
       <c r="X18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>3.66</v>
+        <v>6.09</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>22.46</v>
+        <v>-2.06</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>-15.04</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46208</v>
+        <v>46215</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>49</v>
@@ -2055,10 +2076,10 @@
         <v>51</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>5.03</v>
+        <v>1.5</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>31</v>
@@ -2076,57 +2097,57 @@
         <v>1.5</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>50.5</v>
+        <v>49</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-5.47</v>
+        <v>-1.89</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>49.19</v>
+        <v>51.63</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-6.07</v>
+        <v>-2.6</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>49.41</v>
+        <v>52</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="R19" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.11</v>
+        <v>-0.18</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-1.91</v>
+        <v>-1.84</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.25</v>
+        <v>-0.06</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>1.78</v>
+        <v>2.51</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>3.87</v>
+        <v>3.79</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-3.51</v>
+        <v>-1.87</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>3.66</v>
+        <v>6.09</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>22.46</v>
+        <v>-2.06</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>-15.04</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46208</v>
+        <v>46215</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>49</v>
@@ -2138,10 +2159,10 @@
         <v>51</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>5.03</v>
+        <v>1.5</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>35</v>
@@ -2159,57 +2180,57 @@
         <v>1.5</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>50.5</v>
+        <v>49</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.86</v>
+        <v>-0.98</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>26.35</v>
+        <v>26.75</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-3.03</v>
+        <v>-1.3</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>24.7</v>
+        <v>26</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="R20" s="4" t="n">
         <v>1.25</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.05</v>
+        <v>-0.09</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.96</v>
+        <v>-0.92</v>
       </c>
       <c r="U20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.89</v>
+        <v>1.26</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="X20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>3.66</v>
+        <v>6.09</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>22.46</v>
+        <v>-2.06</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>-15.04</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46208</v>
+        <v>46215</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>49</v>
@@ -2221,10 +2242,10 @@
         <v>51</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>5.03</v>
+        <v>1.5</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>35</v>
@@ -2242,52 +2263,716 @@
         <v>1.5</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>50.5</v>
+        <v>49</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.73</v>
+        <v>-0.95</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>24.6</v>
+        <v>25.82</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-3.03</v>
+        <v>-1.3</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>24.7</v>
+        <v>26</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="R21" s="4" t="n">
         <v>1.25</v>
       </c>
       <c r="S21" s="4" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="T21" s="4" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="U21" s="4" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="V21" s="4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W21" s="4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="X21" s="4" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="Y21" s="4" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="Z21" s="4" t="n">
+        <v>-2.06</v>
+      </c>
+      <c r="AA21" s="4" t="n">
+        <v>6.53</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="M22" s="4" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="N22" s="4" t="n">
+        <v>53.25</v>
+      </c>
+      <c r="O22" s="4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="P22" s="4" t="n">
+        <v>51.13</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="R22" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S22" s="4" t="n">
         <v>-0.05</v>
       </c>
-      <c r="T21" s="4" t="n">
-        <v>-0.96</v>
-      </c>
-      <c r="U21" s="4" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="V21" s="4" t="n">
+      <c r="T22" s="4" t="n">
+        <v>-1.84</v>
+      </c>
+      <c r="U22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="W22" s="4" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="X22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Z22" s="4" t="n">
+        <v>-11.8</v>
+      </c>
+      <c r="AA22" s="4" t="n">
+        <v>11.13</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="M23" s="4" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="N23" s="4" t="n">
+        <v>50.84</v>
+      </c>
+      <c r="O23" s="4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="P23" s="4" t="n">
+        <v>51.13</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="R23" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S23" s="4" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T23" s="4" t="n">
+        <v>-1.84</v>
+      </c>
+      <c r="U23" s="4" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="V23" s="4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="W23" s="4" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="X23" s="4" t="n">
+        <v>-2.41</v>
+      </c>
+      <c r="Y23" s="4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Z23" s="4" t="n">
+        <v>-11.8</v>
+      </c>
+      <c r="AA23" s="4" t="n">
+        <v>11.13</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="M24" s="4" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="N24" s="4" t="n">
+        <v>26.62</v>
+      </c>
+      <c r="O24" s="4" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="P24" s="4" t="n">
+        <v>25.56</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="R24" s="4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S24" s="4" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="T24" s="4" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="U24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="W21" s="4" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="X21" s="4" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="Y21" s="4" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="Z21" s="4" t="n">
-        <v>22.46</v>
-      </c>
-      <c r="AA21" s="4" t="n">
-        <v>-15.04</v>
+      <c r="W24" s="4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="X24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Z24" s="4" t="n">
+        <v>-11.8</v>
+      </c>
+      <c r="AA24" s="4" t="n">
+        <v>11.13</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L25" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="M25" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N25" s="4" t="n">
+        <v>25.42</v>
+      </c>
+      <c r="O25" s="4" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="P25" s="4" t="n">
+        <v>25.56</v>
+      </c>
+      <c r="Q25" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="R25" s="4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S25" s="4" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="T25" s="4" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="U25" s="4" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V25" s="4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="W25" s="4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="X25" s="4" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="Y25" s="4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Z25" s="4" t="n">
+        <v>-11.8</v>
+      </c>
+      <c r="AA25" s="4" t="n">
+        <v>11.13</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" s="4" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="M26" s="4" t="n">
+        <v>-5.91</v>
+      </c>
+      <c r="N26" s="4" t="n">
+        <v>50.71</v>
+      </c>
+      <c r="O26" s="4" t="n">
+        <v>-2.14</v>
+      </c>
+      <c r="P26" s="4" t="n">
+        <v>47.35</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="R26" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S26" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T26" s="4" t="n">
+        <v>-1.84</v>
+      </c>
+      <c r="U26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" s="4" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="X26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Z26" s="4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AA26" s="4" t="n">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" s="4" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L27" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="M27" s="4" t="n">
+        <v>-5.65</v>
+      </c>
+      <c r="N27" s="4" t="n">
+        <v>47.23</v>
+      </c>
+      <c r="O27" s="4" t="n">
+        <v>-2.14</v>
+      </c>
+      <c r="P27" s="4" t="n">
+        <v>47.35</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="R27" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S27" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T27" s="4" t="n">
+        <v>-1.84</v>
+      </c>
+      <c r="U27" s="4" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="V27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" s="4" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="X27" s="4" t="n">
+        <v>-3.48</v>
+      </c>
+      <c r="Y27" s="4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Z27" s="4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AA27" s="4" t="n">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" s="4" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L28" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="M28" s="4" t="n">
+        <v>-2.96</v>
+      </c>
+      <c r="N28" s="4" t="n">
+        <v>25.36</v>
+      </c>
+      <c r="O28" s="4" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="P28" s="4" t="n">
+        <v>23.67</v>
+      </c>
+      <c r="Q28" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="R28" s="4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S28" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T28" s="4" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="U28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" s="4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="X28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Z28" s="4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AA28" s="4" t="n">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" s="4" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="M29" s="4" t="n">
+        <v>-2.83</v>
+      </c>
+      <c r="N29" s="4" t="n">
+        <v>23.61</v>
+      </c>
+      <c r="O29" s="4" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="P29" s="4" t="n">
+        <v>23.67</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="R29" s="4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S29" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T29" s="4" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="U29" s="4" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="V29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" s="4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="X29" s="4" t="n">
+        <v>-1.74</v>
+      </c>
+      <c r="Y29" s="4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Z29" s="4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AA29" s="4" t="n">
+        <v>0.49</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_upcoming_projections.xlsx
+++ b/files/NRL_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -95,103 +95,118 @@
     <t xml:space="preserve">Net Uncapped Form</t>
   </si>
   <si>
+    <t xml:space="preserve">19:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penrith panthers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlueBet Stadium, Penrith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Rain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">diff_city</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sharks Stadium, Sydney</t>
+  </si>
+  <si>
     <t xml:space="preserve">20:00</t>
   </si>
   <si>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melbourne storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allianz Stadium, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">south sydney rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GIO Stadium, Canberra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st george-illawarra dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Go Media Stadium, Auckland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
+  </si>
+  <si>
     <t xml:space="preserve">wests tigers</t>
   </si>
   <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leichhardt Oval, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Rain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">diff_city</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:00</t>
+    <t xml:space="preserve">Accor Stadium, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">same_city_different_ground</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manly-warringah sea eagles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cbus Super Stadium, Gold Coast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:05</t>
   </si>
   <si>
     <t xml:space="preserve">dolphins</t>
   </si>
   <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
+    <t xml:space="preserve">north queensland cowboys</t>
   </si>
   <si>
     <t xml:space="preserve">Suncorp Stadium, Brisbane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberra raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accor Stadium, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allianz Stadium, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">same_city_different_ground</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">south sydney rabbitohs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">newcastle knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manly-warringah sea eagles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north queensland cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 Pines Park, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">melbourne storm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AAMI Park, Melbourne</t>
   </si>
 </sst>
 </file>
@@ -542,9 +557,9 @@
     <col min="1" max="1" width="4.9975" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="4.9975" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="25.5775" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="23.005" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="23.8625" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="14.43" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="22.1475" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="26.435" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="11.8575" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="14.43" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="14.43" hidden="0" customWidth="1"/>
@@ -653,7 +668,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>27</v>
@@ -665,7 +680,7 @@
         <v>29</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.8</v>
+        <v>0.17</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>30</v>
@@ -683,22 +698,22 @@
         <v>1</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>9</v>
+        <v>-14.5</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>45.5</v>
+        <v>46</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>-6.12</v>
+        <v>-8.95</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>49.28</v>
+        <v>50.08</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>-5.66</v>
+        <v>-3.57</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>48.73</v>
+        <v>49.96</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>33</v>
@@ -707,36 +722,36 @@
         <v>2.5</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="T2" s="4" t="n">
-        <v>-1.84</v>
+        <v>-1.97</v>
       </c>
       <c r="U2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>-0.69</v>
+        <v>-0.39</v>
       </c>
       <c r="W2" s="4" t="n">
-        <v>3.79</v>
+        <v>3.72</v>
       </c>
       <c r="X2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Y2" s="4" t="n">
-        <v>-6.7</v>
+        <v>12.69</v>
       </c>
       <c r="Z2" s="4" t="n">
-        <v>7.16</v>
+        <v>-20.83</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>-11.08</v>
+        <v>26.82</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>27</v>
@@ -748,7 +763,7 @@
         <v>29</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.8</v>
+        <v>0.17</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>30</v>
@@ -766,22 +781,22 @@
         <v>1</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>9</v>
+        <v>-14.5</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>45.5</v>
+        <v>46</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>-6.09</v>
+        <v>-8.94</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>48.19</v>
+        <v>49.79</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>-5.66</v>
+        <v>-3.57</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>48.73</v>
+        <v>49.96</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>33</v>
@@ -790,36 +805,36 @@
         <v>2.5</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>-1.84</v>
+        <v>-1.97</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>-0.69</v>
+        <v>-0.39</v>
       </c>
       <c r="W3" s="4" t="n">
-        <v>3.79</v>
+        <v>3.72</v>
       </c>
       <c r="X3" s="4" t="n">
-        <v>-1.1</v>
+        <v>-0.3</v>
       </c>
       <c r="Y3" s="4" t="n">
-        <v>-6.7</v>
+        <v>12.69</v>
       </c>
       <c r="Z3" s="4" t="n">
-        <v>7.16</v>
+        <v>-20.83</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>-11.08</v>
+        <v>26.82</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>27</v>
@@ -831,7 +846,7 @@
         <v>29</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.8</v>
+        <v>0.17</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>30</v>
@@ -849,22 +864,22 @@
         <v>1</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>9</v>
+        <v>-14.5</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>45.5</v>
+        <v>46</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>-3.06</v>
+        <v>-4.48</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>24.64</v>
+        <v>25.04</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>-2.83</v>
+        <v>-1.79</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>24.37</v>
+        <v>24.98</v>
       </c>
       <c r="Q4" s="3" t="s">
         <v>33</v>
@@ -873,36 +888,36 @@
         <v>1.25</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.07</v>
+        <v>0</v>
       </c>
       <c r="T4" s="4" t="n">
-        <v>-0.92</v>
+        <v>-0.98</v>
       </c>
       <c r="U4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>-0.35</v>
+        <v>-0.2</v>
       </c>
       <c r="W4" s="4" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="X4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="4" t="n">
-        <v>-6.7</v>
+        <v>12.69</v>
       </c>
       <c r="Z4" s="4" t="n">
-        <v>7.16</v>
+        <v>-20.83</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>-11.08</v>
+        <v>26.82</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>27</v>
@@ -914,7 +929,7 @@
         <v>29</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.8</v>
+        <v>0.17</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>30</v>
@@ -932,22 +947,22 @@
         <v>1</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>9</v>
+        <v>-14.5</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>45.5</v>
+        <v>46</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>-3.04</v>
+        <v>-4.47</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>24.09</v>
+        <v>24.89</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>-2.83</v>
+        <v>-1.79</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>24.37</v>
+        <v>24.98</v>
       </c>
       <c r="Q5" s="3" t="s">
         <v>33</v>
@@ -956,36 +971,36 @@
         <v>1.25</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>0.07</v>
+        <v>0</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>-0.92</v>
+        <v>-0.98</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>-0.35</v>
+        <v>-0.2</v>
       </c>
       <c r="W5" s="4" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="X5" s="4" t="n">
-        <v>-0.55</v>
+        <v>-0.15</v>
       </c>
       <c r="Y5" s="4" t="n">
-        <v>-6.7</v>
+        <v>12.69</v>
       </c>
       <c r="Z5" s="4" t="n">
-        <v>7.16</v>
+        <v>-20.83</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>-11.08</v>
+        <v>26.82</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>36</v>
@@ -997,7 +1012,7 @@
         <v>38</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.23</v>
+        <v>5.87</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>39</v>
@@ -1015,22 +1030,22 @@
         <v>1</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-4.5</v>
+        <v>-5</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>49.5</v>
+        <v>47.5</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.46</v>
+        <v>-4.62</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>52.44</v>
+        <v>50.54</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-1.55</v>
+        <v>-3.56</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>52.4</v>
+        <v>47.21</v>
       </c>
       <c r="Q6" s="3" t="s">
         <v>33</v>
@@ -1039,36 +1054,36 @@
         <v>2.5</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.12</v>
+        <v>-0.01</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-1.84</v>
+        <v>-1.97</v>
       </c>
       <c r="U6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>3.79</v>
+        <v>3.72</v>
       </c>
       <c r="X6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>14.01</v>
+        <v>3.05</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>3.05</v>
+        <v>-2.06</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>8.77</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>36</v>
@@ -1080,7 +1095,7 @@
         <v>38</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.23</v>
+        <v>5.87</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>39</v>
@@ -1098,22 +1113,22 @@
         <v>1</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-4.5</v>
+        <v>-5</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>49.5</v>
+        <v>47.5</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.46</v>
+        <v>-4.38</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>52.01</v>
+        <v>46.95</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-1.55</v>
+        <v>-3.56</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>52.4</v>
+        <v>47.21</v>
       </c>
       <c r="Q7" s="3" t="s">
         <v>33</v>
@@ -1122,36 +1137,36 @@
         <v>2.5</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.12</v>
+        <v>-0.01</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-1.84</v>
+        <v>-1.97</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0</v>
+        <v>-0.24</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>3.79</v>
+        <v>3.72</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.42</v>
+        <v>-3.59</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>14.01</v>
+        <v>3.05</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>3.05</v>
+        <v>-2.06</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>8.77</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>36</v>
@@ -1163,7 +1178,7 @@
         <v>38</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.23</v>
+        <v>5.87</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>39</v>
@@ -1181,22 +1196,22 @@
         <v>1</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-4.5</v>
+        <v>-5</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>49.5</v>
+        <v>47.5</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.23</v>
+        <v>-2.31</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>26.22</v>
+        <v>25.27</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.78</v>
+        <v>-1.78</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>26.2</v>
+        <v>23.6</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>33</v>
@@ -1205,36 +1220,36 @@
         <v>1.25</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.92</v>
+        <v>-0.98</v>
       </c>
       <c r="U8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="X8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>14.01</v>
+        <v>3.05</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>3.05</v>
+        <v>-2.06</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>8.77</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>36</v>
@@ -1246,7 +1261,7 @@
         <v>38</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.23</v>
+        <v>5.87</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>39</v>
@@ -1264,22 +1279,22 @@
         <v>1</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-4.5</v>
+        <v>-5</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>49.5</v>
+        <v>47.5</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.23</v>
+        <v>-2.19</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>26.01</v>
+        <v>23.48</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.78</v>
+        <v>-1.78</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>26.2</v>
+        <v>23.6</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>33</v>
@@ -1288,36 +1303,36 @@
         <v>1.25</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.92</v>
+        <v>-0.98</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.21</v>
+        <v>-1.79</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>14.01</v>
+        <v>3.05</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>3.05</v>
+        <v>-2.06</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>8.77</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>40</v>
@@ -1329,7 +1344,7 @@
         <v>42</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>43</v>
@@ -1347,22 +1362,22 @@
         <v>1</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-4.5</v>
+        <v>-6</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>45.5</v>
+        <v>45</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-4.63</v>
+        <v>-2.37</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>51.73</v>
+        <v>49.22</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.28</v>
+        <v>-2.17</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>52.14</v>
+        <v>46.01</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>33</v>
@@ -1374,33 +1389,33 @@
         <v>0.01</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-1.84</v>
+        <v>-1.97</v>
       </c>
       <c r="U10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>1.44</v>
+        <v>-0.71</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>3.79</v>
+        <v>3.72</v>
       </c>
       <c r="X10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>2.21</v>
+        <v>0.33</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-10.06</v>
+        <v>2.12</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>9.81</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>40</v>
@@ -1412,7 +1427,7 @@
         <v>42</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>43</v>
@@ -1430,22 +1445,22 @@
         <v>1</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-4.5</v>
+        <v>-6</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>45.5</v>
+        <v>45</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-4.63</v>
+        <v>-2.13</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>51.73</v>
+        <v>45.76</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.28</v>
+        <v>-2.17</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>52.14</v>
+        <v>46.01</v>
       </c>
       <c r="Q11" s="3" t="s">
         <v>33</v>
@@ -1457,33 +1472,33 @@
         <v>0.01</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-1.84</v>
+        <v>-1.97</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0</v>
+        <v>-0.24</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>1.44</v>
+        <v>-0.71</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>3.79</v>
+        <v>3.72</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>0</v>
+        <v>-3.46</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>2.21</v>
+        <v>0.33</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-10.06</v>
+        <v>2.12</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>9.81</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>40</v>
@@ -1495,7 +1510,7 @@
         <v>42</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>43</v>
@@ -1513,22 +1528,22 @@
         <v>1</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-4.5</v>
+        <v>-6</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>45.5</v>
+        <v>45</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.32</v>
+        <v>-1.19</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>25.86</v>
+        <v>24.61</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.14</v>
+        <v>-1.08</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>26.07</v>
+        <v>23.01</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>33</v>
@@ -1540,33 +1555,33 @@
         <v>0</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.92</v>
+        <v>-0.98</v>
       </c>
       <c r="U12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.72</v>
+        <v>-0.36</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="X12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>2.21</v>
+        <v>0.33</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-10.06</v>
+        <v>2.12</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>9.81</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>40</v>
@@ -1578,7 +1593,7 @@
         <v>42</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>43</v>
@@ -1596,22 +1611,22 @@
         <v>1</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-4.5</v>
+        <v>-6</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>45.5</v>
+        <v>45</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.32</v>
+        <v>-1.06</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>25.86</v>
+        <v>22.88</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.14</v>
+        <v>-1.08</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>26.07</v>
+        <v>23.01</v>
       </c>
       <c r="Q13" s="3" t="s">
         <v>33</v>
@@ -1623,33 +1638,33 @@
         <v>0</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.92</v>
+        <v>-0.98</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>0.72</v>
+        <v>-0.36</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>0</v>
+        <v>-1.73</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>2.21</v>
+        <v>0.33</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-10.06</v>
+        <v>2.12</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>9.81</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>44</v>
@@ -1679,60 +1694,60 @@
         <v>1</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-13.5</v>
+        <v>-1.5</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>48</v>
+        <v>48.5</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.3</v>
+        <v>3.57</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>49.93</v>
+        <v>52.8</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.95</v>
+        <v>-1.47</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>50.21</v>
+        <v>53.15</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.07</v>
+        <v>-0.43</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-1.84</v>
+        <v>-1.97</v>
       </c>
       <c r="U14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.36</v>
+        <v>2.23</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>3.79</v>
+        <v>3.72</v>
       </c>
       <c r="X14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>0.33</v>
+        <v>-10.06</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>9.27</v>
+        <v>6.09</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>-7.15</v>
+        <v>-12.92</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>44</v>
@@ -1762,60 +1777,60 @@
         <v>1</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-13.5</v>
+        <v>-1.5</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>48</v>
+        <v>48.5</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.3</v>
+        <v>3.57</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>49.93</v>
+        <v>52.8</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.95</v>
+        <v>-1.47</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>50.21</v>
+        <v>53.15</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.07</v>
+        <v>-0.43</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-1.84</v>
+        <v>-1.97</v>
       </c>
       <c r="U15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.36</v>
+        <v>2.23</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>3.79</v>
+        <v>3.72</v>
       </c>
       <c r="X15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>0.33</v>
+        <v>-10.06</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>9.27</v>
+        <v>6.09</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>-7.15</v>
+        <v>-12.92</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>44</v>
@@ -1845,60 +1860,60 @@
         <v>1</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-13.5</v>
+        <v>-1.5</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>48</v>
+        <v>48.5</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.15</v>
+        <v>1.78</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>24.96</v>
+        <v>26.4</v>
       </c>
       <c r="O16" s="4" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="P16" s="4" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="R16" s="4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S16" s="4" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="T16" s="4" t="n">
         <v>-0.98</v>
       </c>
-      <c r="P16" s="4" t="n">
-        <v>25.11</v>
-      </c>
-      <c r="Q16" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="R16" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S16" s="4" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="T16" s="4" t="n">
-        <v>-0.92</v>
-      </c>
       <c r="U16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.18</v>
+        <v>1.12</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="X16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>0.33</v>
+        <v>-10.06</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>9.27</v>
+        <v>6.09</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>-7.15</v>
+        <v>-12.92</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>44</v>
@@ -1928,75 +1943,75 @@
         <v>1</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-13.5</v>
+        <v>-1.5</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>48</v>
+        <v>48.5</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.15</v>
+        <v>1.78</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>24.96</v>
+        <v>26.4</v>
       </c>
       <c r="O17" s="4" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="P17" s="4" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="R17" s="4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S17" s="4" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="T17" s="4" t="n">
         <v>-0.98</v>
       </c>
-      <c r="P17" s="4" t="n">
-        <v>25.11</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="R17" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S17" s="4" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="T17" s="4" t="n">
-        <v>-0.92</v>
-      </c>
       <c r="U17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.18</v>
+        <v>1.12</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="X17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>0.33</v>
+        <v>-10.06</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>9.27</v>
+        <v>6.09</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>-7.15</v>
+        <v>-12.92</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>31</v>
@@ -2011,22 +2026,22 @@
         <v>1</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.5</v>
+        <v>-15.5</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>49</v>
+        <v>46.5</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.96</v>
+        <v>-4.2</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>53.5</v>
+        <v>49.2</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.6</v>
+        <v>-8.64</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>52</v>
+        <v>48.8</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>33</v>
@@ -2035,51 +2050,51 @@
         <v>2.5</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.18</v>
+        <v>0</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-1.84</v>
+        <v>-1.97</v>
       </c>
       <c r="U18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>2.51</v>
+        <v>-0.38</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>3.79</v>
+        <v>3.72</v>
       </c>
       <c r="X18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>6.09</v>
+        <v>7.16</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-2.06</v>
+        <v>2.73</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>6.53</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="E19" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>31</v>
@@ -2094,22 +2109,22 @@
         <v>1</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.5</v>
+        <v>-15.5</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>49</v>
+        <v>46.5</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.89</v>
+        <v>-4.17</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>51.63</v>
+        <v>48.71</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.6</v>
+        <v>-8.64</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>52</v>
+        <v>48.8</v>
       </c>
       <c r="Q19" s="3" t="s">
         <v>33</v>
@@ -2118,51 +2133,51 @@
         <v>2.5</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.18</v>
+        <v>0</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-1.84</v>
+        <v>-1.97</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>2.51</v>
+        <v>-0.38</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>3.79</v>
+        <v>3.72</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-1.87</v>
+        <v>-0.49</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>6.09</v>
+        <v>7.16</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-2.06</v>
+        <v>2.73</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>6.53</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="E20" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>35</v>
@@ -2177,22 +2192,22 @@
         <v>1</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.5</v>
+        <v>-15.5</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>49</v>
+        <v>46.5</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.98</v>
+        <v>-2.1</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>26.75</v>
+        <v>24.6</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.3</v>
+        <v>-4.32</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>26</v>
+        <v>24.4</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>33</v>
@@ -2201,51 +2216,51 @@
         <v>1.25</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.92</v>
+        <v>-0.98</v>
       </c>
       <c r="U20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>1.26</v>
+        <v>-0.19</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="X20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>6.09</v>
+        <v>7.16</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-2.06</v>
+        <v>2.73</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>6.53</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="E21" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>35</v>
@@ -2260,22 +2275,22 @@
         <v>1</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.5</v>
+        <v>-15.5</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>49</v>
+        <v>46.5</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.95</v>
+        <v>-2.09</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>25.82</v>
+        <v>24.36</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.3</v>
+        <v>-4.32</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>26</v>
+        <v>24.4</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>33</v>
@@ -2284,36 +2299,36 @@
         <v>1.25</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.92</v>
+        <v>-0.98</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>1.26</v>
+        <v>-0.19</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.93</v>
+        <v>-0.25</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>6.09</v>
+        <v>7.16</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-2.06</v>
+        <v>2.73</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>6.53</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>52</v>
@@ -2325,7 +2340,7 @@
         <v>54</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.3</v>
+        <v>4.03</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>55</v>
@@ -2343,60 +2358,60 @@
         <v>1</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-5</v>
+        <v>-6.5</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>49</v>
+        <v>45.5</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.06</v>
+        <v>0.55</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>53.25</v>
+        <v>49.72</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>51.13</v>
+        <v>46.98</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-1.84</v>
+        <v>-1.97</v>
       </c>
       <c r="U22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>1.77</v>
+        <v>-0.36</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>3.79</v>
+        <v>3.72</v>
       </c>
       <c r="X22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-11.8</v>
+        <v>-6.7</v>
       </c>
       <c r="AA22" s="4" t="n">
-        <v>11.13</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>52</v>
@@ -2408,7 +2423,7 @@
         <v>54</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.3</v>
+        <v>4.03</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>55</v>
@@ -2426,60 +2441,60 @@
         <v>1</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-5</v>
+        <v>-6.5</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>49</v>
+        <v>45.5</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.04</v>
+        <v>0.72</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>50.84</v>
+        <v>46.75</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>51.13</v>
+        <v>46.98</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-1.84</v>
+        <v>-1.97</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.1</v>
+        <v>-0.17</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>1.77</v>
+        <v>-0.36</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>3.79</v>
+        <v>3.72</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-2.41</v>
+        <v>-2.97</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-11.8</v>
+        <v>-6.7</v>
       </c>
       <c r="AA23" s="4" t="n">
-        <v>11.13</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>52</v>
@@ -2491,7 +2506,7 @@
         <v>54</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2.3</v>
+        <v>4.03</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>55</v>
@@ -2509,60 +2524,60 @@
         <v>1</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-5</v>
+        <v>-6.5</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>49</v>
+        <v>45.5</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.03</v>
+        <v>0.28</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>26.62</v>
+        <v>24.86</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.99</v>
+        <v>1.08</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>25.56</v>
+        <v>23.49</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.92</v>
+        <v>-0.98</v>
       </c>
       <c r="U24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.89</v>
+        <v>-0.18</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="X24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-11.8</v>
+        <v>-6.7</v>
       </c>
       <c r="AA24" s="4" t="n">
-        <v>11.13</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>52</v>
@@ -2574,7 +2589,7 @@
         <v>54</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.3</v>
+        <v>4.03</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>55</v>
@@ -2592,75 +2607,75 @@
         <v>1</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-5</v>
+        <v>-6.5</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>49</v>
+        <v>45.5</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.02</v>
+        <v>0.36</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>25.42</v>
+        <v>23.37</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.99</v>
+        <v>1.08</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>25.56</v>
+        <v>23.49</v>
       </c>
       <c r="Q25" s="3" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.92</v>
+        <v>-0.98</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.05</v>
+        <v>-0.09</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>0.89</v>
+        <v>-0.18</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-1.2</v>
+        <v>-1.49</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-11.8</v>
+        <v>-6.7</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>11.13</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>5.4</v>
+        <v>23.4</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>31</v>
@@ -2675,22 +2690,22 @@
         <v>1</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-10</v>
+        <v>5.5</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>48</v>
+        <v>48.5</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-5.91</v>
+        <v>-2.35</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>50.71</v>
+        <v>53.47</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.14</v>
+        <v>-2.54</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>47.35</v>
+        <v>47.59</v>
       </c>
       <c r="Q26" s="3" t="s">
         <v>33</v>
@@ -2699,51 +2714,51 @@
         <v>2.5</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.01</v>
+        <v>-0.44</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-1.84</v>
+        <v>-1.97</v>
       </c>
       <c r="U26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>3.79</v>
+        <v>3.72</v>
       </c>
       <c r="X26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Y26" s="4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z26" s="4" t="n">
         <v>2.12</v>
       </c>
-      <c r="Z26" s="4" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AA26" s="4" t="n">
-        <v>0.49</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>5.4</v>
+        <v>23.4</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>31</v>
@@ -2758,22 +2773,22 @@
         <v>1</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-10</v>
+        <v>5.5</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>48</v>
+        <v>48.5</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-5.65</v>
+        <v>-1.4</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>47.23</v>
+        <v>47.3</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.14</v>
+        <v>-2.54</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>47.35</v>
+        <v>47.59</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>33</v>
@@ -2782,51 +2797,51 @@
         <v>2.5</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.01</v>
+        <v>-0.44</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-1.84</v>
+        <v>-1.97</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.26</v>
+        <v>-0.95</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>3.79</v>
+        <v>3.72</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-3.48</v>
+        <v>-6.18</v>
       </c>
       <c r="Y27" s="4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z27" s="4" t="n">
         <v>2.12</v>
       </c>
-      <c r="Z27" s="4" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AA27" s="4" t="n">
-        <v>0.49</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>5.4</v>
+        <v>23.4</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>35</v>
@@ -2841,22 +2856,22 @@
         <v>1</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-10</v>
+        <v>5.5</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>48</v>
+        <v>48.5</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-2.96</v>
+        <v>-1.17</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>25.36</v>
+        <v>26.74</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.07</v>
+        <v>-1.27</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>23.67</v>
+        <v>23.8</v>
       </c>
       <c r="Q28" s="3" t="s">
         <v>33</v>
@@ -2865,51 +2880,51 @@
         <v>1.25</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>0.01</v>
+        <v>-0.22</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.92</v>
+        <v>-0.98</v>
       </c>
       <c r="U28" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="X28" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Y28" s="4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z28" s="4" t="n">
         <v>2.12</v>
       </c>
-      <c r="Z28" s="4" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AA28" s="4" t="n">
-        <v>0.49</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.4</v>
+        <v>23.4</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>35</v>
@@ -2924,22 +2939,22 @@
         <v>1</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-10</v>
+        <v>5.5</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>48</v>
+        <v>48.5</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-2.83</v>
+        <v>-0.7</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>23.61</v>
+        <v>23.65</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.07</v>
+        <v>-1.27</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>23.67</v>
+        <v>23.8</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>33</v>
@@ -2948,31 +2963,363 @@
         <v>1.25</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.01</v>
+        <v>-0.22</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.92</v>
+        <v>-0.98</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.13</v>
+        <v>-0.47</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-1.74</v>
+        <v>-3.09</v>
       </c>
       <c r="Y29" s="4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z29" s="4" t="n">
         <v>2.12</v>
       </c>
-      <c r="Z29" s="4" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AA29" s="4" t="n">
-        <v>0.49</v>
+        <v>-0.49</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="M30" s="4" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>52.52</v>
+      </c>
+      <c r="O30" s="4" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="P30" s="4" t="n">
+        <v>48.73</v>
+      </c>
+      <c r="Q30" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="R30" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S30" s="4" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="T30" s="4" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="U30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="W30" s="4" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="X30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="4" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="Z30" s="4" t="n">
+        <v>-11.8</v>
+      </c>
+      <c r="AA30" s="4" t="n">
+        <v>20.65</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="M31" s="4" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="N31" s="4" t="n">
+        <v>48.47</v>
+      </c>
+      <c r="O31" s="4" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="P31" s="4" t="n">
+        <v>48.73</v>
+      </c>
+      <c r="Q31" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="R31" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S31" s="4" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="T31" s="4" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="U31" s="4" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="V31" s="4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="W31" s="4" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="X31" s="4" t="n">
+        <v>-4.05</v>
+      </c>
+      <c r="Y31" s="4" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="Z31" s="4" t="n">
+        <v>-11.8</v>
+      </c>
+      <c r="AA31" s="4" t="n">
+        <v>20.65</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="M32" s="4" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="N32" s="4" t="n">
+        <v>26.26</v>
+      </c>
+      <c r="O32" s="4" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="P32" s="4" t="n">
+        <v>24.37</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="R32" s="4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S32" s="4" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="T32" s="4" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="U32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="4" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="W32" s="4" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="X32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="4" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="Z32" s="4" t="n">
+        <v>-11.8</v>
+      </c>
+      <c r="AA32" s="4" t="n">
+        <v>20.65</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="L33" s="4" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="M33" s="4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N33" s="4" t="n">
+        <v>24.24</v>
+      </c>
+      <c r="O33" s="4" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="P33" s="4" t="n">
+        <v>24.37</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="R33" s="4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S33" s="4" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="T33" s="4" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="U33" s="4" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="V33" s="4" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="W33" s="4" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="X33" s="4" t="n">
+        <v>-2.03</v>
+      </c>
+      <c r="Y33" s="4" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="Z33" s="4" t="n">
+        <v>-11.8</v>
+      </c>
+      <c r="AA33" s="4" t="n">
+        <v>20.65</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_upcoming_projections.xlsx
+++ b/files/NRL_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -62,30 +62,21 @@
     <t xml:space="preserve">Team Total Ref</t>
   </si>
   <si>
+    <t xml:space="preserve">Player Margin Adjustment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Player Total Adjustment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Model Mode</t>
+  </si>
+  <si>
     <t xml:space="preserve">HGA Type</t>
   </si>
   <si>
     <t xml:space="preserve">HGA Value</t>
   </si>
   <si>
-    <t xml:space="preserve">Daynight Margin Adj</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systemic Margin Adj</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rain Margin Adj</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daynight Total Adj</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systemic Total Adj</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rain Total Adj</t>
-  </si>
-  <si>
     <t xml:space="preserve">Home Raw Form</t>
   </si>
   <si>
@@ -98,115 +89,112 @@
     <t xml:space="preserve">19:50</t>
   </si>
   <si>
+    <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
     <t xml:space="preserve">penrith panthers</t>
   </si>
   <si>
+    <t xml:space="preserve">CommBank Stadium, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Rain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lean_v2_compact_player</t>
+  </si>
+  <si>
+    <t xml:space="preserve">same_home_ground_or_other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">McDonald Jones Stadium, Newcastle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">south sydney rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melbourne storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accor Stadium, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wests tigers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GIO Stadium, Canberra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north queensland cowboys</t>
+  </si>
+  <si>
     <t xml:space="preserve">brisbane broncos</t>
   </si>
   <si>
-    <t xml:space="preserve">BlueBet Stadium, Penrith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Rain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">diff_city</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:00</t>
+    <t xml:space="preserve">Queensland Country Bank Stadium, Townsville</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st george-illawarra dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WIN Stadium, Wollongong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manly-warringah sea eagles</t>
   </si>
   <si>
     <t xml:space="preserve">cronulla-sutherland sharks</t>
   </si>
   <si>
-    <t xml:space="preserve">newcastle knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sharks Stadium, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">melbourne storm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allianz Stadium, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberra raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">south sydney rabbitohs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GIO Stadium, Canberra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st george-illawarra dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Go Media Stadium, Auckland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wests tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accor Stadium, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">same_city_different_ground</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manly-warringah sea eagles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cbus Super Stadium, Gold Coast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north queensland cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suncorp Stadium, Brisbane</t>
+    <t xml:space="preserve">4 Pines Park, Sydney</t>
   </si>
 </sst>
 </file>
@@ -557,9 +545,9 @@
     <col min="1" max="1" width="4.9975" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="4.9975" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="25.5775" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="23.8625" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="23.005" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="14.43" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="26.435" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="37.5825" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="11.8575" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="14.43" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="14.43" hidden="0" customWidth="1"/>
@@ -570,17 +558,14 @@
     <col min="14" max="14" width="14.43" hidden="0" customWidth="1"/>
     <col min="15" max="15" width="16.145" hidden="0" customWidth="1"/>
     <col min="16" max="16" width="12.715" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="23.005" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="8.4275" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="17.0025" hidden="0" customWidth="1"/>
-    <col min="20" max="20" width="17.0025" hidden="0" customWidth="1"/>
-    <col min="21" max="21" width="13.5725" hidden="0" customWidth="1"/>
-    <col min="22" max="22" width="16.145" hidden="0" customWidth="1"/>
-    <col min="23" max="23" width="16.145" hidden="0" customWidth="1"/>
-    <col min="24" max="24" width="12.715" hidden="0" customWidth="1"/>
-    <col min="25" max="25" width="11.8575" hidden="0" customWidth="1"/>
-    <col min="26" max="26" width="11.8575" hidden="0" customWidth="1"/>
-    <col min="27" max="27" width="15.2875" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="21.29" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="20.4325" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="19.575" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="22.1475" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="8.4275" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="11.8575" hidden="0" customWidth="1"/>
+    <col min="23" max="23" width="11.8575" hidden="0" customWidth="1"/>
+    <col min="24" max="24" width="15.2875" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -656,41 +641,32 @@
       <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>26</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="4" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>32</v>
-      </c>
       <c r="I2" s="5" t="n">
         <v>1</v>
       </c>
@@ -698,81 +674,72 @@
         <v>1</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>-14.5</v>
+        <v>15</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>46</v>
+        <v>44.5</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>-8.95</v>
+        <v>11.4</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>50.08</v>
+        <v>40.7</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>-3.57</v>
+        <v>12.92</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>49.96</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R2" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" s="4" t="n">
-        <v>-1.97</v>
+        <v>40.7</v>
+      </c>
+      <c r="Q2" s="4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="R2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>-0.39</v>
+        <v>9.27</v>
       </c>
       <c r="W2" s="4" t="n">
-        <v>3.72</v>
+        <v>12.69</v>
       </c>
       <c r="X2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="4" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="Z2" s="4" t="n">
-        <v>-20.83</v>
-      </c>
-      <c r="AA2" s="4" t="n">
-        <v>26.82</v>
+        <v>-2.74</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="H3" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I3" s="5" t="n">
         <v>1</v>
@@ -781,82 +748,73 @@
         <v>1</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-14.5</v>
+        <v>15</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>46</v>
+        <v>44.5</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>-8.94</v>
+        <v>11.4</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>49.79</v>
+        <v>40.7</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>-3.57</v>
+        <v>12.92</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>49.96</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R3" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" s="4" t="n">
-        <v>-1.97</v>
+        <v>40.7</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="R3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>-0.02</v>
+        <v>1</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>-0.39</v>
+        <v>9.27</v>
       </c>
       <c r="W3" s="4" t="n">
-        <v>3.72</v>
+        <v>12.69</v>
       </c>
       <c r="X3" s="4" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="Y3" s="4" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="Z3" s="4" t="n">
-        <v>-20.83</v>
-      </c>
-      <c r="AA3" s="4" t="n">
-        <v>26.82</v>
+        <v>-2.74</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="G4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="4" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>32</v>
-      </c>
       <c r="I4" s="5" t="n">
         <v>1</v>
       </c>
@@ -864,81 +822,72 @@
         <v>1</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-14.5</v>
+        <v>15</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>46</v>
+        <v>44.5</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>-4.48</v>
+        <v>5.7</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>25.04</v>
+        <v>20.35</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>-1.79</v>
+        <v>6.46</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>24.98</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R4" s="4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="4" t="n">
-        <v>-0.98</v>
+        <v>20.35</v>
+      </c>
+      <c r="Q4" s="4" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="R4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>-0.2</v>
+        <v>9.27</v>
       </c>
       <c r="W4" s="4" t="n">
-        <v>1.86</v>
+        <v>12.69</v>
       </c>
       <c r="X4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="4" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="Z4" s="4" t="n">
-        <v>-20.83</v>
-      </c>
-      <c r="AA4" s="4" t="n">
-        <v>26.82</v>
+        <v>-2.74</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="G5" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>1</v>
@@ -947,81 +896,72 @@
         <v>1</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-14.5</v>
+        <v>15</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>46</v>
+        <v>44.5</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>-4.47</v>
+        <v>5.7</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>24.89</v>
+        <v>20.35</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>-1.79</v>
+        <v>6.46</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>24.98</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R5" s="4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="4" t="n">
-        <v>-0.98</v>
+        <v>20.35</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="R5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>-0.01</v>
+        <v>0.5</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>-0.2</v>
+        <v>9.27</v>
       </c>
       <c r="W5" s="4" t="n">
-        <v>1.86</v>
+        <v>12.69</v>
       </c>
       <c r="X5" s="4" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="Y5" s="4" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="Z5" s="4" t="n">
-        <v>-20.83</v>
-      </c>
-      <c r="AA5" s="4" t="n">
-        <v>26.82</v>
+        <v>-2.74</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="E6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>5.87</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="G6" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>1</v>
@@ -1030,81 +970,72 @@
         <v>1</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-5</v>
+        <v>2.5</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>47.5</v>
+        <v>45.5</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-4.62</v>
+        <v>3.26</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>50.54</v>
+        <v>42.24</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-3.56</v>
+        <v>2</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>47.21</v>
-      </c>
-      <c r="Q6" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R6" s="4" t="n">
+        <v>42.24</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="R6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U6" s="4" t="n">
         <v>2.5</v>
       </c>
-      <c r="S6" s="4" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="T6" s="4" t="n">
-        <v>-1.97</v>
-      </c>
-      <c r="U6" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V6" s="4" t="n">
-        <v>0</v>
+        <v>-2.06</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>3.72</v>
+        <v>0.33</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Z6" s="4" t="n">
-        <v>-2.06</v>
-      </c>
-      <c r="AA6" s="4" t="n">
-        <v>4.09</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="E7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>5.87</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="G7" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>1</v>
@@ -1113,81 +1044,72 @@
         <v>1</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-5</v>
+        <v>2.5</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>47.5</v>
+        <v>45.5</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-4.38</v>
+        <v>3.26</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>46.95</v>
+        <v>42.24</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-3.56</v>
+        <v>2</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>47.21</v>
-      </c>
-      <c r="Q7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R7" s="4" t="n">
+        <v>42.24</v>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="R7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U7" s="4" t="n">
         <v>2.5</v>
       </c>
-      <c r="S7" s="4" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="T7" s="4" t="n">
-        <v>-1.97</v>
-      </c>
-      <c r="U7" s="4" t="n">
-        <v>-0.24</v>
-      </c>
       <c r="V7" s="4" t="n">
-        <v>0</v>
+        <v>-2.06</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>3.72</v>
+        <v>0.33</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-3.59</v>
-      </c>
-      <c r="Y7" s="4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Z7" s="4" t="n">
-        <v>-2.06</v>
-      </c>
-      <c r="AA7" s="4" t="n">
-        <v>4.09</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="E8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>5.87</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="G8" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>1</v>
@@ -1196,81 +1118,72 @@
         <v>1</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-5</v>
+        <v>2.5</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>47.5</v>
+        <v>45.5</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-2.31</v>
+        <v>1.63</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>25.27</v>
+        <v>21.12</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-1.78</v>
+        <v>1</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R8" s="4" t="n">
+        <v>21.12</v>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="R8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U8" s="4" t="n">
         <v>1.25</v>
       </c>
-      <c r="S8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="4" t="n">
-        <v>-0.98</v>
-      </c>
-      <c r="U8" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V8" s="4" t="n">
-        <v>0</v>
+        <v>-2.06</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>1.86</v>
+        <v>0.33</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Z8" s="4" t="n">
-        <v>-2.06</v>
-      </c>
-      <c r="AA8" s="4" t="n">
-        <v>4.09</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="E9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>5.87</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="G9" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>1</v>
@@ -1279,81 +1192,72 @@
         <v>1</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-5</v>
+        <v>2.5</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>47.5</v>
+        <v>45.5</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-2.19</v>
+        <v>1.63</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>23.48</v>
+        <v>21.12</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.78</v>
+        <v>1</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R9" s="4" t="n">
+        <v>21.12</v>
+      </c>
+      <c r="Q9" s="4" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="R9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U9" s="4" t="n">
         <v>1.25</v>
       </c>
-      <c r="S9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" s="4" t="n">
-        <v>-0.98</v>
-      </c>
-      <c r="U9" s="4" t="n">
-        <v>-0.12</v>
-      </c>
       <c r="V9" s="4" t="n">
-        <v>0</v>
+        <v>-2.06</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>1.86</v>
+        <v>0.33</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-1.79</v>
-      </c>
-      <c r="Y9" s="4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Z9" s="4" t="n">
-        <v>-2.06</v>
-      </c>
-      <c r="AA9" s="4" t="n">
-        <v>4.09</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="E10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="G10" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>1</v>
@@ -1365,78 +1269,69 @@
         <v>-6</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>45</v>
+        <v>47.5</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-2.37</v>
+        <v>1.12</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>49.22</v>
+        <v>44.39</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-2.17</v>
+        <v>-1.31</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>46.01</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R10" s="4" t="n">
+        <v>44.39</v>
+      </c>
+      <c r="Q10" s="4" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="R10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U10" s="4" t="n">
         <v>2.5</v>
       </c>
-      <c r="S10" s="4" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="T10" s="4" t="n">
-        <v>-1.97</v>
-      </c>
-      <c r="U10" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V10" s="4" t="n">
-        <v>-0.71</v>
+        <v>6.09</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>3.72</v>
+        <v>2.12</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="4" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="Z10" s="4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AA10" s="4" t="n">
-        <v>-1.43</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="E11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="G11" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I11" s="5" t="n">
         <v>1</v>
@@ -1448,78 +1343,69 @@
         <v>-6</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>45</v>
+        <v>47.5</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-2.13</v>
+        <v>1.12</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>45.76</v>
+        <v>44.39</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.17</v>
+        <v>-1.31</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>46.01</v>
-      </c>
-      <c r="Q11" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R11" s="4" t="n">
+        <v>44.39</v>
+      </c>
+      <c r="Q11" s="4" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="R11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U11" s="4" t="n">
         <v>2.5</v>
       </c>
-      <c r="S11" s="4" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="T11" s="4" t="n">
-        <v>-1.97</v>
-      </c>
-      <c r="U11" s="4" t="n">
-        <v>-0.24</v>
-      </c>
       <c r="V11" s="4" t="n">
-        <v>-0.71</v>
+        <v>6.09</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>3.72</v>
+        <v>2.12</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-3.46</v>
-      </c>
-      <c r="Y11" s="4" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="Z11" s="4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AA11" s="4" t="n">
-        <v>-1.43</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="G12" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I12" s="5" t="n">
         <v>1</v>
@@ -1531,78 +1417,69 @@
         <v>-6</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>45</v>
+        <v>47.5</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.19</v>
+        <v>0.56</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>24.61</v>
+        <v>22.19</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.08</v>
+        <v>-0.66</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>23.01</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R12" s="4" t="n">
+        <v>22.19</v>
+      </c>
+      <c r="Q12" s="4" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="R12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U12" s="4" t="n">
         <v>1.25</v>
       </c>
-      <c r="S12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="4" t="n">
-        <v>-0.98</v>
-      </c>
-      <c r="U12" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V12" s="4" t="n">
-        <v>-0.36</v>
+        <v>6.09</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="4" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="Z12" s="4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AA12" s="4" t="n">
-        <v>-1.43</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="E13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="G13" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I13" s="5" t="n">
         <v>1</v>
@@ -1614,78 +1491,69 @@
         <v>-6</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>45</v>
+        <v>47.5</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.06</v>
+        <v>0.56</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>22.88</v>
+        <v>22.19</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.08</v>
+        <v>-0.66</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>23.01</v>
-      </c>
-      <c r="Q13" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R13" s="4" t="n">
+        <v>22.19</v>
+      </c>
+      <c r="Q13" s="4" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="R13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U13" s="4" t="n">
         <v>1.25</v>
       </c>
-      <c r="S13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="4" t="n">
-        <v>-0.98</v>
-      </c>
-      <c r="U13" s="4" t="n">
-        <v>-0.12</v>
-      </c>
       <c r="V13" s="4" t="n">
-        <v>-0.36</v>
+        <v>6.09</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-1.73</v>
-      </c>
-      <c r="Y13" s="4" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="Z13" s="4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AA13" s="4" t="n">
-        <v>-1.43</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="E14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="G14" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I14" s="5" t="n">
         <v>1</v>
@@ -1694,81 +1562,72 @@
         <v>1</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.5</v>
+        <v>-14</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>48.5</v>
+        <v>51.5</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>3.57</v>
+        <v>-13</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>52.8</v>
+        <v>44.23</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.47</v>
+        <v>-10.98</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>53.15</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R14" s="4" t="n">
+        <v>44.23</v>
+      </c>
+      <c r="Q14" s="4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U14" s="4" t="n">
         <v>2.5</v>
       </c>
-      <c r="S14" s="4" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="T14" s="4" t="n">
-        <v>-1.97</v>
-      </c>
-      <c r="U14" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V14" s="4" t="n">
-        <v>2.23</v>
+        <v>-10.06</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>3.72</v>
+        <v>-6.7</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="4" t="n">
-        <v>-10.06</v>
-      </c>
-      <c r="Z14" s="4" t="n">
-        <v>6.09</v>
-      </c>
-      <c r="AA14" s="4" t="n">
-        <v>-12.92</v>
+        <v>-2.69</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="E15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="G15" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I15" s="5" t="n">
         <v>1</v>
@@ -1777,81 +1636,72 @@
         <v>1</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.5</v>
+        <v>-14</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>48.5</v>
+        <v>51.5</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>3.57</v>
+        <v>-13</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>52.8</v>
+        <v>44.23</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.47</v>
+        <v>-10.98</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>53.15</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R15" s="4" t="n">
+        <v>44.23</v>
+      </c>
+      <c r="Q15" s="4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U15" s="4" t="n">
         <v>2.5</v>
       </c>
-      <c r="S15" s="4" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="T15" s="4" t="n">
-        <v>-1.97</v>
-      </c>
-      <c r="U15" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V15" s="4" t="n">
-        <v>2.23</v>
+        <v>-10.06</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>3.72</v>
+        <v>-6.7</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="4" t="n">
-        <v>-10.06</v>
-      </c>
-      <c r="Z15" s="4" t="n">
-        <v>6.09</v>
-      </c>
-      <c r="AA15" s="4" t="n">
-        <v>-12.92</v>
+        <v>-2.69</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="E16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="G16" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I16" s="5" t="n">
         <v>1</v>
@@ -1860,81 +1710,72 @@
         <v>1</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.5</v>
+        <v>-14</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>48.5</v>
+        <v>51.5</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.78</v>
+        <v>-6.5</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>26.4</v>
+        <v>22.11</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.74</v>
+        <v>-5.49</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>26.57</v>
-      </c>
-      <c r="Q16" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R16" s="4" t="n">
+        <v>22.11</v>
+      </c>
+      <c r="Q16" s="4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U16" s="4" t="n">
         <v>1.25</v>
       </c>
-      <c r="S16" s="4" t="n">
-        <v>-0.21</v>
-      </c>
-      <c r="T16" s="4" t="n">
-        <v>-0.98</v>
-      </c>
-      <c r="U16" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V16" s="4" t="n">
-        <v>1.12</v>
+        <v>-10.06</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>1.86</v>
+        <v>-6.7</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="4" t="n">
-        <v>-10.06</v>
-      </c>
-      <c r="Z16" s="4" t="n">
-        <v>6.09</v>
-      </c>
-      <c r="AA16" s="4" t="n">
-        <v>-12.92</v>
+        <v>-2.69</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="E17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="G17" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I17" s="5" t="n">
         <v>1</v>
@@ -1943,81 +1784,72 @@
         <v>1</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.5</v>
+        <v>-14</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>48.5</v>
+        <v>51.5</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.78</v>
+        <v>-6.5</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>26.4</v>
+        <v>22.11</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.74</v>
+        <v>-5.49</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>26.57</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R17" s="4" t="n">
+        <v>22.11</v>
+      </c>
+      <c r="Q17" s="4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U17" s="4" t="n">
         <v>1.25</v>
       </c>
-      <c r="S17" s="4" t="n">
-        <v>-0.21</v>
-      </c>
-      <c r="T17" s="4" t="n">
-        <v>-0.98</v>
-      </c>
-      <c r="U17" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V17" s="4" t="n">
-        <v>1.12</v>
+        <v>-10.06</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>1.86</v>
+        <v>-6.7</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="4" t="n">
-        <v>-10.06</v>
-      </c>
-      <c r="Z17" s="4" t="n">
-        <v>6.09</v>
-      </c>
-      <c r="AA17" s="4" t="n">
-        <v>-12.92</v>
+        <v>-2.69</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>0.3</v>
+      <c r="E18" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I18" s="5" t="n">
         <v>1</v>
@@ -2026,81 +1858,72 @@
         <v>1</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-15.5</v>
+        <v>5</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>46.5</v>
+        <v>42.5</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-4.2</v>
+        <v>5.57</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>49.2</v>
+        <v>38.62</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-8.64</v>
+        <v>5.43</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R18" s="4" t="n">
+        <v>38.62</v>
+      </c>
+      <c r="Q18" s="4" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="R18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U18" s="4" t="n">
         <v>2.5</v>
       </c>
-      <c r="S18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" s="4" t="n">
-        <v>-1.97</v>
-      </c>
-      <c r="U18" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V18" s="4" t="n">
-        <v>-0.38</v>
+        <v>2.21</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>3.72</v>
+        <v>7.16</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="4" t="n">
-        <v>7.16</v>
-      </c>
-      <c r="Z18" s="4" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AA18" s="4" t="n">
-        <v>3.54</v>
+        <v>-3.96</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>0.3</v>
+      <c r="E19" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I19" s="5" t="n">
         <v>1</v>
@@ -2109,81 +1932,72 @@
         <v>1</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-15.5</v>
+        <v>5</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>46.5</v>
+        <v>42.5</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-4.17</v>
+        <v>5.57</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>48.71</v>
+        <v>38.62</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-8.64</v>
+        <v>5.43</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="Q19" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R19" s="4" t="n">
+        <v>38.62</v>
+      </c>
+      <c r="Q19" s="4" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="R19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U19" s="4" t="n">
         <v>2.5</v>
       </c>
-      <c r="S19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" s="4" t="n">
-        <v>-1.97</v>
-      </c>
-      <c r="U19" s="4" t="n">
-        <v>-0.02</v>
-      </c>
       <c r="V19" s="4" t="n">
-        <v>-0.38</v>
+        <v>2.21</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>3.72</v>
+        <v>7.16</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.49</v>
-      </c>
-      <c r="Y19" s="4" t="n">
-        <v>7.16</v>
-      </c>
-      <c r="Z19" s="4" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AA19" s="4" t="n">
-        <v>3.54</v>
+        <v>-3.96</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>0.3</v>
+      <c r="E20" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I20" s="5" t="n">
         <v>1</v>
@@ -2192,81 +2006,72 @@
         <v>1</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-15.5</v>
+        <v>5</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>46.5</v>
+        <v>42.5</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.1</v>
+        <v>2.79</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>24.6</v>
+        <v>19.31</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-4.32</v>
+        <v>2.72</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R20" s="4" t="n">
+        <v>19.31</v>
+      </c>
+      <c r="Q20" s="4" t="n">
+        <v>-0.07</v>
+      </c>
+      <c r="R20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U20" s="4" t="n">
         <v>1.25</v>
       </c>
-      <c r="S20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" s="4" t="n">
-        <v>-0.98</v>
-      </c>
-      <c r="U20" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V20" s="4" t="n">
-        <v>-0.19</v>
+        <v>2.21</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>1.86</v>
+        <v>7.16</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="4" t="n">
-        <v>7.16</v>
-      </c>
-      <c r="Z20" s="4" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AA20" s="4" t="n">
-        <v>3.54</v>
+        <v>-3.96</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>0.3</v>
+      <c r="E21" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I21" s="5" t="n">
         <v>1</v>
@@ -2275,81 +2080,72 @@
         <v>1</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-15.5</v>
+        <v>5</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>46.5</v>
+        <v>42.5</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.09</v>
+        <v>2.79</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>24.36</v>
+        <v>19.31</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-4.32</v>
+        <v>2.72</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R21" s="4" t="n">
+        <v>19.31</v>
+      </c>
+      <c r="Q21" s="4" t="n">
+        <v>-0.07</v>
+      </c>
+      <c r="R21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U21" s="4" t="n">
         <v>1.25</v>
       </c>
-      <c r="S21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" s="4" t="n">
-        <v>-0.98</v>
-      </c>
-      <c r="U21" s="4" t="n">
-        <v>-0.01</v>
-      </c>
       <c r="V21" s="4" t="n">
-        <v>-0.19</v>
+        <v>2.21</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>1.86</v>
+        <v>7.16</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="Y21" s="4" t="n">
-        <v>7.16</v>
-      </c>
-      <c r="Z21" s="4" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AA21" s="4" t="n">
-        <v>3.54</v>
+        <v>-3.96</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="G22" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I22" s="5" t="n">
         <v>1</v>
@@ -2358,81 +2154,72 @@
         <v>1</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-6.5</v>
+        <v>2.5</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>45.5</v>
+        <v>48.5</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.55</v>
+        <v>-4.45</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>49.72</v>
+        <v>45.07</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.17</v>
+        <v>-3.06</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>46.98</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="R22" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" s="4" t="n">
-        <v>-1.97</v>
+        <v>45.07</v>
+      </c>
+      <c r="Q22" s="4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.36</v>
+        <v>-11.8</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>3.72</v>
+        <v>-20.83</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="4" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Z22" s="4" t="n">
-        <v>-6.7</v>
-      </c>
-      <c r="AA22" s="4" t="n">
-        <v>7.12</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="G23" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I23" s="5" t="n">
         <v>1</v>
@@ -2441,81 +2228,72 @@
         <v>1</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-6.5</v>
+        <v>2.5</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>45.5</v>
+        <v>48.5</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.72</v>
+        <v>-4.45</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>46.75</v>
+        <v>45.07</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.17</v>
+        <v>-3.06</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>46.98</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="R23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" s="4" t="n">
-        <v>-1.97</v>
+        <v>45.07</v>
+      </c>
+      <c r="Q23" s="4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.17</v>
+        <v>2.5</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.36</v>
+        <v>-11.8</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>3.72</v>
+        <v>-20.83</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-2.97</v>
-      </c>
-      <c r="Y23" s="4" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Z23" s="4" t="n">
-        <v>-6.7</v>
-      </c>
-      <c r="AA23" s="4" t="n">
-        <v>7.12</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="G24" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I24" s="5" t="n">
         <v>1</v>
@@ -2524,81 +2302,72 @@
         <v>1</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-6.5</v>
+        <v>2.5</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>45.5</v>
+        <v>48.5</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.28</v>
+        <v>-2.22</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>24.86</v>
+        <v>22.53</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>1.08</v>
+        <v>-1.53</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>23.49</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="R24" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" s="4" t="n">
-        <v>-0.98</v>
+        <v>22.53</v>
+      </c>
+      <c r="Q24" s="4" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="R24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.18</v>
+        <v>-11.8</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>1.86</v>
+        <v>-20.83</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="4" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Z24" s="4" t="n">
-        <v>-6.7</v>
-      </c>
-      <c r="AA24" s="4" t="n">
-        <v>7.12</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="G25" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I25" s="5" t="n">
         <v>1</v>
@@ -2607,81 +2376,72 @@
         <v>1</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-6.5</v>
+        <v>2.5</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>45.5</v>
+        <v>48.5</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.36</v>
+        <v>-2.22</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>23.37</v>
+        <v>22.53</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.08</v>
+        <v>-1.53</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>23.49</v>
-      </c>
-      <c r="Q25" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="R25" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" s="4" t="n">
-        <v>-0.98</v>
+        <v>22.53</v>
+      </c>
+      <c r="Q25" s="4" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="R25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T25" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.09</v>
+        <v>1.25</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.18</v>
+        <v>-11.8</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>1.86</v>
+        <v>-20.83</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-1.49</v>
-      </c>
-      <c r="Y25" s="4" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Z25" s="4" t="n">
-        <v>-6.7</v>
-      </c>
-      <c r="AA25" s="4" t="n">
-        <v>7.12</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>23.4</v>
+        <v>55</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I26" s="5" t="n">
         <v>1</v>
@@ -2690,81 +2450,72 @@
         <v>1</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>5.5</v>
+        <v>0.5</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>48.5</v>
+        <v>46.5</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-2.35</v>
+        <v>-0.55</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>53.47</v>
+        <v>42.91</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.54</v>
+        <v>1.69</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>47.59</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R26" s="4" t="n">
+        <v>42.91</v>
+      </c>
+      <c r="Q26" s="4" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U26" s="4" t="n">
         <v>2.5</v>
       </c>
-      <c r="S26" s="4" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="T26" s="4" t="n">
-        <v>-1.97</v>
-      </c>
-      <c r="U26" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V26" s="4" t="n">
-        <v>2.31</v>
+        <v>2.73</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>3.72</v>
+        <v>1.51</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" s="4" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z26" s="4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AA26" s="4" t="n">
-        <v>-0.49</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>23.4</v>
+        <v>55</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I27" s="5" t="n">
         <v>1</v>
@@ -2773,81 +2524,72 @@
         <v>1</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>5.5</v>
+        <v>0.5</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>48.5</v>
+        <v>46.5</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.4</v>
+        <v>-0.55</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>47.3</v>
+        <v>42.91</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.54</v>
+        <v>1.69</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>47.59</v>
-      </c>
-      <c r="Q27" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R27" s="4" t="n">
+        <v>42.91</v>
+      </c>
+      <c r="Q27" s="4" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T27" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U27" s="4" t="n">
         <v>2.5</v>
       </c>
-      <c r="S27" s="4" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="T27" s="4" t="n">
-        <v>-1.97</v>
-      </c>
-      <c r="U27" s="4" t="n">
-        <v>-0.95</v>
-      </c>
       <c r="V27" s="4" t="n">
-        <v>2.31</v>
+        <v>2.73</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>3.72</v>
+        <v>1.51</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-6.18</v>
-      </c>
-      <c r="Y27" s="4" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z27" s="4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AA27" s="4" t="n">
-        <v>-0.49</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>23.4</v>
+        <v>55</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I28" s="5" t="n">
         <v>1</v>
@@ -2856,81 +2598,72 @@
         <v>1</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>5.5</v>
+        <v>0.5</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>48.5</v>
+        <v>46.5</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.17</v>
+        <v>-0.27</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>26.74</v>
+        <v>21.46</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.27</v>
+        <v>0.85</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="Q28" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R28" s="4" t="n">
+        <v>21.46</v>
+      </c>
+      <c r="Q28" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="R28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U28" s="4" t="n">
         <v>1.25</v>
       </c>
-      <c r="S28" s="4" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="T28" s="4" t="n">
-        <v>-0.98</v>
-      </c>
-      <c r="U28" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="V28" s="4" t="n">
-        <v>1.16</v>
+        <v>2.73</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>1.86</v>
+        <v>1.51</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" s="4" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z28" s="4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AA28" s="4" t="n">
-        <v>-0.49</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>23.4</v>
+        <v>55</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I29" s="5" t="n">
         <v>1</v>
@@ -2939,81 +2672,72 @@
         <v>1</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5.5</v>
+        <v>0.5</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>48.5</v>
+        <v>46.5</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.7</v>
+        <v>-0.27</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>23.65</v>
+        <v>21.46</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.27</v>
+        <v>0.85</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R29" s="4" t="n">
+        <v>21.46</v>
+      </c>
+      <c r="Q29" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="R29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U29" s="4" t="n">
         <v>1.25</v>
       </c>
-      <c r="S29" s="4" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="T29" s="4" t="n">
-        <v>-0.98</v>
-      </c>
-      <c r="U29" s="4" t="n">
-        <v>-0.47</v>
-      </c>
       <c r="V29" s="4" t="n">
-        <v>1.16</v>
+        <v>2.73</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>1.86</v>
+        <v>1.51</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-3.09</v>
-      </c>
-      <c r="Y29" s="4" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z29" s="4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AA29" s="4" t="n">
-        <v>-0.49</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>7.07</v>
+        <v>59</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I30" s="5" t="n">
         <v>1</v>
@@ -3022,81 +2746,72 @@
         <v>1</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-3.5</v>
+        <v>3.5</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>50.5</v>
+        <v>47.5</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>5.47</v>
+        <v>2.05</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>52.52</v>
+        <v>42.45</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>4.89</v>
+        <v>2</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>48.73</v>
-      </c>
-      <c r="Q30" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R30" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S30" s="4" t="n">
-        <v>-0.42</v>
-      </c>
-      <c r="T30" s="4" t="n">
-        <v>-1.97</v>
+        <v>42.45</v>
+      </c>
+      <c r="Q30" s="4" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T30" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>1.66</v>
+        <v>2.12</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>3.72</v>
+        <v>3.05</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" s="4" t="n">
-        <v>14.01</v>
-      </c>
-      <c r="Z30" s="4" t="n">
-        <v>-11.8</v>
-      </c>
-      <c r="AA30" s="4" t="n">
-        <v>20.65</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>7.07</v>
+        <v>59</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I31" s="5" t="n">
         <v>1</v>
@@ -3105,81 +2820,72 @@
         <v>1</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-3.5</v>
+        <v>3.5</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>50.5</v>
+        <v>47.5</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>5.76</v>
+        <v>2.05</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>48.47</v>
+        <v>42.45</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>4.89</v>
+        <v>2</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>48.73</v>
-      </c>
-      <c r="Q31" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R31" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S31" s="4" t="n">
-        <v>-0.42</v>
-      </c>
-      <c r="T31" s="4" t="n">
-        <v>-1.97</v>
+        <v>42.45</v>
+      </c>
+      <c r="Q31" s="4" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T31" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.29</v>
+        <v>1</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>1.66</v>
+        <v>2.12</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>3.72</v>
+        <v>3.05</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-4.05</v>
-      </c>
-      <c r="Y31" s="4" t="n">
-        <v>14.01</v>
-      </c>
-      <c r="Z31" s="4" t="n">
-        <v>-11.8</v>
-      </c>
-      <c r="AA31" s="4" t="n">
-        <v>20.65</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>7.07</v>
+        <v>59</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I32" s="5" t="n">
         <v>1</v>
@@ -3188,81 +2894,72 @@
         <v>1</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-3.5</v>
+        <v>3.5</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>50.5</v>
+        <v>47.5</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>2.73</v>
+        <v>1.02</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>26.26</v>
+        <v>21.22</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>2.44</v>
+        <v>1</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>24.37</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R32" s="4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S32" s="4" t="n">
-        <v>-0.21</v>
-      </c>
-      <c r="T32" s="4" t="n">
-        <v>-0.98</v>
+        <v>21.22</v>
+      </c>
+      <c r="Q32" s="4" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="R32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>0.83</v>
+        <v>2.12</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>1.86</v>
+        <v>3.05</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="4" t="n">
-        <v>14.01</v>
-      </c>
-      <c r="Z32" s="4" t="n">
-        <v>-11.8</v>
-      </c>
-      <c r="AA32" s="4" t="n">
-        <v>20.65</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>7.07</v>
+        <v>59</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I33" s="5" t="n">
         <v>1</v>
@@ -3271,55 +2968,326 @@
         <v>1</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-3.5</v>
+        <v>3.5</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>50.5</v>
+        <v>47.5</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>2.88</v>
+        <v>1.02</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>24.24</v>
+        <v>21.22</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>2.44</v>
+        <v>1</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>24.37</v>
-      </c>
-      <c r="Q33" s="3" t="s">
+        <v>21.22</v>
+      </c>
+      <c r="Q33" s="4" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="R33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T33" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U33" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V33" s="4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="W33" s="4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="X33" s="4" t="n">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N34" s="4" t="n">
+        <v>43.91</v>
+      </c>
+      <c r="O34" s="4" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="P34" s="4" t="n">
+        <v>43.91</v>
+      </c>
+      <c r="Q34" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T34" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U34" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V34" s="4" t="n">
+        <v>-11.8</v>
+      </c>
+      <c r="W34" s="4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="X34" s="4" t="n">
+        <v>-9.71</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+      <c r="M35" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N35" s="4" t="n">
+        <v>43.91</v>
+      </c>
+      <c r="O35" s="4" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="P35" s="4" t="n">
+        <v>43.91</v>
+      </c>
+      <c r="Q35" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T35" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U35" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V35" s="4" t="n">
+        <v>-11.8</v>
+      </c>
+      <c r="W35" s="4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="X35" s="4" t="n">
+        <v>-9.71</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G36" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="R33" s="4" t="n">
+      <c r="H36" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
+      <c r="M36" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N36" s="4" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="O36" s="4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P36" s="4" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="Q36" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T36" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U36" s="4" t="n">
         <v>1.25</v>
       </c>
-      <c r="S33" s="4" t="n">
-        <v>-0.21</v>
-      </c>
-      <c r="T33" s="4" t="n">
-        <v>-0.98</v>
-      </c>
-      <c r="U33" s="4" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="V33" s="4" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="W33" s="4" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="X33" s="4" t="n">
-        <v>-2.03</v>
-      </c>
-      <c r="Y33" s="4" t="n">
-        <v>14.01</v>
-      </c>
-      <c r="Z33" s="4" t="n">
+      <c r="V36" s="4" t="n">
         <v>-11.8</v>
       </c>
-      <c r="AA33" s="4" t="n">
-        <v>20.65</v>
+      <c r="W36" s="4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="X36" s="4" t="n">
+        <v>-9.71</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N37" s="4" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="O37" s="4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P37" s="4" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="Q37" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T37" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U37" s="4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V37" s="4" t="n">
+        <v>-11.8</v>
+      </c>
+      <c r="W37" s="4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="X37" s="4" t="n">
+        <v>-9.71</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_upcoming_projections.xlsx
+++ b/files/NRL_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -48,18 +48,6 @@
   </si>
   <si>
     <t xml:space="preserve">Forecast Rain mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Player Margin Adjustment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Player Total Adjustment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home Lineup Available</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Away Lineup Available</t>
   </si>
   <si>
     <t xml:space="preserve">19:50</t>
@@ -513,10 +501,6 @@
     <col min="10" max="10" width="20.71" hidden="0" customWidth="1"/>
     <col min="11" max="11" width="43.71" hidden="0" customWidth="1"/>
     <col min="12" max="12" width="16.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="24.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="23.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="21.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="21.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -556,31 +540,19 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
         <v>46226</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
         <v>11.4</v>
@@ -589,10 +561,10 @@
         <v>40.7</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I2" t="n">
         <v>15</v>
@@ -601,22 +573,10 @@
         <v>44.5</v>
       </c>
       <c r="K2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -624,13 +584,13 @@
         <v>46226</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
         <v>11.4</v>
@@ -639,10 +599,10 @@
         <v>40.7</v>
       </c>
       <c r="G3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I3" t="n">
         <v>15</v>
@@ -651,22 +611,10 @@
         <v>44.5</v>
       </c>
       <c r="K3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -674,25 +622,25 @@
         <v>46226</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E4" t="n">
         <v>5.7</v>
       </c>
       <c r="F4" t="n">
-        <v>20.35</v>
+        <v>20.4</v>
       </c>
       <c r="G4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I4" t="n">
         <v>15</v>
@@ -701,22 +649,10 @@
         <v>44.5</v>
       </c>
       <c r="K4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -724,25 +660,25 @@
         <v>46226</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
         <v>5.7</v>
       </c>
       <c r="F5" t="n">
-        <v>20.35</v>
+        <v>20.4</v>
       </c>
       <c r="G5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I5" t="n">
         <v>15</v>
@@ -751,22 +687,10 @@
         <v>44.5</v>
       </c>
       <c r="K5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -774,25 +698,25 @@
         <v>46227</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E6" t="n">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="F6" t="n">
-        <v>42.24</v>
+        <v>42.2</v>
       </c>
       <c r="G6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I6" t="n">
         <v>2.5</v>
@@ -801,22 +725,10 @@
         <v>45.5</v>
       </c>
       <c r="K6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>-1.26</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -824,25 +736,25 @@
         <v>46227</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E7" t="n">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="F7" t="n">
-        <v>42.24</v>
+        <v>42.2</v>
       </c>
       <c r="G7" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H7" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I7" t="n">
         <v>2.5</v>
@@ -851,22 +763,10 @@
         <v>45.5</v>
       </c>
       <c r="K7" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>-1.26</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -874,25 +774,25 @@
         <v>46227</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E8" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="F8" t="n">
-        <v>21.12</v>
+        <v>21.1</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H8" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I8" t="n">
         <v>2.5</v>
@@ -901,22 +801,10 @@
         <v>45.5</v>
       </c>
       <c r="K8" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>-0.63</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -924,25 +812,25 @@
         <v>46227</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E9" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="F9" t="n">
-        <v>21.12</v>
+        <v>21.1</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I9" t="n">
         <v>2.5</v>
@@ -951,22 +839,10 @@
         <v>45.5</v>
       </c>
       <c r="K9" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>-0.63</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -974,25 +850,25 @@
         <v>46227</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E10" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="F10" t="n">
-        <v>44.39</v>
+        <v>44.4</v>
       </c>
       <c r="G10" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H10" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I10" t="n">
         <v>-6</v>
@@ -1001,22 +877,10 @@
         <v>47.5</v>
       </c>
       <c r="K10" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>-2.43</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1024,25 +888,25 @@
         <v>46227</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="F11" t="n">
-        <v>44.39</v>
+        <v>44.4</v>
       </c>
       <c r="G11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I11" t="n">
         <v>-6</v>
@@ -1051,22 +915,10 @@
         <v>47.5</v>
       </c>
       <c r="K11" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>-2.43</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1074,25 +926,25 @@
         <v>46227</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D12" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E12" t="n">
-        <v>0.56</v>
+        <v>0.6</v>
       </c>
       <c r="F12" t="n">
-        <v>22.19</v>
+        <v>22.2</v>
       </c>
       <c r="G12" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H12" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I12" t="n">
         <v>-6</v>
@@ -1101,22 +953,10 @@
         <v>47.5</v>
       </c>
       <c r="K12" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>-1.22</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1124,25 +964,25 @@
         <v>46227</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D13" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E13" t="n">
-        <v>0.56</v>
+        <v>0.6</v>
       </c>
       <c r="F13" t="n">
-        <v>22.19</v>
+        <v>22.2</v>
       </c>
       <c r="G13" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H13" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I13" t="n">
         <v>-6</v>
@@ -1151,22 +991,10 @@
         <v>47.5</v>
       </c>
       <c r="K13" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>-1.22</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1174,25 +1002,25 @@
         <v>46228</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D14" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E14" t="n">
         <v>-13</v>
       </c>
       <c r="F14" t="n">
-        <v>44.23</v>
+        <v>44.2</v>
       </c>
       <c r="G14" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I14" t="n">
         <v>-14</v>
@@ -1201,22 +1029,10 @@
         <v>51.5</v>
       </c>
       <c r="K14" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1224,25 +1040,25 @@
         <v>46228</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D15" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E15" t="n">
         <v>-13</v>
       </c>
       <c r="F15" t="n">
-        <v>44.23</v>
+        <v>44.2</v>
       </c>
       <c r="G15" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H15" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I15" t="n">
         <v>-14</v>
@@ -1251,22 +1067,10 @@
         <v>51.5</v>
       </c>
       <c r="K15" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1274,25 +1078,25 @@
         <v>46228</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E16" t="n">
         <v>-6.5</v>
       </c>
       <c r="F16" t="n">
-        <v>22.11</v>
+        <v>22.1</v>
       </c>
       <c r="G16" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H16" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I16" t="n">
         <v>-14</v>
@@ -1301,22 +1105,10 @@
         <v>51.5</v>
       </c>
       <c r="K16" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1324,25 +1116,25 @@
         <v>46228</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D17" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E17" t="n">
         <v>-6.5</v>
       </c>
       <c r="F17" t="n">
-        <v>22.11</v>
+        <v>22.1</v>
       </c>
       <c r="G17" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H17" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I17" t="n">
         <v>-14</v>
@@ -1351,22 +1143,10 @@
         <v>51.5</v>
       </c>
       <c r="K17" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1374,25 +1154,25 @@
         <v>46228</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D18" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E18" t="n">
-        <v>5.57</v>
+        <v>5.6</v>
       </c>
       <c r="F18" t="n">
-        <v>38.62</v>
+        <v>38.6</v>
       </c>
       <c r="G18" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H18" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I18" t="n">
         <v>5</v>
@@ -1401,22 +1181,10 @@
         <v>42.5</v>
       </c>
       <c r="K18" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1424,25 +1192,25 @@
         <v>46228</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D19" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E19" t="n">
-        <v>5.57</v>
+        <v>5.6</v>
       </c>
       <c r="F19" t="n">
-        <v>38.62</v>
+        <v>38.6</v>
       </c>
       <c r="G19" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H19" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I19" t="n">
         <v>5</v>
@@ -1451,22 +1219,10 @@
         <v>42.5</v>
       </c>
       <c r="K19" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1474,25 +1230,25 @@
         <v>46228</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C20" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E20" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="F20" t="n">
-        <v>19.31</v>
+        <v>19.3</v>
       </c>
       <c r="G20" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H20" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I20" t="n">
         <v>5</v>
@@ -1501,22 +1257,10 @@
         <v>42.5</v>
       </c>
       <c r="K20" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>-0.07</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1524,25 +1268,25 @@
         <v>46228</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C21" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D21" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E21" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="F21" t="n">
-        <v>19.31</v>
+        <v>19.3</v>
       </c>
       <c r="G21" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H21" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I21" t="n">
         <v>5</v>
@@ -1551,22 +1295,10 @@
         <v>42.5</v>
       </c>
       <c r="K21" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>-0.07</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1574,25 +1306,25 @@
         <v>46228</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C22" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D22" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.45</v>
+        <v>-4.4</v>
       </c>
       <c r="F22" t="n">
-        <v>45.07</v>
+        <v>45.1</v>
       </c>
       <c r="G22" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I22" t="n">
         <v>2.5</v>
@@ -1601,22 +1333,10 @@
         <v>48.5</v>
       </c>
       <c r="K22" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1624,25 +1344,25 @@
         <v>46228</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C23" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D23" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.45</v>
+        <v>-4.4</v>
       </c>
       <c r="F23" t="n">
-        <v>45.07</v>
+        <v>45.1</v>
       </c>
       <c r="G23" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I23" t="n">
         <v>2.5</v>
@@ -1651,22 +1371,10 @@
         <v>48.5</v>
       </c>
       <c r="K23" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1674,25 +1382,25 @@
         <v>46228</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C24" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D24" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.22</v>
+        <v>-2.2</v>
       </c>
       <c r="F24" t="n">
-        <v>22.53</v>
+        <v>22.5</v>
       </c>
       <c r="G24" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H24" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I24" t="n">
         <v>2.5</v>
@@ -1701,22 +1409,10 @@
         <v>48.5</v>
       </c>
       <c r="K24" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0.69</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1724,25 +1420,25 @@
         <v>46228</v>
       </c>
       <c r="B25" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C25" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D25" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.22</v>
+        <v>-2.2</v>
       </c>
       <c r="F25" t="n">
-        <v>22.53</v>
+        <v>22.5</v>
       </c>
       <c r="G25" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H25" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I25" t="n">
         <v>2.5</v>
@@ -1751,22 +1447,10 @@
         <v>48.5</v>
       </c>
       <c r="K25" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0.69</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1774,25 +1458,25 @@
         <v>46229</v>
       </c>
       <c r="B26" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C26" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D26" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.55</v>
+        <v>-0.6</v>
       </c>
       <c r="F26" t="n">
-        <v>42.91</v>
+        <v>42.9</v>
       </c>
       <c r="G26" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H26" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I26" t="n">
         <v>0.5</v>
@@ -1801,22 +1485,10 @@
         <v>46.5</v>
       </c>
       <c r="K26" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1824,25 +1496,25 @@
         <v>46229</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C27" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D27" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.55</v>
+        <v>-0.6</v>
       </c>
       <c r="F27" t="n">
-        <v>42.91</v>
+        <v>42.9</v>
       </c>
       <c r="G27" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H27" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I27" t="n">
         <v>0.5</v>
@@ -1851,22 +1523,10 @@
         <v>46.5</v>
       </c>
       <c r="K27" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1874,25 +1534,25 @@
         <v>46229</v>
       </c>
       <c r="B28" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C28" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D28" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.27</v>
+        <v>-0.3</v>
       </c>
       <c r="F28" t="n">
-        <v>21.46</v>
+        <v>21.5</v>
       </c>
       <c r="G28" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H28" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I28" t="n">
         <v>0.5</v>
@@ -1901,22 +1561,10 @@
         <v>46.5</v>
       </c>
       <c r="K28" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1924,25 +1572,25 @@
         <v>46229</v>
       </c>
       <c r="B29" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C29" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D29" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.27</v>
+        <v>-0.3</v>
       </c>
       <c r="F29" t="n">
-        <v>21.46</v>
+        <v>21.5</v>
       </c>
       <c r="G29" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H29" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I29" t="n">
         <v>0.5</v>
@@ -1951,22 +1599,10 @@
         <v>46.5</v>
       </c>
       <c r="K29" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1974,25 +1610,25 @@
         <v>46229</v>
       </c>
       <c r="B30" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C30" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D30" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E30" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="F30" t="n">
-        <v>42.45</v>
+        <v>42.5</v>
       </c>
       <c r="G30" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H30" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I30" t="n">
         <v>3.5</v>
@@ -2001,22 +1637,10 @@
         <v>47.5</v>
       </c>
       <c r="K30" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2024,25 +1648,25 @@
         <v>46229</v>
       </c>
       <c r="B31" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C31" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D31" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E31" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>42.45</v>
+        <v>42.5</v>
       </c>
       <c r="G31" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H31" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I31" t="n">
         <v>3.5</v>
@@ -2051,22 +1675,10 @@
         <v>47.5</v>
       </c>
       <c r="K31" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2074,25 +1686,25 @@
         <v>46229</v>
       </c>
       <c r="B32" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C32" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D32" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E32" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>21.22</v>
+        <v>21.2</v>
       </c>
       <c r="G32" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H32" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I32" t="n">
         <v>3.5</v>
@@ -2101,22 +1713,10 @@
         <v>47.5</v>
       </c>
       <c r="K32" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1</v>
-      </c>
-      <c r="P32" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2124,25 +1724,25 @@
         <v>46229</v>
       </c>
       <c r="B33" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C33" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D33" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E33" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>21.22</v>
+        <v>21.2</v>
       </c>
       <c r="G33" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H33" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I33" t="n">
         <v>3.5</v>
@@ -2151,22 +1751,10 @@
         <v>47.5</v>
       </c>
       <c r="K33" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2174,45 +1762,33 @@
         <v>46233</v>
       </c>
       <c r="B34" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C34" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D34" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E34" t="n">
         <v>3</v>
       </c>
       <c r="F34" t="n">
-        <v>43.91</v>
+        <v>43.9</v>
       </c>
       <c r="G34" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H34" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I34"/>
       <c r="J34"/>
       <c r="K34" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2220,45 +1796,33 @@
         <v>46233</v>
       </c>
       <c r="B35" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C35" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D35" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E35" t="n">
         <v>3</v>
       </c>
       <c r="F35" t="n">
-        <v>43.91</v>
+        <v>43.9</v>
       </c>
       <c r="G35" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H35" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I35"/>
       <c r="J35"/>
       <c r="K35" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>1</v>
-      </c>
-      <c r="P35" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2266,45 +1830,33 @@
         <v>46233</v>
       </c>
       <c r="B36" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C36" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D36" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E36" t="n">
         <v>1.5</v>
       </c>
       <c r="F36" t="n">
-        <v>21.95</v>
+        <v>22</v>
       </c>
       <c r="G36" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H36" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I36"/>
       <c r="J36"/>
       <c r="K36" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>1</v>
-      </c>
-      <c r="P36" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2312,45 +1864,33 @@
         <v>46233</v>
       </c>
       <c r="B37" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C37" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D37" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E37" t="n">
         <v>1.5</v>
       </c>
       <c r="F37" t="n">
-        <v>21.95</v>
+        <v>22</v>
       </c>
       <c r="G37" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H37" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I37"/>
       <c r="J37"/>
       <c r="K37" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>1</v>
-      </c>
-      <c r="P37" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_upcoming_projections.xlsx
+++ b/files/NRL_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -50,109 +50,106 @@
     <t xml:space="preserve">Forecast Rain mm</t>
   </si>
   <si>
+    <t xml:space="preserve">18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Rain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">McDonald Jones Stadium, Newcastle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">south sydney rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melbourne storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accor Stadium, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wests tigers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GIO Stadium, Canberra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north queensland cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Queensland Country Bank Stadium, Townsville</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st george-illawarra dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WIN Stadium, Wollongong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manly-warringah sea eagles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Pines Park, Sydney</t>
+  </si>
+  <si>
     <t xml:space="preserve">19:50</t>
   </si>
   <si>
-    <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penrith panthers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Rain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CommBank Stadium, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">newcastle knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">McDonald Jones Stadium, Newcastle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">south sydney rabbitohs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">melbourne storm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accor Stadium, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberra raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wests tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GIO Stadium, Canberra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north queensland cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Queensland Country Bank Stadium, Townsville</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st george-illawarra dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WIN Stadium, Wollongong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manly-warringah sea eagles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 Pines Park, Sydney</t>
+    <t xml:space="preserve">dolphins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AAMI Park, Melbourne</t>
   </si>
 </sst>
 </file>
@@ -492,7 +489,7 @@
     <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="5.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="29.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="26.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="29.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="15.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="13.71" hidden="0" customWidth="1"/>
@@ -543,7 +540,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -555,10 +552,10 @@
         <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>11.4</v>
+        <v>3.3</v>
       </c>
       <c r="F2" t="n">
-        <v>40.7</v>
+        <v>42.2</v>
       </c>
       <c r="G2" t="s">
         <v>15</v>
@@ -566,12 +563,8 @@
       <c r="H2" t="s">
         <v>16</v>
       </c>
-      <c r="I2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J2" t="n">
-        <v>44.5</v>
-      </c>
+      <c r="I2"/>
+      <c r="J2"/>
       <c r="K2" t="s">
         <v>17</v>
       </c>
@@ -581,7 +574,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -593,10 +586,10 @@
         <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>11.4</v>
+        <v>3.3</v>
       </c>
       <c r="F3" t="n">
-        <v>40.7</v>
+        <v>42.2</v>
       </c>
       <c r="G3" t="s">
         <v>15</v>
@@ -604,12 +597,8 @@
       <c r="H3" t="s">
         <v>18</v>
       </c>
-      <c r="I3" t="n">
-        <v>15</v>
-      </c>
-      <c r="J3" t="n">
-        <v>44.5</v>
-      </c>
+      <c r="I3"/>
+      <c r="J3"/>
       <c r="K3" t="s">
         <v>17</v>
       </c>
@@ -619,7 +608,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -631,10 +620,10 @@
         <v>14</v>
       </c>
       <c r="E4" t="n">
-        <v>5.7</v>
+        <v>1.6</v>
       </c>
       <c r="F4" t="n">
-        <v>20.4</v>
+        <v>21.1</v>
       </c>
       <c r="G4" t="s">
         <v>19</v>
@@ -642,12 +631,8 @@
       <c r="H4" t="s">
         <v>16</v>
       </c>
-      <c r="I4" t="n">
-        <v>15</v>
-      </c>
-      <c r="J4" t="n">
-        <v>44.5</v>
-      </c>
+      <c r="I4"/>
+      <c r="J4"/>
       <c r="K4" t="s">
         <v>17</v>
       </c>
@@ -657,7 +642,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -669,10 +654,10 @@
         <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>5.7</v>
+        <v>1.6</v>
       </c>
       <c r="F5" t="n">
-        <v>20.4</v>
+        <v>21.1</v>
       </c>
       <c r="G5" t="s">
         <v>19</v>
@@ -680,12 +665,8 @@
       <c r="H5" t="s">
         <v>18</v>
       </c>
-      <c r="I5" t="n">
-        <v>15</v>
-      </c>
-      <c r="J5" t="n">
-        <v>44.5</v>
-      </c>
+      <c r="I5"/>
+      <c r="J5"/>
       <c r="K5" t="s">
         <v>17</v>
       </c>
@@ -707,10 +688,10 @@
         <v>22</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="F6" t="n">
-        <v>42.2</v>
+        <v>44.4</v>
       </c>
       <c r="G6" t="s">
         <v>15</v>
@@ -718,12 +699,8 @@
       <c r="H6" t="s">
         <v>16</v>
       </c>
-      <c r="I6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>45.5</v>
-      </c>
+      <c r="I6"/>
+      <c r="J6"/>
       <c r="K6" t="s">
         <v>23</v>
       </c>
@@ -745,10 +722,10 @@
         <v>22</v>
       </c>
       <c r="E7" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="F7" t="n">
-        <v>42.2</v>
+        <v>44.4</v>
       </c>
       <c r="G7" t="s">
         <v>15</v>
@@ -756,12 +733,8 @@
       <c r="H7" t="s">
         <v>18</v>
       </c>
-      <c r="I7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>45.5</v>
-      </c>
+      <c r="I7"/>
+      <c r="J7"/>
       <c r="K7" t="s">
         <v>23</v>
       </c>
@@ -783,10 +756,10 @@
         <v>22</v>
       </c>
       <c r="E8" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="F8" t="n">
-        <v>21.1</v>
+        <v>22.2</v>
       </c>
       <c r="G8" t="s">
         <v>19</v>
@@ -794,12 +767,8 @@
       <c r="H8" t="s">
         <v>16</v>
       </c>
-      <c r="I8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>45.5</v>
-      </c>
+      <c r="I8"/>
+      <c r="J8"/>
       <c r="K8" t="s">
         <v>23</v>
       </c>
@@ -821,10 +790,10 @@
         <v>22</v>
       </c>
       <c r="E9" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="F9" t="n">
-        <v>21.1</v>
+        <v>22.2</v>
       </c>
       <c r="G9" t="s">
         <v>19</v>
@@ -832,12 +801,8 @@
       <c r="H9" t="s">
         <v>18</v>
       </c>
-      <c r="I9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J9" t="n">
-        <v>45.5</v>
-      </c>
+      <c r="I9"/>
+      <c r="J9"/>
       <c r="K9" t="s">
         <v>23</v>
       </c>
@@ -847,7 +812,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
@@ -859,10 +824,10 @@
         <v>26</v>
       </c>
       <c r="E10" t="n">
-        <v>1.1</v>
+        <v>-11.8</v>
       </c>
       <c r="F10" t="n">
-        <v>44.4</v>
+        <v>44.2</v>
       </c>
       <c r="G10" t="s">
         <v>15</v>
@@ -871,10 +836,10 @@
         <v>16</v>
       </c>
       <c r="I10" t="n">
-        <v>-6</v>
+        <v>-14.5</v>
       </c>
       <c r="J10" t="n">
-        <v>47.5</v>
+        <v>50.5</v>
       </c>
       <c r="K10" t="s">
         <v>27</v>
@@ -885,7 +850,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B11" t="s">
         <v>24</v>
@@ -897,10 +862,10 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>1.1</v>
+        <v>-11.8</v>
       </c>
       <c r="F11" t="n">
-        <v>44.4</v>
+        <v>44.2</v>
       </c>
       <c r="G11" t="s">
         <v>15</v>
@@ -909,10 +874,10 @@
         <v>18</v>
       </c>
       <c r="I11" t="n">
-        <v>-6</v>
+        <v>-14.5</v>
       </c>
       <c r="J11" t="n">
-        <v>47.5</v>
+        <v>50.5</v>
       </c>
       <c r="K11" t="s">
         <v>27</v>
@@ -923,7 +888,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B12" t="s">
         <v>24</v>
@@ -935,10 +900,10 @@
         <v>26</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6</v>
+        <v>-5.9</v>
       </c>
       <c r="F12" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="G12" t="s">
         <v>19</v>
@@ -947,10 +912,10 @@
         <v>16</v>
       </c>
       <c r="I12" t="n">
-        <v>-6</v>
+        <v>-14.5</v>
       </c>
       <c r="J12" t="n">
-        <v>47.5</v>
+        <v>50.5</v>
       </c>
       <c r="K12" t="s">
         <v>27</v>
@@ -961,7 +926,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B13" t="s">
         <v>24</v>
@@ -973,10 +938,10 @@
         <v>26</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6</v>
+        <v>-5.9</v>
       </c>
       <c r="F13" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="G13" t="s">
         <v>19</v>
@@ -985,10 +950,10 @@
         <v>18</v>
       </c>
       <c r="I13" t="n">
-        <v>-6</v>
+        <v>-14.5</v>
       </c>
       <c r="J13" t="n">
-        <v>47.5</v>
+        <v>50.5</v>
       </c>
       <c r="K13" t="s">
         <v>27</v>
@@ -1011,10 +976,10 @@
         <v>30</v>
       </c>
       <c r="E14" t="n">
-        <v>-13</v>
+        <v>5.6</v>
       </c>
       <c r="F14" t="n">
-        <v>44.2</v>
+        <v>38.6</v>
       </c>
       <c r="G14" t="s">
         <v>15</v>
@@ -1023,13 +988,13 @@
         <v>16</v>
       </c>
       <c r="I14" t="n">
-        <v>-14</v>
+        <v>3.5</v>
       </c>
       <c r="J14" t="n">
-        <v>51.5</v>
+        <v>41</v>
       </c>
       <c r="K14" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1049,10 +1014,10 @@
         <v>30</v>
       </c>
       <c r="E15" t="n">
-        <v>-13</v>
+        <v>5.6</v>
       </c>
       <c r="F15" t="n">
-        <v>44.2</v>
+        <v>38.6</v>
       </c>
       <c r="G15" t="s">
         <v>15</v>
@@ -1061,13 +1026,13 @@
         <v>18</v>
       </c>
       <c r="I15" t="n">
-        <v>-14</v>
+        <v>3.5</v>
       </c>
       <c r="J15" t="n">
-        <v>51.5</v>
+        <v>41</v>
       </c>
       <c r="K15" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1087,10 +1052,10 @@
         <v>30</v>
       </c>
       <c r="E16" t="n">
-        <v>-6.5</v>
+        <v>2.8</v>
       </c>
       <c r="F16" t="n">
-        <v>22.1</v>
+        <v>19.3</v>
       </c>
       <c r="G16" t="s">
         <v>19</v>
@@ -1099,13 +1064,13 @@
         <v>16</v>
       </c>
       <c r="I16" t="n">
-        <v>-14</v>
+        <v>3.5</v>
       </c>
       <c r="J16" t="n">
-        <v>51.5</v>
+        <v>41</v>
       </c>
       <c r="K16" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1125,10 +1090,10 @@
         <v>30</v>
       </c>
       <c r="E17" t="n">
-        <v>-6.5</v>
+        <v>2.8</v>
       </c>
       <c r="F17" t="n">
-        <v>22.1</v>
+        <v>19.3</v>
       </c>
       <c r="G17" t="s">
         <v>19</v>
@@ -1137,13 +1102,13 @@
         <v>18</v>
       </c>
       <c r="I17" t="n">
-        <v>-14</v>
+        <v>3.5</v>
       </c>
       <c r="J17" t="n">
-        <v>51.5</v>
+        <v>41</v>
       </c>
       <c r="K17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1154,19 +1119,19 @@
         <v>46228</v>
       </c>
       <c r="B18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" t="s">
         <v>32</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>33</v>
       </c>
-      <c r="D18" t="s">
-        <v>34</v>
-      </c>
       <c r="E18" t="n">
-        <v>5.6</v>
+        <v>-2.1</v>
       </c>
       <c r="F18" t="n">
-        <v>38.6</v>
+        <v>45.1</v>
       </c>
       <c r="G18" t="s">
         <v>15</v>
@@ -1175,13 +1140,13 @@
         <v>16</v>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="J18" t="n">
-        <v>42.5</v>
+        <v>48.5</v>
       </c>
       <c r="K18" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1192,19 +1157,19 @@
         <v>46228</v>
       </c>
       <c r="B19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" t="s">
         <v>32</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>33</v>
       </c>
-      <c r="D19" t="s">
-        <v>34</v>
-      </c>
       <c r="E19" t="n">
-        <v>5.6</v>
+        <v>-2.1</v>
       </c>
       <c r="F19" t="n">
-        <v>38.6</v>
+        <v>45.1</v>
       </c>
       <c r="G19" t="s">
         <v>15</v>
@@ -1213,13 +1178,13 @@
         <v>18</v>
       </c>
       <c r="I19" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="J19" t="n">
-        <v>42.5</v>
+        <v>48.5</v>
       </c>
       <c r="K19" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1230,19 +1195,19 @@
         <v>46228</v>
       </c>
       <c r="B20" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" t="s">
         <v>32</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>33</v>
       </c>
-      <c r="D20" t="s">
-        <v>34</v>
-      </c>
       <c r="E20" t="n">
-        <v>2.8</v>
+        <v>-1.1</v>
       </c>
       <c r="F20" t="n">
-        <v>19.3</v>
+        <v>22.5</v>
       </c>
       <c r="G20" t="s">
         <v>19</v>
@@ -1251,13 +1216,13 @@
         <v>16</v>
       </c>
       <c r="I20" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="J20" t="n">
-        <v>42.5</v>
+        <v>48.5</v>
       </c>
       <c r="K20" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1268,19 +1233,19 @@
         <v>46228</v>
       </c>
       <c r="B21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" t="s">
         <v>32</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>33</v>
       </c>
-      <c r="D21" t="s">
-        <v>34</v>
-      </c>
       <c r="E21" t="n">
-        <v>2.8</v>
+        <v>-1.1</v>
       </c>
       <c r="F21" t="n">
-        <v>19.3</v>
+        <v>22.5</v>
       </c>
       <c r="G21" t="s">
         <v>19</v>
@@ -1289,13 +1254,13 @@
         <v>18</v>
       </c>
       <c r="I21" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="J21" t="n">
-        <v>42.5</v>
+        <v>48.5</v>
       </c>
       <c r="K21" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -1303,7 +1268,7 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B22" t="s">
         <v>35</v>
@@ -1315,10 +1280,10 @@
         <v>37</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.4</v>
+        <v>-0.8</v>
       </c>
       <c r="F22" t="n">
-        <v>45.1</v>
+        <v>42.9</v>
       </c>
       <c r="G22" t="s">
         <v>15</v>
@@ -1327,10 +1292,10 @@
         <v>16</v>
       </c>
       <c r="I22" t="n">
-        <v>2.5</v>
+        <v>-1</v>
       </c>
       <c r="J22" t="n">
-        <v>48.5</v>
+        <v>47</v>
       </c>
       <c r="K22" t="s">
         <v>38</v>
@@ -1341,7 +1306,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B23" t="s">
         <v>35</v>
@@ -1353,10 +1318,10 @@
         <v>37</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.4</v>
+        <v>-0.8</v>
       </c>
       <c r="F23" t="n">
-        <v>45.1</v>
+        <v>42.9</v>
       </c>
       <c r="G23" t="s">
         <v>15</v>
@@ -1365,10 +1330,10 @@
         <v>18</v>
       </c>
       <c r="I23" t="n">
-        <v>2.5</v>
+        <v>-1</v>
       </c>
       <c r="J23" t="n">
-        <v>48.5</v>
+        <v>47</v>
       </c>
       <c r="K23" t="s">
         <v>38</v>
@@ -1379,7 +1344,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B24" t="s">
         <v>35</v>
@@ -1391,10 +1356,10 @@
         <v>37</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.2</v>
+        <v>-0.4</v>
       </c>
       <c r="F24" t="n">
-        <v>22.5</v>
+        <v>21.5</v>
       </c>
       <c r="G24" t="s">
         <v>19</v>
@@ -1403,10 +1368,10 @@
         <v>16</v>
       </c>
       <c r="I24" t="n">
-        <v>2.5</v>
+        <v>-1</v>
       </c>
       <c r="J24" t="n">
-        <v>48.5</v>
+        <v>47</v>
       </c>
       <c r="K24" t="s">
         <v>38</v>
@@ -1417,7 +1382,7 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B25" t="s">
         <v>35</v>
@@ -1429,10 +1394,10 @@
         <v>37</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.2</v>
+        <v>-0.4</v>
       </c>
       <c r="F25" t="n">
-        <v>22.5</v>
+        <v>21.5</v>
       </c>
       <c r="G25" t="s">
         <v>19</v>
@@ -1441,10 +1406,10 @@
         <v>18</v>
       </c>
       <c r="I25" t="n">
-        <v>2.5</v>
+        <v>-1</v>
       </c>
       <c r="J25" t="n">
-        <v>48.5</v>
+        <v>47</v>
       </c>
       <c r="K25" t="s">
         <v>38</v>
@@ -1467,10 +1432,10 @@
         <v>41</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.6</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>42.9</v>
+        <v>42.5</v>
       </c>
       <c r="G26" t="s">
         <v>15</v>
@@ -1479,10 +1444,10 @@
         <v>16</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J26" t="n">
-        <v>46.5</v>
+        <v>47</v>
       </c>
       <c r="K26" t="s">
         <v>42</v>
@@ -1505,10 +1470,10 @@
         <v>41</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.6</v>
+        <v>2</v>
       </c>
       <c r="F27" t="n">
-        <v>42.9</v>
+        <v>42.5</v>
       </c>
       <c r="G27" t="s">
         <v>15</v>
@@ -1517,10 +1482,10 @@
         <v>18</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J27" t="n">
-        <v>46.5</v>
+        <v>47</v>
       </c>
       <c r="K27" t="s">
         <v>42</v>
@@ -1543,10 +1508,10 @@
         <v>41</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.3</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>21.5</v>
+        <v>21.2</v>
       </c>
       <c r="G28" t="s">
         <v>19</v>
@@ -1555,10 +1520,10 @@
         <v>16</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J28" t="n">
-        <v>46.5</v>
+        <v>47</v>
       </c>
       <c r="K28" t="s">
         <v>42</v>
@@ -1581,10 +1546,10 @@
         <v>41</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.3</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>21.5</v>
+        <v>21.2</v>
       </c>
       <c r="G29" t="s">
         <v>19</v>
@@ -1593,10 +1558,10 @@
         <v>18</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J29" t="n">
-        <v>46.5</v>
+        <v>47</v>
       </c>
       <c r="K29" t="s">
         <v>42</v>
@@ -1607,22 +1572,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46229</v>
+        <v>46233</v>
       </c>
       <c r="B30" t="s">
         <v>43</v>
       </c>
       <c r="C30" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D30" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="F30" t="n">
-        <v>42.5</v>
+        <v>43.9</v>
       </c>
       <c r="G30" t="s">
         <v>15</v>
@@ -1631,13 +1596,13 @@
         <v>16</v>
       </c>
       <c r="I30" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="J30" t="n">
         <v>47.5</v>
       </c>
       <c r="K30" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -1645,22 +1610,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46229</v>
+        <v>46233</v>
       </c>
       <c r="B31" t="s">
         <v>43</v>
       </c>
       <c r="C31" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D31" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="F31" t="n">
-        <v>42.5</v>
+        <v>43.9</v>
       </c>
       <c r="G31" t="s">
         <v>15</v>
@@ -1669,13 +1634,13 @@
         <v>18</v>
       </c>
       <c r="I31" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="J31" t="n">
         <v>47.5</v>
       </c>
       <c r="K31" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -1683,22 +1648,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46229</v>
+        <v>46233</v>
       </c>
       <c r="B32" t="s">
         <v>43</v>
       </c>
       <c r="C32" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D32" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="F32" t="n">
-        <v>21.2</v>
+        <v>22</v>
       </c>
       <c r="G32" t="s">
         <v>19</v>
@@ -1707,13 +1672,13 @@
         <v>16</v>
       </c>
       <c r="I32" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="J32" t="n">
         <v>47.5</v>
       </c>
       <c r="K32" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -1721,22 +1686,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46229</v>
+        <v>46233</v>
       </c>
       <c r="B33" t="s">
         <v>43</v>
       </c>
       <c r="C33" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D33" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="F33" t="n">
-        <v>21.2</v>
+        <v>22</v>
       </c>
       <c r="G33" t="s">
         <v>19</v>
@@ -1745,13 +1710,13 @@
         <v>18</v>
       </c>
       <c r="I33" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="J33" t="n">
         <v>47.5</v>
       </c>
       <c r="K33" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -1759,7 +1724,7 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B34" t="s">
         <v>12</v>
@@ -1768,13 +1733,13 @@
         <v>36</v>
       </c>
       <c r="D34" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="E34" t="n">
-        <v>3</v>
+        <v>8.7</v>
       </c>
       <c r="F34" t="n">
-        <v>43.9</v>
+        <v>45</v>
       </c>
       <c r="G34" t="s">
         <v>15</v>
@@ -1782,18 +1747,22 @@
       <c r="H34" t="s">
         <v>16</v>
       </c>
-      <c r="I34"/>
-      <c r="J34"/>
+      <c r="I34" t="n">
+        <v>10</v>
+      </c>
+      <c r="J34" t="n">
+        <v>49.5</v>
+      </c>
       <c r="K34" t="s">
         <v>38</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B35" t="s">
         <v>12</v>
@@ -1802,13 +1771,13 @@
         <v>36</v>
       </c>
       <c r="D35" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>8.7</v>
       </c>
       <c r="F35" t="n">
-        <v>43.9</v>
+        <v>44.5</v>
       </c>
       <c r="G35" t="s">
         <v>15</v>
@@ -1816,18 +1785,22 @@
       <c r="H35" t="s">
         <v>18</v>
       </c>
-      <c r="I35"/>
-      <c r="J35"/>
+      <c r="I35" t="n">
+        <v>10</v>
+      </c>
+      <c r="J35" t="n">
+        <v>49.5</v>
+      </c>
       <c r="K35" t="s">
         <v>38</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B36" t="s">
         <v>12</v>
@@ -1836,13 +1809,13 @@
         <v>36</v>
       </c>
       <c r="D36" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="E36" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="F36" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="G36" t="s">
         <v>19</v>
@@ -1850,18 +1823,22 @@
       <c r="H36" t="s">
         <v>16</v>
       </c>
-      <c r="I36"/>
-      <c r="J36"/>
+      <c r="I36" t="n">
+        <v>10</v>
+      </c>
+      <c r="J36" t="n">
+        <v>49.5</v>
+      </c>
       <c r="K36" t="s">
         <v>38</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B37" t="s">
         <v>12</v>
@@ -1870,13 +1847,13 @@
         <v>36</v>
       </c>
       <c r="D37" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="E37" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="F37" t="n">
-        <v>22</v>
+        <v>22.3</v>
       </c>
       <c r="G37" t="s">
         <v>19</v>
@@ -1884,12 +1861,152 @@
       <c r="H37" t="s">
         <v>18</v>
       </c>
-      <c r="I37"/>
-      <c r="J37"/>
+      <c r="I37" t="n">
+        <v>10</v>
+      </c>
+      <c r="J37" t="n">
+        <v>49.5</v>
+      </c>
       <c r="K37" t="s">
         <v>38</v>
       </c>
       <c r="L37" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B38" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" t="s">
+        <v>22</v>
+      </c>
+      <c r="D38" t="s">
+        <v>29</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="F38" t="n">
+        <v>39</v>
+      </c>
+      <c r="G38" t="s">
+        <v>15</v>
+      </c>
+      <c r="H38" t="s">
+        <v>16</v>
+      </c>
+      <c r="I38"/>
+      <c r="J38"/>
+      <c r="K38" t="s">
+        <v>45</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B39" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" t="s">
+        <v>22</v>
+      </c>
+      <c r="D39" t="s">
+        <v>29</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="F39" t="n">
+        <v>39</v>
+      </c>
+      <c r="G39" t="s">
+        <v>15</v>
+      </c>
+      <c r="H39" t="s">
+        <v>18</v>
+      </c>
+      <c r="I39"/>
+      <c r="J39"/>
+      <c r="K39" t="s">
+        <v>45</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B40" t="s">
+        <v>20</v>
+      </c>
+      <c r="C40" t="s">
+        <v>22</v>
+      </c>
+      <c r="D40" t="s">
+        <v>29</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="F40" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G40" t="s">
+        <v>19</v>
+      </c>
+      <c r="H40" t="s">
+        <v>16</v>
+      </c>
+      <c r="I40"/>
+      <c r="J40"/>
+      <c r="K40" t="s">
+        <v>45</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B41" t="s">
+        <v>20</v>
+      </c>
+      <c r="C41" t="s">
+        <v>22</v>
+      </c>
+      <c r="D41" t="s">
+        <v>29</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="F41" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G41" t="s">
+        <v>19</v>
+      </c>
+      <c r="H41" t="s">
+        <v>18</v>
+      </c>
+      <c r="I41"/>
+      <c r="J41"/>
+      <c r="K41" t="s">
+        <v>45</v>
+      </c>
+      <c r="L41" t="n">
         <v>0</v>
       </c>
     </row>

--- a/files/NRL_upcoming_projections.xlsx
+++ b/files/NRL_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -50,106 +50,112 @@
     <t xml:space="preserve">Forecast Rain mm</t>
   </si>
   <si>
+    <t xml:space="preserve">19:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north queensland cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Rain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Queensland Country Bank Stadium, Townsville</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1H</t>
+  </si>
+  <si>
     <t xml:space="preserve">18:00</t>
   </si>
   <si>
+    <t xml:space="preserve">st george-illawarra dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dolphins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WIN Stadium, Wollongong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melbourne storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AAMI Park, Melbourne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cbus Super Stadium, Gold Coast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penrith panthers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glen Willow Stadium, Mudgee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
     <t xml:space="preserve">newcastle knights</t>
   </si>
   <si>
-    <t xml:space="preserve">sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Rain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">McDonald Jones Stadium, Newcastle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:00</t>
+    <t xml:space="preserve">Suncorp Stadium, Brisbane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
   </si>
   <si>
     <t xml:space="preserve">south sydney rabbitohs</t>
   </si>
   <si>
-    <t xml:space="preserve">melbourne storm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accor Stadium, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberra raiders</t>
+    <t xml:space="preserve">Sharks Stadium, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:05</t>
   </si>
   <si>
     <t xml:space="preserve">wests tigers</t>
   </si>
   <si>
-    <t xml:space="preserve">GIO Stadium, Canberra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north queensland cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Queensland Country Bank Stadium, Townsville</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st george-illawarra dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WIN Stadium, Wollongong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manly-warringah sea eagles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 Pines Park, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AAMI Park, Melbourne</t>
+    <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leichhardt Oval, Sydney</t>
   </si>
 </sst>
 </file>
@@ -488,7 +494,7 @@
   <cols>
     <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="5.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="29.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="27.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="29.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="15.71" hidden="0" customWidth="1"/>
@@ -540,7 +546,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -552,10 +558,10 @@
         <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="F2" t="n">
-        <v>42.2</v>
+        <v>43.9</v>
       </c>
       <c r="G2" t="s">
         <v>15</v>
@@ -563,8 +569,12 @@
       <c r="H2" t="s">
         <v>16</v>
       </c>
-      <c r="I2"/>
-      <c r="J2"/>
+      <c r="I2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2" t="n">
+        <v>47.5</v>
+      </c>
       <c r="K2" t="s">
         <v>17</v>
       </c>
@@ -574,7 +584,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -586,10 +596,10 @@
         <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="F3" t="n">
-        <v>42.2</v>
+        <v>43.9</v>
       </c>
       <c r="G3" t="s">
         <v>15</v>
@@ -597,8 +607,12 @@
       <c r="H3" t="s">
         <v>18</v>
       </c>
-      <c r="I3"/>
-      <c r="J3"/>
+      <c r="I3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J3" t="n">
+        <v>47.5</v>
+      </c>
       <c r="K3" t="s">
         <v>17</v>
       </c>
@@ -608,7 +622,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -623,7 +637,7 @@
         <v>1.6</v>
       </c>
       <c r="F4" t="n">
-        <v>21.1</v>
+        <v>22</v>
       </c>
       <c r="G4" t="s">
         <v>19</v>
@@ -631,8 +645,12 @@
       <c r="H4" t="s">
         <v>16</v>
       </c>
-      <c r="I4"/>
-      <c r="J4"/>
+      <c r="I4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>47.5</v>
+      </c>
       <c r="K4" t="s">
         <v>17</v>
       </c>
@@ -642,7 +660,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -657,7 +675,7 @@
         <v>1.6</v>
       </c>
       <c r="F5" t="n">
-        <v>21.1</v>
+        <v>22</v>
       </c>
       <c r="G5" t="s">
         <v>19</v>
@@ -665,8 +683,12 @@
       <c r="H5" t="s">
         <v>18</v>
       </c>
-      <c r="I5"/>
-      <c r="J5"/>
+      <c r="I5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>47.5</v>
+      </c>
       <c r="K5" t="s">
         <v>17</v>
       </c>
@@ -676,7 +698,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
@@ -688,10 +710,10 @@
         <v>22</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1</v>
+        <v>9.2</v>
       </c>
       <c r="F6" t="n">
-        <v>44.4</v>
+        <v>45</v>
       </c>
       <c r="G6" t="s">
         <v>15</v>
@@ -699,18 +721,22 @@
       <c r="H6" t="s">
         <v>16</v>
       </c>
-      <c r="I6"/>
-      <c r="J6"/>
+      <c r="I6" t="n">
+        <v>10</v>
+      </c>
+      <c r="J6" t="n">
+        <v>49.5</v>
+      </c>
       <c r="K6" t="s">
         <v>23</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B7" t="s">
         <v>20</v>
@@ -722,10 +748,10 @@
         <v>22</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1</v>
+        <v>9.2</v>
       </c>
       <c r="F7" t="n">
-        <v>44.4</v>
+        <v>44.9</v>
       </c>
       <c r="G7" t="s">
         <v>15</v>
@@ -733,18 +759,22 @@
       <c r="H7" t="s">
         <v>18</v>
       </c>
-      <c r="I7"/>
-      <c r="J7"/>
+      <c r="I7" t="n">
+        <v>10</v>
+      </c>
+      <c r="J7" t="n">
+        <v>49.5</v>
+      </c>
       <c r="K7" t="s">
         <v>23</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B8" t="s">
         <v>20</v>
@@ -756,10 +786,10 @@
         <v>22</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6</v>
+        <v>4.6</v>
       </c>
       <c r="F8" t="n">
-        <v>22.2</v>
+        <v>22.5</v>
       </c>
       <c r="G8" t="s">
         <v>19</v>
@@ -767,18 +797,22 @@
       <c r="H8" t="s">
         <v>16</v>
       </c>
-      <c r="I8"/>
-      <c r="J8"/>
+      <c r="I8" t="n">
+        <v>10</v>
+      </c>
+      <c r="J8" t="n">
+        <v>49.5</v>
+      </c>
       <c r="K8" t="s">
         <v>23</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B9" t="s">
         <v>20</v>
@@ -790,10 +824,10 @@
         <v>22</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6</v>
+        <v>4.6</v>
       </c>
       <c r="F9" t="n">
-        <v>22.2</v>
+        <v>22.5</v>
       </c>
       <c r="G9" t="s">
         <v>19</v>
@@ -801,18 +835,22 @@
       <c r="H9" t="s">
         <v>18</v>
       </c>
-      <c r="I9"/>
-      <c r="J9"/>
+      <c r="I9" t="n">
+        <v>10</v>
+      </c>
+      <c r="J9" t="n">
+        <v>49.5</v>
+      </c>
       <c r="K9" t="s">
         <v>23</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
@@ -824,10 +862,10 @@
         <v>26</v>
       </c>
       <c r="E10" t="n">
-        <v>-11.8</v>
+        <v>-7.4</v>
       </c>
       <c r="F10" t="n">
-        <v>44.2</v>
+        <v>39</v>
       </c>
       <c r="G10" t="s">
         <v>15</v>
@@ -835,12 +873,8 @@
       <c r="H10" t="s">
         <v>16</v>
       </c>
-      <c r="I10" t="n">
-        <v>-14.5</v>
-      </c>
-      <c r="J10" t="n">
-        <v>50.5</v>
-      </c>
+      <c r="I10"/>
+      <c r="J10"/>
       <c r="K10" t="s">
         <v>27</v>
       </c>
@@ -850,7 +884,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c r="B11" t="s">
         <v>24</v>
@@ -862,10 +896,10 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>-11.8</v>
+        <v>-7.4</v>
       </c>
       <c r="F11" t="n">
-        <v>44.2</v>
+        <v>39</v>
       </c>
       <c r="G11" t="s">
         <v>15</v>
@@ -873,12 +907,8 @@
       <c r="H11" t="s">
         <v>18</v>
       </c>
-      <c r="I11" t="n">
-        <v>-14.5</v>
-      </c>
-      <c r="J11" t="n">
-        <v>50.5</v>
-      </c>
+      <c r="I11"/>
+      <c r="J11"/>
       <c r="K11" t="s">
         <v>27</v>
       </c>
@@ -888,7 +918,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c r="B12" t="s">
         <v>24</v>
@@ -900,10 +930,10 @@
         <v>26</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.9</v>
+        <v>-3.7</v>
       </c>
       <c r="F12" t="n">
-        <v>22.1</v>
+        <v>19.5</v>
       </c>
       <c r="G12" t="s">
         <v>19</v>
@@ -911,12 +941,8 @@
       <c r="H12" t="s">
         <v>16</v>
       </c>
-      <c r="I12" t="n">
-        <v>-14.5</v>
-      </c>
-      <c r="J12" t="n">
-        <v>50.5</v>
-      </c>
+      <c r="I12"/>
+      <c r="J12"/>
       <c r="K12" t="s">
         <v>27</v>
       </c>
@@ -926,7 +952,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c r="B13" t="s">
         <v>24</v>
@@ -938,10 +964,10 @@
         <v>26</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.9</v>
+        <v>-3.7</v>
       </c>
       <c r="F13" t="n">
-        <v>22.1</v>
+        <v>19.5</v>
       </c>
       <c r="G13" t="s">
         <v>19</v>
@@ -949,12 +975,8 @@
       <c r="H13" t="s">
         <v>18</v>
       </c>
-      <c r="I13" t="n">
-        <v>-14.5</v>
-      </c>
-      <c r="J13" t="n">
-        <v>50.5</v>
-      </c>
+      <c r="I13"/>
+      <c r="J13"/>
       <c r="K13" t="s">
         <v>27</v>
       </c>
@@ -964,7 +986,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B14" t="s">
         <v>28</v>
@@ -979,7 +1001,7 @@
         <v>5.6</v>
       </c>
       <c r="F14" t="n">
-        <v>38.6</v>
+        <v>42.5</v>
       </c>
       <c r="G14" t="s">
         <v>15</v>
@@ -988,21 +1010,21 @@
         <v>16</v>
       </c>
       <c r="I14" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="J14" t="n">
-        <v>41</v>
+        <v>49.5</v>
       </c>
       <c r="K14" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B15" t="s">
         <v>28</v>
@@ -1017,7 +1039,7 @@
         <v>5.6</v>
       </c>
       <c r="F15" t="n">
-        <v>38.6</v>
+        <v>41.5</v>
       </c>
       <c r="G15" t="s">
         <v>15</v>
@@ -1026,21 +1048,21 @@
         <v>18</v>
       </c>
       <c r="I15" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="J15" t="n">
-        <v>41</v>
+        <v>49.5</v>
       </c>
       <c r="K15" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B16" t="s">
         <v>28</v>
@@ -1055,7 +1077,7 @@
         <v>2.8</v>
       </c>
       <c r="F16" t="n">
-        <v>19.3</v>
+        <v>21.2</v>
       </c>
       <c r="G16" t="s">
         <v>19</v>
@@ -1064,21 +1086,21 @@
         <v>16</v>
       </c>
       <c r="I16" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="J16" t="n">
-        <v>41</v>
+        <v>49.5</v>
       </c>
       <c r="K16" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B17" t="s">
         <v>28</v>
@@ -1093,7 +1115,7 @@
         <v>2.8</v>
       </c>
       <c r="F17" t="n">
-        <v>19.3</v>
+        <v>20.8</v>
       </c>
       <c r="G17" t="s">
         <v>19</v>
@@ -1102,36 +1124,36 @@
         <v>18</v>
       </c>
       <c r="I17" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="J17" t="n">
-        <v>41</v>
+        <v>49.5</v>
       </c>
       <c r="K17" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.1</v>
+        <v>-9.5</v>
       </c>
       <c r="F18" t="n">
-        <v>45.1</v>
+        <v>40.6</v>
       </c>
       <c r="G18" t="s">
         <v>15</v>
@@ -1140,13 +1162,13 @@
         <v>16</v>
       </c>
       <c r="I18" t="n">
-        <v>4.5</v>
+        <v>-10.5</v>
       </c>
       <c r="J18" t="n">
-        <v>48.5</v>
+        <v>42.5</v>
       </c>
       <c r="K18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1154,22 +1176,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1</v>
+        <v>-9.5</v>
       </c>
       <c r="F19" t="n">
-        <v>45.1</v>
+        <v>40.6</v>
       </c>
       <c r="G19" t="s">
         <v>15</v>
@@ -1178,13 +1200,13 @@
         <v>18</v>
       </c>
       <c r="I19" t="n">
-        <v>4.5</v>
+        <v>-10.5</v>
       </c>
       <c r="J19" t="n">
-        <v>48.5</v>
+        <v>42.5</v>
       </c>
       <c r="K19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1192,22 +1214,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1</v>
+        <v>-4.8</v>
       </c>
       <c r="F20" t="n">
-        <v>22.5</v>
+        <v>20.3</v>
       </c>
       <c r="G20" t="s">
         <v>19</v>
@@ -1216,13 +1238,13 @@
         <v>16</v>
       </c>
       <c r="I20" t="n">
-        <v>4.5</v>
+        <v>-10.5</v>
       </c>
       <c r="J20" t="n">
-        <v>48.5</v>
+        <v>42.5</v>
       </c>
       <c r="K20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1230,22 +1252,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1</v>
+        <v>-4.8</v>
       </c>
       <c r="F21" t="n">
-        <v>22.5</v>
+        <v>20.3</v>
       </c>
       <c r="G21" t="s">
         <v>19</v>
@@ -1254,13 +1276,13 @@
         <v>18</v>
       </c>
       <c r="I21" t="n">
-        <v>4.5</v>
+        <v>-10.5</v>
       </c>
       <c r="J21" t="n">
-        <v>48.5</v>
+        <v>42.5</v>
       </c>
       <c r="K21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -1268,22 +1290,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B22" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D22" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8</v>
+        <v>-4.6</v>
       </c>
       <c r="F22" t="n">
-        <v>42.9</v>
+        <v>43.4</v>
       </c>
       <c r="G22" t="s">
         <v>15</v>
@@ -1291,34 +1313,30 @@
       <c r="H22" t="s">
         <v>16</v>
       </c>
-      <c r="I22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J22" t="n">
-        <v>47</v>
-      </c>
+      <c r="I22"/>
+      <c r="J22"/>
       <c r="K22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D23" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8</v>
+        <v>-4.6</v>
       </c>
       <c r="F23" t="n">
         <v>42.9</v>
@@ -1329,37 +1347,33 @@
       <c r="H23" t="s">
         <v>18</v>
       </c>
-      <c r="I23" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J23" t="n">
-        <v>47</v>
-      </c>
+      <c r="I23"/>
+      <c r="J23"/>
       <c r="K23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B24" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.4</v>
+        <v>-2.3</v>
       </c>
       <c r="F24" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="G24" t="s">
         <v>19</v>
@@ -1367,34 +1381,30 @@
       <c r="H24" t="s">
         <v>16</v>
       </c>
-      <c r="I24" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J24" t="n">
-        <v>47</v>
-      </c>
+      <c r="I24"/>
+      <c r="J24"/>
       <c r="K24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D25" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.4</v>
+        <v>-2.3</v>
       </c>
       <c r="F25" t="n">
         <v>21.5</v>
@@ -1405,37 +1415,33 @@
       <c r="H25" t="s">
         <v>18</v>
       </c>
-      <c r="I25" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J25" t="n">
-        <v>47</v>
-      </c>
+      <c r="I25"/>
+      <c r="J25"/>
       <c r="K25" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B26" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C26" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D26" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>-6.7</v>
       </c>
       <c r="F26" t="n">
-        <v>42.5</v>
+        <v>46</v>
       </c>
       <c r="G26" t="s">
         <v>15</v>
@@ -1444,13 +1450,13 @@
         <v>16</v>
       </c>
       <c r="I26" t="n">
-        <v>3.5</v>
+        <v>-7.5</v>
       </c>
       <c r="J26" t="n">
-        <v>47</v>
+        <v>48.5</v>
       </c>
       <c r="K26" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -1458,22 +1464,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B27" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>-6.7</v>
       </c>
       <c r="F27" t="n">
-        <v>42.5</v>
+        <v>46</v>
       </c>
       <c r="G27" t="s">
         <v>15</v>
@@ -1482,13 +1488,13 @@
         <v>18</v>
       </c>
       <c r="I27" t="n">
-        <v>3.5</v>
+        <v>-7.5</v>
       </c>
       <c r="J27" t="n">
-        <v>47</v>
+        <v>48.5</v>
       </c>
       <c r="K27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -1496,22 +1502,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C28" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D28" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>-3.3</v>
       </c>
       <c r="F28" t="n">
-        <v>21.2</v>
+        <v>23</v>
       </c>
       <c r="G28" t="s">
         <v>19</v>
@@ -1520,13 +1526,13 @@
         <v>16</v>
       </c>
       <c r="I28" t="n">
-        <v>3.5</v>
+        <v>-7.5</v>
       </c>
       <c r="J28" t="n">
-        <v>47</v>
+        <v>48.5</v>
       </c>
       <c r="K28" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -1534,22 +1540,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B29" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C29" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D29" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>-3.3</v>
       </c>
       <c r="F29" t="n">
-        <v>21.2</v>
+        <v>23</v>
       </c>
       <c r="G29" t="s">
         <v>19</v>
@@ -1558,13 +1564,13 @@
         <v>18</v>
       </c>
       <c r="I29" t="n">
-        <v>3.5</v>
+        <v>-7.5</v>
       </c>
       <c r="J29" t="n">
-        <v>47</v>
+        <v>48.5</v>
       </c>
       <c r="K29" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -1572,22 +1578,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46233</v>
+        <v>46236</v>
       </c>
       <c r="B30" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D30" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="E30" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="F30" t="n">
-        <v>43.9</v>
+        <v>44.4</v>
       </c>
       <c r="G30" t="s">
         <v>15</v>
@@ -1596,36 +1602,36 @@
         <v>16</v>
       </c>
       <c r="I30" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="J30" t="n">
-        <v>47.5</v>
+        <v>48.5</v>
       </c>
       <c r="K30" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46233</v>
+        <v>46236</v>
       </c>
       <c r="B31" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C31" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D31" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="E31" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="F31" t="n">
-        <v>43.9</v>
+        <v>44.3</v>
       </c>
       <c r="G31" t="s">
         <v>15</v>
@@ -1634,36 +1640,36 @@
         <v>18</v>
       </c>
       <c r="I31" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="J31" t="n">
-        <v>47.5</v>
+        <v>48.5</v>
       </c>
       <c r="K31" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46233</v>
+        <v>46236</v>
       </c>
       <c r="B32" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C32" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D32" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="E32" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="G32" t="s">
         <v>19</v>
@@ -1672,36 +1678,36 @@
         <v>16</v>
       </c>
       <c r="I32" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="J32" t="n">
-        <v>47.5</v>
+        <v>48.5</v>
       </c>
       <c r="K32" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46233</v>
+        <v>46236</v>
       </c>
       <c r="B33" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C33" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D33" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="E33" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="G33" t="s">
         <v>19</v>
@@ -1710,304 +1716,16 @@
         <v>18</v>
       </c>
       <c r="I33" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="J33" t="n">
-        <v>47.5</v>
+        <v>48.5</v>
       </c>
       <c r="K33" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="B34" t="s">
-        <v>12</v>
-      </c>
-      <c r="C34" t="s">
-        <v>36</v>
-      </c>
-      <c r="D34" t="s">
-        <v>44</v>
-      </c>
-      <c r="E34" t="n">
-        <v>8.7</v>
-      </c>
-      <c r="F34" t="n">
-        <v>45</v>
-      </c>
-      <c r="G34" t="s">
-        <v>15</v>
-      </c>
-      <c r="H34" t="s">
-        <v>16</v>
-      </c>
-      <c r="I34" t="n">
-        <v>10</v>
-      </c>
-      <c r="J34" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="K34" t="s">
-        <v>38</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="B35" t="s">
-        <v>12</v>
-      </c>
-      <c r="C35" t="s">
-        <v>36</v>
-      </c>
-      <c r="D35" t="s">
-        <v>44</v>
-      </c>
-      <c r="E35" t="n">
-        <v>8.7</v>
-      </c>
-      <c r="F35" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="G35" t="s">
-        <v>15</v>
-      </c>
-      <c r="H35" t="s">
-        <v>18</v>
-      </c>
-      <c r="I35" t="n">
-        <v>10</v>
-      </c>
-      <c r="J35" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="K35" t="s">
-        <v>38</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="B36" t="s">
-        <v>12</v>
-      </c>
-      <c r="C36" t="s">
-        <v>36</v>
-      </c>
-      <c r="D36" t="s">
-        <v>44</v>
-      </c>
-      <c r="E36" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F36" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="G36" t="s">
-        <v>19</v>
-      </c>
-      <c r="H36" t="s">
-        <v>16</v>
-      </c>
-      <c r="I36" t="n">
-        <v>10</v>
-      </c>
-      <c r="J36" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="K36" t="s">
-        <v>38</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="B37" t="s">
-        <v>12</v>
-      </c>
-      <c r="C37" t="s">
-        <v>36</v>
-      </c>
-      <c r="D37" t="s">
-        <v>44</v>
-      </c>
-      <c r="E37" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F37" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="G37" t="s">
-        <v>19</v>
-      </c>
-      <c r="H37" t="s">
-        <v>18</v>
-      </c>
-      <c r="I37" t="n">
-        <v>10</v>
-      </c>
-      <c r="J37" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="K37" t="s">
-        <v>38</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="B38" t="s">
-        <v>20</v>
-      </c>
-      <c r="C38" t="s">
-        <v>22</v>
-      </c>
-      <c r="D38" t="s">
-        <v>29</v>
-      </c>
-      <c r="E38" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="F38" t="n">
-        <v>39</v>
-      </c>
-      <c r="G38" t="s">
-        <v>15</v>
-      </c>
-      <c r="H38" t="s">
-        <v>16</v>
-      </c>
-      <c r="I38"/>
-      <c r="J38"/>
-      <c r="K38" t="s">
-        <v>45</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="B39" t="s">
-        <v>20</v>
-      </c>
-      <c r="C39" t="s">
-        <v>22</v>
-      </c>
-      <c r="D39" t="s">
-        <v>29</v>
-      </c>
-      <c r="E39" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="F39" t="n">
-        <v>39</v>
-      </c>
-      <c r="G39" t="s">
-        <v>15</v>
-      </c>
-      <c r="H39" t="s">
-        <v>18</v>
-      </c>
-      <c r="I39"/>
-      <c r="J39"/>
-      <c r="K39" t="s">
-        <v>45</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="B40" t="s">
-        <v>20</v>
-      </c>
-      <c r="C40" t="s">
-        <v>22</v>
-      </c>
-      <c r="D40" t="s">
-        <v>29</v>
-      </c>
-      <c r="E40" t="n">
-        <v>-4.2</v>
-      </c>
-      <c r="F40" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="G40" t="s">
-        <v>19</v>
-      </c>
-      <c r="H40" t="s">
-        <v>16</v>
-      </c>
-      <c r="I40"/>
-      <c r="J40"/>
-      <c r="K40" t="s">
-        <v>45</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="B41" t="s">
-        <v>20</v>
-      </c>
-      <c r="C41" t="s">
-        <v>22</v>
-      </c>
-      <c r="D41" t="s">
-        <v>29</v>
-      </c>
-      <c r="E41" t="n">
-        <v>-4.2</v>
-      </c>
-      <c r="F41" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="G41" t="s">
-        <v>19</v>
-      </c>
-      <c r="H41" t="s">
-        <v>18</v>
-      </c>
-      <c r="I41"/>
-      <c r="J41"/>
-      <c r="K41" t="s">
-        <v>45</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_upcoming_projections.xlsx
+++ b/files/NRL_upcoming_projections.xlsx
@@ -558,7 +558,7 @@
         <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="F2" t="n">
         <v>43.9</v>
@@ -596,7 +596,7 @@
         <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="F3" t="n">
         <v>43.9</v>
@@ -634,7 +634,7 @@
         <v>14</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="F4" t="n">
         <v>22</v>
@@ -672,7 +672,7 @@
         <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="F5" t="n">
         <v>22</v>
@@ -710,7 +710,7 @@
         <v>22</v>
       </c>
       <c r="E6" t="n">
-        <v>9.2</v>
+        <v>7.7</v>
       </c>
       <c r="F6" t="n">
         <v>45</v>
@@ -731,7 +731,7 @@
         <v>23</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -748,10 +748,10 @@
         <v>22</v>
       </c>
       <c r="E7" t="n">
-        <v>9.2</v>
+        <v>7.7</v>
       </c>
       <c r="F7" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
       <c r="G7" t="s">
         <v>15</v>
@@ -769,7 +769,7 @@
         <v>23</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -786,7 +786,7 @@
         <v>22</v>
       </c>
       <c r="E8" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="F8" t="n">
         <v>22.5</v>
@@ -807,7 +807,7 @@
         <v>23</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -824,7 +824,7 @@
         <v>22</v>
       </c>
       <c r="E9" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="F9" t="n">
         <v>22.5</v>
@@ -845,7 +845,7 @@
         <v>23</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -862,7 +862,7 @@
         <v>26</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.4</v>
+        <v>-7.5</v>
       </c>
       <c r="F10" t="n">
         <v>39</v>
@@ -896,7 +896,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.4</v>
+        <v>-7.5</v>
       </c>
       <c r="F11" t="n">
         <v>39</v>
@@ -1319,7 +1319,7 @@
         <v>39</v>
       </c>
       <c r="L22" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="23">
@@ -1339,7 +1339,7 @@
         <v>-4.6</v>
       </c>
       <c r="F23" t="n">
-        <v>42.9</v>
+        <v>43.1</v>
       </c>
       <c r="G23" t="s">
         <v>15</v>
@@ -1353,7 +1353,7 @@
         <v>39</v>
       </c>
       <c r="L23" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="24">
@@ -1387,7 +1387,7 @@
         <v>39</v>
       </c>
       <c r="L24" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="25">
@@ -1421,7 +1421,7 @@
         <v>39</v>
       </c>
       <c r="L25" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="26">
@@ -1611,7 +1611,7 @@
         <v>47</v>
       </c>
       <c r="L30" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1631,7 +1631,7 @@
         <v>2.1</v>
       </c>
       <c r="F31" t="n">
-        <v>44.3</v>
+        <v>44.4</v>
       </c>
       <c r="G31" t="s">
         <v>15</v>
@@ -1649,7 +1649,7 @@
         <v>47</v>
       </c>
       <c r="L31" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1687,7 +1687,7 @@
         <v>47</v>
       </c>
       <c r="L32" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1707,7 +1707,7 @@
         <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="G33" t="s">
         <v>19</v>
@@ -1725,7 +1725,143 @@
         <v>47</v>
       </c>
       <c r="L33" t="n">
-        <v>0.1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B34" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" t="s">
+        <v>29</v>
+      </c>
+      <c r="D34" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F34" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="G34" t="s">
+        <v>15</v>
+      </c>
+      <c r="H34" t="s">
+        <v>16</v>
+      </c>
+      <c r="I34"/>
+      <c r="J34"/>
+      <c r="K34" t="s">
+        <v>31</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B35" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" t="s">
+        <v>29</v>
+      </c>
+      <c r="D35" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F35" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="G35" t="s">
+        <v>15</v>
+      </c>
+      <c r="H35" t="s">
+        <v>18</v>
+      </c>
+      <c r="I35"/>
+      <c r="J35"/>
+      <c r="K35" t="s">
+        <v>31</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B36" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" t="s">
+        <v>29</v>
+      </c>
+      <c r="D36" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F36" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="G36" t="s">
+        <v>19</v>
+      </c>
+      <c r="H36" t="s">
+        <v>16</v>
+      </c>
+      <c r="I36"/>
+      <c r="J36"/>
+      <c r="K36" t="s">
+        <v>31</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B37" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" t="s">
+        <v>29</v>
+      </c>
+      <c r="D37" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F37" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="G37" t="s">
+        <v>19</v>
+      </c>
+      <c r="H37" t="s">
+        <v>18</v>
+      </c>
+      <c r="I37"/>
+      <c r="J37"/>
+      <c r="K37" t="s">
+        <v>31</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_upcoming_projections.xlsx
+++ b/files/NRL_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -50,6 +50,102 @@
     <t xml:space="preserve">Forecast Rain mm</t>
   </si>
   <si>
+    <t xml:space="preserve">18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st george-illawarra dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dolphins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Rain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WIN Stadium, Wollongong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melbourne storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AAMI Park, Melbourne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cbus Super Stadium, Gold Coast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penrith panthers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glen Willow Stadium, Mudgee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suncorp Stadium, Brisbane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">south sydney rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sharks Stadium, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wests tigers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leichhardt Oval, Sydney</t>
+  </si>
+  <si>
     <t xml:space="preserve">19:50</t>
   </si>
   <si>
@@ -59,103 +155,10 @@
     <t xml:space="preserve">sydney roosters</t>
   </si>
   <si>
-    <t xml:space="preserve">FT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Rain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Queensland Country Bank Stadium, Townsville</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st george-illawarra dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WIN Stadium, Wollongong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">melbourne storm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AAMI Park, Melbourne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cbus Super Stadium, Gold Coast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penrith panthers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberra raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glen Willow Stadium, Mudgee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">newcastle knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suncorp Stadium, Brisbane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">south sydney rabbitohs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sharks Stadium, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wests tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leichhardt Oval, Sydney</t>
+    <t xml:space="preserve">Allianz Stadium, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Go Media Stadium, Auckland</t>
   </si>
 </sst>
 </file>
@@ -502,7 +505,7 @@
     <col min="8" max="8" width="16.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="19.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="20.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="43.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="30.71" hidden="0" customWidth="1"/>
     <col min="12" max="12" width="16.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
@@ -546,7 +549,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -558,10 +561,10 @@
         <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9</v>
+        <v>5.9</v>
       </c>
       <c r="F2" t="n">
-        <v>43.9</v>
+        <v>45</v>
       </c>
       <c r="G2" t="s">
         <v>15</v>
@@ -570,10 +573,10 @@
         <v>16</v>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J2" t="n">
-        <v>47.5</v>
+        <v>49.5</v>
       </c>
       <c r="K2" t="s">
         <v>17</v>
@@ -584,7 +587,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -596,10 +599,10 @@
         <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9</v>
+        <v>5.9</v>
       </c>
       <c r="F3" t="n">
-        <v>43.9</v>
+        <v>45</v>
       </c>
       <c r="G3" t="s">
         <v>15</v>
@@ -608,10 +611,10 @@
         <v>18</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J3" t="n">
-        <v>47.5</v>
+        <v>49.5</v>
       </c>
       <c r="K3" t="s">
         <v>17</v>
@@ -622,7 +625,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -634,10 +637,10 @@
         <v>14</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="G4" t="s">
         <v>19</v>
@@ -646,10 +649,10 @@
         <v>16</v>
       </c>
       <c r="I4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>47.5</v>
+        <v>49.5</v>
       </c>
       <c r="K4" t="s">
         <v>17</v>
@@ -660,7 +663,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -672,10 +675,10 @@
         <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="G5" t="s">
         <v>19</v>
@@ -684,10 +687,10 @@
         <v>18</v>
       </c>
       <c r="I5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>47.5</v>
+        <v>49.5</v>
       </c>
       <c r="K5" t="s">
         <v>17</v>
@@ -710,10 +713,10 @@
         <v>22</v>
       </c>
       <c r="E6" t="n">
-        <v>7.7</v>
+        <v>-6.2</v>
       </c>
       <c r="F6" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G6" t="s">
         <v>15</v>
@@ -721,12 +724,8 @@
       <c r="H6" t="s">
         <v>16</v>
       </c>
-      <c r="I6" t="n">
-        <v>10</v>
-      </c>
-      <c r="J6" t="n">
-        <v>49.5</v>
-      </c>
+      <c r="I6"/>
+      <c r="J6"/>
       <c r="K6" t="s">
         <v>23</v>
       </c>
@@ -748,10 +747,10 @@
         <v>22</v>
       </c>
       <c r="E7" t="n">
-        <v>7.7</v>
+        <v>-6.2</v>
       </c>
       <c r="F7" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G7" t="s">
         <v>15</v>
@@ -759,12 +758,8 @@
       <c r="H7" t="s">
         <v>18</v>
       </c>
-      <c r="I7" t="n">
-        <v>10</v>
-      </c>
-      <c r="J7" t="n">
-        <v>49.5</v>
-      </c>
+      <c r="I7"/>
+      <c r="J7"/>
       <c r="K7" t="s">
         <v>23</v>
       </c>
@@ -786,10 +781,10 @@
         <v>22</v>
       </c>
       <c r="E8" t="n">
-        <v>3.9</v>
+        <v>-3.1</v>
       </c>
       <c r="F8" t="n">
-        <v>22.5</v>
+        <v>19.5</v>
       </c>
       <c r="G8" t="s">
         <v>19</v>
@@ -797,12 +792,8 @@
       <c r="H8" t="s">
         <v>16</v>
       </c>
-      <c r="I8" t="n">
-        <v>10</v>
-      </c>
-      <c r="J8" t="n">
-        <v>49.5</v>
-      </c>
+      <c r="I8"/>
+      <c r="J8"/>
       <c r="K8" t="s">
         <v>23</v>
       </c>
@@ -824,10 +815,10 @@
         <v>22</v>
       </c>
       <c r="E9" t="n">
-        <v>3.9</v>
+        <v>-3.1</v>
       </c>
       <c r="F9" t="n">
-        <v>22.5</v>
+        <v>19.5</v>
       </c>
       <c r="G9" t="s">
         <v>19</v>
@@ -835,12 +826,8 @@
       <c r="H9" t="s">
         <v>18</v>
       </c>
-      <c r="I9" t="n">
-        <v>10</v>
-      </c>
-      <c r="J9" t="n">
-        <v>49.5</v>
-      </c>
+      <c r="I9"/>
+      <c r="J9"/>
       <c r="K9" t="s">
         <v>23</v>
       </c>
@@ -850,7 +837,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
@@ -862,10 +849,10 @@
         <v>26</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.5</v>
+        <v>6.7</v>
       </c>
       <c r="F10" t="n">
-        <v>39</v>
+        <v>42.5</v>
       </c>
       <c r="G10" t="s">
         <v>15</v>
@@ -873,18 +860,22 @@
       <c r="H10" t="s">
         <v>16</v>
       </c>
-      <c r="I10"/>
-      <c r="J10"/>
+      <c r="I10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>49.5</v>
+      </c>
       <c r="K10" t="s">
         <v>27</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B11" t="s">
         <v>24</v>
@@ -896,10 +887,10 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.5</v>
+        <v>6.7</v>
       </c>
       <c r="F11" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G11" t="s">
         <v>15</v>
@@ -907,18 +898,22 @@
       <c r="H11" t="s">
         <v>18</v>
       </c>
-      <c r="I11"/>
-      <c r="J11"/>
+      <c r="I11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>49.5</v>
+      </c>
       <c r="K11" t="s">
         <v>27</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B12" t="s">
         <v>24</v>
@@ -930,10 +925,10 @@
         <v>26</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7</v>
+        <v>3.3</v>
       </c>
       <c r="F12" t="n">
-        <v>19.5</v>
+        <v>21.2</v>
       </c>
       <c r="G12" t="s">
         <v>19</v>
@@ -941,18 +936,22 @@
       <c r="H12" t="s">
         <v>16</v>
       </c>
-      <c r="I12"/>
-      <c r="J12"/>
+      <c r="I12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>49.5</v>
+      </c>
       <c r="K12" t="s">
         <v>27</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B13" t="s">
         <v>24</v>
@@ -964,10 +963,10 @@
         <v>26</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.7</v>
+        <v>3.3</v>
       </c>
       <c r="F13" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="G13" t="s">
         <v>19</v>
@@ -975,13 +974,17 @@
       <c r="H13" t="s">
         <v>18</v>
       </c>
-      <c r="I13"/>
-      <c r="J13"/>
+      <c r="I13" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>49.5</v>
+      </c>
       <c r="K13" t="s">
         <v>27</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="14">
@@ -998,10 +1001,10 @@
         <v>30</v>
       </c>
       <c r="E14" t="n">
-        <v>5.6</v>
+        <v>-10.7</v>
       </c>
       <c r="F14" t="n">
-        <v>42.5</v>
+        <v>40.6</v>
       </c>
       <c r="G14" t="s">
         <v>15</v>
@@ -1010,16 +1013,16 @@
         <v>16</v>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>-10.5</v>
       </c>
       <c r="J14" t="n">
-        <v>49.5</v>
+        <v>42.5</v>
       </c>
       <c r="K14" t="s">
         <v>31</v>
       </c>
       <c r="L14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1036,10 +1039,10 @@
         <v>30</v>
       </c>
       <c r="E15" t="n">
-        <v>5.6</v>
+        <v>-10.7</v>
       </c>
       <c r="F15" t="n">
-        <v>41.5</v>
+        <v>40.6</v>
       </c>
       <c r="G15" t="s">
         <v>15</v>
@@ -1048,16 +1051,16 @@
         <v>18</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>-10.5</v>
       </c>
       <c r="J15" t="n">
-        <v>49.5</v>
+        <v>42.5</v>
       </c>
       <c r="K15" t="s">
         <v>31</v>
       </c>
       <c r="L15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1074,10 +1077,10 @@
         <v>30</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8</v>
+        <v>-5.3</v>
       </c>
       <c r="F16" t="n">
-        <v>21.2</v>
+        <v>20.3</v>
       </c>
       <c r="G16" t="s">
         <v>19</v>
@@ -1086,16 +1089,16 @@
         <v>16</v>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>-10.5</v>
       </c>
       <c r="J16" t="n">
-        <v>49.5</v>
+        <v>42.5</v>
       </c>
       <c r="K16" t="s">
         <v>31</v>
       </c>
       <c r="L16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1112,10 +1115,10 @@
         <v>30</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8</v>
+        <v>-5.3</v>
       </c>
       <c r="F17" t="n">
-        <v>20.8</v>
+        <v>20.3</v>
       </c>
       <c r="G17" t="s">
         <v>19</v>
@@ -1124,16 +1127,16 @@
         <v>18</v>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>-10.5</v>
       </c>
       <c r="J17" t="n">
-        <v>49.5</v>
+        <v>42.5</v>
       </c>
       <c r="K17" t="s">
         <v>31</v>
       </c>
       <c r="L17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1150,10 +1153,10 @@
         <v>34</v>
       </c>
       <c r="E18" t="n">
-        <v>-9.5</v>
+        <v>-4.1</v>
       </c>
       <c r="F18" t="n">
-        <v>40.6</v>
+        <v>43.4</v>
       </c>
       <c r="G18" t="s">
         <v>15</v>
@@ -1161,17 +1164,13 @@
       <c r="H18" t="s">
         <v>16</v>
       </c>
-      <c r="I18" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="J18" t="n">
-        <v>42.5</v>
-      </c>
+      <c r="I18"/>
+      <c r="J18"/>
       <c r="K18" t="s">
         <v>35</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="19">
@@ -1188,10 +1187,10 @@
         <v>34</v>
       </c>
       <c r="E19" t="n">
-        <v>-9.5</v>
+        <v>-4.1</v>
       </c>
       <c r="F19" t="n">
-        <v>40.6</v>
+        <v>42.7</v>
       </c>
       <c r="G19" t="s">
         <v>15</v>
@@ -1199,17 +1198,13 @@
       <c r="H19" t="s">
         <v>18</v>
       </c>
-      <c r="I19" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="J19" t="n">
-        <v>42.5</v>
-      </c>
+      <c r="I19"/>
+      <c r="J19"/>
       <c r="K19" t="s">
         <v>35</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="20">
@@ -1226,10 +1221,10 @@
         <v>34</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.8</v>
+        <v>-2</v>
       </c>
       <c r="F20" t="n">
-        <v>20.3</v>
+        <v>21.7</v>
       </c>
       <c r="G20" t="s">
         <v>19</v>
@@ -1237,17 +1232,13 @@
       <c r="H20" t="s">
         <v>16</v>
       </c>
-      <c r="I20" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="J20" t="n">
-        <v>42.5</v>
-      </c>
+      <c r="I20"/>
+      <c r="J20"/>
       <c r="K20" t="s">
         <v>35</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="21">
@@ -1264,10 +1255,10 @@
         <v>34</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.8</v>
+        <v>-2</v>
       </c>
       <c r="F21" t="n">
-        <v>20.3</v>
+        <v>21.4</v>
       </c>
       <c r="G21" t="s">
         <v>19</v>
@@ -1275,22 +1266,18 @@
       <c r="H21" t="s">
         <v>18</v>
       </c>
-      <c r="I21" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="J21" t="n">
-        <v>42.5</v>
-      </c>
+      <c r="I21"/>
+      <c r="J21"/>
       <c r="K21" t="s">
         <v>35</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B22" t="s">
         <v>36</v>
@@ -1302,10 +1289,10 @@
         <v>38</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.6</v>
+        <v>-6.7</v>
       </c>
       <c r="F22" t="n">
-        <v>43.4</v>
+        <v>46</v>
       </c>
       <c r="G22" t="s">
         <v>15</v>
@@ -1313,18 +1300,22 @@
       <c r="H22" t="s">
         <v>16</v>
       </c>
-      <c r="I22"/>
-      <c r="J22"/>
+      <c r="I22" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>48.5</v>
+      </c>
       <c r="K22" t="s">
         <v>39</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B23" t="s">
         <v>36</v>
@@ -1336,10 +1327,10 @@
         <v>38</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.6</v>
+        <v>-6.7</v>
       </c>
       <c r="F23" t="n">
-        <v>43.1</v>
+        <v>46</v>
       </c>
       <c r="G23" t="s">
         <v>15</v>
@@ -1347,18 +1338,22 @@
       <c r="H23" t="s">
         <v>18</v>
       </c>
-      <c r="I23"/>
-      <c r="J23"/>
+      <c r="I23" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>48.5</v>
+      </c>
       <c r="K23" t="s">
         <v>39</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B24" t="s">
         <v>36</v>
@@ -1370,10 +1365,10 @@
         <v>38</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.3</v>
+        <v>-3.3</v>
       </c>
       <c r="F24" t="n">
-        <v>21.7</v>
+        <v>23</v>
       </c>
       <c r="G24" t="s">
         <v>19</v>
@@ -1381,18 +1376,22 @@
       <c r="H24" t="s">
         <v>16</v>
       </c>
-      <c r="I24"/>
-      <c r="J24"/>
+      <c r="I24" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="J24" t="n">
+        <v>48.5</v>
+      </c>
       <c r="K24" t="s">
         <v>39</v>
       </c>
       <c r="L24" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B25" t="s">
         <v>36</v>
@@ -1404,10 +1403,10 @@
         <v>38</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.3</v>
+        <v>-3.3</v>
       </c>
       <c r="F25" t="n">
-        <v>21.5</v>
+        <v>23</v>
       </c>
       <c r="G25" t="s">
         <v>19</v>
@@ -1415,13 +1414,17 @@
       <c r="H25" t="s">
         <v>18</v>
       </c>
-      <c r="I25"/>
-      <c r="J25"/>
+      <c r="I25" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>48.5</v>
+      </c>
       <c r="K25" t="s">
         <v>39</v>
       </c>
       <c r="L25" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1438,10 +1441,10 @@
         <v>42</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.7</v>
+        <v>2.1</v>
       </c>
       <c r="F26" t="n">
-        <v>46</v>
+        <v>44.4</v>
       </c>
       <c r="G26" t="s">
         <v>15</v>
@@ -1450,7 +1453,7 @@
         <v>16</v>
       </c>
       <c r="I26" t="n">
-        <v>-7.5</v>
+        <v>2.5</v>
       </c>
       <c r="J26" t="n">
         <v>48.5</v>
@@ -1476,10 +1479,10 @@
         <v>42</v>
       </c>
       <c r="E27" t="n">
-        <v>-6.7</v>
+        <v>2.1</v>
       </c>
       <c r="F27" t="n">
-        <v>46</v>
+        <v>44.4</v>
       </c>
       <c r="G27" t="s">
         <v>15</v>
@@ -1488,7 +1491,7 @@
         <v>18</v>
       </c>
       <c r="I27" t="n">
-        <v>-7.5</v>
+        <v>2.5</v>
       </c>
       <c r="J27" t="n">
         <v>48.5</v>
@@ -1514,10 +1517,10 @@
         <v>42</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.3</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>23</v>
+        <v>22.2</v>
       </c>
       <c r="G28" t="s">
         <v>19</v>
@@ -1526,7 +1529,7 @@
         <v>16</v>
       </c>
       <c r="I28" t="n">
-        <v>-7.5</v>
+        <v>2.5</v>
       </c>
       <c r="J28" t="n">
         <v>48.5</v>
@@ -1552,10 +1555,10 @@
         <v>42</v>
       </c>
       <c r="E29" t="n">
-        <v>-3.3</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>23</v>
+        <v>22.2</v>
       </c>
       <c r="G29" t="s">
         <v>19</v>
@@ -1564,7 +1567,7 @@
         <v>18</v>
       </c>
       <c r="I29" t="n">
-        <v>-7.5</v>
+        <v>2.5</v>
       </c>
       <c r="J29" t="n">
         <v>48.5</v>
@@ -1578,22 +1581,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="B30" t="s">
         <v>44</v>
       </c>
       <c r="C30" t="s">
+        <v>25</v>
+      </c>
+      <c r="D30" t="s">
         <v>45</v>
       </c>
-      <c r="D30" t="s">
-        <v>46</v>
-      </c>
       <c r="E30" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>44.4</v>
+        <v>45.7</v>
       </c>
       <c r="G30" t="s">
         <v>15</v>
@@ -1601,14 +1604,10 @@
       <c r="H30" t="s">
         <v>16</v>
       </c>
-      <c r="I30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J30" t="n">
-        <v>48.5</v>
-      </c>
+      <c r="I30"/>
+      <c r="J30"/>
       <c r="K30" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -1616,22 +1615,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="B31" t="s">
         <v>44</v>
       </c>
       <c r="C31" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" t="s">
         <v>45</v>
       </c>
-      <c r="D31" t="s">
-        <v>46</v>
-      </c>
       <c r="E31" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>44.4</v>
+        <v>45.7</v>
       </c>
       <c r="G31" t="s">
         <v>15</v>
@@ -1639,14 +1638,10 @@
       <c r="H31" t="s">
         <v>18</v>
       </c>
-      <c r="I31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J31" t="n">
-        <v>48.5</v>
-      </c>
+      <c r="I31"/>
+      <c r="J31"/>
       <c r="K31" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -1654,22 +1649,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="B32" t="s">
         <v>44</v>
       </c>
       <c r="C32" t="s">
+        <v>25</v>
+      </c>
+      <c r="D32" t="s">
         <v>45</v>
       </c>
-      <c r="D32" t="s">
-        <v>46</v>
-      </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F32" t="n">
-        <v>22.2</v>
+        <v>22.9</v>
       </c>
       <c r="G32" t="s">
         <v>19</v>
@@ -1677,14 +1672,10 @@
       <c r="H32" t="s">
         <v>16</v>
       </c>
-      <c r="I32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J32" t="n">
-        <v>48.5</v>
-      </c>
+      <c r="I32"/>
+      <c r="J32"/>
       <c r="K32" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -1692,22 +1683,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="B33" t="s">
         <v>44</v>
       </c>
       <c r="C33" t="s">
+        <v>25</v>
+      </c>
+      <c r="D33" t="s">
         <v>45</v>
       </c>
-      <c r="D33" t="s">
-        <v>46</v>
-      </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F33" t="n">
-        <v>22.2</v>
+        <v>22.9</v>
       </c>
       <c r="G33" t="s">
         <v>19</v>
@@ -1715,14 +1706,10 @@
       <c r="H33" t="s">
         <v>18</v>
       </c>
-      <c r="I33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J33" t="n">
-        <v>48.5</v>
-      </c>
+      <c r="I33"/>
+      <c r="J33"/>
       <c r="K33" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -1730,22 +1717,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B34" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C34" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="D34" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E34" t="n">
-        <v>0.7</v>
+        <v>-9.5</v>
       </c>
       <c r="F34" t="n">
-        <v>45.7</v>
+        <v>39.1</v>
       </c>
       <c r="G34" t="s">
         <v>15</v>
@@ -1756,30 +1743,30 @@
       <c r="I34"/>
       <c r="J34"/>
       <c r="K34" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B35" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C35" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="D35" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E35" t="n">
-        <v>0.7</v>
+        <v>-9.5</v>
       </c>
       <c r="F35" t="n">
-        <v>45.7</v>
+        <v>39</v>
       </c>
       <c r="G35" t="s">
         <v>15</v>
@@ -1790,30 +1777,30 @@
       <c r="I35"/>
       <c r="J35"/>
       <c r="K35" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B36" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C36" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="D36" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3</v>
+        <v>-4.7</v>
       </c>
       <c r="F36" t="n">
-        <v>22.9</v>
+        <v>19.6</v>
       </c>
       <c r="G36" t="s">
         <v>19</v>
@@ -1824,30 +1811,30 @@
       <c r="I36"/>
       <c r="J36"/>
       <c r="K36" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B37" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C37" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="D37" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E37" t="n">
-        <v>0.3</v>
+        <v>-4.7</v>
       </c>
       <c r="F37" t="n">
-        <v>22.9</v>
+        <v>19.5</v>
       </c>
       <c r="G37" t="s">
         <v>19</v>
@@ -1858,10 +1845,146 @@
       <c r="I37"/>
       <c r="J37"/>
       <c r="K37" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B38" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" t="s">
+        <v>26</v>
+      </c>
+      <c r="D38" t="s">
+        <v>29</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="F38" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="G38" t="s">
+        <v>15</v>
+      </c>
+      <c r="H38" t="s">
+        <v>16</v>
+      </c>
+      <c r="I38"/>
+      <c r="J38"/>
+      <c r="K38" t="s">
+        <v>48</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B39" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" t="s">
+        <v>26</v>
+      </c>
+      <c r="D39" t="s">
+        <v>29</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="F39" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="G39" t="s">
+        <v>15</v>
+      </c>
+      <c r="H39" t="s">
+        <v>18</v>
+      </c>
+      <c r="I39"/>
+      <c r="J39"/>
+      <c r="K39" t="s">
+        <v>48</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B40" t="s">
+        <v>20</v>
+      </c>
+      <c r="C40" t="s">
+        <v>26</v>
+      </c>
+      <c r="D40" t="s">
+        <v>29</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="G40" t="s">
+        <v>19</v>
+      </c>
+      <c r="H40" t="s">
+        <v>16</v>
+      </c>
+      <c r="I40"/>
+      <c r="J40"/>
+      <c r="K40" t="s">
+        <v>48</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B41" t="s">
+        <v>20</v>
+      </c>
+      <c r="C41" t="s">
+        <v>26</v>
+      </c>
+      <c r="D41" t="s">
+        <v>29</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F41" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="G41" t="s">
+        <v>19</v>
+      </c>
+      <c r="H41" t="s">
+        <v>18</v>
+      </c>
+      <c r="I41"/>
+      <c r="J41"/>
+      <c r="K41" t="s">
+        <v>48</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1.7</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_upcoming_projections.xlsx
+++ b/files/NRL_upcoming_projections.xlsx
@@ -572,12 +572,8 @@
       <c r="H2" t="s">
         <v>16</v>
       </c>
-      <c r="I2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J2" t="n">
-        <v>49.5</v>
-      </c>
+      <c r="I2"/>
+      <c r="J2"/>
       <c r="K2" t="s">
         <v>17</v>
       </c>
@@ -610,12 +606,8 @@
       <c r="H3" t="s">
         <v>18</v>
       </c>
-      <c r="I3" t="n">
-        <v>10</v>
-      </c>
-      <c r="J3" t="n">
-        <v>49.5</v>
-      </c>
+      <c r="I3"/>
+      <c r="J3"/>
       <c r="K3" t="s">
         <v>17</v>
       </c>
@@ -648,12 +640,8 @@
       <c r="H4" t="s">
         <v>16</v>
       </c>
-      <c r="I4" t="n">
-        <v>10</v>
-      </c>
-      <c r="J4" t="n">
-        <v>49.5</v>
-      </c>
+      <c r="I4"/>
+      <c r="J4"/>
       <c r="K4" t="s">
         <v>17</v>
       </c>
@@ -686,12 +674,8 @@
       <c r="H5" t="s">
         <v>18</v>
       </c>
-      <c r="I5" t="n">
-        <v>10</v>
-      </c>
-      <c r="J5" t="n">
-        <v>49.5</v>
-      </c>
+      <c r="I5"/>
+      <c r="J5"/>
       <c r="K5" t="s">
         <v>17</v>
       </c>
@@ -861,7 +845,7 @@
         <v>16</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
         <v>49.5</v>
@@ -899,7 +883,7 @@
         <v>18</v>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
         <v>49.5</v>
@@ -937,7 +921,7 @@
         <v>16</v>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
         <v>49.5</v>
@@ -975,7 +959,7 @@
         <v>18</v>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J13" t="n">
         <v>49.5</v>
@@ -1013,10 +997,10 @@
         <v>16</v>
       </c>
       <c r="I14" t="n">
-        <v>-10.5</v>
+        <v>-9</v>
       </c>
       <c r="J14" t="n">
-        <v>42.5</v>
+        <v>44</v>
       </c>
       <c r="K14" t="s">
         <v>31</v>
@@ -1051,10 +1035,10 @@
         <v>18</v>
       </c>
       <c r="I15" t="n">
-        <v>-10.5</v>
+        <v>-9</v>
       </c>
       <c r="J15" t="n">
-        <v>42.5</v>
+        <v>44</v>
       </c>
       <c r="K15" t="s">
         <v>31</v>
@@ -1089,10 +1073,10 @@
         <v>16</v>
       </c>
       <c r="I16" t="n">
-        <v>-10.5</v>
+        <v>-9</v>
       </c>
       <c r="J16" t="n">
-        <v>42.5</v>
+        <v>44</v>
       </c>
       <c r="K16" t="s">
         <v>31</v>
@@ -1127,10 +1111,10 @@
         <v>18</v>
       </c>
       <c r="I17" t="n">
-        <v>-10.5</v>
+        <v>-9</v>
       </c>
       <c r="J17" t="n">
-        <v>42.5</v>
+        <v>44</v>
       </c>
       <c r="K17" t="s">
         <v>31</v>
@@ -1164,8 +1148,12 @@
       <c r="H18" t="s">
         <v>16</v>
       </c>
-      <c r="I18"/>
-      <c r="J18"/>
+      <c r="I18" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>46</v>
+      </c>
       <c r="K18" t="s">
         <v>35</v>
       </c>
@@ -1198,8 +1186,12 @@
       <c r="H19" t="s">
         <v>18</v>
       </c>
-      <c r="I19"/>
-      <c r="J19"/>
+      <c r="I19" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>46</v>
+      </c>
       <c r="K19" t="s">
         <v>35</v>
       </c>
@@ -1232,8 +1224,12 @@
       <c r="H20" t="s">
         <v>16</v>
       </c>
-      <c r="I20"/>
-      <c r="J20"/>
+      <c r="I20" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>46</v>
+      </c>
       <c r="K20" t="s">
         <v>35</v>
       </c>
@@ -1266,8 +1262,12 @@
       <c r="H21" t="s">
         <v>18</v>
       </c>
-      <c r="I21"/>
-      <c r="J21"/>
+      <c r="I21" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="J21" t="n">
+        <v>46</v>
+      </c>
       <c r="K21" t="s">
         <v>35</v>
       </c>
@@ -1301,10 +1301,10 @@
         <v>16</v>
       </c>
       <c r="I22" t="n">
-        <v>-7.5</v>
+        <v>-12.5</v>
       </c>
       <c r="J22" t="n">
-        <v>48.5</v>
+        <v>52</v>
       </c>
       <c r="K22" t="s">
         <v>39</v>
@@ -1339,10 +1339,10 @@
         <v>18</v>
       </c>
       <c r="I23" t="n">
-        <v>-7.5</v>
+        <v>-12.5</v>
       </c>
       <c r="J23" t="n">
-        <v>48.5</v>
+        <v>52</v>
       </c>
       <c r="K23" t="s">
         <v>39</v>
@@ -1377,10 +1377,10 @@
         <v>16</v>
       </c>
       <c r="I24" t="n">
-        <v>-7.5</v>
+        <v>-12.5</v>
       </c>
       <c r="J24" t="n">
-        <v>48.5</v>
+        <v>52</v>
       </c>
       <c r="K24" t="s">
         <v>39</v>
@@ -1415,10 +1415,10 @@
         <v>18</v>
       </c>
       <c r="I25" t="n">
-        <v>-7.5</v>
+        <v>-12.5</v>
       </c>
       <c r="J25" t="n">
-        <v>48.5</v>
+        <v>52</v>
       </c>
       <c r="K25" t="s">
         <v>39</v>
@@ -1453,10 +1453,10 @@
         <v>16</v>
       </c>
       <c r="I26" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="J26" t="n">
-        <v>48.5</v>
+        <v>49</v>
       </c>
       <c r="K26" t="s">
         <v>43</v>
@@ -1491,10 +1491,10 @@
         <v>18</v>
       </c>
       <c r="I27" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="J27" t="n">
-        <v>48.5</v>
+        <v>49</v>
       </c>
       <c r="K27" t="s">
         <v>43</v>
@@ -1529,10 +1529,10 @@
         <v>16</v>
       </c>
       <c r="I28" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="J28" t="n">
-        <v>48.5</v>
+        <v>49</v>
       </c>
       <c r="K28" t="s">
         <v>43</v>
@@ -1567,10 +1567,10 @@
         <v>18</v>
       </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="J29" t="n">
-        <v>48.5</v>
+        <v>49</v>
       </c>
       <c r="K29" t="s">
         <v>43</v>
@@ -1604,8 +1604,12 @@
       <c r="H30" t="s">
         <v>16</v>
       </c>
-      <c r="I30"/>
-      <c r="J30"/>
+      <c r="I30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J30" t="n">
+        <v>47.5</v>
+      </c>
       <c r="K30" t="s">
         <v>27</v>
       </c>
@@ -1638,8 +1642,12 @@
       <c r="H31" t="s">
         <v>18</v>
       </c>
-      <c r="I31"/>
-      <c r="J31"/>
+      <c r="I31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J31" t="n">
+        <v>47.5</v>
+      </c>
       <c r="K31" t="s">
         <v>27</v>
       </c>
@@ -1672,8 +1680,12 @@
       <c r="H32" t="s">
         <v>16</v>
       </c>
-      <c r="I32"/>
-      <c r="J32"/>
+      <c r="I32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>47.5</v>
+      </c>
       <c r="K32" t="s">
         <v>27</v>
       </c>
@@ -1706,8 +1718,12 @@
       <c r="H33" t="s">
         <v>18</v>
       </c>
-      <c r="I33"/>
-      <c r="J33"/>
+      <c r="I33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J33" t="n">
+        <v>47.5</v>
+      </c>
       <c r="K33" t="s">
         <v>27</v>
       </c>
@@ -1740,8 +1756,12 @@
       <c r="H34" t="s">
         <v>16</v>
       </c>
-      <c r="I34"/>
-      <c r="J34"/>
+      <c r="I34" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="J34" t="n">
+        <v>45.5</v>
+      </c>
       <c r="K34" t="s">
         <v>47</v>
       </c>
@@ -1774,8 +1794,12 @@
       <c r="H35" t="s">
         <v>18</v>
       </c>
-      <c r="I35"/>
-      <c r="J35"/>
+      <c r="I35" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="J35" t="n">
+        <v>45.5</v>
+      </c>
       <c r="K35" t="s">
         <v>47</v>
       </c>
@@ -1808,8 +1832,12 @@
       <c r="H36" t="s">
         <v>16</v>
       </c>
-      <c r="I36"/>
-      <c r="J36"/>
+      <c r="I36" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="J36" t="n">
+        <v>45.5</v>
+      </c>
       <c r="K36" t="s">
         <v>47</v>
       </c>
@@ -1842,8 +1870,12 @@
       <c r="H37" t="s">
         <v>18</v>
       </c>
-      <c r="I37"/>
-      <c r="J37"/>
+      <c r="I37" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="J37" t="n">
+        <v>45.5</v>
+      </c>
       <c r="K37" t="s">
         <v>47</v>
       </c>
@@ -1876,8 +1908,12 @@
       <c r="H38" t="s">
         <v>16</v>
       </c>
-      <c r="I38"/>
-      <c r="J38"/>
+      <c r="I38" t="n">
+        <v>5</v>
+      </c>
+      <c r="J38" t="n">
+        <v>40.5</v>
+      </c>
       <c r="K38" t="s">
         <v>48</v>
       </c>
@@ -1910,8 +1946,12 @@
       <c r="H39" t="s">
         <v>18</v>
       </c>
-      <c r="I39"/>
-      <c r="J39"/>
+      <c r="I39" t="n">
+        <v>5</v>
+      </c>
+      <c r="J39" t="n">
+        <v>40.5</v>
+      </c>
       <c r="K39" t="s">
         <v>48</v>
       </c>
@@ -1944,8 +1984,12 @@
       <c r="H40" t="s">
         <v>16</v>
       </c>
-      <c r="I40"/>
-      <c r="J40"/>
+      <c r="I40" t="n">
+        <v>5</v>
+      </c>
+      <c r="J40" t="n">
+        <v>40.5</v>
+      </c>
       <c r="K40" t="s">
         <v>48</v>
       </c>
@@ -1978,8 +2022,12 @@
       <c r="H41" t="s">
         <v>18</v>
       </c>
-      <c r="I41"/>
-      <c r="J41"/>
+      <c r="I41" t="n">
+        <v>5</v>
+      </c>
+      <c r="J41" t="n">
+        <v>40.5</v>
+      </c>
       <c r="K41" t="s">
         <v>48</v>
       </c>

--- a/files/NRL_upcoming_projections.xlsx
+++ b/files/NRL_upcoming_projections.xlsx
@@ -50,115 +50,115 @@
     <t xml:space="preserve">Forecast Rain mm</t>
   </si>
   <si>
-    <t xml:space="preserve">18:00</t>
+    <t xml:space="preserve">14:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">south sydney rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Rain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sharks Stadium, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wests tigers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leichhardt Oval, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north queensland cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cbus Super Stadium, Gold Coast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allianz Stadium, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penrith panthers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Go Media Stadium, Auckland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melbourne storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manly-warringah sea eagles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBF Park, Perth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dolphins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suncorp Stadium, Brisbane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GIO Stadium, Canberra</t>
   </si>
   <si>
     <t xml:space="preserve">st george-illawarra dragons</t>
   </si>
   <si>
-    <t xml:space="preserve">dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Rain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WIN Stadium, Wollongong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">melbourne storm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AAMI Park, Melbourne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cbus Super Stadium, Gold Coast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penrith panthers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberra raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glen Willow Stadium, Mudgee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">newcastle knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suncorp Stadium, Brisbane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">south sydney rabbitohs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sharks Stadium, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wests tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leichhardt Oval, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north queensland cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allianz Stadium, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Go Media Stadium, Auckland</t>
+    <t xml:space="preserve">Jubilee Oval, Sydney</t>
   </si>
 </sst>
 </file>
@@ -549,7 +549,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -561,10 +561,10 @@
         <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9</v>
+        <v>-8.1</v>
       </c>
       <c r="F2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G2" t="s">
         <v>15</v>
@@ -572,8 +572,12 @@
       <c r="H2" t="s">
         <v>16</v>
       </c>
-      <c r="I2"/>
-      <c r="J2"/>
+      <c r="I2" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>52</v>
+      </c>
       <c r="K2" t="s">
         <v>17</v>
       </c>
@@ -583,7 +587,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -595,10 +599,10 @@
         <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>5.9</v>
+        <v>-8.1</v>
       </c>
       <c r="F3" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G3" t="s">
         <v>15</v>
@@ -606,8 +610,12 @@
       <c r="H3" t="s">
         <v>18</v>
       </c>
-      <c r="I3"/>
-      <c r="J3"/>
+      <c r="I3" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>52</v>
+      </c>
       <c r="K3" t="s">
         <v>17</v>
       </c>
@@ -617,7 +625,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -629,10 +637,10 @@
         <v>14</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="F4" t="n">
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="G4" t="s">
         <v>19</v>
@@ -640,8 +648,12 @@
       <c r="H4" t="s">
         <v>16</v>
       </c>
-      <c r="I4"/>
-      <c r="J4"/>
+      <c r="I4" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>52</v>
+      </c>
       <c r="K4" t="s">
         <v>17</v>
       </c>
@@ -651,7 +663,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -663,10 +675,10 @@
         <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="F5" t="n">
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="G5" t="s">
         <v>19</v>
@@ -674,8 +686,12 @@
       <c r="H5" t="s">
         <v>18</v>
       </c>
-      <c r="I5"/>
-      <c r="J5"/>
+      <c r="I5" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>52</v>
+      </c>
       <c r="K5" t="s">
         <v>17</v>
       </c>
@@ -685,7 +701,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
@@ -697,10 +713,10 @@
         <v>22</v>
       </c>
       <c r="E6" t="n">
-        <v>-6.2</v>
+        <v>3.1</v>
       </c>
       <c r="F6" t="n">
-        <v>39</v>
+        <v>44.4</v>
       </c>
       <c r="G6" t="s">
         <v>15</v>
@@ -708,8 +724,12 @@
       <c r="H6" t="s">
         <v>16</v>
       </c>
-      <c r="I6"/>
-      <c r="J6"/>
+      <c r="I6" t="n">
+        <v>7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>49</v>
+      </c>
       <c r="K6" t="s">
         <v>23</v>
       </c>
@@ -719,7 +739,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B7" t="s">
         <v>20</v>
@@ -731,10 +751,10 @@
         <v>22</v>
       </c>
       <c r="E7" t="n">
-        <v>-6.2</v>
+        <v>3.1</v>
       </c>
       <c r="F7" t="n">
-        <v>39</v>
+        <v>44.4</v>
       </c>
       <c r="G7" t="s">
         <v>15</v>
@@ -742,8 +762,12 @@
       <c r="H7" t="s">
         <v>18</v>
       </c>
-      <c r="I7"/>
-      <c r="J7"/>
+      <c r="I7" t="n">
+        <v>7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>49</v>
+      </c>
       <c r="K7" t="s">
         <v>23</v>
       </c>
@@ -753,7 +777,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B8" t="s">
         <v>20</v>
@@ -765,10 +789,10 @@
         <v>22</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.1</v>
+        <v>1.5</v>
       </c>
       <c r="F8" t="n">
-        <v>19.5</v>
+        <v>22.2</v>
       </c>
       <c r="G8" t="s">
         <v>19</v>
@@ -776,8 +800,12 @@
       <c r="H8" t="s">
         <v>16</v>
       </c>
-      <c r="I8"/>
-      <c r="J8"/>
+      <c r="I8" t="n">
+        <v>7</v>
+      </c>
+      <c r="J8" t="n">
+        <v>49</v>
+      </c>
       <c r="K8" t="s">
         <v>23</v>
       </c>
@@ -787,7 +815,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B9" t="s">
         <v>20</v>
@@ -799,10 +827,10 @@
         <v>22</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.1</v>
+        <v>1.5</v>
       </c>
       <c r="F9" t="n">
-        <v>19.5</v>
+        <v>22.2</v>
       </c>
       <c r="G9" t="s">
         <v>19</v>
@@ -810,8 +838,12 @@
       <c r="H9" t="s">
         <v>18</v>
       </c>
-      <c r="I9"/>
-      <c r="J9"/>
+      <c r="I9" t="n">
+        <v>7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>49</v>
+      </c>
       <c r="K9" t="s">
         <v>23</v>
       </c>
@@ -821,7 +853,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
@@ -833,10 +865,10 @@
         <v>26</v>
       </c>
       <c r="E10" t="n">
-        <v>6.7</v>
+        <v>0.8</v>
       </c>
       <c r="F10" t="n">
-        <v>42.5</v>
+        <v>45.7</v>
       </c>
       <c r="G10" t="s">
         <v>15</v>
@@ -845,21 +877,21 @@
         <v>16</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="J10" t="n">
-        <v>49.5</v>
+        <v>47.5</v>
       </c>
       <c r="K10" t="s">
         <v>27</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B11" t="s">
         <v>24</v>
@@ -871,10 +903,10 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>6.7</v>
+        <v>0.8</v>
       </c>
       <c r="F11" t="n">
-        <v>42</v>
+        <v>45.7</v>
       </c>
       <c r="G11" t="s">
         <v>15</v>
@@ -883,21 +915,21 @@
         <v>18</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="J11" t="n">
-        <v>49.5</v>
+        <v>47.5</v>
       </c>
       <c r="K11" t="s">
         <v>27</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B12" t="s">
         <v>24</v>
@@ -909,10 +941,10 @@
         <v>26</v>
       </c>
       <c r="E12" t="n">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="F12" t="n">
-        <v>21.2</v>
+        <v>22.9</v>
       </c>
       <c r="G12" t="s">
         <v>19</v>
@@ -921,21 +953,21 @@
         <v>16</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="J12" t="n">
-        <v>49.5</v>
+        <v>47.5</v>
       </c>
       <c r="K12" t="s">
         <v>27</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B13" t="s">
         <v>24</v>
@@ -947,10 +979,10 @@
         <v>26</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="F13" t="n">
-        <v>21</v>
+        <v>22.9</v>
       </c>
       <c r="G13" t="s">
         <v>19</v>
@@ -959,21 +991,21 @@
         <v>18</v>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="J13" t="n">
-        <v>49.5</v>
+        <v>47.5</v>
       </c>
       <c r="K13" t="s">
         <v>27</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B14" t="s">
         <v>28</v>
@@ -985,10 +1017,10 @@
         <v>30</v>
       </c>
       <c r="E14" t="n">
-        <v>-10.7</v>
+        <v>-9.5</v>
       </c>
       <c r="F14" t="n">
-        <v>40.6</v>
+        <v>39.1</v>
       </c>
       <c r="G14" t="s">
         <v>15</v>
@@ -997,10 +1029,10 @@
         <v>16</v>
       </c>
       <c r="I14" t="n">
-        <v>-9</v>
+        <v>-8.5</v>
       </c>
       <c r="J14" t="n">
-        <v>44</v>
+        <v>45.5</v>
       </c>
       <c r="K14" t="s">
         <v>31</v>
@@ -1011,7 +1043,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B15" t="s">
         <v>28</v>
@@ -1023,10 +1055,10 @@
         <v>30</v>
       </c>
       <c r="E15" t="n">
-        <v>-10.7</v>
+        <v>-9.5</v>
       </c>
       <c r="F15" t="n">
-        <v>40.6</v>
+        <v>39.1</v>
       </c>
       <c r="G15" t="s">
         <v>15</v>
@@ -1035,10 +1067,10 @@
         <v>18</v>
       </c>
       <c r="I15" t="n">
-        <v>-9</v>
+        <v>-8.5</v>
       </c>
       <c r="J15" t="n">
-        <v>44</v>
+        <v>45.5</v>
       </c>
       <c r="K15" t="s">
         <v>31</v>
@@ -1049,7 +1081,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B16" t="s">
         <v>28</v>
@@ -1061,10 +1093,10 @@
         <v>30</v>
       </c>
       <c r="E16" t="n">
-        <v>-5.3</v>
+        <v>-4.7</v>
       </c>
       <c r="F16" t="n">
-        <v>20.3</v>
+        <v>19.6</v>
       </c>
       <c r="G16" t="s">
         <v>19</v>
@@ -1073,10 +1105,10 @@
         <v>16</v>
       </c>
       <c r="I16" t="n">
-        <v>-9</v>
+        <v>-8.5</v>
       </c>
       <c r="J16" t="n">
-        <v>44</v>
+        <v>45.5</v>
       </c>
       <c r="K16" t="s">
         <v>31</v>
@@ -1087,7 +1119,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B17" t="s">
         <v>28</v>
@@ -1099,10 +1131,10 @@
         <v>30</v>
       </c>
       <c r="E17" t="n">
-        <v>-5.3</v>
+        <v>-4.7</v>
       </c>
       <c r="F17" t="n">
-        <v>20.3</v>
+        <v>19.6</v>
       </c>
       <c r="G17" t="s">
         <v>19</v>
@@ -1111,10 +1143,10 @@
         <v>18</v>
       </c>
       <c r="I17" t="n">
-        <v>-9</v>
+        <v>-8.5</v>
       </c>
       <c r="J17" t="n">
-        <v>44</v>
+        <v>45.5</v>
       </c>
       <c r="K17" t="s">
         <v>31</v>
@@ -1125,22 +1157,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" t="s">
         <v>32</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>33</v>
       </c>
-      <c r="D18" t="s">
-        <v>34</v>
-      </c>
       <c r="E18" t="n">
-        <v>-4.1</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>43.4</v>
+        <v>38.3</v>
       </c>
       <c r="G18" t="s">
         <v>15</v>
@@ -1149,36 +1181,36 @@
         <v>16</v>
       </c>
       <c r="I18" t="n">
-        <v>-5.5</v>
+        <v>5</v>
       </c>
       <c r="J18" t="n">
-        <v>46</v>
+        <v>40.5</v>
       </c>
       <c r="K18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" t="s">
         <v>32</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>33</v>
       </c>
-      <c r="D19" t="s">
-        <v>34</v>
-      </c>
       <c r="E19" t="n">
-        <v>-4.1</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>42.7</v>
+        <v>38.3</v>
       </c>
       <c r="G19" t="s">
         <v>15</v>
@@ -1187,36 +1219,36 @@
         <v>18</v>
       </c>
       <c r="I19" t="n">
-        <v>-5.5</v>
+        <v>5</v>
       </c>
       <c r="J19" t="n">
-        <v>46</v>
+        <v>40.5</v>
       </c>
       <c r="K19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" t="s">
         <v>32</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>33</v>
       </c>
-      <c r="D20" t="s">
-        <v>34</v>
-      </c>
       <c r="E20" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>21.7</v>
+        <v>19.2</v>
       </c>
       <c r="G20" t="s">
         <v>19</v>
@@ -1225,36 +1257,36 @@
         <v>16</v>
       </c>
       <c r="I20" t="n">
-        <v>-5.5</v>
+        <v>5</v>
       </c>
       <c r="J20" t="n">
-        <v>46</v>
+        <v>40.5</v>
       </c>
       <c r="K20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B21" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" t="s">
         <v>32</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>33</v>
       </c>
-      <c r="D21" t="s">
-        <v>34</v>
-      </c>
       <c r="E21" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>21.4</v>
+        <v>19.2</v>
       </c>
       <c r="G21" t="s">
         <v>19</v>
@@ -1263,36 +1295,36 @@
         <v>18</v>
       </c>
       <c r="I21" t="n">
-        <v>-5.5</v>
+        <v>5</v>
       </c>
       <c r="J21" t="n">
-        <v>46</v>
+        <v>40.5</v>
       </c>
       <c r="K21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" t="s">
         <v>36</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>37</v>
       </c>
-      <c r="D22" t="s">
-        <v>38</v>
-      </c>
       <c r="E22" t="n">
-        <v>-6.7</v>
+        <v>1.8</v>
       </c>
       <c r="F22" t="n">
-        <v>46</v>
+        <v>40.9</v>
       </c>
       <c r="G22" t="s">
         <v>15</v>
@@ -1301,36 +1333,36 @@
         <v>16</v>
       </c>
       <c r="I22" t="n">
-        <v>-12.5</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
-        <v>52</v>
+        <v>48.5</v>
       </c>
       <c r="K22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" t="s">
         <v>36</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>37</v>
       </c>
-      <c r="D23" t="s">
-        <v>38</v>
-      </c>
       <c r="E23" t="n">
-        <v>-6.7</v>
+        <v>1.8</v>
       </c>
       <c r="F23" t="n">
-        <v>46</v>
+        <v>40.5</v>
       </c>
       <c r="G23" t="s">
         <v>15</v>
@@ -1339,36 +1371,36 @@
         <v>18</v>
       </c>
       <c r="I23" t="n">
-        <v>-12.5</v>
+        <v>0.5</v>
       </c>
       <c r="J23" t="n">
-        <v>52</v>
+        <v>48.5</v>
       </c>
       <c r="K23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" t="s">
         <v>36</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>37</v>
       </c>
-      <c r="D24" t="s">
-        <v>38</v>
-      </c>
       <c r="E24" t="n">
-        <v>-3.3</v>
+        <v>0.9</v>
       </c>
       <c r="F24" t="n">
-        <v>23</v>
+        <v>20.4</v>
       </c>
       <c r="G24" t="s">
         <v>19</v>
@@ -1377,36 +1409,36 @@
         <v>16</v>
       </c>
       <c r="I24" t="n">
-        <v>-12.5</v>
+        <v>0.5</v>
       </c>
       <c r="J24" t="n">
-        <v>52</v>
+        <v>48.5</v>
       </c>
       <c r="K24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" t="s">
         <v>36</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>37</v>
       </c>
-      <c r="D25" t="s">
-        <v>38</v>
-      </c>
       <c r="E25" t="n">
-        <v>-3.3</v>
+        <v>0.9</v>
       </c>
       <c r="F25" t="n">
-        <v>23</v>
+        <v>20.3</v>
       </c>
       <c r="G25" t="s">
         <v>19</v>
@@ -1415,36 +1447,36 @@
         <v>18</v>
       </c>
       <c r="I25" t="n">
-        <v>-12.5</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
-        <v>52</v>
+        <v>48.5</v>
       </c>
       <c r="K25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B26" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" t="s">
         <v>40</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>41</v>
       </c>
-      <c r="D26" t="s">
-        <v>42</v>
-      </c>
       <c r="E26" t="n">
-        <v>2.1</v>
+        <v>-4</v>
       </c>
       <c r="F26" t="n">
-        <v>44.4</v>
+        <v>46.3</v>
       </c>
       <c r="G26" t="s">
         <v>15</v>
@@ -1453,13 +1485,13 @@
         <v>16</v>
       </c>
       <c r="I26" t="n">
-        <v>7</v>
+        <v>-4.5</v>
       </c>
       <c r="J26" t="n">
-        <v>49</v>
+        <v>48.5</v>
       </c>
       <c r="K26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -1467,22 +1499,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B27" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" t="s">
         <v>40</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>41</v>
       </c>
-      <c r="D27" t="s">
-        <v>42</v>
-      </c>
       <c r="E27" t="n">
-        <v>2.1</v>
+        <v>-4</v>
       </c>
       <c r="F27" t="n">
-        <v>44.4</v>
+        <v>46.3</v>
       </c>
       <c r="G27" t="s">
         <v>15</v>
@@ -1491,13 +1523,13 @@
         <v>18</v>
       </c>
       <c r="I27" t="n">
-        <v>7</v>
+        <v>-4.5</v>
       </c>
       <c r="J27" t="n">
-        <v>49</v>
+        <v>48.5</v>
       </c>
       <c r="K27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -1505,22 +1537,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B28" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" t="s">
         <v>40</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>41</v>
       </c>
-      <c r="D28" t="s">
-        <v>42</v>
-      </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="F28" t="n">
-        <v>22.2</v>
+        <v>23.1</v>
       </c>
       <c r="G28" t="s">
         <v>19</v>
@@ -1529,13 +1561,13 @@
         <v>16</v>
       </c>
       <c r="I28" t="n">
-        <v>7</v>
+        <v>-4.5</v>
       </c>
       <c r="J28" t="n">
-        <v>49</v>
+        <v>48.5</v>
       </c>
       <c r="K28" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -1543,22 +1575,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B29" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" t="s">
         <v>40</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>41</v>
       </c>
-      <c r="D29" t="s">
-        <v>42</v>
-      </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="F29" t="n">
-        <v>22.2</v>
+        <v>23.1</v>
       </c>
       <c r="G29" t="s">
         <v>19</v>
@@ -1567,13 +1599,13 @@
         <v>18</v>
       </c>
       <c r="I29" t="n">
-        <v>7</v>
+        <v>-4.5</v>
       </c>
       <c r="J29" t="n">
-        <v>49</v>
+        <v>48.5</v>
       </c>
       <c r="K29" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -1581,22 +1613,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46240</v>
+        <v>46242</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C30" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D30" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>-3.4</v>
       </c>
       <c r="F30" t="n">
-        <v>45.7</v>
+        <v>46.3</v>
       </c>
       <c r="G30" t="s">
         <v>15</v>
@@ -1605,36 +1637,36 @@
         <v>16</v>
       </c>
       <c r="I30" t="n">
-        <v>2.5</v>
+        <v>-6</v>
       </c>
       <c r="J30" t="n">
-        <v>47.5</v>
+        <v>45.5</v>
       </c>
       <c r="K30" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46240</v>
+        <v>46242</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C31" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D31" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>-3.4</v>
       </c>
       <c r="F31" t="n">
-        <v>45.7</v>
+        <v>46.1</v>
       </c>
       <c r="G31" t="s">
         <v>15</v>
@@ -1643,36 +1675,36 @@
         <v>18</v>
       </c>
       <c r="I31" t="n">
-        <v>2.5</v>
+        <v>-6</v>
       </c>
       <c r="J31" t="n">
-        <v>47.5</v>
+        <v>45.5</v>
       </c>
       <c r="K31" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46240</v>
+        <v>46242</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C32" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D32" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="E32" t="n">
-        <v>0.5</v>
+        <v>-1.7</v>
       </c>
       <c r="F32" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="G32" t="s">
         <v>19</v>
@@ -1681,36 +1713,36 @@
         <v>16</v>
       </c>
       <c r="I32" t="n">
-        <v>2.5</v>
+        <v>-6</v>
       </c>
       <c r="J32" t="n">
-        <v>47.5</v>
+        <v>45.5</v>
       </c>
       <c r="K32" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46240</v>
+        <v>46242</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C33" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D33" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5</v>
+        <v>-1.7</v>
       </c>
       <c r="F33" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="G33" t="s">
         <v>19</v>
@@ -1719,36 +1751,36 @@
         <v>18</v>
       </c>
       <c r="I33" t="n">
-        <v>2.5</v>
+        <v>-6</v>
       </c>
       <c r="J33" t="n">
-        <v>47.5</v>
+        <v>45.5</v>
       </c>
       <c r="K33" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="B34" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C34" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D34" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="E34" t="n">
-        <v>-9.5</v>
+        <v>-1.9</v>
       </c>
       <c r="F34" t="n">
-        <v>39.1</v>
+        <v>44</v>
       </c>
       <c r="G34" t="s">
         <v>15</v>
@@ -1757,36 +1789,36 @@
         <v>16</v>
       </c>
       <c r="I34" t="n">
-        <v>-8.5</v>
+        <v>-4.5</v>
       </c>
       <c r="J34" t="n">
-        <v>45.5</v>
+        <v>51.5</v>
       </c>
       <c r="K34" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L34" t="n">
-        <v>0.2</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="B35" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C35" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D35" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="E35" t="n">
-        <v>-9.5</v>
+        <v>-1.9</v>
       </c>
       <c r="F35" t="n">
-        <v>39</v>
+        <v>41.6</v>
       </c>
       <c r="G35" t="s">
         <v>15</v>
@@ -1795,36 +1827,36 @@
         <v>18</v>
       </c>
       <c r="I35" t="n">
-        <v>-8.5</v>
+        <v>-4.5</v>
       </c>
       <c r="J35" t="n">
-        <v>45.5</v>
+        <v>51.5</v>
       </c>
       <c r="K35" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="B36" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C36" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D36" t="s">
+        <v>45</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="F36" t="n">
         <v>22</v>
-      </c>
-      <c r="E36" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="F36" t="n">
-        <v>19.6</v>
       </c>
       <c r="G36" t="s">
         <v>19</v>
@@ -1833,36 +1865,36 @@
         <v>16</v>
       </c>
       <c r="I36" t="n">
-        <v>-8.5</v>
+        <v>-4.5</v>
       </c>
       <c r="J36" t="n">
-        <v>45.5</v>
+        <v>51.5</v>
       </c>
       <c r="K36" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L36" t="n">
-        <v>0.2</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="B37" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C37" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D37" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="E37" t="n">
-        <v>-4.7</v>
+        <v>-0.9</v>
       </c>
       <c r="F37" t="n">
-        <v>19.5</v>
+        <v>20.8</v>
       </c>
       <c r="G37" t="s">
         <v>19</v>
@@ -1871,36 +1903,36 @@
         <v>18</v>
       </c>
       <c r="I37" t="n">
-        <v>-8.5</v>
+        <v>-4.5</v>
       </c>
       <c r="J37" t="n">
-        <v>45.5</v>
+        <v>51.5</v>
       </c>
       <c r="K37" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L37" t="n">
-        <v>0.2</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="B38" t="s">
         <v>20</v>
       </c>
       <c r="C38" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="D38" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.2</v>
+        <v>10.8</v>
       </c>
       <c r="F38" t="n">
-        <v>38.3</v>
+        <v>42.6</v>
       </c>
       <c r="G38" t="s">
         <v>15</v>
@@ -1909,36 +1941,36 @@
         <v>16</v>
       </c>
       <c r="I38" t="n">
-        <v>5</v>
+        <v>14.5</v>
       </c>
       <c r="J38" t="n">
-        <v>40.5</v>
+        <v>50.5</v>
       </c>
       <c r="K38" t="s">
         <v>48</v>
       </c>
       <c r="L38" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="B39" t="s">
         <v>20</v>
       </c>
       <c r="C39" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="D39" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.2</v>
+        <v>10.8</v>
       </c>
       <c r="F39" t="n">
-        <v>37.5</v>
+        <v>41.7</v>
       </c>
       <c r="G39" t="s">
         <v>15</v>
@@ -1947,36 +1979,36 @@
         <v>18</v>
       </c>
       <c r="I39" t="n">
-        <v>5</v>
+        <v>14.5</v>
       </c>
       <c r="J39" t="n">
-        <v>40.5</v>
+        <v>50.5</v>
       </c>
       <c r="K39" t="s">
         <v>48</v>
       </c>
       <c r="L39" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="B40" t="s">
         <v>20</v>
       </c>
       <c r="C40" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="D40" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.1</v>
+        <v>5.4</v>
       </c>
       <c r="F40" t="n">
-        <v>19.2</v>
+        <v>21.3</v>
       </c>
       <c r="G40" t="s">
         <v>19</v>
@@ -1985,36 +2017,36 @@
         <v>16</v>
       </c>
       <c r="I40" t="n">
-        <v>5</v>
+        <v>14.5</v>
       </c>
       <c r="J40" t="n">
-        <v>40.5</v>
+        <v>50.5</v>
       </c>
       <c r="K40" t="s">
         <v>48</v>
       </c>
       <c r="L40" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="B41" t="s">
         <v>20</v>
       </c>
       <c r="C41" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="D41" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.1</v>
+        <v>5.4</v>
       </c>
       <c r="F41" t="n">
-        <v>18.8</v>
+        <v>20.9</v>
       </c>
       <c r="G41" t="s">
         <v>19</v>
@@ -2023,16 +2055,16 @@
         <v>18</v>
       </c>
       <c r="I41" t="n">
-        <v>5</v>
+        <v>14.5</v>
       </c>
       <c r="J41" t="n">
-        <v>40.5</v>
+        <v>50.5</v>
       </c>
       <c r="K41" t="s">
         <v>48</v>
       </c>
       <c r="L41" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_upcoming_projections.xlsx
+++ b/files/NRL_upcoming_projections.xlsx
@@ -561,7 +561,7 @@
         <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>-8.1</v>
+        <v>-5.3</v>
       </c>
       <c r="F2" t="n">
         <v>46</v>
@@ -599,7 +599,7 @@
         <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>-8.1</v>
+        <v>-5.3</v>
       </c>
       <c r="F3" t="n">
         <v>46</v>
@@ -637,7 +637,7 @@
         <v>14</v>
       </c>
       <c r="E4" t="n">
-        <v>-4</v>
+        <v>-2.7</v>
       </c>
       <c r="F4" t="n">
         <v>23</v>
@@ -675,7 +675,7 @@
         <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>-4</v>
+        <v>-2.7</v>
       </c>
       <c r="F5" t="n">
         <v>23</v>
@@ -713,7 +713,7 @@
         <v>22</v>
       </c>
       <c r="E6" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="F6" t="n">
         <v>44.4</v>
@@ -751,7 +751,7 @@
         <v>22</v>
       </c>
       <c r="E7" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="F7" t="n">
         <v>44.4</v>
@@ -789,7 +789,7 @@
         <v>22</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="F8" t="n">
         <v>22.2</v>
@@ -827,7 +827,7 @@
         <v>22</v>
       </c>
       <c r="E9" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="F9" t="n">
         <v>22.2</v>
@@ -865,7 +865,7 @@
         <v>26</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>45.7</v>
@@ -903,7 +903,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>45.7</v>
@@ -941,7 +941,7 @@
         <v>26</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>22.9</v>
@@ -979,7 +979,7 @@
         <v>26</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>22.9</v>
@@ -1017,7 +1017,7 @@
         <v>30</v>
       </c>
       <c r="E14" t="n">
-        <v>-9.5</v>
+        <v>-8.1</v>
       </c>
       <c r="F14" t="n">
         <v>39.1</v>
@@ -1055,7 +1055,7 @@
         <v>30</v>
       </c>
       <c r="E15" t="n">
-        <v>-9.5</v>
+        <v>-8.1</v>
       </c>
       <c r="F15" t="n">
         <v>39.1</v>
@@ -1093,7 +1093,7 @@
         <v>30</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.7</v>
+        <v>-4</v>
       </c>
       <c r="F16" t="n">
         <v>19.6</v>
@@ -1131,7 +1131,7 @@
         <v>30</v>
       </c>
       <c r="E17" t="n">
-        <v>-4.7</v>
+        <v>-4</v>
       </c>
       <c r="F17" t="n">
         <v>19.6</v>
@@ -1169,7 +1169,7 @@
         <v>33</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="F18" t="n">
         <v>38.3</v>
@@ -1207,7 +1207,7 @@
         <v>33</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="F19" t="n">
         <v>38.3</v>
@@ -1245,7 +1245,7 @@
         <v>33</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F20" t="n">
         <v>19.2</v>
@@ -1283,7 +1283,7 @@
         <v>33</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F21" t="n">
         <v>19.2</v>
@@ -1321,7 +1321,7 @@
         <v>37</v>
       </c>
       <c r="E22" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="F22" t="n">
         <v>40.9</v>
@@ -1359,7 +1359,7 @@
         <v>37</v>
       </c>
       <c r="E23" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="F23" t="n">
         <v>40.5</v>
@@ -1397,7 +1397,7 @@
         <v>37</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
         <v>20.4</v>
@@ -1435,7 +1435,7 @@
         <v>37</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
         <v>20.3</v>
@@ -1473,7 +1473,7 @@
         <v>41</v>
       </c>
       <c r="E26" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="F26" t="n">
         <v>46.3</v>
@@ -1511,7 +1511,7 @@
         <v>41</v>
       </c>
       <c r="E27" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="F27" t="n">
         <v>46.3</v>
@@ -1549,7 +1549,7 @@
         <v>41</v>
       </c>
       <c r="E28" t="n">
-        <v>-2</v>
+        <v>-2.5</v>
       </c>
       <c r="F28" t="n">
         <v>23.1</v>
@@ -1587,7 +1587,7 @@
         <v>41</v>
       </c>
       <c r="E29" t="n">
-        <v>-2</v>
+        <v>-2.5</v>
       </c>
       <c r="F29" t="n">
         <v>23.1</v>
@@ -1625,7 +1625,7 @@
         <v>22</v>
       </c>
       <c r="E30" t="n">
-        <v>-3.4</v>
+        <v>-8</v>
       </c>
       <c r="F30" t="n">
         <v>46.3</v>
@@ -1663,7 +1663,7 @@
         <v>22</v>
       </c>
       <c r="E31" t="n">
-        <v>-3.4</v>
+        <v>-8</v>
       </c>
       <c r="F31" t="n">
         <v>46.1</v>
@@ -1701,7 +1701,7 @@
         <v>22</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.7</v>
+        <v>-4</v>
       </c>
       <c r="F32" t="n">
         <v>23.1</v>
@@ -1739,7 +1739,7 @@
         <v>22</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.7</v>
+        <v>-4</v>
       </c>
       <c r="F33" t="n">
         <v>23.1</v>
@@ -1777,7 +1777,7 @@
         <v>45</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.9</v>
+        <v>-1.8</v>
       </c>
       <c r="F34" t="n">
         <v>44</v>
@@ -1815,7 +1815,7 @@
         <v>45</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.9</v>
+        <v>-1.8</v>
       </c>
       <c r="F35" t="n">
         <v>41.6</v>
@@ -1929,7 +1929,7 @@
         <v>13</v>
       </c>
       <c r="E38" t="n">
-        <v>10.8</v>
+        <v>12.1</v>
       </c>
       <c r="F38" t="n">
         <v>42.6</v>
@@ -1967,7 +1967,7 @@
         <v>13</v>
       </c>
       <c r="E39" t="n">
-        <v>10.8</v>
+        <v>12.1</v>
       </c>
       <c r="F39" t="n">
         <v>41.7</v>
@@ -2005,7 +2005,7 @@
         <v>13</v>
       </c>
       <c r="E40" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="F40" t="n">
         <v>21.3</v>
@@ -2043,7 +2043,7 @@
         <v>13</v>
       </c>
       <c r="E41" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="F41" t="n">
         <v>20.9</v>

--- a/files/NRL_upcoming_projections.xlsx
+++ b/files/NRL_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -26,22 +26,22 @@
     <t xml:space="preserve">Away Team</t>
   </si>
   <si>
-    <t xml:space="preserve">Projected Line</t>
+    <t xml:space="preserve">Selected / Hybrid Home Line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEAM Home Line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLAYER Home Line</t>
   </si>
   <si>
     <t xml:space="preserve">Projected Total</t>
   </si>
   <si>
-    <t xml:space="preserve">Market Period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Projection Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Closing Market Line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Closing Market Total</t>
+    <t xml:space="preserve">Market Line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Market Total</t>
   </si>
   <si>
     <t xml:space="preserve">Venue</t>
@@ -59,19 +59,7 @@
     <t xml:space="preserve">south sydney rabbitohs</t>
   </si>
   <si>
-    <t xml:space="preserve">FT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Rain</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sharks Stadium, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1H</t>
   </si>
   <si>
     <t xml:space="preserve">16:05</t>
@@ -499,12 +487,12 @@
     <col min="2" max="2" width="5.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="27.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="29.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="15.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="13.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="16.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="19.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="20.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="27.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="16.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="15.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="11.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="12.71" hidden="0" customWidth="1"/>
     <col min="11" max="11" width="30.71" hidden="0" customWidth="1"/>
     <col min="12" max="12" width="16.71" hidden="0" customWidth="1"/>
   </cols>
@@ -564,13 +552,13 @@
         <v>-5.3</v>
       </c>
       <c r="F2" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H2" t="n">
         <v>46</v>
-      </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" t="s">
-        <v>16</v>
       </c>
       <c r="I2" t="n">
         <v>-12.5</v>
@@ -579,7 +567,7 @@
         <v>52</v>
       </c>
       <c r="K2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -602,13 +590,13 @@
         <v>-5.3</v>
       </c>
       <c r="F3" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H3" t="n">
         <v>46</v>
-      </c>
-      <c r="G3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" t="s">
-        <v>18</v>
       </c>
       <c r="I3" t="n">
         <v>-12.5</v>
@@ -617,7 +605,7 @@
         <v>52</v>
       </c>
       <c r="K3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -640,13 +628,13 @@
         <v>-2.7</v>
       </c>
       <c r="F4" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H4" t="n">
         <v>23</v>
-      </c>
-      <c r="G4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" t="s">
-        <v>16</v>
       </c>
       <c r="I4" t="n">
         <v>-12.5</v>
@@ -655,7 +643,7 @@
         <v>52</v>
       </c>
       <c r="K4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -678,13 +666,13 @@
         <v>-2.7</v>
       </c>
       <c r="F5" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H5" t="n">
         <v>23</v>
-      </c>
-      <c r="G5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" t="s">
-        <v>18</v>
       </c>
       <c r="I5" t="n">
         <v>-12.5</v>
@@ -693,7 +681,7 @@
         <v>52</v>
       </c>
       <c r="K5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -704,25 +692,25 @@
         <v>46236</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E6" t="n">
         <v>3.9</v>
       </c>
       <c r="F6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H6" t="n">
         <v>44.4</v>
-      </c>
-      <c r="G6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" t="s">
-        <v>16</v>
       </c>
       <c r="I6" t="n">
         <v>7</v>
@@ -731,7 +719,7 @@
         <v>49</v>
       </c>
       <c r="K6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -742,25 +730,25 @@
         <v>46236</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E7" t="n">
         <v>3.9</v>
       </c>
       <c r="F7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H7" t="n">
         <v>44.4</v>
-      </c>
-      <c r="G7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" t="s">
-        <v>18</v>
       </c>
       <c r="I7" t="n">
         <v>7</v>
@@ -769,7 +757,7 @@
         <v>49</v>
       </c>
       <c r="K7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -780,25 +768,25 @@
         <v>46236</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E8" t="n">
         <v>1.9</v>
       </c>
       <c r="F8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H8" t="n">
         <v>22.2</v>
-      </c>
-      <c r="G8" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" t="s">
-        <v>16</v>
       </c>
       <c r="I8" t="n">
         <v>7</v>
@@ -807,7 +795,7 @@
         <v>49</v>
       </c>
       <c r="K8" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -818,25 +806,25 @@
         <v>46236</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E9" t="n">
         <v>1.9</v>
       </c>
       <c r="F9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H9" t="n">
         <v>22.2</v>
-      </c>
-      <c r="G9" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" t="s">
-        <v>18</v>
       </c>
       <c r="I9" t="n">
         <v>7</v>
@@ -845,7 +833,7 @@
         <v>49</v>
       </c>
       <c r="K9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -856,25 +844,25 @@
         <v>46240</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="H10" t="n">
         <v>45.7</v>
-      </c>
-      <c r="G10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H10" t="s">
-        <v>16</v>
       </c>
       <c r="I10" t="n">
         <v>2.5</v>
@@ -883,7 +871,7 @@
         <v>47.5</v>
       </c>
       <c r="K10" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -894,25 +882,25 @@
         <v>46240</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="H11" t="n">
         <v>45.7</v>
-      </c>
-      <c r="G11" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" t="s">
-        <v>18</v>
       </c>
       <c r="I11" t="n">
         <v>2.5</v>
@@ -921,7 +909,7 @@
         <v>47.5</v>
       </c>
       <c r="K11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -932,25 +920,25 @@
         <v>46240</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="H12" t="n">
         <v>22.9</v>
-      </c>
-      <c r="G12" t="s">
-        <v>19</v>
-      </c>
-      <c r="H12" t="s">
-        <v>16</v>
       </c>
       <c r="I12" t="n">
         <v>2.5</v>
@@ -959,7 +947,7 @@
         <v>47.5</v>
       </c>
       <c r="K12" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -970,25 +958,25 @@
         <v>46240</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="H13" t="n">
         <v>22.9</v>
-      </c>
-      <c r="G13" t="s">
-        <v>19</v>
-      </c>
-      <c r="H13" t="s">
-        <v>18</v>
       </c>
       <c r="I13" t="n">
         <v>2.5</v>
@@ -997,7 +985,7 @@
         <v>47.5</v>
       </c>
       <c r="K13" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1008,25 +996,25 @@
         <v>46241</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D14" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E14" t="n">
         <v>-8.1</v>
       </c>
       <c r="F14" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="H14" t="n">
         <v>39.1</v>
-      </c>
-      <c r="G14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" t="s">
-        <v>16</v>
       </c>
       <c r="I14" t="n">
         <v>-8.5</v>
@@ -1035,7 +1023,7 @@
         <v>45.5</v>
       </c>
       <c r="K14" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1046,25 +1034,25 @@
         <v>46241</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D15" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E15" t="n">
         <v>-8.1</v>
       </c>
       <c r="F15" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="H15" t="n">
         <v>39.1</v>
-      </c>
-      <c r="G15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H15" t="s">
-        <v>18</v>
       </c>
       <c r="I15" t="n">
         <v>-8.5</v>
@@ -1073,7 +1061,7 @@
         <v>45.5</v>
       </c>
       <c r="K15" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1084,25 +1072,25 @@
         <v>46241</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E16" t="n">
         <v>-4</v>
       </c>
       <c r="F16" t="n">
+        <v>-4</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="H16" t="n">
         <v>19.6</v>
-      </c>
-      <c r="G16" t="s">
-        <v>19</v>
-      </c>
-      <c r="H16" t="s">
-        <v>16</v>
       </c>
       <c r="I16" t="n">
         <v>-8.5</v>
@@ -1111,7 +1099,7 @@
         <v>45.5</v>
       </c>
       <c r="K16" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1122,25 +1110,25 @@
         <v>46241</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D17" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E17" t="n">
         <v>-4</v>
       </c>
       <c r="F17" t="n">
+        <v>-4</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="H17" t="n">
         <v>19.6</v>
-      </c>
-      <c r="G17" t="s">
-        <v>19</v>
-      </c>
-      <c r="H17" t="s">
-        <v>18</v>
       </c>
       <c r="I17" t="n">
         <v>-8.5</v>
@@ -1149,7 +1137,7 @@
         <v>45.5</v>
       </c>
       <c r="K17" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1160,25 +1148,25 @@
         <v>46241</v>
       </c>
       <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" t="s">
         <v>28</v>
       </c>
-      <c r="C18" t="s">
-        <v>32</v>
-      </c>
       <c r="D18" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E18" t="n">
         <v>1.1</v>
       </c>
       <c r="F18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H18" t="n">
         <v>38.3</v>
-      </c>
-      <c r="G18" t="s">
-        <v>15</v>
-      </c>
-      <c r="H18" t="s">
-        <v>16</v>
       </c>
       <c r="I18" t="n">
         <v>5</v>
@@ -1187,7 +1175,7 @@
         <v>40.5</v>
       </c>
       <c r="K18" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1198,25 +1186,25 @@
         <v>46241</v>
       </c>
       <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" t="s">
         <v>28</v>
       </c>
-      <c r="C19" t="s">
-        <v>32</v>
-      </c>
       <c r="D19" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E19" t="n">
         <v>1.1</v>
       </c>
       <c r="F19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H19" t="n">
         <v>38.3</v>
-      </c>
-      <c r="G19" t="s">
-        <v>15</v>
-      </c>
-      <c r="H19" t="s">
-        <v>18</v>
       </c>
       <c r="I19" t="n">
         <v>5</v>
@@ -1225,7 +1213,7 @@
         <v>40.5</v>
       </c>
       <c r="K19" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1236,25 +1224,25 @@
         <v>46241</v>
       </c>
       <c r="B20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" t="s">
         <v>28</v>
       </c>
-      <c r="C20" t="s">
-        <v>32</v>
-      </c>
       <c r="D20" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E20" t="n">
         <v>0.5</v>
       </c>
       <c r="F20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H20" t="n">
         <v>19.2</v>
-      </c>
-      <c r="G20" t="s">
-        <v>19</v>
-      </c>
-      <c r="H20" t="s">
-        <v>16</v>
       </c>
       <c r="I20" t="n">
         <v>5</v>
@@ -1263,7 +1251,7 @@
         <v>40.5</v>
       </c>
       <c r="K20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1274,25 +1262,25 @@
         <v>46241</v>
       </c>
       <c r="B21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" t="s">
         <v>28</v>
       </c>
-      <c r="C21" t="s">
-        <v>32</v>
-      </c>
       <c r="D21" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E21" t="n">
         <v>0.5</v>
       </c>
       <c r="F21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H21" t="n">
         <v>19.2</v>
-      </c>
-      <c r="G21" t="s">
-        <v>19</v>
-      </c>
-      <c r="H21" t="s">
-        <v>18</v>
       </c>
       <c r="I21" t="n">
         <v>5</v>
@@ -1301,7 +1289,7 @@
         <v>40.5</v>
       </c>
       <c r="K21" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -1312,25 +1300,25 @@
         <v>46242</v>
       </c>
       <c r="B22" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C22" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D22" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E22" t="n">
         <v>2.1</v>
       </c>
       <c r="F22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
         <v>40.9</v>
-      </c>
-      <c r="G22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H22" t="s">
-        <v>16</v>
       </c>
       <c r="I22" t="n">
         <v>0.5</v>
@@ -1339,7 +1327,7 @@
         <v>48.5</v>
       </c>
       <c r="K22" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="L22" t="n">
         <v>0.5</v>
@@ -1350,25 +1338,25 @@
         <v>46242</v>
       </c>
       <c r="B23" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C23" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D23" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E23" t="n">
         <v>2.1</v>
       </c>
       <c r="F23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
         <v>40.5</v>
-      </c>
-      <c r="G23" t="s">
-        <v>15</v>
-      </c>
-      <c r="H23" t="s">
-        <v>18</v>
       </c>
       <c r="I23" t="n">
         <v>0.5</v>
@@ -1377,7 +1365,7 @@
         <v>48.5</v>
       </c>
       <c r="K23" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="L23" t="n">
         <v>0.5</v>
@@ -1388,25 +1376,25 @@
         <v>46242</v>
       </c>
       <c r="B24" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C24" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D24" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
       </c>
       <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H24" t="n">
         <v>20.4</v>
-      </c>
-      <c r="G24" t="s">
-        <v>19</v>
-      </c>
-      <c r="H24" t="s">
-        <v>16</v>
       </c>
       <c r="I24" t="n">
         <v>0.5</v>
@@ -1415,7 +1403,7 @@
         <v>48.5</v>
       </c>
       <c r="K24" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="L24" t="n">
         <v>0.5</v>
@@ -1426,25 +1414,25 @@
         <v>46242</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C25" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D25" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
       </c>
       <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H25" t="n">
         <v>20.3</v>
-      </c>
-      <c r="G25" t="s">
-        <v>19</v>
-      </c>
-      <c r="H25" t="s">
-        <v>18</v>
       </c>
       <c r="I25" t="n">
         <v>0.5</v>
@@ -1453,7 +1441,7 @@
         <v>48.5</v>
       </c>
       <c r="K25" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="L25" t="n">
         <v>0.5</v>
@@ -1464,25 +1452,25 @@
         <v>46242</v>
       </c>
       <c r="B26" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C26" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D26" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E26" t="n">
         <v>-5</v>
       </c>
       <c r="F26" t="n">
+        <v>-5</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H26" t="n">
         <v>46.3</v>
-      </c>
-      <c r="G26" t="s">
-        <v>15</v>
-      </c>
-      <c r="H26" t="s">
-        <v>16</v>
       </c>
       <c r="I26" t="n">
         <v>-4.5</v>
@@ -1491,7 +1479,7 @@
         <v>48.5</v>
       </c>
       <c r="K26" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -1502,25 +1490,25 @@
         <v>46242</v>
       </c>
       <c r="B27" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C27" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D27" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E27" t="n">
         <v>-5</v>
       </c>
       <c r="F27" t="n">
+        <v>-5</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H27" t="n">
         <v>46.3</v>
-      </c>
-      <c r="G27" t="s">
-        <v>15</v>
-      </c>
-      <c r="H27" t="s">
-        <v>18</v>
       </c>
       <c r="I27" t="n">
         <v>-4.5</v>
@@ -1529,7 +1517,7 @@
         <v>48.5</v>
       </c>
       <c r="K27" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -1540,25 +1528,25 @@
         <v>46242</v>
       </c>
       <c r="B28" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C28" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D28" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E28" t="n">
         <v>-2.5</v>
       </c>
       <c r="F28" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H28" t="n">
         <v>23.1</v>
-      </c>
-      <c r="G28" t="s">
-        <v>19</v>
-      </c>
-      <c r="H28" t="s">
-        <v>16</v>
       </c>
       <c r="I28" t="n">
         <v>-4.5</v>
@@ -1567,7 +1555,7 @@
         <v>48.5</v>
       </c>
       <c r="K28" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -1578,25 +1566,25 @@
         <v>46242</v>
       </c>
       <c r="B29" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C29" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D29" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E29" t="n">
         <v>-2.5</v>
       </c>
       <c r="F29" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H29" t="n">
         <v>23.1</v>
-      </c>
-      <c r="G29" t="s">
-        <v>19</v>
-      </c>
-      <c r="H29" t="s">
-        <v>18</v>
       </c>
       <c r="I29" t="n">
         <v>-4.5</v>
@@ -1605,7 +1593,7 @@
         <v>48.5</v>
       </c>
       <c r="K29" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -1616,25 +1604,25 @@
         <v>46242</v>
       </c>
       <c r="B30" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C30" t="s">
         <v>14</v>
       </c>
       <c r="D30" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E30" t="n">
         <v>-8</v>
       </c>
       <c r="F30" t="n">
+        <v>-8</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H30" t="n">
         <v>46.3</v>
-      </c>
-      <c r="G30" t="s">
-        <v>15</v>
-      </c>
-      <c r="H30" t="s">
-        <v>16</v>
       </c>
       <c r="I30" t="n">
         <v>-6</v>
@@ -1643,7 +1631,7 @@
         <v>45.5</v>
       </c>
       <c r="K30" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L30" t="n">
         <v>0.2</v>
@@ -1654,25 +1642,25 @@
         <v>46242</v>
       </c>
       <c r="B31" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C31" t="s">
         <v>14</v>
       </c>
       <c r="D31" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E31" t="n">
         <v>-8</v>
       </c>
       <c r="F31" t="n">
+        <v>-8</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H31" t="n">
         <v>46.1</v>
-      </c>
-      <c r="G31" t="s">
-        <v>15</v>
-      </c>
-      <c r="H31" t="s">
-        <v>18</v>
       </c>
       <c r="I31" t="n">
         <v>-6</v>
@@ -1681,7 +1669,7 @@
         <v>45.5</v>
       </c>
       <c r="K31" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L31" t="n">
         <v>0.2</v>
@@ -1692,25 +1680,25 @@
         <v>46242</v>
       </c>
       <c r="B32" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C32" t="s">
         <v>14</v>
       </c>
       <c r="D32" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E32" t="n">
         <v>-4</v>
       </c>
       <c r="F32" t="n">
+        <v>-4</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H32" t="n">
         <v>23.1</v>
-      </c>
-      <c r="G32" t="s">
-        <v>19</v>
-      </c>
-      <c r="H32" t="s">
-        <v>16</v>
       </c>
       <c r="I32" t="n">
         <v>-6</v>
@@ -1719,7 +1707,7 @@
         <v>45.5</v>
       </c>
       <c r="K32" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L32" t="n">
         <v>0.2</v>
@@ -1730,25 +1718,25 @@
         <v>46242</v>
       </c>
       <c r="B33" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C33" t="s">
         <v>14</v>
       </c>
       <c r="D33" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E33" t="n">
         <v>-4</v>
       </c>
       <c r="F33" t="n">
+        <v>-4</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H33" t="n">
         <v>23.1</v>
-      </c>
-      <c r="G33" t="s">
-        <v>19</v>
-      </c>
-      <c r="H33" t="s">
-        <v>18</v>
       </c>
       <c r="I33" t="n">
         <v>-6</v>
@@ -1757,7 +1745,7 @@
         <v>45.5</v>
       </c>
       <c r="K33" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L33" t="n">
         <v>0.2</v>
@@ -1771,22 +1759,22 @@
         <v>12</v>
       </c>
       <c r="C34" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D34" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E34" t="n">
         <v>-1.8</v>
       </c>
       <c r="F34" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="H34" t="n">
         <v>44</v>
-      </c>
-      <c r="G34" t="s">
-        <v>15</v>
-      </c>
-      <c r="H34" t="s">
-        <v>16</v>
       </c>
       <c r="I34" t="n">
         <v>-4.5</v>
@@ -1795,7 +1783,7 @@
         <v>51.5</v>
       </c>
       <c r="K34" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L34" t="n">
         <v>17.8</v>
@@ -1809,22 +1797,22 @@
         <v>12</v>
       </c>
       <c r="C35" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D35" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E35" t="n">
         <v>-1.8</v>
       </c>
       <c r="F35" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="H35" t="n">
         <v>41.6</v>
-      </c>
-      <c r="G35" t="s">
-        <v>15</v>
-      </c>
-      <c r="H35" t="s">
-        <v>18</v>
       </c>
       <c r="I35" t="n">
         <v>-4.5</v>
@@ -1833,7 +1821,7 @@
         <v>51.5</v>
       </c>
       <c r="K35" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L35" t="n">
         <v>17.8</v>
@@ -1847,22 +1835,22 @@
         <v>12</v>
       </c>
       <c r="C36" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D36" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E36" t="n">
         <v>-0.9</v>
       </c>
       <c r="F36" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H36" t="n">
         <v>22</v>
-      </c>
-      <c r="G36" t="s">
-        <v>19</v>
-      </c>
-      <c r="H36" t="s">
-        <v>16</v>
       </c>
       <c r="I36" t="n">
         <v>-4.5</v>
@@ -1871,7 +1859,7 @@
         <v>51.5</v>
       </c>
       <c r="K36" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L36" t="n">
         <v>17.8</v>
@@ -1885,22 +1873,22 @@
         <v>12</v>
       </c>
       <c r="C37" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D37" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E37" t="n">
         <v>-0.9</v>
       </c>
       <c r="F37" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H37" t="n">
         <v>20.8</v>
-      </c>
-      <c r="G37" t="s">
-        <v>19</v>
-      </c>
-      <c r="H37" t="s">
-        <v>18</v>
       </c>
       <c r="I37" t="n">
         <v>-4.5</v>
@@ -1909,7 +1897,7 @@
         <v>51.5</v>
       </c>
       <c r="K37" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L37" t="n">
         <v>17.8</v>
@@ -1920,10 +1908,10 @@
         <v>46243</v>
       </c>
       <c r="B38" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C38" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D38" t="s">
         <v>13</v>
@@ -1932,13 +1920,13 @@
         <v>12.1</v>
       </c>
       <c r="F38" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="n">
         <v>42.6</v>
-      </c>
-      <c r="G38" t="s">
-        <v>15</v>
-      </c>
-      <c r="H38" t="s">
-        <v>16</v>
       </c>
       <c r="I38" t="n">
         <v>14.5</v>
@@ -1947,7 +1935,7 @@
         <v>50.5</v>
       </c>
       <c r="K38" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="L38" t="n">
         <v>2</v>
@@ -1958,10 +1946,10 @@
         <v>46243</v>
       </c>
       <c r="B39" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C39" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D39" t="s">
         <v>13</v>
@@ -1970,13 +1958,13 @@
         <v>12.1</v>
       </c>
       <c r="F39" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" t="n">
         <v>41.7</v>
-      </c>
-      <c r="G39" t="s">
-        <v>15</v>
-      </c>
-      <c r="H39" t="s">
-        <v>18</v>
       </c>
       <c r="I39" t="n">
         <v>14.5</v>
@@ -1985,7 +1973,7 @@
         <v>50.5</v>
       </c>
       <c r="K39" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="L39" t="n">
         <v>2</v>
@@ -1996,10 +1984,10 @@
         <v>46243</v>
       </c>
       <c r="B40" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C40" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D40" t="s">
         <v>13</v>
@@ -2008,13 +1996,13 @@
         <v>6</v>
       </c>
       <c r="F40" t="n">
+        <v>6</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H40" t="n">
         <v>21.3</v>
-      </c>
-      <c r="G40" t="s">
-        <v>19</v>
-      </c>
-      <c r="H40" t="s">
-        <v>16</v>
       </c>
       <c r="I40" t="n">
         <v>14.5</v>
@@ -2023,7 +2011,7 @@
         <v>50.5</v>
       </c>
       <c r="K40" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="L40" t="n">
         <v>2</v>
@@ -2034,10 +2022,10 @@
         <v>46243</v>
       </c>
       <c r="B41" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C41" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D41" t="s">
         <v>13</v>
@@ -2046,13 +2034,13 @@
         <v>6</v>
       </c>
       <c r="F41" t="n">
+        <v>6</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H41" t="n">
         <v>20.9</v>
-      </c>
-      <c r="G41" t="s">
-        <v>19</v>
-      </c>
-      <c r="H41" t="s">
-        <v>18</v>
       </c>
       <c r="I41" t="n">
         <v>14.5</v>
@@ -2061,7 +2049,7 @@
         <v>50.5</v>
       </c>
       <c r="K41" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="L41" t="n">
         <v>2</v>

--- a/files/NRL_upcoming_projections.xlsx
+++ b/files/NRL_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -38,6 +38,12 @@
     <t xml:space="preserve">Projected Total</t>
   </si>
   <si>
+    <t xml:space="preserve">Market Period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projection Type</t>
+  </si>
+  <si>
     <t xml:space="preserve">Market Line</t>
   </si>
   <si>
@@ -59,7 +65,19 @@
     <t xml:space="preserve">south sydney rabbitohs</t>
   </si>
   <si>
+    <t xml:space="preserve">FT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Rain</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sharks Stadium, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1H</t>
   </si>
   <si>
     <t xml:space="preserve">16:05</t>
@@ -491,10 +509,12 @@
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="16.71" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="15.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="11.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="12.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="30.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="16.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="13.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="16.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="11.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="12.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="30.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="16.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -534,19 +554,25 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
         <v>46236</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E2" t="n">
         <v>-5.3</v>
@@ -560,16 +586,22 @@
       <c r="H2" t="n">
         <v>46</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" t="n">
         <v>-12.5</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>52</v>
       </c>
-      <c r="K2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" t="n">
+      <c r="M2" t="s">
+        <v>19</v>
+      </c>
+      <c r="N2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -578,13 +610,13 @@
         <v>46236</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
         <v>-5.3</v>
@@ -598,16 +630,22 @@
       <c r="H3" t="n">
         <v>46</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" t="n">
         <v>-12.5</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>52</v>
       </c>
-      <c r="K3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L3" t="n">
+      <c r="M3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -616,13 +654,13 @@
         <v>46236</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E4" t="n">
         <v>-2.7</v>
@@ -636,16 +674,22 @@
       <c r="H4" t="n">
         <v>23</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K4" t="n">
         <v>-12.5</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>52</v>
       </c>
-      <c r="K4" t="s">
-        <v>15</v>
-      </c>
-      <c r="L4" t="n">
+      <c r="M4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -654,13 +698,13 @@
         <v>46236</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
         <v>-2.7</v>
@@ -674,16 +718,22 @@
       <c r="H5" t="n">
         <v>23</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" t="n">
         <v>-12.5</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>52</v>
       </c>
-      <c r="K5" t="s">
-        <v>15</v>
-      </c>
-      <c r="L5" t="n">
+      <c r="M5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -692,13 +742,13 @@
         <v>46236</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E6" t="n">
         <v>3.9</v>
@@ -712,16 +762,22 @@
       <c r="H6" t="n">
         <v>44.4</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K6" t="n">
         <v>7</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>49</v>
       </c>
-      <c r="K6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L6" t="n">
+      <c r="M6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -730,13 +786,13 @@
         <v>46236</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E7" t="n">
         <v>3.9</v>
@@ -750,16 +806,22 @@
       <c r="H7" t="n">
         <v>44.4</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" t="n">
         <v>7</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>49</v>
       </c>
-      <c r="K7" t="s">
-        <v>19</v>
-      </c>
-      <c r="L7" t="n">
+      <c r="M7" t="s">
+        <v>25</v>
+      </c>
+      <c r="N7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -768,13 +830,13 @@
         <v>46236</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E8" t="n">
         <v>1.9</v>
@@ -788,16 +850,22 @@
       <c r="H8" t="n">
         <v>22.2</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" t="s">
+        <v>18</v>
+      </c>
+      <c r="K8" t="n">
         <v>7</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>49</v>
       </c>
-      <c r="K8" t="s">
-        <v>19</v>
-      </c>
-      <c r="L8" t="n">
+      <c r="M8" t="s">
+        <v>25</v>
+      </c>
+      <c r="N8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -806,13 +874,13 @@
         <v>46236</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E9" t="n">
         <v>1.9</v>
@@ -826,16 +894,22 @@
       <c r="H9" t="n">
         <v>22.2</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K9" t="n">
         <v>7</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>49</v>
       </c>
-      <c r="K9" t="s">
-        <v>19</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="M9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -844,13 +918,13 @@
         <v>46240</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -864,16 +938,22 @@
       <c r="H10" t="n">
         <v>45.7</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" t="s">
+        <v>18</v>
+      </c>
+      <c r="K10" t="n">
         <v>2.5</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>47.5</v>
       </c>
-      <c r="K10" t="s">
-        <v>23</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="M10" t="s">
+        <v>29</v>
+      </c>
+      <c r="N10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -882,13 +962,13 @@
         <v>46240</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -902,16 +982,22 @@
       <c r="H11" t="n">
         <v>45.7</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" t="s">
+        <v>20</v>
+      </c>
+      <c r="K11" t="n">
         <v>2.5</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>47.5</v>
       </c>
-      <c r="K11" t="s">
-        <v>23</v>
-      </c>
-      <c r="L11" t="n">
+      <c r="M11" t="s">
+        <v>29</v>
+      </c>
+      <c r="N11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -920,13 +1006,13 @@
         <v>46240</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -940,16 +1026,22 @@
       <c r="H12" t="n">
         <v>22.9</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" t="s">
+        <v>21</v>
+      </c>
+      <c r="J12" t="s">
+        <v>18</v>
+      </c>
+      <c r="K12" t="n">
         <v>2.5</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>47.5</v>
       </c>
-      <c r="K12" t="s">
-        <v>23</v>
-      </c>
-      <c r="L12" t="n">
+      <c r="M12" t="s">
+        <v>29</v>
+      </c>
+      <c r="N12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -958,13 +1050,13 @@
         <v>46240</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D13" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -978,16 +1070,22 @@
       <c r="H13" t="n">
         <v>22.9</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K13" t="n">
         <v>2.5</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>47.5</v>
       </c>
-      <c r="K13" t="s">
-        <v>23</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="M13" t="s">
+        <v>29</v>
+      </c>
+      <c r="N13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -996,13 +1094,13 @@
         <v>46241</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E14" t="n">
         <v>-8.1</v>
@@ -1016,16 +1114,22 @@
       <c r="H14" t="n">
         <v>39.1</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" t="s">
+        <v>18</v>
+      </c>
+      <c r="K14" t="n">
         <v>-8.5</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>45.5</v>
       </c>
-      <c r="K14" t="s">
-        <v>27</v>
-      </c>
-      <c r="L14" t="n">
+      <c r="M14" t="s">
+        <v>33</v>
+      </c>
+      <c r="N14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1034,13 +1138,13 @@
         <v>46241</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D15" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E15" t="n">
         <v>-8.1</v>
@@ -1054,16 +1158,22 @@
       <c r="H15" t="n">
         <v>39.1</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K15" t="n">
         <v>-8.5</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>45.5</v>
       </c>
-      <c r="K15" t="s">
-        <v>27</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="M15" t="s">
+        <v>33</v>
+      </c>
+      <c r="N15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1072,13 +1182,13 @@
         <v>46241</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D16" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E16" t="n">
         <v>-4</v>
@@ -1092,16 +1202,22 @@
       <c r="H16" t="n">
         <v>19.6</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16" t="s">
+        <v>21</v>
+      </c>
+      <c r="J16" t="s">
+        <v>18</v>
+      </c>
+      <c r="K16" t="n">
         <v>-8.5</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>45.5</v>
       </c>
-      <c r="K16" t="s">
-        <v>27</v>
-      </c>
-      <c r="L16" t="n">
+      <c r="M16" t="s">
+        <v>33</v>
+      </c>
+      <c r="N16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1110,13 +1226,13 @@
         <v>46241</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D17" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E17" t="n">
         <v>-4</v>
@@ -1130,16 +1246,22 @@
       <c r="H17" t="n">
         <v>19.6</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" t="s">
+        <v>20</v>
+      </c>
+      <c r="K17" t="n">
         <v>-8.5</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>45.5</v>
       </c>
-      <c r="K17" t="s">
-        <v>27</v>
-      </c>
-      <c r="L17" t="n">
+      <c r="M17" t="s">
+        <v>33</v>
+      </c>
+      <c r="N17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1148,13 +1270,13 @@
         <v>46241</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D18" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E18" t="n">
         <v>1.1</v>
@@ -1168,16 +1290,22 @@
       <c r="H18" t="n">
         <v>38.3</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" t="s">
+        <v>18</v>
+      </c>
+      <c r="K18" t="n">
         <v>5</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>40.5</v>
       </c>
-      <c r="K18" t="s">
-        <v>30</v>
-      </c>
-      <c r="L18" t="n">
+      <c r="M18" t="s">
+        <v>36</v>
+      </c>
+      <c r="N18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1186,13 +1314,13 @@
         <v>46241</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D19" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E19" t="n">
         <v>1.1</v>
@@ -1206,16 +1334,22 @@
       <c r="H19" t="n">
         <v>38.3</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" t="s">
+        <v>20</v>
+      </c>
+      <c r="K19" t="n">
         <v>5</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>40.5</v>
       </c>
-      <c r="K19" t="s">
-        <v>30</v>
-      </c>
-      <c r="L19" t="n">
+      <c r="M19" t="s">
+        <v>36</v>
+      </c>
+      <c r="N19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1224,13 +1358,13 @@
         <v>46241</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D20" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E20" t="n">
         <v>0.5</v>
@@ -1244,16 +1378,22 @@
       <c r="H20" t="n">
         <v>19.2</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" t="s">
+        <v>18</v>
+      </c>
+      <c r="K20" t="n">
         <v>5</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>40.5</v>
       </c>
-      <c r="K20" t="s">
-        <v>30</v>
-      </c>
-      <c r="L20" t="n">
+      <c r="M20" t="s">
+        <v>36</v>
+      </c>
+      <c r="N20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1262,13 +1402,13 @@
         <v>46241</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D21" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E21" t="n">
         <v>0.5</v>
@@ -1282,16 +1422,22 @@
       <c r="H21" t="n">
         <v>19.2</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" t="s">
+        <v>20</v>
+      </c>
+      <c r="K21" t="n">
         <v>5</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>40.5</v>
       </c>
-      <c r="K21" t="s">
-        <v>30</v>
-      </c>
-      <c r="L21" t="n">
+      <c r="M21" t="s">
+        <v>36</v>
+      </c>
+      <c r="N21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1300,13 +1446,13 @@
         <v>46242</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D22" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E22" t="n">
         <v>2.1</v>
@@ -1320,16 +1466,22 @@
       <c r="H22" t="n">
         <v>40.9</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I22" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" t="s">
+        <v>18</v>
+      </c>
+      <c r="K22" t="n">
         <v>0.5</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>48.5</v>
       </c>
-      <c r="K22" t="s">
-        <v>34</v>
-      </c>
-      <c r="L22" t="n">
+      <c r="M22" t="s">
+        <v>40</v>
+      </c>
+      <c r="N22" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1338,13 +1490,13 @@
         <v>46242</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C23" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D23" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E23" t="n">
         <v>2.1</v>
@@ -1358,16 +1510,22 @@
       <c r="H23" t="n">
         <v>40.5</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I23" t="s">
+        <v>17</v>
+      </c>
+      <c r="J23" t="s">
+        <v>20</v>
+      </c>
+      <c r="K23" t="n">
         <v>0.5</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>48.5</v>
       </c>
-      <c r="K23" t="s">
-        <v>34</v>
-      </c>
-      <c r="L23" t="n">
+      <c r="M23" t="s">
+        <v>40</v>
+      </c>
+      <c r="N23" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1376,13 +1534,13 @@
         <v>46242</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C24" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D24" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
@@ -1396,16 +1554,22 @@
       <c r="H24" t="n">
         <v>20.4</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J24" t="s">
+        <v>18</v>
+      </c>
+      <c r="K24" t="n">
         <v>0.5</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>48.5</v>
       </c>
-      <c r="K24" t="s">
-        <v>34</v>
-      </c>
-      <c r="L24" t="n">
+      <c r="M24" t="s">
+        <v>40</v>
+      </c>
+      <c r="N24" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1414,13 +1578,13 @@
         <v>46242</v>
       </c>
       <c r="B25" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C25" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D25" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -1434,16 +1598,22 @@
       <c r="H25" t="n">
         <v>20.3</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I25" t="s">
+        <v>21</v>
+      </c>
+      <c r="J25" t="s">
+        <v>20</v>
+      </c>
+      <c r="K25" t="n">
         <v>0.5</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>48.5</v>
       </c>
-      <c r="K25" t="s">
-        <v>34</v>
-      </c>
-      <c r="L25" t="n">
+      <c r="M25" t="s">
+        <v>40</v>
+      </c>
+      <c r="N25" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1452,13 +1622,13 @@
         <v>46242</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C26" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D26" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E26" t="n">
         <v>-5</v>
@@ -1472,16 +1642,22 @@
       <c r="H26" t="n">
         <v>46.3</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I26" t="s">
+        <v>17</v>
+      </c>
+      <c r="J26" t="s">
+        <v>18</v>
+      </c>
+      <c r="K26" t="n">
         <v>-4.5</v>
       </c>
-      <c r="J26" t="n">
+      <c r="L26" t="n">
         <v>48.5</v>
       </c>
-      <c r="K26" t="s">
-        <v>38</v>
-      </c>
-      <c r="L26" t="n">
+      <c r="M26" t="s">
+        <v>44</v>
+      </c>
+      <c r="N26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1490,13 +1666,13 @@
         <v>46242</v>
       </c>
       <c r="B27" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C27" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D27" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E27" t="n">
         <v>-5</v>
@@ -1510,16 +1686,22 @@
       <c r="H27" t="n">
         <v>46.3</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I27" t="s">
+        <v>17</v>
+      </c>
+      <c r="J27" t="s">
+        <v>20</v>
+      </c>
+      <c r="K27" t="n">
         <v>-4.5</v>
       </c>
-      <c r="J27" t="n">
+      <c r="L27" t="n">
         <v>48.5</v>
       </c>
-      <c r="K27" t="s">
-        <v>38</v>
-      </c>
-      <c r="L27" t="n">
+      <c r="M27" t="s">
+        <v>44</v>
+      </c>
+      <c r="N27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1528,13 +1710,13 @@
         <v>46242</v>
       </c>
       <c r="B28" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C28" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D28" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E28" t="n">
         <v>-2.5</v>
@@ -1548,16 +1730,22 @@
       <c r="H28" t="n">
         <v>23.1</v>
       </c>
-      <c r="I28" t="n">
+      <c r="I28" t="s">
+        <v>21</v>
+      </c>
+      <c r="J28" t="s">
+        <v>18</v>
+      </c>
+      <c r="K28" t="n">
         <v>-4.5</v>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>48.5</v>
       </c>
-      <c r="K28" t="s">
-        <v>38</v>
-      </c>
-      <c r="L28" t="n">
+      <c r="M28" t="s">
+        <v>44</v>
+      </c>
+      <c r="N28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1566,13 +1754,13 @@
         <v>46242</v>
       </c>
       <c r="B29" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C29" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D29" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E29" t="n">
         <v>-2.5</v>
@@ -1586,16 +1774,22 @@
       <c r="H29" t="n">
         <v>23.1</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I29" t="s">
+        <v>21</v>
+      </c>
+      <c r="J29" t="s">
+        <v>20</v>
+      </c>
+      <c r="K29" t="n">
         <v>-4.5</v>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>48.5</v>
       </c>
-      <c r="K29" t="s">
-        <v>38</v>
-      </c>
-      <c r="L29" t="n">
+      <c r="M29" t="s">
+        <v>44</v>
+      </c>
+      <c r="N29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1604,13 +1798,13 @@
         <v>46242</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D30" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E30" t="n">
         <v>-8</v>
@@ -1624,16 +1818,22 @@
       <c r="H30" t="n">
         <v>46.3</v>
       </c>
-      <c r="I30" t="n">
+      <c r="I30" t="s">
+        <v>17</v>
+      </c>
+      <c r="J30" t="s">
+        <v>18</v>
+      </c>
+      <c r="K30" t="n">
         <v>-6</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>45.5</v>
       </c>
-      <c r="K30" t="s">
-        <v>27</v>
-      </c>
-      <c r="L30" t="n">
+      <c r="M30" t="s">
+        <v>33</v>
+      </c>
+      <c r="N30" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -1642,13 +1842,13 @@
         <v>46242</v>
       </c>
       <c r="B31" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C31" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D31" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E31" t="n">
         <v>-8</v>
@@ -1662,16 +1862,22 @@
       <c r="H31" t="n">
         <v>46.1</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I31" t="s">
+        <v>17</v>
+      </c>
+      <c r="J31" t="s">
+        <v>20</v>
+      </c>
+      <c r="K31" t="n">
         <v>-6</v>
       </c>
-      <c r="J31" t="n">
+      <c r="L31" t="n">
         <v>45.5</v>
       </c>
-      <c r="K31" t="s">
-        <v>27</v>
-      </c>
-      <c r="L31" t="n">
+      <c r="M31" t="s">
+        <v>33</v>
+      </c>
+      <c r="N31" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -1680,13 +1886,13 @@
         <v>46242</v>
       </c>
       <c r="B32" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C32" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D32" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E32" t="n">
         <v>-4</v>
@@ -1700,16 +1906,22 @@
       <c r="H32" t="n">
         <v>23.1</v>
       </c>
-      <c r="I32" t="n">
+      <c r="I32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J32" t="s">
+        <v>18</v>
+      </c>
+      <c r="K32" t="n">
         <v>-6</v>
       </c>
-      <c r="J32" t="n">
+      <c r="L32" t="n">
         <v>45.5</v>
       </c>
-      <c r="K32" t="s">
-        <v>27</v>
-      </c>
-      <c r="L32" t="n">
+      <c r="M32" t="s">
+        <v>33</v>
+      </c>
+      <c r="N32" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -1718,13 +1930,13 @@
         <v>46242</v>
       </c>
       <c r="B33" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C33" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D33" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E33" t="n">
         <v>-4</v>
@@ -1738,16 +1950,22 @@
       <c r="H33" t="n">
         <v>23.1</v>
       </c>
-      <c r="I33" t="n">
+      <c r="I33" t="s">
+        <v>21</v>
+      </c>
+      <c r="J33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K33" t="n">
         <v>-6</v>
       </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
         <v>45.5</v>
       </c>
-      <c r="K33" t="s">
-        <v>27</v>
-      </c>
-      <c r="L33" t="n">
+      <c r="M33" t="s">
+        <v>33</v>
+      </c>
+      <c r="N33" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -1756,13 +1974,13 @@
         <v>46243</v>
       </c>
       <c r="B34" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C34" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D34" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E34" t="n">
         <v>-1.8</v>
@@ -1776,16 +1994,22 @@
       <c r="H34" t="n">
         <v>44</v>
       </c>
-      <c r="I34" t="n">
+      <c r="I34" t="s">
+        <v>17</v>
+      </c>
+      <c r="J34" t="s">
+        <v>18</v>
+      </c>
+      <c r="K34" t="n">
         <v>-4.5</v>
       </c>
-      <c r="J34" t="n">
+      <c r="L34" t="n">
         <v>51.5</v>
       </c>
-      <c r="K34" t="s">
-        <v>42</v>
-      </c>
-      <c r="L34" t="n">
+      <c r="M34" t="s">
+        <v>48</v>
+      </c>
+      <c r="N34" t="n">
         <v>17.8</v>
       </c>
     </row>
@@ -1794,13 +2018,13 @@
         <v>46243</v>
       </c>
       <c r="B35" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C35" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D35" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E35" t="n">
         <v>-1.8</v>
@@ -1814,16 +2038,22 @@
       <c r="H35" t="n">
         <v>41.6</v>
       </c>
-      <c r="I35" t="n">
+      <c r="I35" t="s">
+        <v>17</v>
+      </c>
+      <c r="J35" t="s">
+        <v>20</v>
+      </c>
+      <c r="K35" t="n">
         <v>-4.5</v>
       </c>
-      <c r="J35" t="n">
+      <c r="L35" t="n">
         <v>51.5</v>
       </c>
-      <c r="K35" t="s">
-        <v>42</v>
-      </c>
-      <c r="L35" t="n">
+      <c r="M35" t="s">
+        <v>48</v>
+      </c>
+      <c r="N35" t="n">
         <v>17.8</v>
       </c>
     </row>
@@ -1832,13 +2062,13 @@
         <v>46243</v>
       </c>
       <c r="B36" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C36" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D36" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E36" t="n">
         <v>-0.9</v>
@@ -1852,16 +2082,22 @@
       <c r="H36" t="n">
         <v>22</v>
       </c>
-      <c r="I36" t="n">
+      <c r="I36" t="s">
+        <v>21</v>
+      </c>
+      <c r="J36" t="s">
+        <v>18</v>
+      </c>
+      <c r="K36" t="n">
         <v>-4.5</v>
       </c>
-      <c r="J36" t="n">
+      <c r="L36" t="n">
         <v>51.5</v>
       </c>
-      <c r="K36" t="s">
-        <v>42</v>
-      </c>
-      <c r="L36" t="n">
+      <c r="M36" t="s">
+        <v>48</v>
+      </c>
+      <c r="N36" t="n">
         <v>17.8</v>
       </c>
     </row>
@@ -1870,13 +2106,13 @@
         <v>46243</v>
       </c>
       <c r="B37" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C37" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D37" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E37" t="n">
         <v>-0.9</v>
@@ -1890,16 +2126,22 @@
       <c r="H37" t="n">
         <v>20.8</v>
       </c>
-      <c r="I37" t="n">
+      <c r="I37" t="s">
+        <v>21</v>
+      </c>
+      <c r="J37" t="s">
+        <v>20</v>
+      </c>
+      <c r="K37" t="n">
         <v>-4.5</v>
       </c>
-      <c r="J37" t="n">
+      <c r="L37" t="n">
         <v>51.5</v>
       </c>
-      <c r="K37" t="s">
-        <v>42</v>
-      </c>
-      <c r="L37" t="n">
+      <c r="M37" t="s">
+        <v>48</v>
+      </c>
+      <c r="N37" t="n">
         <v>17.8</v>
       </c>
     </row>
@@ -1908,13 +2150,13 @@
         <v>46243</v>
       </c>
       <c r="B38" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C38" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D38" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E38" t="n">
         <v>12.1</v>
@@ -1928,16 +2170,22 @@
       <c r="H38" t="n">
         <v>42.6</v>
       </c>
-      <c r="I38" t="n">
+      <c r="I38" t="s">
+        <v>17</v>
+      </c>
+      <c r="J38" t="s">
+        <v>18</v>
+      </c>
+      <c r="K38" t="n">
         <v>14.5</v>
       </c>
-      <c r="J38" t="n">
+      <c r="L38" t="n">
         <v>50.5</v>
       </c>
-      <c r="K38" t="s">
-        <v>44</v>
-      </c>
-      <c r="L38" t="n">
+      <c r="M38" t="s">
+        <v>50</v>
+      </c>
+      <c r="N38" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1946,13 +2194,13 @@
         <v>46243</v>
       </c>
       <c r="B39" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C39" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D39" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E39" t="n">
         <v>12.1</v>
@@ -1966,16 +2214,22 @@
       <c r="H39" t="n">
         <v>41.7</v>
       </c>
-      <c r="I39" t="n">
+      <c r="I39" t="s">
+        <v>17</v>
+      </c>
+      <c r="J39" t="s">
+        <v>20</v>
+      </c>
+      <c r="K39" t="n">
         <v>14.5</v>
       </c>
-      <c r="J39" t="n">
+      <c r="L39" t="n">
         <v>50.5</v>
       </c>
-      <c r="K39" t="s">
-        <v>44</v>
-      </c>
-      <c r="L39" t="n">
+      <c r="M39" t="s">
+        <v>50</v>
+      </c>
+      <c r="N39" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1984,13 +2238,13 @@
         <v>46243</v>
       </c>
       <c r="B40" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C40" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D40" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E40" t="n">
         <v>6</v>
@@ -2004,16 +2258,22 @@
       <c r="H40" t="n">
         <v>21.3</v>
       </c>
-      <c r="I40" t="n">
+      <c r="I40" t="s">
+        <v>21</v>
+      </c>
+      <c r="J40" t="s">
+        <v>18</v>
+      </c>
+      <c r="K40" t="n">
         <v>14.5</v>
       </c>
-      <c r="J40" t="n">
+      <c r="L40" t="n">
         <v>50.5</v>
       </c>
-      <c r="K40" t="s">
-        <v>44</v>
-      </c>
-      <c r="L40" t="n">
+      <c r="M40" t="s">
+        <v>50</v>
+      </c>
+      <c r="N40" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2022,13 +2282,13 @@
         <v>46243</v>
       </c>
       <c r="B41" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C41" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D41" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E41" t="n">
         <v>6</v>
@@ -2042,16 +2302,22 @@
       <c r="H41" t="n">
         <v>20.9</v>
       </c>
-      <c r="I41" t="n">
+      <c r="I41" t="s">
+        <v>21</v>
+      </c>
+      <c r="J41" t="s">
+        <v>20</v>
+      </c>
+      <c r="K41" t="n">
         <v>14.5</v>
       </c>
-      <c r="J41" t="n">
+      <c r="L41" t="n">
         <v>50.5</v>
       </c>
-      <c r="K41" t="s">
-        <v>44</v>
-      </c>
-      <c r="L41" t="n">
+      <c r="M41" t="s">
+        <v>50</v>
+      </c>
+      <c r="N41" t="n">
         <v>2</v>
       </c>
     </row>

--- a/files/NRL_upcoming_projections.xlsx
+++ b/files/NRL_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -56,112 +56,103 @@
     <t xml:space="preserve">Forecast Rain mm</t>
   </si>
   <si>
+    <t xml:space="preserve">19:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north queensland cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Rain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cbus Super Stadium, Gold Coast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allianz Stadium, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penrith panthers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Go Media Stadium, Auckland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melbourne storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manly-warringah sea eagles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBF Park, Perth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dolphins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suncorp Stadium, Brisbane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">south sydney rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
     <t xml:space="preserve">14:00</t>
   </si>
   <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GIO Stadium, Canberra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st george-illawarra dragons</t>
+  </si>
+  <si>
     <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">south sydney rabbitohs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Rain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sharks Stadium, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wests tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leichhardt Oval, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north queensland cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cbus Super Stadium, Gold Coast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allianz Stadium, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penrith panthers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Go Media Stadium, Auckland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">melbourne storm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manly-warringah sea eagles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HBF Park, Perth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suncorp Stadium, Brisbane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberra raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">newcastle knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GIO Stadium, Canberra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st george-illawarra dragons</t>
   </si>
   <si>
     <t xml:space="preserve">Jubilee Oval, Sydney</t>
@@ -563,7 +554,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -575,16 +566,16 @@
         <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>-5.3</v>
+        <v>-1.3</v>
       </c>
       <c r="F2" t="n">
-        <v>-5.3</v>
+        <v>-1.3</v>
       </c>
       <c r="G2" t="n">
         <v>-1</v>
       </c>
       <c r="H2" t="n">
-        <v>46</v>
+        <v>49.1</v>
       </c>
       <c r="I2" t="s">
         <v>17</v>
@@ -593,10 +584,10 @@
         <v>18</v>
       </c>
       <c r="K2" t="n">
-        <v>-12.5</v>
+        <v>2.5</v>
       </c>
       <c r="L2" t="n">
-        <v>52</v>
+        <v>47.5</v>
       </c>
       <c r="M2" t="s">
         <v>19</v>
@@ -607,7 +598,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -619,16 +610,16 @@
         <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>-5.3</v>
+        <v>-1.3</v>
       </c>
       <c r="F3" t="n">
-        <v>-5.3</v>
+        <v>-1.3</v>
       </c>
       <c r="G3" t="n">
         <v>-1</v>
       </c>
       <c r="H3" t="n">
-        <v>46</v>
+        <v>49.1</v>
       </c>
       <c r="I3" t="s">
         <v>17</v>
@@ -637,10 +628,10 @@
         <v>20</v>
       </c>
       <c r="K3" t="n">
-        <v>-12.5</v>
+        <v>2.5</v>
       </c>
       <c r="L3" t="n">
-        <v>52</v>
+        <v>47.5</v>
       </c>
       <c r="M3" t="s">
         <v>19</v>
@@ -651,7 +642,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -663,16 +654,16 @@
         <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.7</v>
+        <v>-0.6</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.7</v>
+        <v>-0.6</v>
       </c>
       <c r="G4" t="n">
         <v>-0.5</v>
       </c>
       <c r="H4" t="n">
-        <v>23</v>
+        <v>24.6</v>
       </c>
       <c r="I4" t="s">
         <v>21</v>
@@ -681,10 +672,10 @@
         <v>18</v>
       </c>
       <c r="K4" t="n">
-        <v>-12.5</v>
+        <v>2.5</v>
       </c>
       <c r="L4" t="n">
-        <v>52</v>
+        <v>47.5</v>
       </c>
       <c r="M4" t="s">
         <v>19</v>
@@ -695,7 +686,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -707,16 +698,16 @@
         <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.7</v>
+        <v>-0.6</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.7</v>
+        <v>-0.6</v>
       </c>
       <c r="G5" t="n">
         <v>-0.5</v>
       </c>
       <c r="H5" t="n">
-        <v>23</v>
+        <v>24.6</v>
       </c>
       <c r="I5" t="s">
         <v>21</v>
@@ -725,10 +716,10 @@
         <v>20</v>
       </c>
       <c r="K5" t="n">
-        <v>-12.5</v>
+        <v>2.5</v>
       </c>
       <c r="L5" t="n">
-        <v>52</v>
+        <v>47.5</v>
       </c>
       <c r="M5" t="s">
         <v>19</v>
@@ -739,7 +730,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46236</v>
+        <v>46241</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
@@ -751,16 +742,16 @@
         <v>24</v>
       </c>
       <c r="E6" t="n">
-        <v>3.9</v>
+        <v>-9.4</v>
       </c>
       <c r="F6" t="n">
-        <v>3.9</v>
+        <v>-9.4</v>
       </c>
       <c r="G6" t="n">
-        <v>5.6</v>
+        <v>-10.5</v>
       </c>
       <c r="H6" t="n">
-        <v>44.4</v>
+        <v>43.1</v>
       </c>
       <c r="I6" t="s">
         <v>17</v>
@@ -769,10 +760,10 @@
         <v>18</v>
       </c>
       <c r="K6" t="n">
-        <v>7</v>
+        <v>-8.5</v>
       </c>
       <c r="L6" t="n">
-        <v>49</v>
+        <v>45.5</v>
       </c>
       <c r="M6" t="s">
         <v>25</v>
@@ -783,7 +774,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46236</v>
+        <v>46241</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
@@ -795,16 +786,16 @@
         <v>24</v>
       </c>
       <c r="E7" t="n">
-        <v>3.9</v>
+        <v>-9.4</v>
       </c>
       <c r="F7" t="n">
-        <v>3.9</v>
+        <v>-9.4</v>
       </c>
       <c r="G7" t="n">
-        <v>5.6</v>
+        <v>-10.5</v>
       </c>
       <c r="H7" t="n">
-        <v>44.4</v>
+        <v>43.1</v>
       </c>
       <c r="I7" t="s">
         <v>17</v>
@@ -813,10 +804,10 @@
         <v>20</v>
       </c>
       <c r="K7" t="n">
-        <v>7</v>
+        <v>-8.5</v>
       </c>
       <c r="L7" t="n">
-        <v>49</v>
+        <v>45.5</v>
       </c>
       <c r="M7" t="s">
         <v>25</v>
@@ -827,7 +818,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46236</v>
+        <v>46241</v>
       </c>
       <c r="B8" t="s">
         <v>22</v>
@@ -839,16 +830,16 @@
         <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9</v>
+        <v>-4.7</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9</v>
+        <v>-4.7</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8</v>
+        <v>-5.3</v>
       </c>
       <c r="H8" t="n">
-        <v>22.2</v>
+        <v>21.6</v>
       </c>
       <c r="I8" t="s">
         <v>21</v>
@@ -857,10 +848,10 @@
         <v>18</v>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>-8.5</v>
       </c>
       <c r="L8" t="n">
-        <v>49</v>
+        <v>45.5</v>
       </c>
       <c r="M8" t="s">
         <v>25</v>
@@ -871,7 +862,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46236</v>
+        <v>46241</v>
       </c>
       <c r="B9" t="s">
         <v>22</v>
@@ -883,16 +874,16 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9</v>
+        <v>-4.7</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9</v>
+        <v>-4.7</v>
       </c>
       <c r="G9" t="n">
-        <v>2.8</v>
+        <v>-5.3</v>
       </c>
       <c r="H9" t="n">
-        <v>22.2</v>
+        <v>21.6</v>
       </c>
       <c r="I9" t="s">
         <v>21</v>
@@ -901,10 +892,10 @@
         <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>7</v>
+        <v>-8.5</v>
       </c>
       <c r="L9" t="n">
-        <v>49</v>
+        <v>45.5</v>
       </c>
       <c r="M9" t="s">
         <v>25</v>
@@ -915,28 +906,28 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
         <v>26</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>27</v>
       </c>
-      <c r="D10" t="s">
-        <v>28</v>
-      </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.7</v>
+        <v>0.3</v>
       </c>
       <c r="H10" t="n">
-        <v>45.7</v>
+        <v>40.3</v>
       </c>
       <c r="I10" t="s">
         <v>17</v>
@@ -945,13 +936,13 @@
         <v>18</v>
       </c>
       <c r="K10" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>47.5</v>
+        <v>40.5</v>
       </c>
       <c r="M10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -959,28 +950,28 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
         <v>26</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>27</v>
       </c>
-      <c r="D11" t="s">
-        <v>28</v>
-      </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.7</v>
+        <v>0.3</v>
       </c>
       <c r="H11" t="n">
-        <v>45.7</v>
+        <v>40.3</v>
       </c>
       <c r="I11" t="s">
         <v>17</v>
@@ -989,13 +980,13 @@
         <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
-        <v>47.5</v>
+        <v>40.5</v>
       </c>
       <c r="M11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1003,28 +994,28 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
         <v>26</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>27</v>
       </c>
-      <c r="D12" t="s">
-        <v>28</v>
-      </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.8</v>
+        <v>0.2</v>
       </c>
       <c r="H12" t="n">
-        <v>22.9</v>
+        <v>20.1</v>
       </c>
       <c r="I12" t="s">
         <v>21</v>
@@ -1033,13 +1024,13 @@
         <v>18</v>
       </c>
       <c r="K12" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="L12" t="n">
-        <v>47.5</v>
+        <v>40.5</v>
       </c>
       <c r="M12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1047,28 +1038,28 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
         <v>26</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>27</v>
       </c>
-      <c r="D13" t="s">
-        <v>28</v>
-      </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.8</v>
+        <v>0.2</v>
       </c>
       <c r="H13" t="n">
-        <v>22.9</v>
+        <v>20.1</v>
       </c>
       <c r="I13" t="s">
         <v>21</v>
@@ -1077,13 +1068,13 @@
         <v>20</v>
       </c>
       <c r="K13" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="L13" t="n">
-        <v>47.5</v>
+        <v>40.5</v>
       </c>
       <c r="M13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1091,28 +1082,28 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" t="s">
         <v>30</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>31</v>
       </c>
-      <c r="D14" t="s">
-        <v>32</v>
-      </c>
       <c r="E14" t="n">
-        <v>-8.1</v>
+        <v>-0.4</v>
       </c>
       <c r="F14" t="n">
-        <v>-8.1</v>
+        <v>-0.4</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.1</v>
+        <v>-1.5</v>
       </c>
       <c r="H14" t="n">
-        <v>39.1</v>
+        <v>44.5</v>
       </c>
       <c r="I14" t="s">
         <v>17</v>
@@ -1121,42 +1112,42 @@
         <v>18</v>
       </c>
       <c r="K14" t="n">
-        <v>-8.5</v>
+        <v>0.5</v>
       </c>
       <c r="L14" t="n">
-        <v>45.5</v>
+        <v>48.5</v>
       </c>
       <c r="M14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" t="s">
         <v>30</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>31</v>
       </c>
-      <c r="D15" t="s">
-        <v>32</v>
-      </c>
       <c r="E15" t="n">
-        <v>-8.1</v>
+        <v>-0.4</v>
       </c>
       <c r="F15" t="n">
-        <v>-8.1</v>
+        <v>-0.4</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.1</v>
+        <v>-1.5</v>
       </c>
       <c r="H15" t="n">
-        <v>39.1</v>
+        <v>44</v>
       </c>
       <c r="I15" t="s">
         <v>17</v>
@@ -1165,42 +1156,42 @@
         <v>20</v>
       </c>
       <c r="K15" t="n">
-        <v>-8.5</v>
+        <v>0.5</v>
       </c>
       <c r="L15" t="n">
-        <v>45.5</v>
+        <v>48.5</v>
       </c>
       <c r="M15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" t="s">
         <v>30</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>31</v>
       </c>
-      <c r="D16" t="s">
-        <v>32</v>
-      </c>
       <c r="E16" t="n">
-        <v>-4</v>
+        <v>-0.2</v>
       </c>
       <c r="F16" t="n">
-        <v>-4</v>
+        <v>-0.2</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6</v>
+        <v>-0.7</v>
       </c>
       <c r="H16" t="n">
-        <v>19.6</v>
+        <v>22.2</v>
       </c>
       <c r="I16" t="s">
         <v>21</v>
@@ -1209,42 +1200,42 @@
         <v>18</v>
       </c>
       <c r="K16" t="n">
-        <v>-8.5</v>
+        <v>0.5</v>
       </c>
       <c r="L16" t="n">
-        <v>45.5</v>
+        <v>48.5</v>
       </c>
       <c r="M16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" t="s">
         <v>30</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>31</v>
       </c>
-      <c r="D17" t="s">
-        <v>32</v>
-      </c>
       <c r="E17" t="n">
-        <v>-4</v>
+        <v>-0.2</v>
       </c>
       <c r="F17" t="n">
-        <v>-4</v>
+        <v>-0.2</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6</v>
+        <v>-0.7</v>
       </c>
       <c r="H17" t="n">
-        <v>19.6</v>
+        <v>22</v>
       </c>
       <c r="I17" t="s">
         <v>21</v>
@@ -1253,24 +1244,24 @@
         <v>20</v>
       </c>
       <c r="K17" t="n">
-        <v>-8.5</v>
+        <v>0.5</v>
       </c>
       <c r="L17" t="n">
-        <v>45.5</v>
+        <v>48.5</v>
       </c>
       <c r="M17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C18" t="s">
         <v>34</v>
@@ -1279,16 +1270,16 @@
         <v>35</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1</v>
+        <v>-5.4</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1</v>
+        <v>-5.4</v>
       </c>
       <c r="G18" t="n">
-        <v>2.6</v>
+        <v>-6</v>
       </c>
       <c r="H18" t="n">
-        <v>38.3</v>
+        <v>47.3</v>
       </c>
       <c r="I18" t="s">
         <v>17</v>
@@ -1297,10 +1288,10 @@
         <v>18</v>
       </c>
       <c r="K18" t="n">
-        <v>5</v>
+        <v>-4.5</v>
       </c>
       <c r="L18" t="n">
-        <v>40.5</v>
+        <v>48.5</v>
       </c>
       <c r="M18" t="s">
         <v>36</v>
@@ -1311,10 +1302,10 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C19" t="s">
         <v>34</v>
@@ -1323,16 +1314,16 @@
         <v>35</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1</v>
+        <v>-5.4</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1</v>
+        <v>-5.4</v>
       </c>
       <c r="G19" t="n">
-        <v>2.6</v>
+        <v>-6</v>
       </c>
       <c r="H19" t="n">
-        <v>38.3</v>
+        <v>47.3</v>
       </c>
       <c r="I19" t="s">
         <v>17</v>
@@ -1341,10 +1332,10 @@
         <v>20</v>
       </c>
       <c r="K19" t="n">
-        <v>5</v>
+        <v>-4.5</v>
       </c>
       <c r="L19" t="n">
-        <v>40.5</v>
+        <v>48.5</v>
       </c>
       <c r="M19" t="s">
         <v>36</v>
@@ -1355,10 +1346,10 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C20" t="s">
         <v>34</v>
@@ -1367,16 +1358,16 @@
         <v>35</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5</v>
+        <v>-2.7</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5</v>
+        <v>-2.7</v>
       </c>
       <c r="G20" t="n">
-        <v>1.3</v>
+        <v>-3</v>
       </c>
       <c r="H20" t="n">
-        <v>19.2</v>
+        <v>23.6</v>
       </c>
       <c r="I20" t="s">
         <v>21</v>
@@ -1385,10 +1376,10 @@
         <v>18</v>
       </c>
       <c r="K20" t="n">
-        <v>5</v>
+        <v>-4.5</v>
       </c>
       <c r="L20" t="n">
-        <v>40.5</v>
+        <v>48.5</v>
       </c>
       <c r="M20" t="s">
         <v>36</v>
@@ -1399,10 +1390,10 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C21" t="s">
         <v>34</v>
@@ -1411,16 +1402,16 @@
         <v>35</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5</v>
+        <v>-2.7</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5</v>
+        <v>-2.7</v>
       </c>
       <c r="G21" t="n">
-        <v>1.3</v>
+        <v>-3</v>
       </c>
       <c r="H21" t="n">
-        <v>19.2</v>
+        <v>23.6</v>
       </c>
       <c r="I21" t="s">
         <v>21</v>
@@ -1429,10 +1420,10 @@
         <v>20</v>
       </c>
       <c r="K21" t="n">
-        <v>5</v>
+        <v>-4.5</v>
       </c>
       <c r="L21" t="n">
-        <v>40.5</v>
+        <v>48.5</v>
       </c>
       <c r="M21" t="s">
         <v>36</v>
@@ -1455,16 +1446,16 @@
         <v>39</v>
       </c>
       <c r="E22" t="n">
-        <v>2.1</v>
+        <v>-6.4</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1</v>
+        <v>-6.4</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>-7.1</v>
       </c>
       <c r="H22" t="n">
-        <v>40.9</v>
+        <v>47.9</v>
       </c>
       <c r="I22" t="s">
         <v>17</v>
@@ -1473,16 +1464,16 @@
         <v>18</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5</v>
+        <v>-6</v>
       </c>
       <c r="L22" t="n">
-        <v>48.5</v>
+        <v>45.5</v>
       </c>
       <c r="M22" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="23">
@@ -1499,16 +1490,16 @@
         <v>39</v>
       </c>
       <c r="E23" t="n">
-        <v>2.1</v>
+        <v>-6.4</v>
       </c>
       <c r="F23" t="n">
-        <v>2.1</v>
+        <v>-6.4</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>-7.1</v>
       </c>
       <c r="H23" t="n">
-        <v>40.5</v>
+        <v>47.8</v>
       </c>
       <c r="I23" t="s">
         <v>17</v>
@@ -1517,16 +1508,16 @@
         <v>20</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5</v>
+        <v>-6</v>
       </c>
       <c r="L23" t="n">
-        <v>48.5</v>
+        <v>45.5</v>
       </c>
       <c r="M23" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="N23" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="24">
@@ -1543,16 +1534,16 @@
         <v>39</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>-3.2</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>-3.2</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5</v>
+        <v>-3.5</v>
       </c>
       <c r="H24" t="n">
-        <v>20.4</v>
+        <v>24</v>
       </c>
       <c r="I24" t="s">
         <v>21</v>
@@ -1561,16 +1552,16 @@
         <v>18</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5</v>
+        <v>-6</v>
       </c>
       <c r="L24" t="n">
-        <v>48.5</v>
+        <v>45.5</v>
       </c>
       <c r="M24" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="N24" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="25">
@@ -1587,16 +1578,16 @@
         <v>39</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>-3.2</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>-3.2</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5</v>
+        <v>-3.5</v>
       </c>
       <c r="H25" t="n">
-        <v>20.3</v>
+        <v>23.9</v>
       </c>
       <c r="I25" t="s">
         <v>21</v>
@@ -1605,42 +1596,42 @@
         <v>20</v>
       </c>
       <c r="K25" t="n">
-        <v>0.5</v>
+        <v>-6</v>
       </c>
       <c r="L25" t="n">
-        <v>48.5</v>
+        <v>45.5</v>
       </c>
       <c r="M25" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="N25" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" t="s">
         <v>41</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>42</v>
       </c>
-      <c r="D26" t="s">
-        <v>43</v>
-      </c>
       <c r="E26" t="n">
-        <v>-5</v>
+        <v>-2.8</v>
       </c>
       <c r="F26" t="n">
-        <v>-5</v>
+        <v>-2.8</v>
       </c>
       <c r="G26" t="n">
-        <v>-5</v>
+        <v>-4.2</v>
       </c>
       <c r="H26" t="n">
-        <v>46.3</v>
+        <v>47.1</v>
       </c>
       <c r="I26" t="s">
         <v>17</v>
@@ -1652,39 +1643,39 @@
         <v>-4.5</v>
       </c>
       <c r="L26" t="n">
-        <v>48.5</v>
+        <v>51.5</v>
       </c>
       <c r="M26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" t="s">
         <v>41</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>42</v>
       </c>
-      <c r="D27" t="s">
-        <v>43</v>
-      </c>
       <c r="E27" t="n">
-        <v>-5</v>
+        <v>-2.8</v>
       </c>
       <c r="F27" t="n">
-        <v>-5</v>
+        <v>-2.8</v>
       </c>
       <c r="G27" t="n">
-        <v>-5</v>
+        <v>-4.2</v>
       </c>
       <c r="H27" t="n">
-        <v>46.3</v>
+        <v>44.1</v>
       </c>
       <c r="I27" t="s">
         <v>17</v>
@@ -1696,39 +1687,39 @@
         <v>-4.5</v>
       </c>
       <c r="L27" t="n">
-        <v>48.5</v>
+        <v>51.5</v>
       </c>
       <c r="M27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B28" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" t="s">
         <v>41</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>42</v>
       </c>
-      <c r="D28" t="s">
-        <v>43</v>
-      </c>
       <c r="E28" t="n">
-        <v>-2.5</v>
+        <v>-1.4</v>
       </c>
       <c r="F28" t="n">
-        <v>-2.5</v>
+        <v>-1.4</v>
       </c>
       <c r="G28" t="n">
-        <v>-2.5</v>
+        <v>-2.1</v>
       </c>
       <c r="H28" t="n">
-        <v>23.1</v>
+        <v>23.6</v>
       </c>
       <c r="I28" t="s">
         <v>21</v>
@@ -1740,39 +1731,39 @@
         <v>-4.5</v>
       </c>
       <c r="L28" t="n">
-        <v>48.5</v>
+        <v>51.5</v>
       </c>
       <c r="M28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B29" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29" t="s">
         <v>41</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>42</v>
       </c>
-      <c r="D29" t="s">
-        <v>43</v>
-      </c>
       <c r="E29" t="n">
-        <v>-2.5</v>
+        <v>-1.4</v>
       </c>
       <c r="F29" t="n">
-        <v>-2.5</v>
+        <v>-1.4</v>
       </c>
       <c r="G29" t="n">
-        <v>-2.5</v>
+        <v>-2.1</v>
       </c>
       <c r="H29" t="n">
-        <v>23.1</v>
+        <v>22</v>
       </c>
       <c r="I29" t="s">
         <v>21</v>
@@ -1784,39 +1775,39 @@
         <v>-4.5</v>
       </c>
       <c r="L29" t="n">
-        <v>48.5</v>
+        <v>51.5</v>
       </c>
       <c r="M29" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B30" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" t="s">
         <v>45</v>
       </c>
-      <c r="C30" t="s">
-        <v>16</v>
-      </c>
       <c r="D30" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="E30" t="n">
-        <v>-8</v>
+        <v>15.8</v>
       </c>
       <c r="F30" t="n">
-        <v>-8</v>
+        <v>15.8</v>
       </c>
       <c r="G30" t="n">
-        <v>-1</v>
+        <v>13.6</v>
       </c>
       <c r="H30" t="n">
-        <v>46.3</v>
+        <v>45.6</v>
       </c>
       <c r="I30" t="s">
         <v>17</v>
@@ -1825,42 +1816,42 @@
         <v>18</v>
       </c>
       <c r="K30" t="n">
-        <v>-6</v>
+        <v>14.5</v>
       </c>
       <c r="L30" t="n">
-        <v>45.5</v>
+        <v>50.5</v>
       </c>
       <c r="M30" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="N30" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B31" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" t="s">
         <v>45</v>
       </c>
-      <c r="C31" t="s">
-        <v>16</v>
-      </c>
       <c r="D31" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="E31" t="n">
-        <v>-8</v>
+        <v>15.8</v>
       </c>
       <c r="F31" t="n">
-        <v>-8</v>
+        <v>15.8</v>
       </c>
       <c r="G31" t="n">
-        <v>-1</v>
+        <v>13.6</v>
       </c>
       <c r="H31" t="n">
-        <v>46.1</v>
+        <v>44.4</v>
       </c>
       <c r="I31" t="s">
         <v>17</v>
@@ -1869,42 +1860,42 @@
         <v>20</v>
       </c>
       <c r="K31" t="n">
-        <v>-6</v>
+        <v>14.5</v>
       </c>
       <c r="L31" t="n">
-        <v>45.5</v>
+        <v>50.5</v>
       </c>
       <c r="M31" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="N31" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B32" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" t="s">
         <v>45</v>
       </c>
-      <c r="C32" t="s">
-        <v>16</v>
-      </c>
       <c r="D32" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="E32" t="n">
-        <v>-4</v>
+        <v>7.9</v>
       </c>
       <c r="F32" t="n">
-        <v>-4</v>
+        <v>7.9</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.5</v>
+        <v>6.8</v>
       </c>
       <c r="H32" t="n">
-        <v>23.1</v>
+        <v>22.8</v>
       </c>
       <c r="I32" t="s">
         <v>21</v>
@@ -1913,42 +1904,42 @@
         <v>18</v>
       </c>
       <c r="K32" t="n">
-        <v>-6</v>
+        <v>14.5</v>
       </c>
       <c r="L32" t="n">
-        <v>45.5</v>
+        <v>50.5</v>
       </c>
       <c r="M32" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="N32" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C33" t="s">
         <v>45</v>
       </c>
-      <c r="C33" t="s">
-        <v>16</v>
-      </c>
       <c r="D33" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="E33" t="n">
-        <v>-4</v>
+        <v>7.9</v>
       </c>
       <c r="F33" t="n">
-        <v>-4</v>
+        <v>7.9</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.5</v>
+        <v>6.8</v>
       </c>
       <c r="H33" t="n">
-        <v>23.1</v>
+        <v>22.2</v>
       </c>
       <c r="I33" t="s">
         <v>21</v>
@@ -1957,367 +1948,15 @@
         <v>20</v>
       </c>
       <c r="K33" t="n">
-        <v>-6</v>
+        <v>14.5</v>
       </c>
       <c r="L33" t="n">
-        <v>45.5</v>
+        <v>50.5</v>
       </c>
       <c r="M33" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="N33" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>46243</v>
-      </c>
-      <c r="B34" t="s">
-        <v>14</v>
-      </c>
-      <c r="C34" t="s">
-        <v>46</v>
-      </c>
-      <c r="D34" t="s">
-        <v>47</v>
-      </c>
-      <c r="E34" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="F34" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="G34" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="H34" t="n">
-        <v>44</v>
-      </c>
-      <c r="I34" t="s">
-        <v>17</v>
-      </c>
-      <c r="J34" t="s">
-        <v>18</v>
-      </c>
-      <c r="K34" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="L34" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="M34" t="s">
-        <v>48</v>
-      </c>
-      <c r="N34" t="n">
-        <v>17.8</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>46243</v>
-      </c>
-      <c r="B35" t="s">
-        <v>14</v>
-      </c>
-      <c r="C35" t="s">
-        <v>46</v>
-      </c>
-      <c r="D35" t="s">
-        <v>47</v>
-      </c>
-      <c r="E35" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="F35" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="G35" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="H35" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="I35" t="s">
-        <v>17</v>
-      </c>
-      <c r="J35" t="s">
-        <v>20</v>
-      </c>
-      <c r="K35" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="L35" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="M35" t="s">
-        <v>48</v>
-      </c>
-      <c r="N35" t="n">
-        <v>17.8</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>46243</v>
-      </c>
-      <c r="B36" t="s">
-        <v>14</v>
-      </c>
-      <c r="C36" t="s">
-        <v>46</v>
-      </c>
-      <c r="D36" t="s">
-        <v>47</v>
-      </c>
-      <c r="E36" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="F36" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="G36" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H36" t="n">
-        <v>22</v>
-      </c>
-      <c r="I36" t="s">
-        <v>21</v>
-      </c>
-      <c r="J36" t="s">
-        <v>18</v>
-      </c>
-      <c r="K36" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="L36" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="M36" t="s">
-        <v>48</v>
-      </c>
-      <c r="N36" t="n">
-        <v>17.8</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>46243</v>
-      </c>
-      <c r="B37" t="s">
-        <v>14</v>
-      </c>
-      <c r="C37" t="s">
-        <v>46</v>
-      </c>
-      <c r="D37" t="s">
-        <v>47</v>
-      </c>
-      <c r="E37" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="F37" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="G37" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H37" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="I37" t="s">
-        <v>21</v>
-      </c>
-      <c r="J37" t="s">
-        <v>20</v>
-      </c>
-      <c r="K37" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="L37" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="M37" t="s">
-        <v>48</v>
-      </c>
-      <c r="N37" t="n">
-        <v>17.8</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>46243</v>
-      </c>
-      <c r="B38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C38" t="s">
-        <v>49</v>
-      </c>
-      <c r="D38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E38" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="F38" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="G38" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="I38" t="s">
-        <v>17</v>
-      </c>
-      <c r="J38" t="s">
-        <v>18</v>
-      </c>
-      <c r="K38" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="L38" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="M38" t="s">
-        <v>50</v>
-      </c>
-      <c r="N38" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>46243</v>
-      </c>
-      <c r="B39" t="s">
-        <v>22</v>
-      </c>
-      <c r="C39" t="s">
-        <v>49</v>
-      </c>
-      <c r="D39" t="s">
-        <v>15</v>
-      </c>
-      <c r="E39" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="F39" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="G39" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="I39" t="s">
-        <v>17</v>
-      </c>
-      <c r="J39" t="s">
-        <v>20</v>
-      </c>
-      <c r="K39" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="L39" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="M39" t="s">
-        <v>50</v>
-      </c>
-      <c r="N39" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>46243</v>
-      </c>
-      <c r="B40" t="s">
-        <v>22</v>
-      </c>
-      <c r="C40" t="s">
-        <v>49</v>
-      </c>
-      <c r="D40" t="s">
-        <v>15</v>
-      </c>
-      <c r="E40" t="n">
-        <v>6</v>
-      </c>
-      <c r="F40" t="n">
-        <v>6</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H40" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="I40" t="s">
-        <v>21</v>
-      </c>
-      <c r="J40" t="s">
-        <v>18</v>
-      </c>
-      <c r="K40" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="L40" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="M40" t="s">
-        <v>50</v>
-      </c>
-      <c r="N40" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>46243</v>
-      </c>
-      <c r="B41" t="s">
-        <v>22</v>
-      </c>
-      <c r="C41" t="s">
-        <v>49</v>
-      </c>
-      <c r="D41" t="s">
-        <v>15</v>
-      </c>
-      <c r="E41" t="n">
-        <v>6</v>
-      </c>
-      <c r="F41" t="n">
-        <v>6</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H41" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="I41" t="s">
-        <v>21</v>
-      </c>
-      <c r="J41" t="s">
-        <v>20</v>
-      </c>
-      <c r="K41" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="L41" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="M41" t="s">
-        <v>50</v>
-      </c>
-      <c r="N41" t="n">
         <v>2</v>
       </c>
     </row>

--- a/files/NRL_upcoming_projections.xlsx
+++ b/files/NRL_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -56,106 +56,118 @@
     <t xml:space="preserve">Forecast Rain mm</t>
   </si>
   <si>
+    <t xml:space="preserve">14:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Rain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GIO Stadium, Canberra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st george-illawarra dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jubilee Oval, Sydney</t>
+  </si>
+  <si>
     <t xml:space="preserve">19:50</t>
   </si>
   <si>
+    <t xml:space="preserve">penrith panthers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlueBet Stadium, Penrith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manly-warringah sea eagles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dolphins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Pines Park, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">south sydney rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accor Stadium, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sharks Stadium, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north queensland cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CommBank Stadium, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suncorp Stadium, Brisbane</t>
+  </si>
+  <si>
     <t xml:space="preserve">gold coast titans</t>
   </si>
   <si>
-    <t xml:space="preserve">north queensland cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Rain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cbus Super Stadium, Gold Coast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allianz Stadium, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penrith panthers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Go Media Stadium, Auckland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">melbourne storm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manly-warringah sea eagles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HBF Park, Perth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suncorp Stadium, Brisbane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">south sydney rabbitohs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberra raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">newcastle knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GIO Stadium, Canberra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st george-illawarra dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jubilee Oval, Sydney</t>
+    <t xml:space="preserve">McDonald Jones Stadium, Newcastle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wests tigers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leichhardt Oval, Sydney</t>
   </si>
 </sst>
 </file>
@@ -494,8 +506,8 @@
   <cols>
     <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="5.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="27.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="29.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="29.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="27.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="27.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="16.71" hidden="0" customWidth="1"/>
@@ -504,7 +516,7 @@
     <col min="10" max="10" width="16.71" hidden="0" customWidth="1"/>
     <col min="11" max="11" width="11.71" hidden="0" customWidth="1"/>
     <col min="12" max="12" width="12.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="30.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="33.71" hidden="0" customWidth="1"/>
     <col min="14" max="14" width="16.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
@@ -554,7 +566,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46240</v>
+        <v>46243</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -566,16 +578,16 @@
         <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.3</v>
+        <v>-3.2</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.3</v>
+        <v>-3.2</v>
       </c>
       <c r="G2" t="n">
-        <v>-1</v>
+        <v>0.4</v>
       </c>
       <c r="H2" t="n">
-        <v>49.1</v>
+        <v>47.1</v>
       </c>
       <c r="I2" t="s">
         <v>17</v>
@@ -583,22 +595,18 @@
       <c r="J2" t="s">
         <v>18</v>
       </c>
-      <c r="K2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L2" t="n">
-        <v>47.5</v>
-      </c>
+      <c r="K2"/>
+      <c r="L2"/>
       <c r="M2" t="s">
         <v>19</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46240</v>
+        <v>46243</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -610,16 +618,16 @@
         <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.3</v>
+        <v>-3.2</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.3</v>
+        <v>-3.2</v>
       </c>
       <c r="G3" t="n">
-        <v>-1</v>
+        <v>0.4</v>
       </c>
       <c r="H3" t="n">
-        <v>49.1</v>
+        <v>44.3</v>
       </c>
       <c r="I3" t="s">
         <v>17</v>
@@ -627,22 +635,18 @@
       <c r="J3" t="s">
         <v>20</v>
       </c>
-      <c r="K3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L3" t="n">
-        <v>47.5</v>
-      </c>
+      <c r="K3"/>
+      <c r="L3"/>
       <c r="M3" t="s">
         <v>19</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46240</v>
+        <v>46243</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -654,16 +658,16 @@
         <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6</v>
+        <v>-1.6</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6</v>
+        <v>-1.6</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5</v>
+        <v>0.2</v>
       </c>
       <c r="H4" t="n">
-        <v>24.6</v>
+        <v>23.6</v>
       </c>
       <c r="I4" t="s">
         <v>21</v>
@@ -671,22 +675,18 @@
       <c r="J4" t="s">
         <v>18</v>
       </c>
-      <c r="K4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L4" t="n">
-        <v>47.5</v>
-      </c>
+      <c r="K4"/>
+      <c r="L4"/>
       <c r="M4" t="s">
         <v>19</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46240</v>
+        <v>46243</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -698,16 +698,16 @@
         <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6</v>
+        <v>-1.6</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6</v>
+        <v>-1.6</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5</v>
+        <v>0.2</v>
       </c>
       <c r="H5" t="n">
-        <v>24.6</v>
+        <v>22.1</v>
       </c>
       <c r="I5" t="s">
         <v>21</v>
@@ -715,22 +715,18 @@
       <c r="J5" t="s">
         <v>20</v>
       </c>
-      <c r="K5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L5" t="n">
-        <v>47.5</v>
-      </c>
+      <c r="K5"/>
+      <c r="L5"/>
       <c r="M5" t="s">
         <v>19</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
@@ -742,16 +738,16 @@
         <v>24</v>
       </c>
       <c r="E6" t="n">
-        <v>-9.4</v>
+        <v>15.1</v>
       </c>
       <c r="F6" t="n">
-        <v>-9.4</v>
+        <v>15.1</v>
       </c>
       <c r="G6" t="n">
-        <v>-10.5</v>
+        <v>15</v>
       </c>
       <c r="H6" t="n">
-        <v>43.1</v>
+        <v>45.6</v>
       </c>
       <c r="I6" t="s">
         <v>17</v>
@@ -759,22 +755,18 @@
       <c r="J6" t="s">
         <v>18</v>
       </c>
-      <c r="K6" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="L6" t="n">
-        <v>45.5</v>
-      </c>
+      <c r="K6"/>
+      <c r="L6"/>
       <c r="M6" t="s">
         <v>25</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
@@ -786,16 +778,16 @@
         <v>24</v>
       </c>
       <c r="E7" t="n">
-        <v>-9.4</v>
+        <v>15.1</v>
       </c>
       <c r="F7" t="n">
-        <v>-9.4</v>
+        <v>15.1</v>
       </c>
       <c r="G7" t="n">
-        <v>-10.5</v>
+        <v>15</v>
       </c>
       <c r="H7" t="n">
-        <v>43.1</v>
+        <v>43.4</v>
       </c>
       <c r="I7" t="s">
         <v>17</v>
@@ -803,22 +795,18 @@
       <c r="J7" t="s">
         <v>20</v>
       </c>
-      <c r="K7" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="L7" t="n">
-        <v>45.5</v>
-      </c>
+      <c r="K7"/>
+      <c r="L7"/>
       <c r="M7" t="s">
         <v>25</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="B8" t="s">
         <v>22</v>
@@ -830,16 +818,16 @@
         <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.7</v>
+        <v>7.6</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.7</v>
+        <v>7.6</v>
       </c>
       <c r="G8" t="n">
-        <v>-5.3</v>
+        <v>7.5</v>
       </c>
       <c r="H8" t="n">
-        <v>21.6</v>
+        <v>22.8</v>
       </c>
       <c r="I8" t="s">
         <v>21</v>
@@ -847,22 +835,18 @@
       <c r="J8" t="s">
         <v>18</v>
       </c>
-      <c r="K8" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="L8" t="n">
-        <v>45.5</v>
-      </c>
+      <c r="K8"/>
+      <c r="L8"/>
       <c r="M8" t="s">
         <v>25</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="B9" t="s">
         <v>22</v>
@@ -874,16 +858,16 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.7</v>
+        <v>7.6</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.7</v>
+        <v>7.6</v>
       </c>
       <c r="G9" t="n">
-        <v>-5.3</v>
+        <v>7.5</v>
       </c>
       <c r="H9" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="I9" t="s">
         <v>21</v>
@@ -891,43 +875,39 @@
       <c r="J9" t="s">
         <v>20</v>
       </c>
-      <c r="K9" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="L9" t="n">
-        <v>45.5</v>
-      </c>
+      <c r="K9"/>
+      <c r="L9"/>
       <c r="M9" t="s">
         <v>25</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46241</v>
+        <v>46247</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8</v>
+        <v>-0.5</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8</v>
+        <v>-0.5</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="H10" t="n">
-        <v>40.3</v>
+        <v>43.3</v>
       </c>
       <c r="I10" t="s">
         <v>17</v>
@@ -936,13 +916,13 @@
         <v>18</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>-1.5</v>
       </c>
       <c r="L10" t="n">
         <v>40.5</v>
       </c>
       <c r="M10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -950,28 +930,28 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46241</v>
+        <v>46247</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8</v>
+        <v>-0.5</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8</v>
+        <v>-0.5</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="H11" t="n">
-        <v>40.3</v>
+        <v>43.3</v>
       </c>
       <c r="I11" t="s">
         <v>17</v>
@@ -980,13 +960,13 @@
         <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>5</v>
+        <v>-1.5</v>
       </c>
       <c r="L11" t="n">
         <v>40.5</v>
       </c>
       <c r="M11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -994,28 +974,28 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46241</v>
+        <v>46247</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4</v>
+        <v>-0.2</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4</v>
+        <v>-0.2</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="H12" t="n">
-        <v>20.1</v>
+        <v>21.6</v>
       </c>
       <c r="I12" t="s">
         <v>21</v>
@@ -1024,13 +1004,13 @@
         <v>18</v>
       </c>
       <c r="K12" t="n">
-        <v>5</v>
+        <v>-1.5</v>
       </c>
       <c r="L12" t="n">
         <v>40.5</v>
       </c>
       <c r="M12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1038,28 +1018,28 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46241</v>
+        <v>46247</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.4</v>
+        <v>-0.2</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4</v>
+        <v>-0.2</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="H13" t="n">
-        <v>20.1</v>
+        <v>21.6</v>
       </c>
       <c r="I13" t="s">
         <v>21</v>
@@ -1068,13 +1048,13 @@
         <v>20</v>
       </c>
       <c r="K13" t="n">
-        <v>5</v>
+        <v>-1.5</v>
       </c>
       <c r="L13" t="n">
         <v>40.5</v>
       </c>
       <c r="M13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1082,28 +1062,28 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.4</v>
+        <v>-1</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4</v>
+        <v>-1</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.5</v>
+        <v>2.2</v>
       </c>
       <c r="H14" t="n">
-        <v>44.5</v>
+        <v>47.5</v>
       </c>
       <c r="I14" t="s">
         <v>17</v>
@@ -1112,42 +1092,42 @@
         <v>18</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5</v>
+        <v>8.5</v>
       </c>
       <c r="L14" t="n">
-        <v>48.5</v>
+        <v>50</v>
       </c>
       <c r="M14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4</v>
+        <v>-1</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4</v>
+        <v>-1</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.5</v>
+        <v>2.2</v>
       </c>
       <c r="H15" t="n">
-        <v>44</v>
+        <v>47.3</v>
       </c>
       <c r="I15" t="s">
         <v>17</v>
@@ -1156,42 +1136,42 @@
         <v>20</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5</v>
+        <v>8.5</v>
       </c>
       <c r="L15" t="n">
-        <v>48.5</v>
+        <v>50</v>
       </c>
       <c r="M15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2</v>
+        <v>-0.5</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2</v>
+        <v>-0.5</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.7</v>
+        <v>1.1</v>
       </c>
       <c r="H16" t="n">
-        <v>22.2</v>
+        <v>23.7</v>
       </c>
       <c r="I16" t="s">
         <v>21</v>
@@ -1200,42 +1180,42 @@
         <v>18</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5</v>
+        <v>8.5</v>
       </c>
       <c r="L16" t="n">
-        <v>48.5</v>
+        <v>50</v>
       </c>
       <c r="M16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2</v>
+        <v>-0.5</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2</v>
+        <v>-0.5</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.7</v>
+        <v>1.1</v>
       </c>
       <c r="H17" t="n">
-        <v>22</v>
+        <v>23.7</v>
       </c>
       <c r="I17" t="s">
         <v>21</v>
@@ -1244,42 +1224,42 @@
         <v>20</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5</v>
+        <v>8.5</v>
       </c>
       <c r="L17" t="n">
-        <v>48.5</v>
+        <v>50</v>
       </c>
       <c r="M17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E18" t="n">
-        <v>-5.4</v>
+        <v>1.1</v>
       </c>
       <c r="F18" t="n">
-        <v>-5.4</v>
+        <v>1.1</v>
       </c>
       <c r="G18" t="n">
-        <v>-6</v>
+        <v>-1.9</v>
       </c>
       <c r="H18" t="n">
-        <v>47.3</v>
+        <v>44.8</v>
       </c>
       <c r="I18" t="s">
         <v>17</v>
@@ -1288,13 +1268,13 @@
         <v>18</v>
       </c>
       <c r="K18" t="n">
-        <v>-4.5</v>
+        <v>-3.5</v>
       </c>
       <c r="L18" t="n">
-        <v>48.5</v>
+        <v>42.5</v>
       </c>
       <c r="M18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1302,28 +1282,28 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E19" t="n">
-        <v>-5.4</v>
+        <v>1.1</v>
       </c>
       <c r="F19" t="n">
-        <v>-5.4</v>
+        <v>1.1</v>
       </c>
       <c r="G19" t="n">
-        <v>-6</v>
+        <v>-1.9</v>
       </c>
       <c r="H19" t="n">
-        <v>47.3</v>
+        <v>44.8</v>
       </c>
       <c r="I19" t="s">
         <v>17</v>
@@ -1332,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="K19" t="n">
-        <v>-4.5</v>
+        <v>-3.5</v>
       </c>
       <c r="L19" t="n">
-        <v>48.5</v>
+        <v>42.5</v>
       </c>
       <c r="M19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -1346,28 +1326,28 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.7</v>
+        <v>0.6</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.7</v>
+        <v>0.6</v>
       </c>
       <c r="G20" t="n">
-        <v>-3</v>
+        <v>-0.9</v>
       </c>
       <c r="H20" t="n">
-        <v>23.6</v>
+        <v>22.4</v>
       </c>
       <c r="I20" t="s">
         <v>21</v>
@@ -1376,13 +1356,13 @@
         <v>18</v>
       </c>
       <c r="K20" t="n">
-        <v>-4.5</v>
+        <v>-3.5</v>
       </c>
       <c r="L20" t="n">
-        <v>48.5</v>
+        <v>42.5</v>
       </c>
       <c r="M20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -1390,28 +1370,28 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.7</v>
+        <v>0.6</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.7</v>
+        <v>0.6</v>
       </c>
       <c r="G21" t="n">
-        <v>-3</v>
+        <v>-0.9</v>
       </c>
       <c r="H21" t="n">
-        <v>23.6</v>
+        <v>22.4</v>
       </c>
       <c r="I21" t="s">
         <v>21</v>
@@ -1420,13 +1400,13 @@
         <v>20</v>
       </c>
       <c r="K21" t="n">
-        <v>-4.5</v>
+        <v>-3.5</v>
       </c>
       <c r="L21" t="n">
-        <v>48.5</v>
+        <v>42.5</v>
       </c>
       <c r="M21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -1434,28 +1414,28 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46242</v>
+        <v>46249</v>
       </c>
       <c r="B22" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C22" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D22" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.4</v>
+        <v>-10.4</v>
       </c>
       <c r="F22" t="n">
-        <v>-6.4</v>
+        <v>-10.4</v>
       </c>
       <c r="G22" t="n">
-        <v>-7.1</v>
+        <v>-13.4</v>
       </c>
       <c r="H22" t="n">
-        <v>47.9</v>
+        <v>48.4</v>
       </c>
       <c r="I22" t="s">
         <v>17</v>
@@ -1464,42 +1444,42 @@
         <v>18</v>
       </c>
       <c r="K22" t="n">
-        <v>-6</v>
+        <v>-10.5</v>
       </c>
       <c r="L22" t="n">
-        <v>45.5</v>
+        <v>50.5</v>
       </c>
       <c r="M22" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46242</v>
+        <v>46249</v>
       </c>
       <c r="B23" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C23" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D23" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.4</v>
+        <v>-10.4</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.4</v>
+        <v>-10.4</v>
       </c>
       <c r="G23" t="n">
-        <v>-7.1</v>
+        <v>-13.4</v>
       </c>
       <c r="H23" t="n">
-        <v>47.8</v>
+        <v>47</v>
       </c>
       <c r="I23" t="s">
         <v>17</v>
@@ -1508,42 +1488,42 @@
         <v>20</v>
       </c>
       <c r="K23" t="n">
-        <v>-6</v>
+        <v>-10.5</v>
       </c>
       <c r="L23" t="n">
-        <v>45.5</v>
+        <v>50.5</v>
       </c>
       <c r="M23" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="N23" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46242</v>
+        <v>46249</v>
       </c>
       <c r="B24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C24" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D24" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.2</v>
+        <v>-5.2</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.2</v>
+        <v>-5.2</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.5</v>
+        <v>-6.7</v>
       </c>
       <c r="H24" t="n">
-        <v>24</v>
+        <v>24.2</v>
       </c>
       <c r="I24" t="s">
         <v>21</v>
@@ -1552,42 +1532,42 @@
         <v>18</v>
       </c>
       <c r="K24" t="n">
-        <v>-6</v>
+        <v>-10.5</v>
       </c>
       <c r="L24" t="n">
-        <v>45.5</v>
+        <v>50.5</v>
       </c>
       <c r="M24" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="N24" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46242</v>
+        <v>46249</v>
       </c>
       <c r="B25" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C25" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D25" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.2</v>
+        <v>-5.2</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.2</v>
+        <v>-5.2</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.5</v>
+        <v>-6.7</v>
       </c>
       <c r="H25" t="n">
-        <v>23.9</v>
+        <v>23.5</v>
       </c>
       <c r="I25" t="s">
         <v>21</v>
@@ -1596,21 +1576,21 @@
         <v>20</v>
       </c>
       <c r="K25" t="n">
-        <v>-6</v>
+        <v>-10.5</v>
       </c>
       <c r="L25" t="n">
-        <v>45.5</v>
+        <v>50.5</v>
       </c>
       <c r="M25" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="N25" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46243</v>
+        <v>46249</v>
       </c>
       <c r="B26" t="s">
         <v>40</v>
@@ -1622,16 +1602,16 @@
         <v>42</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.8</v>
+        <v>-1.6</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.8</v>
+        <v>-1.6</v>
       </c>
       <c r="G26" t="n">
-        <v>-4.2</v>
+        <v>-1.4</v>
       </c>
       <c r="H26" t="n">
-        <v>47.1</v>
+        <v>48.2</v>
       </c>
       <c r="I26" t="s">
         <v>17</v>
@@ -1640,21 +1620,21 @@
         <v>18</v>
       </c>
       <c r="K26" t="n">
-        <v>-4.5</v>
+        <v>4.5</v>
       </c>
       <c r="L26" t="n">
-        <v>51.5</v>
+        <v>50</v>
       </c>
       <c r="M26" t="s">
         <v>43</v>
       </c>
       <c r="N26" t="n">
-        <v>17.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46243</v>
+        <v>46249</v>
       </c>
       <c r="B27" t="s">
         <v>40</v>
@@ -1666,16 +1646,16 @@
         <v>42</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.8</v>
+        <v>-1.6</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.8</v>
+        <v>-1.6</v>
       </c>
       <c r="G27" t="n">
-        <v>-4.2</v>
+        <v>-1.4</v>
       </c>
       <c r="H27" t="n">
-        <v>44.1</v>
+        <v>47</v>
       </c>
       <c r="I27" t="s">
         <v>17</v>
@@ -1684,21 +1664,21 @@
         <v>20</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.5</v>
+        <v>4.5</v>
       </c>
       <c r="L27" t="n">
-        <v>51.5</v>
+        <v>50</v>
       </c>
       <c r="M27" t="s">
         <v>43</v>
       </c>
       <c r="N27" t="n">
-        <v>17.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46243</v>
+        <v>46249</v>
       </c>
       <c r="B28" t="s">
         <v>40</v>
@@ -1710,16 +1690,16 @@
         <v>42</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.4</v>
+        <v>-0.8</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.4</v>
+        <v>-0.8</v>
       </c>
       <c r="G28" t="n">
-        <v>-2.1</v>
+        <v>-0.7</v>
       </c>
       <c r="H28" t="n">
-        <v>23.6</v>
+        <v>24.1</v>
       </c>
       <c r="I28" t="s">
         <v>21</v>
@@ -1728,21 +1708,21 @@
         <v>18</v>
       </c>
       <c r="K28" t="n">
-        <v>-4.5</v>
+        <v>4.5</v>
       </c>
       <c r="L28" t="n">
-        <v>51.5</v>
+        <v>50</v>
       </c>
       <c r="M28" t="s">
         <v>43</v>
       </c>
       <c r="N28" t="n">
-        <v>17.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46243</v>
+        <v>46249</v>
       </c>
       <c r="B29" t="s">
         <v>40</v>
@@ -1754,16 +1734,16 @@
         <v>42</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.4</v>
+        <v>-0.8</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.4</v>
+        <v>-0.8</v>
       </c>
       <c r="G29" t="n">
-        <v>-2.1</v>
+        <v>-0.7</v>
       </c>
       <c r="H29" t="n">
-        <v>22</v>
+        <v>23.5</v>
       </c>
       <c r="I29" t="s">
         <v>21</v>
@@ -1772,21 +1752,21 @@
         <v>20</v>
       </c>
       <c r="K29" t="n">
-        <v>-4.5</v>
+        <v>4.5</v>
       </c>
       <c r="L29" t="n">
-        <v>51.5</v>
+        <v>50</v>
       </c>
       <c r="M29" t="s">
         <v>43</v>
       </c>
       <c r="N29" t="n">
-        <v>17.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46243</v>
+        <v>46249</v>
       </c>
       <c r="B30" t="s">
         <v>44</v>
@@ -1798,16 +1778,16 @@
         <v>46</v>
       </c>
       <c r="E30" t="n">
-        <v>15.8</v>
+        <v>6.8</v>
       </c>
       <c r="F30" t="n">
-        <v>15.8</v>
+        <v>6.8</v>
       </c>
       <c r="G30" t="n">
-        <v>13.6</v>
+        <v>5.4</v>
       </c>
       <c r="H30" t="n">
-        <v>45.6</v>
+        <v>42.2</v>
       </c>
       <c r="I30" t="s">
         <v>17</v>
@@ -1816,21 +1796,21 @@
         <v>18</v>
       </c>
       <c r="K30" t="n">
-        <v>14.5</v>
+        <v>7</v>
       </c>
       <c r="L30" t="n">
-        <v>50.5</v>
+        <v>46</v>
       </c>
       <c r="M30" t="s">
         <v>47</v>
       </c>
       <c r="N30" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46243</v>
+        <v>46249</v>
       </c>
       <c r="B31" t="s">
         <v>44</v>
@@ -1842,16 +1822,16 @@
         <v>46</v>
       </c>
       <c r="E31" t="n">
-        <v>15.8</v>
+        <v>6.8</v>
       </c>
       <c r="F31" t="n">
-        <v>15.8</v>
+        <v>6.8</v>
       </c>
       <c r="G31" t="n">
-        <v>13.6</v>
+        <v>5.4</v>
       </c>
       <c r="H31" t="n">
-        <v>44.4</v>
+        <v>41.1</v>
       </c>
       <c r="I31" t="s">
         <v>17</v>
@@ -1860,21 +1840,21 @@
         <v>20</v>
       </c>
       <c r="K31" t="n">
-        <v>14.5</v>
+        <v>7</v>
       </c>
       <c r="L31" t="n">
-        <v>50.5</v>
+        <v>46</v>
       </c>
       <c r="M31" t="s">
         <v>47</v>
       </c>
       <c r="N31" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46243</v>
+        <v>46249</v>
       </c>
       <c r="B32" t="s">
         <v>44</v>
@@ -1886,16 +1866,16 @@
         <v>46</v>
       </c>
       <c r="E32" t="n">
-        <v>7.9</v>
+        <v>3.4</v>
       </c>
       <c r="F32" t="n">
-        <v>7.9</v>
+        <v>3.4</v>
       </c>
       <c r="G32" t="n">
-        <v>6.8</v>
+        <v>2.7</v>
       </c>
       <c r="H32" t="n">
-        <v>22.8</v>
+        <v>21.1</v>
       </c>
       <c r="I32" t="s">
         <v>21</v>
@@ -1904,21 +1884,21 @@
         <v>18</v>
       </c>
       <c r="K32" t="n">
-        <v>14.5</v>
+        <v>7</v>
       </c>
       <c r="L32" t="n">
-        <v>50.5</v>
+        <v>46</v>
       </c>
       <c r="M32" t="s">
         <v>47</v>
       </c>
       <c r="N32" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46243</v>
+        <v>46249</v>
       </c>
       <c r="B33" t="s">
         <v>44</v>
@@ -1930,16 +1910,16 @@
         <v>46</v>
       </c>
       <c r="E33" t="n">
-        <v>7.9</v>
+        <v>3.4</v>
       </c>
       <c r="F33" t="n">
-        <v>7.9</v>
+        <v>3.4</v>
       </c>
       <c r="G33" t="n">
-        <v>6.8</v>
+        <v>2.7</v>
       </c>
       <c r="H33" t="n">
-        <v>22.2</v>
+        <v>20.6</v>
       </c>
       <c r="I33" t="s">
         <v>21</v>
@@ -1948,16 +1928,368 @@
         <v>20</v>
       </c>
       <c r="K33" t="n">
-        <v>14.5</v>
+        <v>7</v>
       </c>
       <c r="L33" t="n">
-        <v>50.5</v>
+        <v>46</v>
       </c>
       <c r="M33" t="s">
         <v>47</v>
       </c>
       <c r="N33" t="n">
-        <v>2</v>
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>46250</v>
+      </c>
+      <c r="B34" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" t="s">
+        <v>16</v>
+      </c>
+      <c r="D34" t="s">
+        <v>48</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-9</v>
+      </c>
+      <c r="H34" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="I34" t="s">
+        <v>17</v>
+      </c>
+      <c r="J34" t="s">
+        <v>18</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="L34" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="M34" t="s">
+        <v>49</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46250</v>
+      </c>
+      <c r="B35" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" t="s">
+        <v>16</v>
+      </c>
+      <c r="D35" t="s">
+        <v>48</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-9</v>
+      </c>
+      <c r="H35" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="I35" t="s">
+        <v>17</v>
+      </c>
+      <c r="J35" t="s">
+        <v>20</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="L35" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="M35" t="s">
+        <v>49</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>46250</v>
+      </c>
+      <c r="B36" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" t="s">
+        <v>16</v>
+      </c>
+      <c r="D36" t="s">
+        <v>48</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H36" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I36" t="s">
+        <v>21</v>
+      </c>
+      <c r="J36" t="s">
+        <v>18</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="L36" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="M36" t="s">
+        <v>49</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>46250</v>
+      </c>
+      <c r="B37" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" t="s">
+        <v>16</v>
+      </c>
+      <c r="D37" t="s">
+        <v>48</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H37" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="I37" t="s">
+        <v>21</v>
+      </c>
+      <c r="J37" t="s">
+        <v>20</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="L37" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="M37" t="s">
+        <v>49</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>46250</v>
+      </c>
+      <c r="B38" t="s">
+        <v>22</v>
+      </c>
+      <c r="C38" t="s">
+        <v>50</v>
+      </c>
+      <c r="D38" t="s">
+        <v>23</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H38" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="I38" t="s">
+        <v>17</v>
+      </c>
+      <c r="J38" t="s">
+        <v>18</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L38" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="M38" t="s">
+        <v>51</v>
+      </c>
+      <c r="N38" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>46250</v>
+      </c>
+      <c r="B39" t="s">
+        <v>22</v>
+      </c>
+      <c r="C39" t="s">
+        <v>50</v>
+      </c>
+      <c r="D39" t="s">
+        <v>23</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H39" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="I39" t="s">
+        <v>17</v>
+      </c>
+      <c r="J39" t="s">
+        <v>20</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L39" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="M39" t="s">
+        <v>51</v>
+      </c>
+      <c r="N39" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>46250</v>
+      </c>
+      <c r="B40" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" t="s">
+        <v>50</v>
+      </c>
+      <c r="D40" t="s">
+        <v>23</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H40" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="I40" t="s">
+        <v>21</v>
+      </c>
+      <c r="J40" t="s">
+        <v>18</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L40" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="M40" t="s">
+        <v>51</v>
+      </c>
+      <c r="N40" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>46250</v>
+      </c>
+      <c r="B41" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" t="s">
+        <v>50</v>
+      </c>
+      <c r="D41" t="s">
+        <v>23</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H41" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="I41" t="s">
+        <v>21</v>
+      </c>
+      <c r="J41" t="s">
+        <v>20</v>
+      </c>
+      <c r="K41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L41" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="M41" t="s">
+        <v>51</v>
+      </c>
+      <c r="N41" t="n">
+        <v>5.2</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_upcoming_projections.xlsx
+++ b/files/NRL_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -56,115 +56,109 @@
     <t xml:space="preserve">Forecast Rain mm</t>
   </si>
   <si>
+    <t xml:space="preserve">19:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penrith panthers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Rain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlueBet Stadium, Penrith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manly-warringah sea eagles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dolphins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Pines Park, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">south sydney rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accor Stadium, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sharks Stadium, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north queensland cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CommBank Stadium, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suncorp Stadium, Brisbane</t>
+  </si>
+  <si>
     <t xml:space="preserve">14:00</t>
   </si>
   <si>
-    <t xml:space="preserve">canberra raiders</t>
-  </si>
-  <si>
     <t xml:space="preserve">newcastle knights</t>
   </si>
   <si>
-    <t xml:space="preserve">FT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Rain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GIO Stadium, Canberra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1H</t>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">McDonald Jones Stadium, Newcastle</t>
   </si>
   <si>
     <t xml:space="preserve">16:05</t>
   </si>
   <si>
+    <t xml:space="preserve">wests tigers</t>
+  </si>
+  <si>
     <t xml:space="preserve">st george-illawarra dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jubilee Oval, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penrith panthers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BlueBet Stadium, Penrith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manly-warringah sea eagles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 Pines Park, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">south sydney rabbitohs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accor Stadium, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sharks Stadium, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north queensland cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CommBank Stadium, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suncorp Stadium, Brisbane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">McDonald Jones Stadium, Newcastle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wests tigers</t>
   </si>
   <si>
     <t xml:space="preserve">Leichhardt Oval, Sydney</t>
@@ -566,7 +560,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46243</v>
+        <v>46247</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -578,16 +572,16 @@
         <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.2</v>
+        <v>0.8</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.2</v>
+        <v>0.8</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="H2" t="n">
-        <v>47.1</v>
+        <v>43.3</v>
       </c>
       <c r="I2" t="s">
         <v>17</v>
@@ -595,18 +589,22 @@
       <c r="J2" t="s">
         <v>18</v>
       </c>
-      <c r="K2"/>
-      <c r="L2"/>
+      <c r="K2" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="L2" t="n">
+        <v>42</v>
+      </c>
       <c r="M2" t="s">
         <v>19</v>
       </c>
       <c r="N2" t="n">
-        <v>14.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46243</v>
+        <v>46247</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -618,16 +616,16 @@
         <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.2</v>
+        <v>0.8</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.2</v>
+        <v>0.8</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="H3" t="n">
-        <v>44.3</v>
+        <v>43.3</v>
       </c>
       <c r="I3" t="s">
         <v>17</v>
@@ -635,18 +633,22 @@
       <c r="J3" t="s">
         <v>20</v>
       </c>
-      <c r="K3"/>
-      <c r="L3"/>
+      <c r="K3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>42</v>
+      </c>
       <c r="M3" t="s">
         <v>19</v>
       </c>
       <c r="N3" t="n">
-        <v>14.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46243</v>
+        <v>46247</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -658,16 +660,16 @@
         <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.6</v>
+        <v>0.4</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.6</v>
+        <v>0.4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="H4" t="n">
-        <v>23.6</v>
+        <v>21.6</v>
       </c>
       <c r="I4" t="s">
         <v>21</v>
@@ -675,18 +677,22 @@
       <c r="J4" t="s">
         <v>18</v>
       </c>
-      <c r="K4"/>
-      <c r="L4"/>
+      <c r="K4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>42</v>
+      </c>
       <c r="M4" t="s">
         <v>19</v>
       </c>
       <c r="N4" t="n">
-        <v>14.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46243</v>
+        <v>46247</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -698,16 +704,16 @@
         <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.6</v>
+        <v>0.4</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.6</v>
+        <v>0.4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="H5" t="n">
-        <v>22.1</v>
+        <v>21.6</v>
       </c>
       <c r="I5" t="s">
         <v>21</v>
@@ -715,18 +721,22 @@
       <c r="J5" t="s">
         <v>20</v>
       </c>
-      <c r="K5"/>
-      <c r="L5"/>
+      <c r="K5" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>42</v>
+      </c>
       <c r="M5" t="s">
         <v>19</v>
       </c>
       <c r="N5" t="n">
-        <v>14.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
@@ -738,16 +748,16 @@
         <v>24</v>
       </c>
       <c r="E6" t="n">
-        <v>15.1</v>
+        <v>0.1</v>
       </c>
       <c r="F6" t="n">
-        <v>15.1</v>
+        <v>0.1</v>
       </c>
       <c r="G6" t="n">
-        <v>15</v>
+        <v>2.5</v>
       </c>
       <c r="H6" t="n">
-        <v>45.6</v>
+        <v>47.5</v>
       </c>
       <c r="I6" t="s">
         <v>17</v>
@@ -755,18 +765,22 @@
       <c r="J6" t="s">
         <v>18</v>
       </c>
-      <c r="K6"/>
-      <c r="L6"/>
+      <c r="K6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>50.5</v>
+      </c>
       <c r="M6" t="s">
         <v>25</v>
       </c>
       <c r="N6" t="n">
-        <v>7.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
@@ -778,16 +792,16 @@
         <v>24</v>
       </c>
       <c r="E7" t="n">
-        <v>15.1</v>
+        <v>0.1</v>
       </c>
       <c r="F7" t="n">
-        <v>15.1</v>
+        <v>0.1</v>
       </c>
       <c r="G7" t="n">
-        <v>15</v>
+        <v>2.5</v>
       </c>
       <c r="H7" t="n">
-        <v>43.4</v>
+        <v>47.3</v>
       </c>
       <c r="I7" t="s">
         <v>17</v>
@@ -795,18 +809,22 @@
       <c r="J7" t="s">
         <v>20</v>
       </c>
-      <c r="K7"/>
-      <c r="L7"/>
+      <c r="K7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>50.5</v>
+      </c>
       <c r="M7" t="s">
         <v>25</v>
       </c>
       <c r="N7" t="n">
-        <v>7.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B8" t="s">
         <v>22</v>
@@ -818,16 +836,16 @@
         <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>7.5</v>
+        <v>1.2</v>
       </c>
       <c r="H8" t="n">
-        <v>22.8</v>
+        <v>23.7</v>
       </c>
       <c r="I8" t="s">
         <v>21</v>
@@ -835,18 +853,22 @@
       <c r="J8" t="s">
         <v>18</v>
       </c>
-      <c r="K8"/>
-      <c r="L8"/>
+      <c r="K8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>50.5</v>
+      </c>
       <c r="M8" t="s">
         <v>25</v>
       </c>
       <c r="N8" t="n">
-        <v>7.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B9" t="s">
         <v>22</v>
@@ -858,16 +880,16 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>7.5</v>
+        <v>1.2</v>
       </c>
       <c r="H9" t="n">
-        <v>21.7</v>
+        <v>23.6</v>
       </c>
       <c r="I9" t="s">
         <v>21</v>
@@ -875,18 +897,22 @@
       <c r="J9" t="s">
         <v>20</v>
       </c>
-      <c r="K9"/>
-      <c r="L9"/>
+      <c r="K9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>50.5</v>
+      </c>
       <c r="M9" t="s">
         <v>25</v>
       </c>
       <c r="N9" t="n">
-        <v>7.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B10" t="s">
         <v>26</v>
@@ -898,16 +924,16 @@
         <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5</v>
+        <v>3.6</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5</v>
+        <v>3.6</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3</v>
+        <v>1.2</v>
       </c>
       <c r="H10" t="n">
-        <v>43.3</v>
+        <v>44.8</v>
       </c>
       <c r="I10" t="s">
         <v>17</v>
@@ -916,10 +942,10 @@
         <v>18</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.5</v>
+        <v>-3.5</v>
       </c>
       <c r="L10" t="n">
-        <v>40.5</v>
+        <v>43.5</v>
       </c>
       <c r="M10" t="s">
         <v>29</v>
@@ -930,7 +956,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B11" t="s">
         <v>26</v>
@@ -942,16 +968,16 @@
         <v>28</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5</v>
+        <v>3.6</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5</v>
+        <v>3.6</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.3</v>
+        <v>1.2</v>
       </c>
       <c r="H11" t="n">
-        <v>43.3</v>
+        <v>44.8</v>
       </c>
       <c r="I11" t="s">
         <v>17</v>
@@ -960,10 +986,10 @@
         <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.5</v>
+        <v>-3.5</v>
       </c>
       <c r="L11" t="n">
-        <v>40.5</v>
+        <v>43.5</v>
       </c>
       <c r="M11" t="s">
         <v>29</v>
@@ -974,7 +1000,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B12" t="s">
         <v>26</v>
@@ -986,16 +1012,16 @@
         <v>28</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2</v>
+        <v>1.8</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2</v>
+        <v>1.8</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1</v>
+        <v>0.6</v>
       </c>
       <c r="H12" t="n">
-        <v>21.6</v>
+        <v>22.4</v>
       </c>
       <c r="I12" t="s">
         <v>21</v>
@@ -1004,10 +1030,10 @@
         <v>18</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.5</v>
+        <v>-3.5</v>
       </c>
       <c r="L12" t="n">
-        <v>40.5</v>
+        <v>43.5</v>
       </c>
       <c r="M12" t="s">
         <v>29</v>
@@ -1018,7 +1044,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B13" t="s">
         <v>26</v>
@@ -1030,16 +1056,16 @@
         <v>28</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.2</v>
+        <v>1.8</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2</v>
+        <v>1.8</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1</v>
+        <v>0.6</v>
       </c>
       <c r="H13" t="n">
-        <v>21.6</v>
+        <v>22.4</v>
       </c>
       <c r="I13" t="s">
         <v>21</v>
@@ -1048,10 +1074,10 @@
         <v>20</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.5</v>
+        <v>-3.5</v>
       </c>
       <c r="L13" t="n">
-        <v>40.5</v>
+        <v>43.5</v>
       </c>
       <c r="M13" t="s">
         <v>29</v>
@@ -1062,7 +1088,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B14" t="s">
         <v>30</v>
@@ -1074,16 +1100,16 @@
         <v>32</v>
       </c>
       <c r="E14" t="n">
-        <v>-1</v>
+        <v>-12.5</v>
       </c>
       <c r="F14" t="n">
-        <v>-1</v>
+        <v>-12.5</v>
       </c>
       <c r="G14" t="n">
-        <v>2.2</v>
+        <v>-12.6</v>
       </c>
       <c r="H14" t="n">
-        <v>47.5</v>
+        <v>48.4</v>
       </c>
       <c r="I14" t="s">
         <v>17</v>
@@ -1092,21 +1118,21 @@
         <v>18</v>
       </c>
       <c r="K14" t="n">
-        <v>8.5</v>
+        <v>-10.5</v>
       </c>
       <c r="L14" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M14" t="s">
         <v>33</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B15" t="s">
         <v>30</v>
@@ -1118,16 +1144,16 @@
         <v>32</v>
       </c>
       <c r="E15" t="n">
-        <v>-1</v>
+        <v>-12.5</v>
       </c>
       <c r="F15" t="n">
-        <v>-1</v>
+        <v>-12.5</v>
       </c>
       <c r="G15" t="n">
-        <v>2.2</v>
+        <v>-12.6</v>
       </c>
       <c r="H15" t="n">
-        <v>47.3</v>
+        <v>47.4</v>
       </c>
       <c r="I15" t="s">
         <v>17</v>
@@ -1136,21 +1162,21 @@
         <v>20</v>
       </c>
       <c r="K15" t="n">
-        <v>8.5</v>
+        <v>-10.5</v>
       </c>
       <c r="L15" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M15" t="s">
         <v>33</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B16" t="s">
         <v>30</v>
@@ -1162,16 +1188,16 @@
         <v>32</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5</v>
+        <v>-6.2</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5</v>
+        <v>-6.2</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1</v>
+        <v>-6.3</v>
       </c>
       <c r="H16" t="n">
-        <v>23.7</v>
+        <v>24.2</v>
       </c>
       <c r="I16" t="s">
         <v>21</v>
@@ -1180,21 +1206,21 @@
         <v>18</v>
       </c>
       <c r="K16" t="n">
-        <v>8.5</v>
+        <v>-10.5</v>
       </c>
       <c r="L16" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M16" t="s">
         <v>33</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B17" t="s">
         <v>30</v>
@@ -1206,13 +1232,13 @@
         <v>32</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5</v>
+        <v>-6.2</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5</v>
+        <v>-6.2</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1</v>
+        <v>-6.3</v>
       </c>
       <c r="H17" t="n">
         <v>23.7</v>
@@ -1224,21 +1250,21 @@
         <v>20</v>
       </c>
       <c r="K17" t="n">
-        <v>8.5</v>
+        <v>-10.5</v>
       </c>
       <c r="L17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M17" t="s">
         <v>33</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
@@ -1250,16 +1276,16 @@
         <v>36</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1</v>
+        <v>-2.2</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1</v>
+        <v>-2.2</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.9</v>
+        <v>-3.1</v>
       </c>
       <c r="H18" t="n">
-        <v>44.8</v>
+        <v>48.2</v>
       </c>
       <c r="I18" t="s">
         <v>17</v>
@@ -1268,21 +1294,21 @@
         <v>18</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.5</v>
+        <v>6</v>
       </c>
       <c r="L18" t="n">
-        <v>42.5</v>
+        <v>50.5</v>
       </c>
       <c r="M18" t="s">
         <v>37</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B19" t="s">
         <v>34</v>
@@ -1294,16 +1320,16 @@
         <v>36</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1</v>
+        <v>-2.2</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1</v>
+        <v>-2.2</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.9</v>
+        <v>-3.1</v>
       </c>
       <c r="H19" t="n">
-        <v>44.8</v>
+        <v>47.7</v>
       </c>
       <c r="I19" t="s">
         <v>17</v>
@@ -1312,21 +1338,21 @@
         <v>20</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.5</v>
+        <v>6</v>
       </c>
       <c r="L19" t="n">
-        <v>42.5</v>
+        <v>50.5</v>
       </c>
       <c r="M19" t="s">
         <v>37</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B20" t="s">
         <v>34</v>
@@ -1338,16 +1364,16 @@
         <v>36</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6</v>
+        <v>-1.1</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6</v>
+        <v>-1.1</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9</v>
+        <v>-1.6</v>
       </c>
       <c r="H20" t="n">
-        <v>22.4</v>
+        <v>24.1</v>
       </c>
       <c r="I20" t="s">
         <v>21</v>
@@ -1356,21 +1382,21 @@
         <v>18</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.5</v>
+        <v>6</v>
       </c>
       <c r="L20" t="n">
-        <v>42.5</v>
+        <v>50.5</v>
       </c>
       <c r="M20" t="s">
         <v>37</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B21" t="s">
         <v>34</v>
@@ -1382,16 +1408,16 @@
         <v>36</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6</v>
+        <v>-1.1</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6</v>
+        <v>-1.1</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9</v>
+        <v>-1.6</v>
       </c>
       <c r="H21" t="n">
-        <v>22.4</v>
+        <v>23.8</v>
       </c>
       <c r="I21" t="s">
         <v>21</v>
@@ -1400,16 +1426,16 @@
         <v>20</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.5</v>
+        <v>6</v>
       </c>
       <c r="L21" t="n">
-        <v>42.5</v>
+        <v>50.5</v>
       </c>
       <c r="M21" t="s">
         <v>37</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="22">
@@ -1420,22 +1446,22 @@
         <v>38</v>
       </c>
       <c r="C22" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="D22" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="E22" t="n">
-        <v>-10.4</v>
+        <v>6.4</v>
       </c>
       <c r="F22" t="n">
-        <v>-10.4</v>
+        <v>6.4</v>
       </c>
       <c r="G22" t="n">
-        <v>-13.4</v>
+        <v>5.4</v>
       </c>
       <c r="H22" t="n">
-        <v>48.4</v>
+        <v>42.2</v>
       </c>
       <c r="I22" t="s">
         <v>17</v>
@@ -1444,16 +1470,16 @@
         <v>18</v>
       </c>
       <c r="K22" t="n">
-        <v>-10.5</v>
+        <v>7</v>
       </c>
       <c r="L22" t="n">
-        <v>50.5</v>
+        <v>46.5</v>
       </c>
       <c r="M22" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="23">
@@ -1464,22 +1490,22 @@
         <v>38</v>
       </c>
       <c r="C23" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="D23" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="E23" t="n">
-        <v>-10.4</v>
+        <v>6.4</v>
       </c>
       <c r="F23" t="n">
-        <v>-10.4</v>
+        <v>6.4</v>
       </c>
       <c r="G23" t="n">
-        <v>-13.4</v>
+        <v>5.4</v>
       </c>
       <c r="H23" t="n">
-        <v>47</v>
+        <v>41.1</v>
       </c>
       <c r="I23" t="s">
         <v>17</v>
@@ -1488,16 +1514,16 @@
         <v>20</v>
       </c>
       <c r="K23" t="n">
-        <v>-10.5</v>
+        <v>7</v>
       </c>
       <c r="L23" t="n">
-        <v>50.5</v>
+        <v>46.5</v>
       </c>
       <c r="M23" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="24">
@@ -1508,22 +1534,22 @@
         <v>38</v>
       </c>
       <c r="C24" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="D24" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.2</v>
+        <v>3.2</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.2</v>
+        <v>3.2</v>
       </c>
       <c r="G24" t="n">
-        <v>-6.7</v>
+        <v>2.7</v>
       </c>
       <c r="H24" t="n">
-        <v>24.2</v>
+        <v>21.1</v>
       </c>
       <c r="I24" t="s">
         <v>21</v>
@@ -1532,16 +1558,16 @@
         <v>18</v>
       </c>
       <c r="K24" t="n">
-        <v>-10.5</v>
+        <v>7</v>
       </c>
       <c r="L24" t="n">
-        <v>50.5</v>
+        <v>46.5</v>
       </c>
       <c r="M24" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="N24" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="25">
@@ -1552,22 +1578,22 @@
         <v>38</v>
       </c>
       <c r="C25" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="D25" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.2</v>
+        <v>3.2</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.2</v>
+        <v>3.2</v>
       </c>
       <c r="G25" t="n">
-        <v>-6.7</v>
+        <v>2.7</v>
       </c>
       <c r="H25" t="n">
-        <v>23.5</v>
+        <v>20.6</v>
       </c>
       <c r="I25" t="s">
         <v>21</v>
@@ -1576,42 +1602,42 @@
         <v>20</v>
       </c>
       <c r="K25" t="n">
-        <v>-10.5</v>
+        <v>7</v>
       </c>
       <c r="L25" t="n">
-        <v>50.5</v>
+        <v>46.5</v>
       </c>
       <c r="M25" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="N25" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B26" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C26" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D26" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.6</v>
+        <v>-6.4</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.6</v>
+        <v>-6.4</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.4</v>
+        <v>-8.6</v>
       </c>
       <c r="H26" t="n">
-        <v>48.2</v>
+        <v>46.1</v>
       </c>
       <c r="I26" t="s">
         <v>17</v>
@@ -1620,42 +1646,42 @@
         <v>18</v>
       </c>
       <c r="K26" t="n">
-        <v>4.5</v>
+        <v>-13</v>
       </c>
       <c r="L26" t="n">
         <v>50</v>
       </c>
       <c r="M26" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N26" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B27" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C27" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D27" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.6</v>
+        <v>-6.4</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.6</v>
+        <v>-6.4</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.4</v>
+        <v>-8.6</v>
       </c>
       <c r="H27" t="n">
-        <v>47</v>
+        <v>44.6</v>
       </c>
       <c r="I27" t="s">
         <v>17</v>
@@ -1664,42 +1690,42 @@
         <v>20</v>
       </c>
       <c r="K27" t="n">
-        <v>4.5</v>
+        <v>-13</v>
       </c>
       <c r="L27" t="n">
         <v>50</v>
       </c>
       <c r="M27" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N27" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B28" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C28" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D28" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.8</v>
+        <v>-3.2</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.8</v>
+        <v>-3.2</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.7</v>
+        <v>-4.3</v>
       </c>
       <c r="H28" t="n">
-        <v>24.1</v>
+        <v>23.1</v>
       </c>
       <c r="I28" t="s">
         <v>21</v>
@@ -1708,42 +1734,42 @@
         <v>18</v>
       </c>
       <c r="K28" t="n">
-        <v>4.5</v>
+        <v>-13</v>
       </c>
       <c r="L28" t="n">
         <v>50</v>
       </c>
       <c r="M28" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N28" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C29" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D29" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.8</v>
+        <v>-3.2</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.8</v>
+        <v>-3.2</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.7</v>
+        <v>-4.3</v>
       </c>
       <c r="H29" t="n">
-        <v>23.5</v>
+        <v>22.3</v>
       </c>
       <c r="I29" t="s">
         <v>21</v>
@@ -1752,42 +1778,42 @@
         <v>20</v>
       </c>
       <c r="K29" t="n">
-        <v>4.5</v>
+        <v>-13</v>
       </c>
       <c r="L29" t="n">
         <v>50</v>
       </c>
       <c r="M29" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N29" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C30" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E30" t="n">
-        <v>6.8</v>
+        <v>0.3</v>
       </c>
       <c r="F30" t="n">
-        <v>6.8</v>
+        <v>0.3</v>
       </c>
       <c r="G30" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="H30" t="n">
-        <v>42.2</v>
+        <v>45.1</v>
       </c>
       <c r="I30" t="s">
         <v>17</v>
@@ -1796,42 +1822,42 @@
         <v>18</v>
       </c>
       <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="M30" t="s">
+        <v>49</v>
+      </c>
+      <c r="N30" t="n">
         <v>7</v>
-      </c>
-      <c r="L30" t="n">
-        <v>46</v>
-      </c>
-      <c r="M30" t="s">
-        <v>47</v>
-      </c>
-      <c r="N30" t="n">
-        <v>1.8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C31" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D31" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E31" t="n">
-        <v>6.8</v>
+        <v>0.3</v>
       </c>
       <c r="F31" t="n">
-        <v>6.8</v>
+        <v>0.3</v>
       </c>
       <c r="G31" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="H31" t="n">
-        <v>41.1</v>
+        <v>42.9</v>
       </c>
       <c r="I31" t="s">
         <v>17</v>
@@ -1840,42 +1866,42 @@
         <v>20</v>
       </c>
       <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="M31" t="s">
+        <v>49</v>
+      </c>
+      <c r="N31" t="n">
         <v>7</v>
-      </c>
-      <c r="L31" t="n">
-        <v>46</v>
-      </c>
-      <c r="M31" t="s">
-        <v>47</v>
-      </c>
-      <c r="N31" t="n">
-        <v>1.8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C32" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D32" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E32" t="n">
-        <v>3.4</v>
+        <v>0.1</v>
       </c>
       <c r="F32" t="n">
-        <v>3.4</v>
+        <v>0.1</v>
       </c>
       <c r="G32" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="H32" t="n">
-        <v>21.1</v>
+        <v>22.5</v>
       </c>
       <c r="I32" t="s">
         <v>21</v>
@@ -1884,42 +1910,42 @@
         <v>18</v>
       </c>
       <c r="K32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="M32" t="s">
+        <v>49</v>
+      </c>
+      <c r="N32" t="n">
         <v>7</v>
-      </c>
-      <c r="L32" t="n">
-        <v>46</v>
-      </c>
-      <c r="M32" t="s">
-        <v>47</v>
-      </c>
-      <c r="N32" t="n">
-        <v>1.8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C33" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D33" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E33" t="n">
-        <v>3.4</v>
+        <v>0.1</v>
       </c>
       <c r="F33" t="n">
-        <v>3.4</v>
+        <v>0.1</v>
       </c>
       <c r="G33" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="H33" t="n">
-        <v>20.6</v>
+        <v>21.4</v>
       </c>
       <c r="I33" t="s">
         <v>21</v>
@@ -1928,368 +1954,16 @@
         <v>20</v>
       </c>
       <c r="K33" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="M33" t="s">
+        <v>49</v>
+      </c>
+      <c r="N33" t="n">
         <v>7</v>
-      </c>
-      <c r="L33" t="n">
-        <v>46</v>
-      </c>
-      <c r="M33" t="s">
-        <v>47</v>
-      </c>
-      <c r="N33" t="n">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>46250</v>
-      </c>
-      <c r="B34" t="s">
-        <v>14</v>
-      </c>
-      <c r="C34" t="s">
-        <v>16</v>
-      </c>
-      <c r="D34" t="s">
-        <v>48</v>
-      </c>
-      <c r="E34" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="F34" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="G34" t="n">
-        <v>-9</v>
-      </c>
-      <c r="H34" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="I34" t="s">
-        <v>17</v>
-      </c>
-      <c r="J34" t="s">
-        <v>18</v>
-      </c>
-      <c r="K34" t="n">
-        <v>-11.5</v>
-      </c>
-      <c r="L34" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="M34" t="s">
-        <v>49</v>
-      </c>
-      <c r="N34" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>46250</v>
-      </c>
-      <c r="B35" t="s">
-        <v>14</v>
-      </c>
-      <c r="C35" t="s">
-        <v>16</v>
-      </c>
-      <c r="D35" t="s">
-        <v>48</v>
-      </c>
-      <c r="E35" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="F35" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="G35" t="n">
-        <v>-9</v>
-      </c>
-      <c r="H35" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="I35" t="s">
-        <v>17</v>
-      </c>
-      <c r="J35" t="s">
-        <v>20</v>
-      </c>
-      <c r="K35" t="n">
-        <v>-11.5</v>
-      </c>
-      <c r="L35" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="M35" t="s">
-        <v>49</v>
-      </c>
-      <c r="N35" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>46250</v>
-      </c>
-      <c r="B36" t="s">
-        <v>14</v>
-      </c>
-      <c r="C36" t="s">
-        <v>16</v>
-      </c>
-      <c r="D36" t="s">
-        <v>48</v>
-      </c>
-      <c r="E36" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="F36" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="G36" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="H36" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="I36" t="s">
-        <v>21</v>
-      </c>
-      <c r="J36" t="s">
-        <v>18</v>
-      </c>
-      <c r="K36" t="n">
-        <v>-11.5</v>
-      </c>
-      <c r="L36" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="M36" t="s">
-        <v>49</v>
-      </c>
-      <c r="N36" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>46250</v>
-      </c>
-      <c r="B37" t="s">
-        <v>14</v>
-      </c>
-      <c r="C37" t="s">
-        <v>16</v>
-      </c>
-      <c r="D37" t="s">
-        <v>48</v>
-      </c>
-      <c r="E37" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="F37" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="G37" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="H37" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="I37" t="s">
-        <v>21</v>
-      </c>
-      <c r="J37" t="s">
-        <v>20</v>
-      </c>
-      <c r="K37" t="n">
-        <v>-11.5</v>
-      </c>
-      <c r="L37" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="M37" t="s">
-        <v>49</v>
-      </c>
-      <c r="N37" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>46250</v>
-      </c>
-      <c r="B38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C38" t="s">
-        <v>50</v>
-      </c>
-      <c r="D38" t="s">
-        <v>23</v>
-      </c>
-      <c r="E38" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F38" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="G38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="H38" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="I38" t="s">
-        <v>17</v>
-      </c>
-      <c r="J38" t="s">
-        <v>18</v>
-      </c>
-      <c r="K38" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L38" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="M38" t="s">
-        <v>51</v>
-      </c>
-      <c r="N38" t="n">
-        <v>5.2</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>46250</v>
-      </c>
-      <c r="B39" t="s">
-        <v>22</v>
-      </c>
-      <c r="C39" t="s">
-        <v>50</v>
-      </c>
-      <c r="D39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E39" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F39" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="G39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="H39" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="I39" t="s">
-        <v>17</v>
-      </c>
-      <c r="J39" t="s">
-        <v>20</v>
-      </c>
-      <c r="K39" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L39" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="M39" t="s">
-        <v>51</v>
-      </c>
-      <c r="N39" t="n">
-        <v>5.2</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>46250</v>
-      </c>
-      <c r="B40" t="s">
-        <v>22</v>
-      </c>
-      <c r="C40" t="s">
-        <v>50</v>
-      </c>
-      <c r="D40" t="s">
-        <v>23</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H40" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="I40" t="s">
-        <v>21</v>
-      </c>
-      <c r="J40" t="s">
-        <v>18</v>
-      </c>
-      <c r="K40" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L40" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="M40" t="s">
-        <v>51</v>
-      </c>
-      <c r="N40" t="n">
-        <v>5.2</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>46250</v>
-      </c>
-      <c r="B41" t="s">
-        <v>22</v>
-      </c>
-      <c r="C41" t="s">
-        <v>50</v>
-      </c>
-      <c r="D41" t="s">
-        <v>23</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H41" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="I41" t="s">
-        <v>21</v>
-      </c>
-      <c r="J41" t="s">
-        <v>20</v>
-      </c>
-      <c r="K41" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L41" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="M41" t="s">
-        <v>51</v>
-      </c>
-      <c r="N41" t="n">
-        <v>5.2</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_upcoming_projections.xlsx
+++ b/files/NRL_upcoming_projections.xlsx
@@ -572,16 +572,16 @@
         <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="G2" t="n">
-        <v>1.2</v>
+        <v>-0.2</v>
       </c>
       <c r="H2" t="n">
-        <v>43.3</v>
+        <v>43.8</v>
       </c>
       <c r="I2" t="s">
         <v>17</v>
@@ -590,10 +590,10 @@
         <v>18</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.5</v>
+        <v>-4.5</v>
       </c>
       <c r="L2" t="n">
-        <v>42</v>
+        <v>42.5</v>
       </c>
       <c r="M2" t="s">
         <v>19</v>
@@ -616,16 +616,16 @@
         <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2</v>
+        <v>-0.2</v>
       </c>
       <c r="H3" t="n">
-        <v>43.3</v>
+        <v>43.8</v>
       </c>
       <c r="I3" t="s">
         <v>17</v>
@@ -634,10 +634,10 @@
         <v>20</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.5</v>
+        <v>-4.5</v>
       </c>
       <c r="L3" t="n">
-        <v>42</v>
+        <v>42.5</v>
       </c>
       <c r="M3" t="s">
         <v>19</v>
@@ -660,16 +660,16 @@
         <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6</v>
+        <v>-0.1</v>
       </c>
       <c r="H4" t="n">
-        <v>21.6</v>
+        <v>21.9</v>
       </c>
       <c r="I4" t="s">
         <v>21</v>
@@ -678,10 +678,10 @@
         <v>18</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.5</v>
+        <v>-4.5</v>
       </c>
       <c r="L4" t="n">
-        <v>42</v>
+        <v>42.5</v>
       </c>
       <c r="M4" t="s">
         <v>19</v>
@@ -704,16 +704,16 @@
         <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6</v>
+        <v>-0.1</v>
       </c>
       <c r="H5" t="n">
-        <v>21.6</v>
+        <v>21.9</v>
       </c>
       <c r="I5" t="s">
         <v>21</v>
@@ -722,10 +722,10 @@
         <v>20</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.5</v>
+        <v>-4.5</v>
       </c>
       <c r="L5" t="n">
-        <v>42</v>
+        <v>42.5</v>
       </c>
       <c r="M5" t="s">
         <v>19</v>
@@ -748,16 +748,16 @@
         <v>24</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1</v>
+        <v>-0.9</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1</v>
+        <v>-0.9</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5</v>
+        <v>4.9</v>
       </c>
       <c r="H6" t="n">
-        <v>47.5</v>
+        <v>50.3</v>
       </c>
       <c r="I6" t="s">
         <v>17</v>
@@ -766,7 +766,7 @@
         <v>18</v>
       </c>
       <c r="K6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="L6" t="n">
         <v>50.5</v>
@@ -775,7 +775,7 @@
         <v>25</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="7">
@@ -792,16 +792,16 @@
         <v>24</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1</v>
+        <v>-0.9</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1</v>
+        <v>-0.9</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5</v>
+        <v>4.9</v>
       </c>
       <c r="H7" t="n">
-        <v>47.3</v>
+        <v>50.2</v>
       </c>
       <c r="I7" t="s">
         <v>17</v>
@@ -810,7 +810,7 @@
         <v>20</v>
       </c>
       <c r="K7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="L7" t="n">
         <v>50.5</v>
@@ -819,7 +819,7 @@
         <v>25</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="8">
@@ -836,16 +836,16 @@
         <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="H8" t="n">
-        <v>23.7</v>
+        <v>25.1</v>
       </c>
       <c r="I8" t="s">
         <v>21</v>
@@ -854,7 +854,7 @@
         <v>18</v>
       </c>
       <c r="K8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
         <v>50.5</v>
@@ -863,7 +863,7 @@
         <v>25</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="9">
@@ -880,16 +880,16 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="G9" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="H9" t="n">
-        <v>23.6</v>
+        <v>25.1</v>
       </c>
       <c r="I9" t="s">
         <v>21</v>
@@ -898,7 +898,7 @@
         <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="L9" t="n">
         <v>50.5</v>
@@ -907,7 +907,7 @@
         <v>25</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="10">
@@ -924,16 +924,16 @@
         <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="F10" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="G10" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="H10" t="n">
-        <v>44.8</v>
+        <v>45.5</v>
       </c>
       <c r="I10" t="s">
         <v>17</v>
@@ -968,16 +968,16 @@
         <v>28</v>
       </c>
       <c r="E11" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="F11" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="G11" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="H11" t="n">
-        <v>44.8</v>
+        <v>45.5</v>
       </c>
       <c r="I11" t="s">
         <v>17</v>
@@ -1018,10 +1018,10 @@
         <v>1.8</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H12" t="n">
-        <v>22.4</v>
+        <v>22.7</v>
       </c>
       <c r="I12" t="s">
         <v>21</v>
@@ -1062,10 +1062,10 @@
         <v>1.8</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H13" t="n">
-        <v>22.4</v>
+        <v>22.7</v>
       </c>
       <c r="I13" t="s">
         <v>21</v>
@@ -1100,16 +1100,16 @@
         <v>32</v>
       </c>
       <c r="E14" t="n">
-        <v>-12.5</v>
+        <v>-13</v>
       </c>
       <c r="F14" t="n">
-        <v>-12.5</v>
+        <v>-13</v>
       </c>
       <c r="G14" t="n">
-        <v>-12.6</v>
+        <v>-12</v>
       </c>
       <c r="H14" t="n">
-        <v>48.4</v>
+        <v>49.1</v>
       </c>
       <c r="I14" t="s">
         <v>17</v>
@@ -1121,13 +1121,13 @@
         <v>-10.5</v>
       </c>
       <c r="L14" t="n">
-        <v>52</v>
+        <v>52.5</v>
       </c>
       <c r="M14" t="s">
         <v>33</v>
       </c>
       <c r="N14" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="15">
@@ -1144,16 +1144,16 @@
         <v>32</v>
       </c>
       <c r="E15" t="n">
-        <v>-12.5</v>
+        <v>-13</v>
       </c>
       <c r="F15" t="n">
-        <v>-12.5</v>
+        <v>-13</v>
       </c>
       <c r="G15" t="n">
-        <v>-12.6</v>
+        <v>-12</v>
       </c>
       <c r="H15" t="n">
-        <v>47.4</v>
+        <v>48.1</v>
       </c>
       <c r="I15" t="s">
         <v>17</v>
@@ -1165,13 +1165,13 @@
         <v>-10.5</v>
       </c>
       <c r="L15" t="n">
-        <v>52</v>
+        <v>52.5</v>
       </c>
       <c r="M15" t="s">
         <v>33</v>
       </c>
       <c r="N15" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="16">
@@ -1188,16 +1188,16 @@
         <v>32</v>
       </c>
       <c r="E16" t="n">
-        <v>-6.2</v>
+        <v>-6.5</v>
       </c>
       <c r="F16" t="n">
-        <v>-6.2</v>
+        <v>-6.5</v>
       </c>
       <c r="G16" t="n">
-        <v>-6.3</v>
+        <v>-6</v>
       </c>
       <c r="H16" t="n">
-        <v>24.2</v>
+        <v>24.6</v>
       </c>
       <c r="I16" t="s">
         <v>21</v>
@@ -1209,13 +1209,13 @@
         <v>-10.5</v>
       </c>
       <c r="L16" t="n">
-        <v>52</v>
+        <v>52.5</v>
       </c>
       <c r="M16" t="s">
         <v>33</v>
       </c>
       <c r="N16" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="17">
@@ -1232,16 +1232,16 @@
         <v>32</v>
       </c>
       <c r="E17" t="n">
-        <v>-6.2</v>
+        <v>-6.5</v>
       </c>
       <c r="F17" t="n">
-        <v>-6.2</v>
+        <v>-6.5</v>
       </c>
       <c r="G17" t="n">
-        <v>-6.3</v>
+        <v>-6</v>
       </c>
       <c r="H17" t="n">
-        <v>23.7</v>
+        <v>24.1</v>
       </c>
       <c r="I17" t="s">
         <v>21</v>
@@ -1253,13 +1253,13 @@
         <v>-10.5</v>
       </c>
       <c r="L17" t="n">
-        <v>52</v>
+        <v>52.5</v>
       </c>
       <c r="M17" t="s">
         <v>33</v>
       </c>
       <c r="N17" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="18">
@@ -1276,16 +1276,16 @@
         <v>36</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.2</v>
+        <v>-0.4</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.2</v>
+        <v>-0.4</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.1</v>
+        <v>-3.3</v>
       </c>
       <c r="H18" t="n">
-        <v>48.2</v>
+        <v>48.6</v>
       </c>
       <c r="I18" t="s">
         <v>17</v>
@@ -1294,7 +1294,7 @@
         <v>18</v>
       </c>
       <c r="K18" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="L18" t="n">
         <v>50.5</v>
@@ -1303,7 +1303,7 @@
         <v>37</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1320,16 +1320,16 @@
         <v>36</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.2</v>
+        <v>-0.4</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2</v>
+        <v>-0.4</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.1</v>
+        <v>-3.3</v>
       </c>
       <c r="H19" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
       <c r="I19" t="s">
         <v>17</v>
@@ -1338,7 +1338,7 @@
         <v>20</v>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="L19" t="n">
         <v>50.5</v>
@@ -1347,7 +1347,7 @@
         <v>37</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1364,16 +1364,16 @@
         <v>36</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1</v>
+        <v>-0.2</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1</v>
+        <v>-0.2</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.6</v>
+        <v>-1.7</v>
       </c>
       <c r="H20" t="n">
-        <v>24.1</v>
+        <v>24.3</v>
       </c>
       <c r="I20" t="s">
         <v>21</v>
@@ -1382,7 +1382,7 @@
         <v>18</v>
       </c>
       <c r="K20" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="L20" t="n">
         <v>50.5</v>
@@ -1391,7 +1391,7 @@
         <v>37</v>
       </c>
       <c r="N20" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1408,16 +1408,16 @@
         <v>36</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1</v>
+        <v>-0.2</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1</v>
+        <v>-0.2</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.6</v>
+        <v>-1.7</v>
       </c>
       <c r="H21" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="I21" t="s">
         <v>21</v>
@@ -1426,7 +1426,7 @@
         <v>20</v>
       </c>
       <c r="K21" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="L21" t="n">
         <v>50.5</v>
@@ -1435,7 +1435,7 @@
         <v>37</v>
       </c>
       <c r="N21" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1452,16 +1452,16 @@
         <v>40</v>
       </c>
       <c r="E22" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="F22" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="G22" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="H22" t="n">
-        <v>42.2</v>
+        <v>44.2</v>
       </c>
       <c r="I22" t="s">
         <v>17</v>
@@ -1470,16 +1470,16 @@
         <v>18</v>
       </c>
       <c r="K22" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="L22" t="n">
-        <v>46.5</v>
+        <v>47</v>
       </c>
       <c r="M22" t="s">
         <v>41</v>
       </c>
       <c r="N22" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1496,16 +1496,16 @@
         <v>40</v>
       </c>
       <c r="E23" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="F23" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="G23" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="H23" t="n">
-        <v>41.1</v>
+        <v>43.6</v>
       </c>
       <c r="I23" t="s">
         <v>17</v>
@@ -1514,16 +1514,16 @@
         <v>20</v>
       </c>
       <c r="K23" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="L23" t="n">
-        <v>46.5</v>
+        <v>47</v>
       </c>
       <c r="M23" t="s">
         <v>41</v>
       </c>
       <c r="N23" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1540,16 +1540,16 @@
         <v>40</v>
       </c>
       <c r="E24" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="F24" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="G24" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="H24" t="n">
-        <v>21.1</v>
+        <v>22.1</v>
       </c>
       <c r="I24" t="s">
         <v>21</v>
@@ -1558,16 +1558,16 @@
         <v>18</v>
       </c>
       <c r="K24" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="L24" t="n">
-        <v>46.5</v>
+        <v>47</v>
       </c>
       <c r="M24" t="s">
         <v>41</v>
       </c>
       <c r="N24" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1584,16 +1584,16 @@
         <v>40</v>
       </c>
       <c r="E25" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="F25" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="G25" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="H25" t="n">
-        <v>20.6</v>
+        <v>21.8</v>
       </c>
       <c r="I25" t="s">
         <v>21</v>
@@ -1602,16 +1602,16 @@
         <v>20</v>
       </c>
       <c r="K25" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="L25" t="n">
-        <v>46.5</v>
+        <v>47</v>
       </c>
       <c r="M25" t="s">
         <v>41</v>
       </c>
       <c r="N25" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1628,16 +1628,16 @@
         <v>44</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.4</v>
+        <v>-11.1</v>
       </c>
       <c r="F26" t="n">
-        <v>-6.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G26" t="n">
-        <v>-8.6</v>
+        <v>-11</v>
       </c>
       <c r="H26" t="n">
-        <v>46.1</v>
+        <v>46.7</v>
       </c>
       <c r="I26" t="s">
         <v>17</v>
@@ -1649,7 +1649,7 @@
         <v>-13</v>
       </c>
       <c r="L26" t="n">
-        <v>50</v>
+        <v>50.5</v>
       </c>
       <c r="M26" t="s">
         <v>45</v>
@@ -1672,16 +1672,16 @@
         <v>44</v>
       </c>
       <c r="E27" t="n">
-        <v>-6.4</v>
+        <v>-11.1</v>
       </c>
       <c r="F27" t="n">
-        <v>-6.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G27" t="n">
-        <v>-8.6</v>
+        <v>-11</v>
       </c>
       <c r="H27" t="n">
-        <v>44.6</v>
+        <v>45.6</v>
       </c>
       <c r="I27" t="s">
         <v>17</v>
@@ -1693,7 +1693,7 @@
         <v>-13</v>
       </c>
       <c r="L27" t="n">
-        <v>50</v>
+        <v>50.5</v>
       </c>
       <c r="M27" t="s">
         <v>45</v>
@@ -1716,16 +1716,16 @@
         <v>44</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.2</v>
+        <v>-5.6</v>
       </c>
       <c r="F28" t="n">
-        <v>-3.2</v>
+        <v>-5.6</v>
       </c>
       <c r="G28" t="n">
-        <v>-4.3</v>
+        <v>-5.5</v>
       </c>
       <c r="H28" t="n">
-        <v>23.1</v>
+        <v>23.4</v>
       </c>
       <c r="I28" t="s">
         <v>21</v>
@@ -1737,7 +1737,7 @@
         <v>-13</v>
       </c>
       <c r="L28" t="n">
-        <v>50</v>
+        <v>50.5</v>
       </c>
       <c r="M28" t="s">
         <v>45</v>
@@ -1760,16 +1760,16 @@
         <v>44</v>
       </c>
       <c r="E29" t="n">
-        <v>-3.2</v>
+        <v>-5.6</v>
       </c>
       <c r="F29" t="n">
-        <v>-3.2</v>
+        <v>-5.6</v>
       </c>
       <c r="G29" t="n">
-        <v>-4.3</v>
+        <v>-5.5</v>
       </c>
       <c r="H29" t="n">
-        <v>22.3</v>
+        <v>22.8</v>
       </c>
       <c r="I29" t="s">
         <v>21</v>
@@ -1781,7 +1781,7 @@
         <v>-13</v>
       </c>
       <c r="L29" t="n">
-        <v>50</v>
+        <v>50.5</v>
       </c>
       <c r="M29" t="s">
         <v>45</v>
@@ -1804,16 +1804,16 @@
         <v>48</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="H30" t="n">
-        <v>45.1</v>
+        <v>45.5</v>
       </c>
       <c r="I30" t="s">
         <v>17</v>
@@ -1831,7 +1831,7 @@
         <v>49</v>
       </c>
       <c r="N30" t="n">
-        <v>7</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="31">
@@ -1848,16 +1848,16 @@
         <v>48</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="H31" t="n">
-        <v>42.9</v>
+        <v>44.2</v>
       </c>
       <c r="I31" t="s">
         <v>17</v>
@@ -1875,7 +1875,7 @@
         <v>49</v>
       </c>
       <c r="N31" t="n">
-        <v>7</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="32">
@@ -1892,16 +1892,16 @@
         <v>48</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="G32" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="H32" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="I32" t="s">
         <v>21</v>
@@ -1919,7 +1919,7 @@
         <v>49</v>
       </c>
       <c r="N32" t="n">
-        <v>7</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="33">
@@ -1936,16 +1936,16 @@
         <v>48</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="G33" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="H33" t="n">
-        <v>21.4</v>
+        <v>22.1</v>
       </c>
       <c r="I33" t="s">
         <v>21</v>
@@ -1963,7 +1963,7 @@
         <v>49</v>
       </c>
       <c r="N33" t="n">
-        <v>7</v>
+        <v>3.9</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_upcoming_projections.xlsx
+++ b/files/NRL_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -56,112 +56,115 @@
     <t xml:space="preserve">Forecast Rain mm</t>
   </si>
   <si>
+    <t xml:space="preserve">14:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Rain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">McDonald Jones Stadium, Newcastle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wests tigers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st george-illawarra dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leichhardt Oval, Sydney</t>
+  </si>
+  <si>
     <t xml:space="preserve">19:50</t>
   </si>
   <si>
+    <t xml:space="preserve">melbourne storm</t>
+  </si>
+  <si>
     <t xml:space="preserve">penrith panthers</t>
   </si>
   <si>
+    <t xml:space="preserve">AAMI Park, Melbourne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GIO Stadium, Canberra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dolphins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suncorp Stadium, Brisbane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manly-warringah sea eagles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">south sydney rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accor Stadium, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WIN Stadium, Wollongong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cbus Super Stadium, Gold Coast</t>
+  </si>
+  <si>
     <t xml:space="preserve">sydney roosters</t>
   </si>
   <si>
-    <t xml:space="preserve">FT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Rain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BlueBet Stadium, Penrith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manly-warringah sea eagles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 Pines Park, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">south sydney rabbitohs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accor Stadium, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberra raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sharks Stadium, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north queensland cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CommBank Stadium, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suncorp Stadium, Brisbane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">newcastle knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">McDonald Jones Stadium, Newcastle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wests tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st george-illawarra dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leichhardt Oval, Sydney</t>
+    <t xml:space="preserve">Allianz Stadium, Sydney</t>
   </si>
 </sst>
 </file>
@@ -500,8 +503,8 @@
   <cols>
     <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="5.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="29.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="27.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="27.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="29.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="27.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="16.71" hidden="0" customWidth="1"/>
@@ -560,7 +563,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46247</v>
+        <v>46250</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -572,16 +575,16 @@
         <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3</v>
+        <v>-9.2</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3</v>
+        <v>-9.2</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.2</v>
+        <v>-6</v>
       </c>
       <c r="H2" t="n">
-        <v>43.8</v>
+        <v>47.2</v>
       </c>
       <c r="I2" t="s">
         <v>17</v>
@@ -589,22 +592,18 @@
       <c r="J2" t="s">
         <v>18</v>
       </c>
-      <c r="K2" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="L2" t="n">
-        <v>42.5</v>
-      </c>
+      <c r="K2"/>
+      <c r="L2"/>
       <c r="M2" t="s">
         <v>19</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46247</v>
+        <v>46250</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -616,16 +615,16 @@
         <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3</v>
+        <v>-9.2</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3</v>
+        <v>-9.2</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2</v>
+        <v>-6</v>
       </c>
       <c r="H3" t="n">
-        <v>43.8</v>
+        <v>46.6</v>
       </c>
       <c r="I3" t="s">
         <v>17</v>
@@ -633,22 +632,18 @@
       <c r="J3" t="s">
         <v>20</v>
       </c>
-      <c r="K3" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="L3" t="n">
-        <v>42.5</v>
-      </c>
+      <c r="K3"/>
+      <c r="L3"/>
       <c r="M3" t="s">
         <v>19</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46247</v>
+        <v>46250</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -660,16 +655,16 @@
         <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2</v>
+        <v>-4.6</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2</v>
+        <v>-4.6</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1</v>
+        <v>-3</v>
       </c>
       <c r="H4" t="n">
-        <v>21.9</v>
+        <v>23.6</v>
       </c>
       <c r="I4" t="s">
         <v>21</v>
@@ -677,22 +672,18 @@
       <c r="J4" t="s">
         <v>18</v>
       </c>
-      <c r="K4" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="L4" t="n">
-        <v>42.5</v>
-      </c>
+      <c r="K4"/>
+      <c r="L4"/>
       <c r="M4" t="s">
         <v>19</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46247</v>
+        <v>46250</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -704,16 +695,16 @@
         <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2</v>
+        <v>-4.6</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2</v>
+        <v>-4.6</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1</v>
+        <v>-3</v>
       </c>
       <c r="H5" t="n">
-        <v>21.9</v>
+        <v>23.3</v>
       </c>
       <c r="I5" t="s">
         <v>21</v>
@@ -721,22 +712,18 @@
       <c r="J5" t="s">
         <v>20</v>
       </c>
-      <c r="K5" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="L5" t="n">
-        <v>42.5</v>
-      </c>
+      <c r="K5"/>
+      <c r="L5"/>
       <c r="M5" t="s">
         <v>19</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46248</v>
+        <v>46250</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
@@ -748,16 +735,16 @@
         <v>24</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9</v>
+        <v>4.5</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9</v>
+        <v>4.5</v>
       </c>
       <c r="G6" t="n">
-        <v>4.9</v>
+        <v>-1</v>
       </c>
       <c r="H6" t="n">
-        <v>50.3</v>
+        <v>44.5</v>
       </c>
       <c r="I6" t="s">
         <v>17</v>
@@ -765,22 +752,18 @@
       <c r="J6" t="s">
         <v>18</v>
       </c>
-      <c r="K6" t="n">
-        <v>10</v>
-      </c>
-      <c r="L6" t="n">
-        <v>50.5</v>
-      </c>
+      <c r="K6"/>
+      <c r="L6"/>
       <c r="M6" t="s">
         <v>25</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46248</v>
+        <v>46250</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
@@ -792,16 +775,16 @@
         <v>24</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9</v>
+        <v>4.5</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9</v>
+        <v>4.5</v>
       </c>
       <c r="G7" t="n">
-        <v>4.9</v>
+        <v>-1</v>
       </c>
       <c r="H7" t="n">
-        <v>50.2</v>
+        <v>43.7</v>
       </c>
       <c r="I7" t="s">
         <v>17</v>
@@ -809,22 +792,18 @@
       <c r="J7" t="s">
         <v>20</v>
       </c>
-      <c r="K7" t="n">
-        <v>10</v>
-      </c>
-      <c r="L7" t="n">
-        <v>50.5</v>
-      </c>
+      <c r="K7"/>
+      <c r="L7"/>
       <c r="M7" t="s">
         <v>25</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46248</v>
+        <v>46250</v>
       </c>
       <c r="B8" t="s">
         <v>22</v>
@@ -836,16 +815,16 @@
         <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4</v>
+        <v>2.2</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4</v>
+        <v>2.2</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4</v>
+        <v>-0.5</v>
       </c>
       <c r="H8" t="n">
-        <v>25.1</v>
+        <v>22.2</v>
       </c>
       <c r="I8" t="s">
         <v>21</v>
@@ -853,22 +832,18 @@
       <c r="J8" t="s">
         <v>18</v>
       </c>
-      <c r="K8" t="n">
-        <v>10</v>
-      </c>
-      <c r="L8" t="n">
-        <v>50.5</v>
-      </c>
+      <c r="K8"/>
+      <c r="L8"/>
       <c r="M8" t="s">
         <v>25</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46248</v>
+        <v>46250</v>
       </c>
       <c r="B9" t="s">
         <v>22</v>
@@ -880,16 +855,16 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4</v>
+        <v>2.2</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4</v>
+        <v>2.2</v>
       </c>
       <c r="G9" t="n">
-        <v>2.4</v>
+        <v>-0.5</v>
       </c>
       <c r="H9" t="n">
-        <v>25.1</v>
+        <v>21.8</v>
       </c>
       <c r="I9" t="s">
         <v>21</v>
@@ -897,22 +872,18 @@
       <c r="J9" t="s">
         <v>20</v>
       </c>
-      <c r="K9" t="n">
-        <v>10</v>
-      </c>
-      <c r="L9" t="n">
-        <v>50.5</v>
-      </c>
+      <c r="K9"/>
+      <c r="L9"/>
       <c r="M9" t="s">
         <v>25</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46248</v>
+        <v>46254</v>
       </c>
       <c r="B10" t="s">
         <v>26</v>
@@ -924,16 +895,16 @@
         <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="F10" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="G10" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="H10" t="n">
-        <v>45.5</v>
+        <v>42.1</v>
       </c>
       <c r="I10" t="s">
         <v>17</v>
@@ -942,7 +913,7 @@
         <v>18</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.5</v>
+        <v>8.5</v>
       </c>
       <c r="L10" t="n">
         <v>43.5</v>
@@ -951,12 +922,12 @@
         <v>29</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46248</v>
+        <v>46254</v>
       </c>
       <c r="B11" t="s">
         <v>26</v>
@@ -968,16 +939,16 @@
         <v>28</v>
       </c>
       <c r="E11" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="F11" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="G11" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="H11" t="n">
-        <v>45.5</v>
+        <v>41.7</v>
       </c>
       <c r="I11" t="s">
         <v>17</v>
@@ -986,7 +957,7 @@
         <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.5</v>
+        <v>8.5</v>
       </c>
       <c r="L11" t="n">
         <v>43.5</v>
@@ -995,12 +966,12 @@
         <v>29</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46248</v>
+        <v>46254</v>
       </c>
       <c r="B12" t="s">
         <v>26</v>
@@ -1012,16 +983,16 @@
         <v>28</v>
       </c>
       <c r="E12" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="H12" t="n">
-        <v>22.7</v>
+        <v>21</v>
       </c>
       <c r="I12" t="s">
         <v>21</v>
@@ -1030,7 +1001,7 @@
         <v>18</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.5</v>
+        <v>8.5</v>
       </c>
       <c r="L12" t="n">
         <v>43.5</v>
@@ -1039,12 +1010,12 @@
         <v>29</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46248</v>
+        <v>46254</v>
       </c>
       <c r="B13" t="s">
         <v>26</v>
@@ -1056,16 +1027,16 @@
         <v>28</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="H13" t="n">
-        <v>22.7</v>
+        <v>20.9</v>
       </c>
       <c r="I13" t="s">
         <v>21</v>
@@ -1074,7 +1045,7 @@
         <v>20</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.5</v>
+        <v>8.5</v>
       </c>
       <c r="L13" t="n">
         <v>43.5</v>
@@ -1083,12 +1054,12 @@
         <v>29</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46249</v>
+        <v>46255</v>
       </c>
       <c r="B14" t="s">
         <v>30</v>
@@ -1100,16 +1071,16 @@
         <v>32</v>
       </c>
       <c r="E14" t="n">
-        <v>-13</v>
+        <v>-4.8</v>
       </c>
       <c r="F14" t="n">
-        <v>-13</v>
+        <v>-4.8</v>
       </c>
       <c r="G14" t="n">
-        <v>-12</v>
+        <v>-4.2</v>
       </c>
       <c r="H14" t="n">
-        <v>49.1</v>
+        <v>47.7</v>
       </c>
       <c r="I14" t="s">
         <v>17</v>
@@ -1118,21 +1089,21 @@
         <v>18</v>
       </c>
       <c r="K14" t="n">
-        <v>-10.5</v>
+        <v>-9</v>
       </c>
       <c r="L14" t="n">
-        <v>52.5</v>
+        <v>51.5</v>
       </c>
       <c r="M14" t="s">
         <v>33</v>
       </c>
       <c r="N14" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46249</v>
+        <v>46255</v>
       </c>
       <c r="B15" t="s">
         <v>30</v>
@@ -1144,16 +1115,16 @@
         <v>32</v>
       </c>
       <c r="E15" t="n">
-        <v>-13</v>
+        <v>-4.8</v>
       </c>
       <c r="F15" t="n">
-        <v>-13</v>
+        <v>-4.8</v>
       </c>
       <c r="G15" t="n">
-        <v>-12</v>
+        <v>-4.2</v>
       </c>
       <c r="H15" t="n">
-        <v>48.1</v>
+        <v>47.7</v>
       </c>
       <c r="I15" t="s">
         <v>17</v>
@@ -1162,21 +1133,21 @@
         <v>20</v>
       </c>
       <c r="K15" t="n">
-        <v>-10.5</v>
+        <v>-9</v>
       </c>
       <c r="L15" t="n">
-        <v>52.5</v>
+        <v>51.5</v>
       </c>
       <c r="M15" t="s">
         <v>33</v>
       </c>
       <c r="N15" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46249</v>
+        <v>46255</v>
       </c>
       <c r="B16" t="s">
         <v>30</v>
@@ -1188,16 +1159,16 @@
         <v>32</v>
       </c>
       <c r="E16" t="n">
-        <v>-6.5</v>
+        <v>-2.4</v>
       </c>
       <c r="F16" t="n">
-        <v>-6.5</v>
+        <v>-2.4</v>
       </c>
       <c r="G16" t="n">
-        <v>-6</v>
+        <v>-2.1</v>
       </c>
       <c r="H16" t="n">
-        <v>24.6</v>
+        <v>23.9</v>
       </c>
       <c r="I16" t="s">
         <v>21</v>
@@ -1206,21 +1177,21 @@
         <v>18</v>
       </c>
       <c r="K16" t="n">
-        <v>-10.5</v>
+        <v>-9</v>
       </c>
       <c r="L16" t="n">
-        <v>52.5</v>
+        <v>51.5</v>
       </c>
       <c r="M16" t="s">
         <v>33</v>
       </c>
       <c r="N16" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46249</v>
+        <v>46255</v>
       </c>
       <c r="B17" t="s">
         <v>30</v>
@@ -1232,16 +1203,16 @@
         <v>32</v>
       </c>
       <c r="E17" t="n">
-        <v>-6.5</v>
+        <v>-2.4</v>
       </c>
       <c r="F17" t="n">
-        <v>-6.5</v>
+        <v>-2.4</v>
       </c>
       <c r="G17" t="n">
-        <v>-6</v>
+        <v>-2.1</v>
       </c>
       <c r="H17" t="n">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="I17" t="s">
         <v>21</v>
@@ -1250,21 +1221,21 @@
         <v>20</v>
       </c>
       <c r="K17" t="n">
-        <v>-10.5</v>
+        <v>-9</v>
       </c>
       <c r="L17" t="n">
-        <v>52.5</v>
+        <v>51.5</v>
       </c>
       <c r="M17" t="s">
         <v>33</v>
       </c>
       <c r="N17" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46249</v>
+        <v>46255</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
@@ -1276,16 +1247,16 @@
         <v>36</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4</v>
+        <v>-11.3</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4</v>
+        <v>-11.3</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.3</v>
+        <v>-14</v>
       </c>
       <c r="H18" t="n">
-        <v>48.6</v>
+        <v>49.1</v>
       </c>
       <c r="I18" t="s">
         <v>17</v>
@@ -1294,21 +1265,21 @@
         <v>18</v>
       </c>
       <c r="K18" t="n">
-        <v>5.5</v>
+        <v>-14</v>
       </c>
       <c r="L18" t="n">
-        <v>50.5</v>
+        <v>51.5</v>
       </c>
       <c r="M18" t="s">
         <v>37</v>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46249</v>
+        <v>46255</v>
       </c>
       <c r="B19" t="s">
         <v>34</v>
@@ -1320,16 +1291,16 @@
         <v>36</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4</v>
+        <v>-11.3</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4</v>
+        <v>-11.3</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.3</v>
+        <v>-14</v>
       </c>
       <c r="H19" t="n">
-        <v>47.8</v>
+        <v>49</v>
       </c>
       <c r="I19" t="s">
         <v>17</v>
@@ -1338,21 +1309,21 @@
         <v>20</v>
       </c>
       <c r="K19" t="n">
-        <v>5.5</v>
+        <v>-14</v>
       </c>
       <c r="L19" t="n">
-        <v>50.5</v>
+        <v>51.5</v>
       </c>
       <c r="M19" t="s">
         <v>37</v>
       </c>
       <c r="N19" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46249</v>
+        <v>46255</v>
       </c>
       <c r="B20" t="s">
         <v>34</v>
@@ -1364,16 +1335,16 @@
         <v>36</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2</v>
+        <v>-5.7</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2</v>
+        <v>-5.7</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.7</v>
+        <v>-7</v>
       </c>
       <c r="H20" t="n">
-        <v>24.3</v>
+        <v>24.6</v>
       </c>
       <c r="I20" t="s">
         <v>21</v>
@@ -1382,21 +1353,21 @@
         <v>18</v>
       </c>
       <c r="K20" t="n">
-        <v>5.5</v>
+        <v>-14</v>
       </c>
       <c r="L20" t="n">
-        <v>50.5</v>
+        <v>51.5</v>
       </c>
       <c r="M20" t="s">
         <v>37</v>
       </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46249</v>
+        <v>46255</v>
       </c>
       <c r="B21" t="s">
         <v>34</v>
@@ -1408,16 +1379,16 @@
         <v>36</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2</v>
+        <v>-5.7</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2</v>
+        <v>-5.7</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.7</v>
+        <v>-7</v>
       </c>
       <c r="H21" t="n">
-        <v>23.9</v>
+        <v>24.5</v>
       </c>
       <c r="I21" t="s">
         <v>21</v>
@@ -1426,42 +1397,42 @@
         <v>20</v>
       </c>
       <c r="K21" t="n">
-        <v>5.5</v>
+        <v>-14</v>
       </c>
       <c r="L21" t="n">
-        <v>50.5</v>
+        <v>51.5</v>
       </c>
       <c r="M21" t="s">
         <v>37</v>
       </c>
       <c r="N21" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46249</v>
+        <v>46256</v>
       </c>
       <c r="B22" t="s">
         <v>38</v>
       </c>
       <c r="C22" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" t="s">
         <v>39</v>
       </c>
-      <c r="D22" t="s">
-        <v>40</v>
-      </c>
       <c r="E22" t="n">
-        <v>7</v>
+        <v>-3.3</v>
       </c>
       <c r="F22" t="n">
-        <v>7</v>
+        <v>-3.3</v>
       </c>
       <c r="G22" t="n">
-        <v>5.7</v>
+        <v>-8.8</v>
       </c>
       <c r="H22" t="n">
-        <v>44.2</v>
+        <v>44.7</v>
       </c>
       <c r="I22" t="s">
         <v>17</v>
@@ -1470,42 +1441,42 @@
         <v>18</v>
       </c>
       <c r="K22" t="n">
-        <v>7.5</v>
+        <v>-8</v>
       </c>
       <c r="L22" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M22" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46249</v>
+        <v>46256</v>
       </c>
       <c r="B23" t="s">
         <v>38</v>
       </c>
       <c r="C23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" t="s">
         <v>39</v>
       </c>
-      <c r="D23" t="s">
-        <v>40</v>
-      </c>
       <c r="E23" t="n">
-        <v>7</v>
+        <v>-3.3</v>
       </c>
       <c r="F23" t="n">
-        <v>7</v>
+        <v>-3.3</v>
       </c>
       <c r="G23" t="n">
-        <v>5.7</v>
+        <v>-8.8</v>
       </c>
       <c r="H23" t="n">
-        <v>43.6</v>
+        <v>44.1</v>
       </c>
       <c r="I23" t="s">
         <v>17</v>
@@ -1514,42 +1485,42 @@
         <v>20</v>
       </c>
       <c r="K23" t="n">
-        <v>7.5</v>
+        <v>-8</v>
       </c>
       <c r="L23" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M23" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46249</v>
+        <v>46256</v>
       </c>
       <c r="B24" t="s">
         <v>38</v>
       </c>
       <c r="C24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" t="s">
         <v>39</v>
       </c>
-      <c r="D24" t="s">
-        <v>40</v>
-      </c>
       <c r="E24" t="n">
-        <v>3.5</v>
+        <v>-1.6</v>
       </c>
       <c r="F24" t="n">
-        <v>3.5</v>
+        <v>-1.6</v>
       </c>
       <c r="G24" t="n">
-        <v>2.9</v>
+        <v>-4.4</v>
       </c>
       <c r="H24" t="n">
-        <v>22.1</v>
+        <v>22.3</v>
       </c>
       <c r="I24" t="s">
         <v>21</v>
@@ -1558,42 +1529,42 @@
         <v>18</v>
       </c>
       <c r="K24" t="n">
-        <v>7.5</v>
+        <v>-8</v>
       </c>
       <c r="L24" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M24" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46249</v>
+        <v>46256</v>
       </c>
       <c r="B25" t="s">
         <v>38</v>
       </c>
       <c r="C25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" t="s">
         <v>39</v>
       </c>
-      <c r="D25" t="s">
-        <v>40</v>
-      </c>
       <c r="E25" t="n">
-        <v>3.5</v>
+        <v>-1.6</v>
       </c>
       <c r="F25" t="n">
-        <v>3.5</v>
+        <v>-1.6</v>
       </c>
       <c r="G25" t="n">
-        <v>2.9</v>
+        <v>-4.4</v>
       </c>
       <c r="H25" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="I25" t="s">
         <v>21</v>
@@ -1602,42 +1573,42 @@
         <v>20</v>
       </c>
       <c r="K25" t="n">
-        <v>7.5</v>
+        <v>-8</v>
       </c>
       <c r="L25" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M25" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46250</v>
+        <v>46256</v>
       </c>
       <c r="B26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" t="s">
         <v>42</v>
       </c>
-      <c r="C26" t="s">
-        <v>43</v>
-      </c>
-      <c r="D26" t="s">
-        <v>44</v>
-      </c>
       <c r="E26" t="n">
-        <v>-11.1</v>
+        <v>5.6</v>
       </c>
       <c r="F26" t="n">
-        <v>-11.1</v>
+        <v>5.6</v>
       </c>
       <c r="G26" t="n">
-        <v>-11</v>
+        <v>4.9</v>
       </c>
       <c r="H26" t="n">
-        <v>46.7</v>
+        <v>44.8</v>
       </c>
       <c r="I26" t="s">
         <v>17</v>
@@ -1646,42 +1617,42 @@
         <v>18</v>
       </c>
       <c r="K26" t="n">
-        <v>-13</v>
+        <v>3.5</v>
       </c>
       <c r="L26" t="n">
-        <v>50.5</v>
+        <v>45.5</v>
       </c>
       <c r="M26" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N26" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46250</v>
+        <v>46256</v>
       </c>
       <c r="B27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" t="s">
         <v>42</v>
       </c>
-      <c r="C27" t="s">
-        <v>43</v>
-      </c>
-      <c r="D27" t="s">
-        <v>44</v>
-      </c>
       <c r="E27" t="n">
-        <v>-11.1</v>
+        <v>5.6</v>
       </c>
       <c r="F27" t="n">
-        <v>-11.1</v>
+        <v>5.6</v>
       </c>
       <c r="G27" t="n">
-        <v>-11</v>
+        <v>4.9</v>
       </c>
       <c r="H27" t="n">
-        <v>45.6</v>
+        <v>44.4</v>
       </c>
       <c r="I27" t="s">
         <v>17</v>
@@ -1690,42 +1661,42 @@
         <v>20</v>
       </c>
       <c r="K27" t="n">
-        <v>-13</v>
+        <v>3.5</v>
       </c>
       <c r="L27" t="n">
-        <v>50.5</v>
+        <v>45.5</v>
       </c>
       <c r="M27" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N27" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46250</v>
+        <v>46256</v>
       </c>
       <c r="B28" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" t="s">
+        <v>41</v>
+      </c>
+      <c r="D28" t="s">
         <v>42</v>
       </c>
-      <c r="C28" t="s">
-        <v>43</v>
-      </c>
-      <c r="D28" t="s">
-        <v>44</v>
-      </c>
       <c r="E28" t="n">
-        <v>-5.6</v>
+        <v>2.8</v>
       </c>
       <c r="F28" t="n">
-        <v>-5.6</v>
+        <v>2.8</v>
       </c>
       <c r="G28" t="n">
-        <v>-5.5</v>
+        <v>2.4</v>
       </c>
       <c r="H28" t="n">
-        <v>23.4</v>
+        <v>22.4</v>
       </c>
       <c r="I28" t="s">
         <v>21</v>
@@ -1734,42 +1705,42 @@
         <v>18</v>
       </c>
       <c r="K28" t="n">
-        <v>-13</v>
+        <v>3.5</v>
       </c>
       <c r="L28" t="n">
-        <v>50.5</v>
+        <v>45.5</v>
       </c>
       <c r="M28" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N28" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46250</v>
+        <v>46256</v>
       </c>
       <c r="B29" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29" t="s">
+        <v>41</v>
+      </c>
+      <c r="D29" t="s">
         <v>42</v>
       </c>
-      <c r="C29" t="s">
-        <v>43</v>
-      </c>
-      <c r="D29" t="s">
-        <v>44</v>
-      </c>
       <c r="E29" t="n">
-        <v>-5.6</v>
+        <v>2.8</v>
       </c>
       <c r="F29" t="n">
-        <v>-5.6</v>
+        <v>2.8</v>
       </c>
       <c r="G29" t="n">
-        <v>-5.5</v>
+        <v>2.4</v>
       </c>
       <c r="H29" t="n">
-        <v>22.8</v>
+        <v>22.2</v>
       </c>
       <c r="I29" t="s">
         <v>21</v>
@@ -1778,42 +1749,42 @@
         <v>20</v>
       </c>
       <c r="K29" t="n">
-        <v>-13</v>
+        <v>3.5</v>
       </c>
       <c r="L29" t="n">
-        <v>50.5</v>
+        <v>45.5</v>
       </c>
       <c r="M29" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N29" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46250</v>
+        <v>46256</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="D30" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>5.8</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>5.8</v>
       </c>
       <c r="G30" t="n">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="H30" t="n">
-        <v>45.5</v>
+        <v>40.1</v>
       </c>
       <c r="I30" t="s">
         <v>17</v>
@@ -1822,42 +1793,42 @@
         <v>18</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L30" t="n">
-        <v>47.5</v>
+        <v>43.5</v>
       </c>
       <c r="M30" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N30" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46250</v>
+        <v>46256</v>
       </c>
       <c r="B31" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C31" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="D31" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>5.8</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>5.8</v>
       </c>
       <c r="G31" t="n">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="H31" t="n">
-        <v>44.2</v>
+        <v>40.1</v>
       </c>
       <c r="I31" t="s">
         <v>17</v>
@@ -1866,42 +1837,42 @@
         <v>20</v>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L31" t="n">
-        <v>47.5</v>
+        <v>43.5</v>
       </c>
       <c r="M31" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N31" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46250</v>
+        <v>46256</v>
       </c>
       <c r="B32" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C32" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="D32" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E32" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="G32" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="H32" t="n">
-        <v>22.7</v>
+        <v>20.1</v>
       </c>
       <c r="I32" t="s">
         <v>21</v>
@@ -1910,42 +1881,42 @@
         <v>18</v>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L32" t="n">
-        <v>47.5</v>
+        <v>43.5</v>
       </c>
       <c r="M32" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N32" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46250</v>
+        <v>46256</v>
       </c>
       <c r="B33" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C33" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="D33" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="F33" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="G33" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="H33" t="n">
-        <v>22.1</v>
+        <v>20.1</v>
       </c>
       <c r="I33" t="s">
         <v>21</v>
@@ -1954,16 +1925,368 @@
         <v>20</v>
       </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L33" t="n">
-        <v>47.5</v>
+        <v>43.5</v>
       </c>
       <c r="M33" t="s">
+        <v>46</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>46257</v>
+      </c>
+      <c r="B34" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" t="s">
+        <v>16</v>
+      </c>
+      <c r="D34" t="s">
+        <v>47</v>
+      </c>
+      <c r="E34" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="F34" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="G34" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H34" t="n">
+        <v>47</v>
+      </c>
+      <c r="I34" t="s">
+        <v>17</v>
+      </c>
+      <c r="J34" t="s">
+        <v>18</v>
+      </c>
+      <c r="K34" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="L34" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="M34" t="s">
+        <v>48</v>
+      </c>
+      <c r="N34" t="n">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46257</v>
+      </c>
+      <c r="B35" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" t="s">
+        <v>16</v>
+      </c>
+      <c r="D35" t="s">
+        <v>47</v>
+      </c>
+      <c r="E35" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="F35" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="G35" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H35" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="I35" t="s">
+        <v>17</v>
+      </c>
+      <c r="J35" t="s">
+        <v>20</v>
+      </c>
+      <c r="K35" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="L35" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="M35" t="s">
+        <v>48</v>
+      </c>
+      <c r="N35" t="n">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>46257</v>
+      </c>
+      <c r="B36" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" t="s">
+        <v>16</v>
+      </c>
+      <c r="D36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E36" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F36" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H36" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I36" t="s">
+        <v>21</v>
+      </c>
+      <c r="J36" t="s">
+        <v>18</v>
+      </c>
+      <c r="K36" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="L36" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="M36" t="s">
+        <v>48</v>
+      </c>
+      <c r="N36" t="n">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>46257</v>
+      </c>
+      <c r="B37" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" t="s">
+        <v>16</v>
+      </c>
+      <c r="D37" t="s">
+        <v>47</v>
+      </c>
+      <c r="E37" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H37" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="I37" t="s">
+        <v>21</v>
+      </c>
+      <c r="J37" t="s">
+        <v>20</v>
+      </c>
+      <c r="K37" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="L37" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="M37" t="s">
+        <v>48</v>
+      </c>
+      <c r="N37" t="n">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>46257</v>
+      </c>
+      <c r="B38" t="s">
+        <v>22</v>
+      </c>
+      <c r="C38" t="s">
         <v>49</v>
       </c>
-      <c r="N33" t="n">
-        <v>3.9</v>
+      <c r="D38" t="s">
+        <v>23</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-20.4</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-20.4</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-15.6</v>
+      </c>
+      <c r="H38" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="I38" t="s">
+        <v>17</v>
+      </c>
+      <c r="J38" t="s">
+        <v>18</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-18</v>
+      </c>
+      <c r="L38" t="n">
+        <v>51</v>
+      </c>
+      <c r="M38" t="s">
+        <v>50</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>46257</v>
+      </c>
+      <c r="B39" t="s">
+        <v>22</v>
+      </c>
+      <c r="C39" t="s">
+        <v>49</v>
+      </c>
+      <c r="D39" t="s">
+        <v>23</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-20.4</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-20.4</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-15.6</v>
+      </c>
+      <c r="H39" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="I39" t="s">
+        <v>17</v>
+      </c>
+      <c r="J39" t="s">
+        <v>20</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-18</v>
+      </c>
+      <c r="L39" t="n">
+        <v>51</v>
+      </c>
+      <c r="M39" t="s">
+        <v>50</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>46257</v>
+      </c>
+      <c r="B40" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" t="s">
+        <v>49</v>
+      </c>
+      <c r="D40" t="s">
+        <v>23</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-10.2</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-10.2</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-7.8</v>
+      </c>
+      <c r="H40" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="I40" t="s">
+        <v>21</v>
+      </c>
+      <c r="J40" t="s">
+        <v>18</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-18</v>
+      </c>
+      <c r="L40" t="n">
+        <v>51</v>
+      </c>
+      <c r="M40" t="s">
+        <v>50</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>46257</v>
+      </c>
+      <c r="B41" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" t="s">
+        <v>49</v>
+      </c>
+      <c r="D41" t="s">
+        <v>23</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-10.2</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-10.2</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-7.8</v>
+      </c>
+      <c r="H41" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="I41" t="s">
+        <v>21</v>
+      </c>
+      <c r="J41" t="s">
+        <v>20</v>
+      </c>
+      <c r="K41" t="n">
+        <v>-18</v>
+      </c>
+      <c r="L41" t="n">
+        <v>51</v>
+      </c>
+      <c r="M41" t="s">
+        <v>50</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_upcoming_projections.xlsx
+++ b/files/NRL_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -56,112 +56,109 @@
     <t xml:space="preserve">Forecast Rain mm</t>
   </si>
   <si>
+    <t xml:space="preserve">19:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melbourne storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penrith panthers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Rain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AAMI Park, Melbourne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GIO Stadium, Canberra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dolphins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suncorp Stadium, Brisbane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manly-warringah sea eagles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">McDonald Jones Stadium, Newcastle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">south sydney rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accor Stadium, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st george-illawarra dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WIN Stadium, Wollongong</t>
+  </si>
+  <si>
     <t xml:space="preserve">14:00</t>
   </si>
   <si>
-    <t xml:space="preserve">newcastle knights</t>
-  </si>
-  <si>
     <t xml:space="preserve">gold coast titans</t>
   </si>
   <si>
-    <t xml:space="preserve">FT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Rain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">McDonald Jones Stadium, Newcastle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1H</t>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cbus Super Stadium, Gold Coast</t>
   </si>
   <si>
     <t xml:space="preserve">16:05</t>
   </si>
   <si>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
     <t xml:space="preserve">wests tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st george-illawarra dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leichhardt Oval, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">melbourne storm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penrith panthers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AAMI Park, Melbourne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberra raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GIO Stadium, Canberra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suncorp Stadium, Brisbane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manly-warringah sea eagles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">south sydney rabbitohs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accor Stadium, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WIN Stadium, Wollongong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cbus Super Stadium, Gold Coast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney roosters</t>
   </si>
   <si>
     <t xml:space="preserve">Allianz Stadium, Sydney</t>
@@ -563,7 +560,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46250</v>
+        <v>46254</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -575,16 +572,16 @@
         <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>-9.2</v>
+        <v>3.1</v>
       </c>
       <c r="F2" t="n">
-        <v>-9.2</v>
+        <v>3.1</v>
       </c>
       <c r="G2" t="n">
-        <v>-6</v>
+        <v>5.2</v>
       </c>
       <c r="H2" t="n">
-        <v>47.2</v>
+        <v>42.1</v>
       </c>
       <c r="I2" t="s">
         <v>17</v>
@@ -592,18 +589,22 @@
       <c r="J2" t="s">
         <v>18</v>
       </c>
-      <c r="K2"/>
-      <c r="L2"/>
+      <c r="K2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="L2" t="n">
+        <v>43</v>
+      </c>
       <c r="M2" t="s">
         <v>19</v>
       </c>
       <c r="N2" t="n">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46250</v>
+        <v>46254</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -615,16 +616,16 @@
         <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>-9.2</v>
+        <v>3.1</v>
       </c>
       <c r="F3" t="n">
-        <v>-9.2</v>
+        <v>3.1</v>
       </c>
       <c r="G3" t="n">
-        <v>-6</v>
+        <v>5.2</v>
       </c>
       <c r="H3" t="n">
-        <v>46.6</v>
+        <v>41.1</v>
       </c>
       <c r="I3" t="s">
         <v>17</v>
@@ -632,18 +633,22 @@
       <c r="J3" t="s">
         <v>20</v>
       </c>
-      <c r="K3"/>
-      <c r="L3"/>
+      <c r="K3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>43</v>
+      </c>
       <c r="M3" t="s">
         <v>19</v>
       </c>
       <c r="N3" t="n">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46250</v>
+        <v>46254</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -655,16 +660,16 @@
         <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>-4.6</v>
+        <v>1.6</v>
       </c>
       <c r="F4" t="n">
-        <v>-4.6</v>
+        <v>1.6</v>
       </c>
       <c r="G4" t="n">
-        <v>-3</v>
+        <v>2.6</v>
       </c>
       <c r="H4" t="n">
-        <v>23.6</v>
+        <v>21</v>
       </c>
       <c r="I4" t="s">
         <v>21</v>
@@ -672,18 +677,22 @@
       <c r="J4" t="s">
         <v>18</v>
       </c>
-      <c r="K4"/>
-      <c r="L4"/>
+      <c r="K4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>43</v>
+      </c>
       <c r="M4" t="s">
         <v>19</v>
       </c>
       <c r="N4" t="n">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46250</v>
+        <v>46254</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -695,16 +704,16 @@
         <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>-4.6</v>
+        <v>1.6</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.6</v>
+        <v>1.6</v>
       </c>
       <c r="G5" t="n">
-        <v>-3</v>
+        <v>2.6</v>
       </c>
       <c r="H5" t="n">
-        <v>23.3</v>
+        <v>20.5</v>
       </c>
       <c r="I5" t="s">
         <v>21</v>
@@ -712,18 +721,22 @@
       <c r="J5" t="s">
         <v>20</v>
       </c>
-      <c r="K5"/>
-      <c r="L5"/>
+      <c r="K5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>43</v>
+      </c>
       <c r="M5" t="s">
         <v>19</v>
       </c>
       <c r="N5" t="n">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46250</v>
+        <v>46255</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
@@ -735,16 +748,16 @@
         <v>24</v>
       </c>
       <c r="E6" t="n">
-        <v>4.5</v>
+        <v>-8.7</v>
       </c>
       <c r="F6" t="n">
-        <v>4.5</v>
+        <v>-8.7</v>
       </c>
       <c r="G6" t="n">
-        <v>-1</v>
+        <v>-9.1</v>
       </c>
       <c r="H6" t="n">
-        <v>44.5</v>
+        <v>47.7</v>
       </c>
       <c r="I6" t="s">
         <v>17</v>
@@ -752,18 +765,22 @@
       <c r="J6" t="s">
         <v>18</v>
       </c>
-      <c r="K6"/>
-      <c r="L6"/>
+      <c r="K6" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>51</v>
+      </c>
       <c r="M6" t="s">
         <v>25</v>
       </c>
       <c r="N6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46250</v>
+        <v>46255</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
@@ -775,16 +792,16 @@
         <v>24</v>
       </c>
       <c r="E7" t="n">
-        <v>4.5</v>
+        <v>-8.7</v>
       </c>
       <c r="F7" t="n">
-        <v>4.5</v>
+        <v>-8.7</v>
       </c>
       <c r="G7" t="n">
-        <v>-1</v>
+        <v>-9.1</v>
       </c>
       <c r="H7" t="n">
-        <v>43.7</v>
+        <v>47.7</v>
       </c>
       <c r="I7" t="s">
         <v>17</v>
@@ -792,18 +809,22 @@
       <c r="J7" t="s">
         <v>20</v>
       </c>
-      <c r="K7"/>
-      <c r="L7"/>
+      <c r="K7" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>51</v>
+      </c>
       <c r="M7" t="s">
         <v>25</v>
       </c>
       <c r="N7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46250</v>
+        <v>46255</v>
       </c>
       <c r="B8" t="s">
         <v>22</v>
@@ -815,16 +836,16 @@
         <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2</v>
+        <v>-4.3</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2</v>
+        <v>-4.3</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5</v>
+        <v>-4.6</v>
       </c>
       <c r="H8" t="n">
-        <v>22.2</v>
+        <v>23.9</v>
       </c>
       <c r="I8" t="s">
         <v>21</v>
@@ -832,18 +853,22 @@
       <c r="J8" t="s">
         <v>18</v>
       </c>
-      <c r="K8"/>
-      <c r="L8"/>
+      <c r="K8" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>51</v>
+      </c>
       <c r="M8" t="s">
         <v>25</v>
       </c>
       <c r="N8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46250</v>
+        <v>46255</v>
       </c>
       <c r="B9" t="s">
         <v>22</v>
@@ -855,16 +880,16 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>2.2</v>
+        <v>-4.3</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2</v>
+        <v>-4.3</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5</v>
+        <v>-4.6</v>
       </c>
       <c r="H9" t="n">
-        <v>21.8</v>
+        <v>23.9</v>
       </c>
       <c r="I9" t="s">
         <v>21</v>
@@ -872,18 +897,22 @@
       <c r="J9" t="s">
         <v>20</v>
       </c>
-      <c r="K9"/>
-      <c r="L9"/>
+      <c r="K9" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>51</v>
+      </c>
       <c r="M9" t="s">
         <v>25</v>
       </c>
       <c r="N9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B10" t="s">
         <v>26</v>
@@ -895,16 +924,16 @@
         <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>2.7</v>
+        <v>-11.3</v>
       </c>
       <c r="F10" t="n">
-        <v>2.7</v>
+        <v>-11.3</v>
       </c>
       <c r="G10" t="n">
-        <v>3.1</v>
+        <v>-12.2</v>
       </c>
       <c r="H10" t="n">
-        <v>42.1</v>
+        <v>49.1</v>
       </c>
       <c r="I10" t="s">
         <v>17</v>
@@ -913,21 +942,21 @@
         <v>18</v>
       </c>
       <c r="K10" t="n">
-        <v>8.5</v>
+        <v>-14</v>
       </c>
       <c r="L10" t="n">
-        <v>43.5</v>
+        <v>51</v>
       </c>
       <c r="M10" t="s">
         <v>29</v>
       </c>
       <c r="N10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B11" t="s">
         <v>26</v>
@@ -939,16 +968,16 @@
         <v>28</v>
       </c>
       <c r="E11" t="n">
-        <v>2.7</v>
+        <v>-11.3</v>
       </c>
       <c r="F11" t="n">
-        <v>2.7</v>
+        <v>-11.3</v>
       </c>
       <c r="G11" t="n">
-        <v>3.1</v>
+        <v>-12.2</v>
       </c>
       <c r="H11" t="n">
-        <v>41.7</v>
+        <v>49.1</v>
       </c>
       <c r="I11" t="s">
         <v>17</v>
@@ -957,21 +986,21 @@
         <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>8.5</v>
+        <v>-14</v>
       </c>
       <c r="L11" t="n">
-        <v>43.5</v>
+        <v>51</v>
       </c>
       <c r="M11" t="s">
         <v>29</v>
       </c>
       <c r="N11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B12" t="s">
         <v>26</v>
@@ -983,16 +1012,16 @@
         <v>28</v>
       </c>
       <c r="E12" t="n">
-        <v>1.4</v>
+        <v>-5.7</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4</v>
+        <v>-5.7</v>
       </c>
       <c r="G12" t="n">
-        <v>1.5</v>
+        <v>-6.1</v>
       </c>
       <c r="H12" t="n">
-        <v>21</v>
+        <v>24.6</v>
       </c>
       <c r="I12" t="s">
         <v>21</v>
@@ -1001,21 +1030,21 @@
         <v>18</v>
       </c>
       <c r="K12" t="n">
-        <v>8.5</v>
+        <v>-14</v>
       </c>
       <c r="L12" t="n">
-        <v>43.5</v>
+        <v>51</v>
       </c>
       <c r="M12" t="s">
         <v>29</v>
       </c>
       <c r="N12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B13" t="s">
         <v>26</v>
@@ -1027,16 +1056,16 @@
         <v>28</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4</v>
+        <v>-5.7</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4</v>
+        <v>-5.7</v>
       </c>
       <c r="G13" t="n">
-        <v>1.5</v>
+        <v>-6.1</v>
       </c>
       <c r="H13" t="n">
-        <v>20.9</v>
+        <v>24.6</v>
       </c>
       <c r="I13" t="s">
         <v>21</v>
@@ -1045,21 +1074,21 @@
         <v>20</v>
       </c>
       <c r="K13" t="n">
-        <v>8.5</v>
+        <v>-14</v>
       </c>
       <c r="L13" t="n">
-        <v>43.5</v>
+        <v>51</v>
       </c>
       <c r="M13" t="s">
         <v>29</v>
       </c>
       <c r="N13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B14" t="s">
         <v>30</v>
@@ -1071,16 +1100,16 @@
         <v>32</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.8</v>
+        <v>-1.6</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.8</v>
+        <v>-1.6</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.2</v>
+        <v>-4</v>
       </c>
       <c r="H14" t="n">
-        <v>47.7</v>
+        <v>44.7</v>
       </c>
       <c r="I14" t="s">
         <v>17</v>
@@ -1089,21 +1118,21 @@
         <v>18</v>
       </c>
       <c r="K14" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L14" t="n">
-        <v>51.5</v>
+        <v>50.5</v>
       </c>
       <c r="M14" t="s">
         <v>33</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B15" t="s">
         <v>30</v>
@@ -1115,16 +1144,16 @@
         <v>32</v>
       </c>
       <c r="E15" t="n">
-        <v>-4.8</v>
+        <v>-1.6</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.8</v>
+        <v>-1.6</v>
       </c>
       <c r="G15" t="n">
-        <v>-4.2</v>
+        <v>-4</v>
       </c>
       <c r="H15" t="n">
-        <v>47.7</v>
+        <v>43.7</v>
       </c>
       <c r="I15" t="s">
         <v>17</v>
@@ -1133,21 +1162,21 @@
         <v>20</v>
       </c>
       <c r="K15" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L15" t="n">
-        <v>51.5</v>
+        <v>50.5</v>
       </c>
       <c r="M15" t="s">
         <v>33</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B16" t="s">
         <v>30</v>
@@ -1159,16 +1188,16 @@
         <v>32</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.4</v>
+        <v>-0.8</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.4</v>
+        <v>-0.8</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.1</v>
+        <v>-2</v>
       </c>
       <c r="H16" t="n">
-        <v>23.9</v>
+        <v>22.3</v>
       </c>
       <c r="I16" t="s">
         <v>21</v>
@@ -1177,21 +1206,21 @@
         <v>18</v>
       </c>
       <c r="K16" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L16" t="n">
-        <v>51.5</v>
+        <v>50.5</v>
       </c>
       <c r="M16" t="s">
         <v>33</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B17" t="s">
         <v>30</v>
@@ -1203,16 +1232,16 @@
         <v>32</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.4</v>
+        <v>-0.8</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.4</v>
+        <v>-0.8</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.1</v>
+        <v>-2</v>
       </c>
       <c r="H17" t="n">
-        <v>23.9</v>
+        <v>21.8</v>
       </c>
       <c r="I17" t="s">
         <v>21</v>
@@ -1221,21 +1250,21 @@
         <v>20</v>
       </c>
       <c r="K17" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L17" t="n">
-        <v>51.5</v>
+        <v>50.5</v>
       </c>
       <c r="M17" t="s">
         <v>33</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
@@ -1247,16 +1276,16 @@
         <v>36</v>
       </c>
       <c r="E18" t="n">
-        <v>-11.3</v>
+        <v>3.1</v>
       </c>
       <c r="F18" t="n">
-        <v>-11.3</v>
+        <v>3.1</v>
       </c>
       <c r="G18" t="n">
-        <v>-14</v>
+        <v>0.8</v>
       </c>
       <c r="H18" t="n">
-        <v>49.1</v>
+        <v>44.8</v>
       </c>
       <c r="I18" t="s">
         <v>17</v>
@@ -1265,21 +1294,21 @@
         <v>18</v>
       </c>
       <c r="K18" t="n">
-        <v>-14</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
-        <v>51.5</v>
+        <v>45.5</v>
       </c>
       <c r="M18" t="s">
         <v>37</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B19" t="s">
         <v>34</v>
@@ -1291,16 +1320,16 @@
         <v>36</v>
       </c>
       <c r="E19" t="n">
-        <v>-11.3</v>
+        <v>3.1</v>
       </c>
       <c r="F19" t="n">
-        <v>-11.3</v>
+        <v>3.1</v>
       </c>
       <c r="G19" t="n">
-        <v>-14</v>
+        <v>0.8</v>
       </c>
       <c r="H19" t="n">
-        <v>49</v>
+        <v>44.8</v>
       </c>
       <c r="I19" t="s">
         <v>17</v>
@@ -1309,21 +1338,21 @@
         <v>20</v>
       </c>
       <c r="K19" t="n">
-        <v>-14</v>
+        <v>4</v>
       </c>
       <c r="L19" t="n">
-        <v>51.5</v>
+        <v>45.5</v>
       </c>
       <c r="M19" t="s">
         <v>37</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B20" t="s">
         <v>34</v>
@@ -1335,16 +1364,16 @@
         <v>36</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.7</v>
+        <v>1.5</v>
       </c>
       <c r="F20" t="n">
-        <v>-5.7</v>
+        <v>1.5</v>
       </c>
       <c r="G20" t="n">
-        <v>-7</v>
+        <v>0.4</v>
       </c>
       <c r="H20" t="n">
-        <v>24.6</v>
+        <v>22.4</v>
       </c>
       <c r="I20" t="s">
         <v>21</v>
@@ -1353,21 +1382,21 @@
         <v>18</v>
       </c>
       <c r="K20" t="n">
-        <v>-14</v>
+        <v>4</v>
       </c>
       <c r="L20" t="n">
-        <v>51.5</v>
+        <v>45.5</v>
       </c>
       <c r="M20" t="s">
         <v>37</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B21" t="s">
         <v>34</v>
@@ -1379,16 +1408,16 @@
         <v>36</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.7</v>
+        <v>1.5</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.7</v>
+        <v>1.5</v>
       </c>
       <c r="G21" t="n">
-        <v>-7</v>
+        <v>0.4</v>
       </c>
       <c r="H21" t="n">
-        <v>24.5</v>
+        <v>22.4</v>
       </c>
       <c r="I21" t="s">
         <v>21</v>
@@ -1397,16 +1426,16 @@
         <v>20</v>
       </c>
       <c r="K21" t="n">
-        <v>-14</v>
+        <v>4</v>
       </c>
       <c r="L21" t="n">
-        <v>51.5</v>
+        <v>45.5</v>
       </c>
       <c r="M21" t="s">
         <v>37</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="22">
@@ -1417,22 +1446,22 @@
         <v>38</v>
       </c>
       <c r="C22" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="D22" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.3</v>
+        <v>5.7</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.3</v>
+        <v>5.7</v>
       </c>
       <c r="G22" t="n">
-        <v>-8.8</v>
+        <v>2.2</v>
       </c>
       <c r="H22" t="n">
-        <v>44.7</v>
+        <v>40.1</v>
       </c>
       <c r="I22" t="s">
         <v>17</v>
@@ -1441,16 +1470,16 @@
         <v>18</v>
       </c>
       <c r="K22" t="n">
-        <v>-8</v>
+        <v>6</v>
       </c>
       <c r="L22" t="n">
-        <v>51</v>
+        <v>43.5</v>
       </c>
       <c r="M22" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="N22" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="23">
@@ -1461,22 +1490,22 @@
         <v>38</v>
       </c>
       <c r="C23" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="D23" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3</v>
+        <v>5.7</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.3</v>
+        <v>5.7</v>
       </c>
       <c r="G23" t="n">
-        <v>-8.8</v>
+        <v>2.2</v>
       </c>
       <c r="H23" t="n">
-        <v>44.1</v>
+        <v>39.6</v>
       </c>
       <c r="I23" t="s">
         <v>17</v>
@@ -1485,16 +1514,16 @@
         <v>20</v>
       </c>
       <c r="K23" t="n">
-        <v>-8</v>
+        <v>6</v>
       </c>
       <c r="L23" t="n">
-        <v>51</v>
+        <v>43.5</v>
       </c>
       <c r="M23" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="N23" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="24">
@@ -1505,22 +1534,22 @@
         <v>38</v>
       </c>
       <c r="C24" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="D24" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.6</v>
+        <v>2.8</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.6</v>
+        <v>2.8</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.4</v>
+        <v>1.1</v>
       </c>
       <c r="H24" t="n">
-        <v>22.3</v>
+        <v>20.1</v>
       </c>
       <c r="I24" t="s">
         <v>21</v>
@@ -1529,16 +1558,16 @@
         <v>18</v>
       </c>
       <c r="K24" t="n">
-        <v>-8</v>
+        <v>6</v>
       </c>
       <c r="L24" t="n">
-        <v>51</v>
+        <v>43.5</v>
       </c>
       <c r="M24" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="N24" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="25">
@@ -1549,22 +1578,22 @@
         <v>38</v>
       </c>
       <c r="C25" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="D25" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.6</v>
+        <v>2.8</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.6</v>
+        <v>2.8</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.4</v>
+        <v>1.1</v>
       </c>
       <c r="H25" t="n">
-        <v>22</v>
+        <v>19.8</v>
       </c>
       <c r="I25" t="s">
         <v>21</v>
@@ -1573,42 +1602,42 @@
         <v>20</v>
       </c>
       <c r="K25" t="n">
-        <v>-8</v>
+        <v>6</v>
       </c>
       <c r="L25" t="n">
-        <v>51</v>
+        <v>43.5</v>
       </c>
       <c r="M25" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="N25" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B26" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C26" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D26" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E26" t="n">
-        <v>5.6</v>
+        <v>10.1</v>
       </c>
       <c r="F26" t="n">
-        <v>5.6</v>
+        <v>10.1</v>
       </c>
       <c r="G26" t="n">
-        <v>4.9</v>
+        <v>12.1</v>
       </c>
       <c r="H26" t="n">
-        <v>44.8</v>
+        <v>47</v>
       </c>
       <c r="I26" t="s">
         <v>17</v>
@@ -1617,42 +1646,42 @@
         <v>18</v>
       </c>
       <c r="K26" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="L26" t="n">
-        <v>45.5</v>
+        <v>49.5</v>
       </c>
       <c r="M26" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N26" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B27" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C27" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D27" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E27" t="n">
-        <v>5.6</v>
+        <v>10.1</v>
       </c>
       <c r="F27" t="n">
-        <v>5.6</v>
+        <v>10.1</v>
       </c>
       <c r="G27" t="n">
-        <v>4.9</v>
+        <v>12.1</v>
       </c>
       <c r="H27" t="n">
-        <v>44.4</v>
+        <v>46.1</v>
       </c>
       <c r="I27" t="s">
         <v>17</v>
@@ -1661,42 +1690,42 @@
         <v>20</v>
       </c>
       <c r="K27" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="L27" t="n">
-        <v>45.5</v>
+        <v>49.5</v>
       </c>
       <c r="M27" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N27" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B28" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C28" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D28" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E28" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="F28" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H28" t="n">
-        <v>22.4</v>
+        <v>23.5</v>
       </c>
       <c r="I28" t="s">
         <v>21</v>
@@ -1705,42 +1734,42 @@
         <v>18</v>
       </c>
       <c r="K28" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="L28" t="n">
-        <v>45.5</v>
+        <v>49.5</v>
       </c>
       <c r="M28" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N28" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C29" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D29" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E29" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="F29" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="G29" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H29" t="n">
-        <v>22.2</v>
+        <v>23</v>
       </c>
       <c r="I29" t="s">
         <v>21</v>
@@ -1749,42 +1778,42 @@
         <v>20</v>
       </c>
       <c r="K29" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="L29" t="n">
-        <v>45.5</v>
+        <v>49.5</v>
       </c>
       <c r="M29" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N29" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C30" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="D30" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E30" t="n">
-        <v>5.8</v>
+        <v>-20.5</v>
       </c>
       <c r="F30" t="n">
-        <v>5.8</v>
+        <v>-20.5</v>
       </c>
       <c r="G30" t="n">
-        <v>5</v>
+        <v>-22.7</v>
       </c>
       <c r="H30" t="n">
-        <v>40.1</v>
+        <v>45.1</v>
       </c>
       <c r="I30" t="s">
         <v>17</v>
@@ -1793,42 +1822,42 @@
         <v>18</v>
       </c>
       <c r="K30" t="n">
-        <v>6</v>
+        <v>-24.5</v>
       </c>
       <c r="L30" t="n">
-        <v>43.5</v>
+        <v>52</v>
       </c>
       <c r="M30" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C31" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="D31" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E31" t="n">
-        <v>5.8</v>
+        <v>-20.5</v>
       </c>
       <c r="F31" t="n">
-        <v>5.8</v>
+        <v>-20.5</v>
       </c>
       <c r="G31" t="n">
-        <v>5</v>
+        <v>-22.7</v>
       </c>
       <c r="H31" t="n">
-        <v>40.1</v>
+        <v>44.8</v>
       </c>
       <c r="I31" t="s">
         <v>17</v>
@@ -1837,42 +1866,42 @@
         <v>20</v>
       </c>
       <c r="K31" t="n">
-        <v>6</v>
+        <v>-24.5</v>
       </c>
       <c r="L31" t="n">
-        <v>43.5</v>
+        <v>52</v>
       </c>
       <c r="M31" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C32" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="D32" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E32" t="n">
-        <v>2.9</v>
+        <v>-10.2</v>
       </c>
       <c r="F32" t="n">
-        <v>2.9</v>
+        <v>-10.2</v>
       </c>
       <c r="G32" t="n">
-        <v>2.5</v>
+        <v>-11.4</v>
       </c>
       <c r="H32" t="n">
-        <v>20.1</v>
+        <v>22.6</v>
       </c>
       <c r="I32" t="s">
         <v>21</v>
@@ -1881,42 +1910,42 @@
         <v>18</v>
       </c>
       <c r="K32" t="n">
-        <v>6</v>
+        <v>-24.5</v>
       </c>
       <c r="L32" t="n">
-        <v>43.5</v>
+        <v>52</v>
       </c>
       <c r="M32" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C33" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="D33" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E33" t="n">
-        <v>2.9</v>
+        <v>-10.2</v>
       </c>
       <c r="F33" t="n">
-        <v>2.9</v>
+        <v>-10.2</v>
       </c>
       <c r="G33" t="n">
-        <v>2.5</v>
+        <v>-11.4</v>
       </c>
       <c r="H33" t="n">
-        <v>20.1</v>
+        <v>22.4</v>
       </c>
       <c r="I33" t="s">
         <v>21</v>
@@ -1925,367 +1954,15 @@
         <v>20</v>
       </c>
       <c r="K33" t="n">
-        <v>6</v>
+        <v>-24.5</v>
       </c>
       <c r="L33" t="n">
-        <v>43.5</v>
+        <v>52</v>
       </c>
       <c r="M33" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>46257</v>
-      </c>
-      <c r="B34" t="s">
-        <v>14</v>
-      </c>
-      <c r="C34" t="s">
-        <v>16</v>
-      </c>
-      <c r="D34" t="s">
-        <v>47</v>
-      </c>
-      <c r="E34" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="F34" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="G34" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="H34" t="n">
-        <v>47</v>
-      </c>
-      <c r="I34" t="s">
-        <v>17</v>
-      </c>
-      <c r="J34" t="s">
-        <v>18</v>
-      </c>
-      <c r="K34" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="L34" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="M34" t="s">
-        <v>48</v>
-      </c>
-      <c r="N34" t="n">
-        <v>14.7</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>46257</v>
-      </c>
-      <c r="B35" t="s">
-        <v>14</v>
-      </c>
-      <c r="C35" t="s">
-        <v>16</v>
-      </c>
-      <c r="D35" t="s">
-        <v>47</v>
-      </c>
-      <c r="E35" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="F35" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="G35" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="H35" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="I35" t="s">
-        <v>17</v>
-      </c>
-      <c r="J35" t="s">
-        <v>20</v>
-      </c>
-      <c r="K35" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="L35" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="M35" t="s">
-        <v>48</v>
-      </c>
-      <c r="N35" t="n">
-        <v>14.7</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>46257</v>
-      </c>
-      <c r="B36" t="s">
-        <v>14</v>
-      </c>
-      <c r="C36" t="s">
-        <v>16</v>
-      </c>
-      <c r="D36" t="s">
-        <v>47</v>
-      </c>
-      <c r="E36" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F36" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="G36" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H36" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="I36" t="s">
-        <v>21</v>
-      </c>
-      <c r="J36" t="s">
-        <v>18</v>
-      </c>
-      <c r="K36" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="L36" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="M36" t="s">
-        <v>48</v>
-      </c>
-      <c r="N36" t="n">
-        <v>14.7</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>46257</v>
-      </c>
-      <c r="B37" t="s">
-        <v>14</v>
-      </c>
-      <c r="C37" t="s">
-        <v>16</v>
-      </c>
-      <c r="D37" t="s">
-        <v>47</v>
-      </c>
-      <c r="E37" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F37" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="G37" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H37" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="I37" t="s">
-        <v>21</v>
-      </c>
-      <c r="J37" t="s">
-        <v>20</v>
-      </c>
-      <c r="K37" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="L37" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="M37" t="s">
-        <v>48</v>
-      </c>
-      <c r="N37" t="n">
-        <v>14.7</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>46257</v>
-      </c>
-      <c r="B38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C38" t="s">
-        <v>49</v>
-      </c>
-      <c r="D38" t="s">
-        <v>23</v>
-      </c>
-      <c r="E38" t="n">
-        <v>-20.4</v>
-      </c>
-      <c r="F38" t="n">
-        <v>-20.4</v>
-      </c>
-      <c r="G38" t="n">
-        <v>-15.6</v>
-      </c>
-      <c r="H38" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="I38" t="s">
-        <v>17</v>
-      </c>
-      <c r="J38" t="s">
-        <v>18</v>
-      </c>
-      <c r="K38" t="n">
-        <v>-18</v>
-      </c>
-      <c r="L38" t="n">
-        <v>51</v>
-      </c>
-      <c r="M38" t="s">
-        <v>50</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>46257</v>
-      </c>
-      <c r="B39" t="s">
-        <v>22</v>
-      </c>
-      <c r="C39" t="s">
-        <v>49</v>
-      </c>
-      <c r="D39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E39" t="n">
-        <v>-20.4</v>
-      </c>
-      <c r="F39" t="n">
-        <v>-20.4</v>
-      </c>
-      <c r="G39" t="n">
-        <v>-15.6</v>
-      </c>
-      <c r="H39" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="I39" t="s">
-        <v>17</v>
-      </c>
-      <c r="J39" t="s">
-        <v>20</v>
-      </c>
-      <c r="K39" t="n">
-        <v>-18</v>
-      </c>
-      <c r="L39" t="n">
-        <v>51</v>
-      </c>
-      <c r="M39" t="s">
-        <v>50</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>46257</v>
-      </c>
-      <c r="B40" t="s">
-        <v>22</v>
-      </c>
-      <c r="C40" t="s">
-        <v>49</v>
-      </c>
-      <c r="D40" t="s">
-        <v>23</v>
-      </c>
-      <c r="E40" t="n">
-        <v>-10.2</v>
-      </c>
-      <c r="F40" t="n">
-        <v>-10.2</v>
-      </c>
-      <c r="G40" t="n">
-        <v>-7.8</v>
-      </c>
-      <c r="H40" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="I40" t="s">
-        <v>21</v>
-      </c>
-      <c r="J40" t="s">
-        <v>18</v>
-      </c>
-      <c r="K40" t="n">
-        <v>-18</v>
-      </c>
-      <c r="L40" t="n">
-        <v>51</v>
-      </c>
-      <c r="M40" t="s">
-        <v>50</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>46257</v>
-      </c>
-      <c r="B41" t="s">
-        <v>22</v>
-      </c>
-      <c r="C41" t="s">
-        <v>49</v>
-      </c>
-      <c r="D41" t="s">
-        <v>23</v>
-      </c>
-      <c r="E41" t="n">
-        <v>-10.2</v>
-      </c>
-      <c r="F41" t="n">
-        <v>-10.2</v>
-      </c>
-      <c r="G41" t="n">
-        <v>-7.8</v>
-      </c>
-      <c r="H41" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="I41" t="s">
-        <v>21</v>
-      </c>
-      <c r="J41" t="s">
-        <v>20</v>
-      </c>
-      <c r="K41" t="n">
-        <v>-18</v>
-      </c>
-      <c r="L41" t="n">
-        <v>51</v>
-      </c>
-      <c r="M41" t="s">
-        <v>50</v>
-      </c>
-      <c r="N41" t="n">
         <v>0.9</v>
       </c>
     </row>

--- a/files/NRL_upcoming_projections.xlsx
+++ b/files/NRL_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -56,112 +56,115 @@
     <t xml:space="preserve">Forecast Rain mm</t>
   </si>
   <si>
+    <t xml:space="preserve">18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Rain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GIO Stadium, Canberra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dolphins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suncorp Stadium, Brisbane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manly-warringah sea eagles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">McDonald Jones Stadium, Newcastle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">south sydney rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accor Stadium, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st george-illawarra dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WIN Stadium, Wollongong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cbus Super Stadium, Gold Coast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wests tigers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allianz Stadium, Sydney</t>
+  </si>
+  <si>
     <t xml:space="preserve">19:50</t>
   </si>
   <si>
     <t xml:space="preserve">melbourne storm</t>
   </si>
   <si>
+    <t xml:space="preserve">4 Pines Park, Sydney</t>
+  </si>
+  <si>
     <t xml:space="preserve">penrith panthers</t>
   </si>
   <si>
-    <t xml:space="preserve">FT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Rain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AAMI Park, Melbourne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberra raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GIO Stadium, Canberra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suncorp Stadium, Brisbane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">newcastle knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manly-warringah sea eagles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">McDonald Jones Stadium, Newcastle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">south sydney rabbitohs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accor Stadium, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st george-illawarra dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WIN Stadium, Wollongong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cbus Super Stadium, Gold Coast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wests tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allianz Stadium, Sydney</t>
+    <t xml:space="preserve">BlueBet Stadium, Penrith</t>
   </si>
 </sst>
 </file>
@@ -560,7 +563,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -572,16 +575,16 @@
         <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1</v>
+        <v>-8.7</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1</v>
+        <v>-8.7</v>
       </c>
       <c r="G2" t="n">
-        <v>5.2</v>
+        <v>-4.6</v>
       </c>
       <c r="H2" t="n">
-        <v>42.1</v>
+        <v>47.7</v>
       </c>
       <c r="I2" t="s">
         <v>17</v>
@@ -589,22 +592,18 @@
       <c r="J2" t="s">
         <v>18</v>
       </c>
-      <c r="K2" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="L2" t="n">
-        <v>43</v>
-      </c>
+      <c r="K2"/>
+      <c r="L2"/>
       <c r="M2" t="s">
         <v>19</v>
       </c>
       <c r="N2" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -616,16 +615,16 @@
         <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1</v>
+        <v>-8.7</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1</v>
+        <v>-8.7</v>
       </c>
       <c r="G3" t="n">
-        <v>5.2</v>
+        <v>-4.6</v>
       </c>
       <c r="H3" t="n">
-        <v>41.1</v>
+        <v>47.3</v>
       </c>
       <c r="I3" t="s">
         <v>17</v>
@@ -633,22 +632,18 @@
       <c r="J3" t="s">
         <v>20</v>
       </c>
-      <c r="K3" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="L3" t="n">
-        <v>43</v>
-      </c>
+      <c r="K3"/>
+      <c r="L3"/>
       <c r="M3" t="s">
         <v>19</v>
       </c>
       <c r="N3" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -660,16 +655,16 @@
         <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6</v>
+        <v>-4.3</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6</v>
+        <v>-4.3</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6</v>
+        <v>-2.3</v>
       </c>
       <c r="H4" t="n">
-        <v>21</v>
+        <v>23.9</v>
       </c>
       <c r="I4" t="s">
         <v>21</v>
@@ -677,22 +672,18 @@
       <c r="J4" t="s">
         <v>18</v>
       </c>
-      <c r="K4" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="L4" t="n">
-        <v>43</v>
-      </c>
+      <c r="K4"/>
+      <c r="L4"/>
       <c r="M4" t="s">
         <v>19</v>
       </c>
       <c r="N4" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -704,16 +695,16 @@
         <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6</v>
+        <v>-4.3</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6</v>
+        <v>-4.3</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6</v>
+        <v>-2.3</v>
       </c>
       <c r="H5" t="n">
-        <v>20.5</v>
+        <v>23.7</v>
       </c>
       <c r="I5" t="s">
         <v>21</v>
@@ -721,17 +712,13 @@
       <c r="J5" t="s">
         <v>20</v>
       </c>
-      <c r="K5" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="L5" t="n">
-        <v>43</v>
-      </c>
+      <c r="K5"/>
+      <c r="L5"/>
       <c r="M5" t="s">
         <v>19</v>
       </c>
       <c r="N5" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -748,16 +735,16 @@
         <v>24</v>
       </c>
       <c r="E6" t="n">
-        <v>-8.7</v>
+        <v>-11.8</v>
       </c>
       <c r="F6" t="n">
-        <v>-8.7</v>
+        <v>-11.8</v>
       </c>
       <c r="G6" t="n">
-        <v>-9.1</v>
+        <v>-14.5</v>
       </c>
       <c r="H6" t="n">
-        <v>47.7</v>
+        <v>49.1</v>
       </c>
       <c r="I6" t="s">
         <v>17</v>
@@ -765,12 +752,8 @@
       <c r="J6" t="s">
         <v>18</v>
       </c>
-      <c r="K6" t="n">
-        <v>-11.5</v>
-      </c>
-      <c r="L6" t="n">
-        <v>51</v>
-      </c>
+      <c r="K6"/>
+      <c r="L6"/>
       <c r="M6" t="s">
         <v>25</v>
       </c>
@@ -792,16 +775,16 @@
         <v>24</v>
       </c>
       <c r="E7" t="n">
-        <v>-8.7</v>
+        <v>-11.8</v>
       </c>
       <c r="F7" t="n">
-        <v>-8.7</v>
+        <v>-11.8</v>
       </c>
       <c r="G7" t="n">
-        <v>-9.1</v>
+        <v>-14.5</v>
       </c>
       <c r="H7" t="n">
-        <v>47.7</v>
+        <v>49.1</v>
       </c>
       <c r="I7" t="s">
         <v>17</v>
@@ -809,12 +792,8 @@
       <c r="J7" t="s">
         <v>20</v>
       </c>
-      <c r="K7" t="n">
-        <v>-11.5</v>
-      </c>
-      <c r="L7" t="n">
-        <v>51</v>
-      </c>
+      <c r="K7"/>
+      <c r="L7"/>
       <c r="M7" t="s">
         <v>25</v>
       </c>
@@ -836,16 +815,16 @@
         <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.3</v>
+        <v>-5.9</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.3</v>
+        <v>-5.9</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.6</v>
+        <v>-7.2</v>
       </c>
       <c r="H8" t="n">
-        <v>23.9</v>
+        <v>24.6</v>
       </c>
       <c r="I8" t="s">
         <v>21</v>
@@ -853,12 +832,8 @@
       <c r="J8" t="s">
         <v>18</v>
       </c>
-      <c r="K8" t="n">
-        <v>-11.5</v>
-      </c>
-      <c r="L8" t="n">
-        <v>51</v>
-      </c>
+      <c r="K8"/>
+      <c r="L8"/>
       <c r="M8" t="s">
         <v>25</v>
       </c>
@@ -880,16 +855,16 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.3</v>
+        <v>-5.9</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.3</v>
+        <v>-5.9</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.6</v>
+        <v>-7.2</v>
       </c>
       <c r="H9" t="n">
-        <v>23.9</v>
+        <v>24.6</v>
       </c>
       <c r="I9" t="s">
         <v>21</v>
@@ -897,12 +872,8 @@
       <c r="J9" t="s">
         <v>20</v>
       </c>
-      <c r="K9" t="n">
-        <v>-11.5</v>
-      </c>
-      <c r="L9" t="n">
-        <v>51</v>
-      </c>
+      <c r="K9"/>
+      <c r="L9"/>
       <c r="M9" t="s">
         <v>25</v>
       </c>
@@ -912,7 +883,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B10" t="s">
         <v>26</v>
@@ -924,16 +895,16 @@
         <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>-11.3</v>
+        <v>-1.6</v>
       </c>
       <c r="F10" t="n">
-        <v>-11.3</v>
+        <v>-1.6</v>
       </c>
       <c r="G10" t="n">
-        <v>-12.2</v>
+        <v>0.3</v>
       </c>
       <c r="H10" t="n">
-        <v>49.1</v>
+        <v>44.7</v>
       </c>
       <c r="I10" t="s">
         <v>17</v>
@@ -942,10 +913,10 @@
         <v>18</v>
       </c>
       <c r="K10" t="n">
-        <v>-14</v>
+        <v>-8.5</v>
       </c>
       <c r="L10" t="n">
-        <v>51</v>
+        <v>50.5</v>
       </c>
       <c r="M10" t="s">
         <v>29</v>
@@ -956,7 +927,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B11" t="s">
         <v>26</v>
@@ -968,16 +939,16 @@
         <v>28</v>
       </c>
       <c r="E11" t="n">
-        <v>-11.3</v>
+        <v>-1.6</v>
       </c>
       <c r="F11" t="n">
-        <v>-11.3</v>
+        <v>-1.6</v>
       </c>
       <c r="G11" t="n">
-        <v>-12.2</v>
+        <v>0.3</v>
       </c>
       <c r="H11" t="n">
-        <v>49.1</v>
+        <v>44.7</v>
       </c>
       <c r="I11" t="s">
         <v>17</v>
@@ -986,10 +957,10 @@
         <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>-14</v>
+        <v>-8.5</v>
       </c>
       <c r="L11" t="n">
-        <v>51</v>
+        <v>50.5</v>
       </c>
       <c r="M11" t="s">
         <v>29</v>
@@ -1000,7 +971,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B12" t="s">
         <v>26</v>
@@ -1012,16 +983,16 @@
         <v>28</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.7</v>
+        <v>-0.8</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.7</v>
+        <v>-0.8</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.1</v>
+        <v>0.2</v>
       </c>
       <c r="H12" t="n">
-        <v>24.6</v>
+        <v>22.3</v>
       </c>
       <c r="I12" t="s">
         <v>21</v>
@@ -1030,10 +1001,10 @@
         <v>18</v>
       </c>
       <c r="K12" t="n">
-        <v>-14</v>
+        <v>-8.5</v>
       </c>
       <c r="L12" t="n">
-        <v>51</v>
+        <v>50.5</v>
       </c>
       <c r="M12" t="s">
         <v>29</v>
@@ -1044,7 +1015,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B13" t="s">
         <v>26</v>
@@ -1056,16 +1027,16 @@
         <v>28</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.7</v>
+        <v>-0.8</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.7</v>
+        <v>-0.8</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.1</v>
+        <v>0.2</v>
       </c>
       <c r="H13" t="n">
-        <v>24.6</v>
+        <v>22.3</v>
       </c>
       <c r="I13" t="s">
         <v>21</v>
@@ -1074,10 +1045,10 @@
         <v>20</v>
       </c>
       <c r="K13" t="n">
-        <v>-14</v>
+        <v>-8.5</v>
       </c>
       <c r="L13" t="n">
-        <v>51</v>
+        <v>50.5</v>
       </c>
       <c r="M13" t="s">
         <v>29</v>
@@ -1100,16 +1071,16 @@
         <v>32</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.6</v>
+        <v>3.1</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.6</v>
+        <v>3.1</v>
       </c>
       <c r="G14" t="n">
-        <v>-4</v>
+        <v>0.8</v>
       </c>
       <c r="H14" t="n">
-        <v>44.7</v>
+        <v>44.8</v>
       </c>
       <c r="I14" t="s">
         <v>17</v>
@@ -1118,16 +1089,16 @@
         <v>18</v>
       </c>
       <c r="K14" t="n">
-        <v>-7</v>
+        <v>4</v>
       </c>
       <c r="L14" t="n">
-        <v>50.5</v>
+        <v>46</v>
       </c>
       <c r="M14" t="s">
         <v>33</v>
       </c>
       <c r="N14" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1144,16 +1115,16 @@
         <v>32</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.6</v>
+        <v>3.1</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6</v>
+        <v>3.1</v>
       </c>
       <c r="G15" t="n">
-        <v>-4</v>
+        <v>0.8</v>
       </c>
       <c r="H15" t="n">
-        <v>43.7</v>
+        <v>44.8</v>
       </c>
       <c r="I15" t="s">
         <v>17</v>
@@ -1162,16 +1133,16 @@
         <v>20</v>
       </c>
       <c r="K15" t="n">
-        <v>-7</v>
+        <v>4</v>
       </c>
       <c r="L15" t="n">
-        <v>50.5</v>
+        <v>46</v>
       </c>
       <c r="M15" t="s">
         <v>33</v>
       </c>
       <c r="N15" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1188,16 +1159,16 @@
         <v>32</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8</v>
+        <v>1.5</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8</v>
+        <v>1.5</v>
       </c>
       <c r="G16" t="n">
-        <v>-2</v>
+        <v>0.4</v>
       </c>
       <c r="H16" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="I16" t="s">
         <v>21</v>
@@ -1206,16 +1177,16 @@
         <v>18</v>
       </c>
       <c r="K16" t="n">
-        <v>-7</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
-        <v>50.5</v>
+        <v>46</v>
       </c>
       <c r="M16" t="s">
         <v>33</v>
       </c>
       <c r="N16" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1232,16 +1203,16 @@
         <v>32</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8</v>
+        <v>1.5</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8</v>
+        <v>1.5</v>
       </c>
       <c r="G17" t="n">
-        <v>-2</v>
+        <v>0.4</v>
       </c>
       <c r="H17" t="n">
-        <v>21.8</v>
+        <v>22.4</v>
       </c>
       <c r="I17" t="s">
         <v>21</v>
@@ -1250,16 +1221,16 @@
         <v>20</v>
       </c>
       <c r="K17" t="n">
-        <v>-7</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
-        <v>50.5</v>
+        <v>46</v>
       </c>
       <c r="M17" t="s">
         <v>33</v>
       </c>
       <c r="N17" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1276,16 +1247,16 @@
         <v>36</v>
       </c>
       <c r="E18" t="n">
-        <v>3.1</v>
+        <v>6.7</v>
       </c>
       <c r="F18" t="n">
-        <v>3.1</v>
+        <v>6.7</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="H18" t="n">
-        <v>44.8</v>
+        <v>40.1</v>
       </c>
       <c r="I18" t="s">
         <v>17</v>
@@ -1294,16 +1265,16 @@
         <v>18</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L18" t="n">
-        <v>45.5</v>
+        <v>43</v>
       </c>
       <c r="M18" t="s">
         <v>37</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1320,16 +1291,16 @@
         <v>36</v>
       </c>
       <c r="E19" t="n">
-        <v>3.1</v>
+        <v>6.7</v>
       </c>
       <c r="F19" t="n">
-        <v>3.1</v>
+        <v>6.7</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="H19" t="n">
-        <v>44.8</v>
+        <v>40.1</v>
       </c>
       <c r="I19" t="s">
         <v>17</v>
@@ -1338,16 +1309,16 @@
         <v>20</v>
       </c>
       <c r="K19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L19" t="n">
-        <v>45.5</v>
+        <v>43</v>
       </c>
       <c r="M19" t="s">
         <v>37</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1364,16 +1335,16 @@
         <v>36</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="H20" t="n">
-        <v>22.4</v>
+        <v>20.1</v>
       </c>
       <c r="I20" t="s">
         <v>21</v>
@@ -1382,16 +1353,16 @@
         <v>18</v>
       </c>
       <c r="K20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L20" t="n">
-        <v>45.5</v>
+        <v>43</v>
       </c>
       <c r="M20" t="s">
         <v>37</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1408,16 +1379,16 @@
         <v>36</v>
       </c>
       <c r="E21" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="H21" t="n">
-        <v>22.4</v>
+        <v>20.1</v>
       </c>
       <c r="I21" t="s">
         <v>21</v>
@@ -1426,21 +1397,21 @@
         <v>20</v>
       </c>
       <c r="K21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L21" t="n">
-        <v>45.5</v>
+        <v>43</v>
       </c>
       <c r="M21" t="s">
         <v>37</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B22" t="s">
         <v>38</v>
@@ -1452,16 +1423,16 @@
         <v>40</v>
       </c>
       <c r="E22" t="n">
-        <v>5.7</v>
+        <v>10.1</v>
       </c>
       <c r="F22" t="n">
-        <v>5.7</v>
+        <v>10.1</v>
       </c>
       <c r="G22" t="n">
-        <v>2.2</v>
+        <v>12.1</v>
       </c>
       <c r="H22" t="n">
-        <v>40.1</v>
+        <v>47</v>
       </c>
       <c r="I22" t="s">
         <v>17</v>
@@ -1470,21 +1441,21 @@
         <v>18</v>
       </c>
       <c r="K22" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="L22" t="n">
-        <v>43.5</v>
+        <v>50</v>
       </c>
       <c r="M22" t="s">
         <v>41</v>
       </c>
       <c r="N22" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B23" t="s">
         <v>38</v>
@@ -1496,16 +1467,16 @@
         <v>40</v>
       </c>
       <c r="E23" t="n">
-        <v>5.7</v>
+        <v>10.1</v>
       </c>
       <c r="F23" t="n">
-        <v>5.7</v>
+        <v>10.1</v>
       </c>
       <c r="G23" t="n">
-        <v>2.2</v>
+        <v>12.1</v>
       </c>
       <c r="H23" t="n">
-        <v>39.6</v>
+        <v>46.7</v>
       </c>
       <c r="I23" t="s">
         <v>17</v>
@@ -1514,21 +1485,21 @@
         <v>20</v>
       </c>
       <c r="K23" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="L23" t="n">
-        <v>43.5</v>
+        <v>50</v>
       </c>
       <c r="M23" t="s">
         <v>41</v>
       </c>
       <c r="N23" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B24" t="s">
         <v>38</v>
@@ -1540,16 +1511,16 @@
         <v>40</v>
       </c>
       <c r="E24" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="F24" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="G24" t="n">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="H24" t="n">
-        <v>20.1</v>
+        <v>23.5</v>
       </c>
       <c r="I24" t="s">
         <v>21</v>
@@ -1558,21 +1529,21 @@
         <v>18</v>
       </c>
       <c r="K24" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="L24" t="n">
-        <v>43.5</v>
+        <v>50</v>
       </c>
       <c r="M24" t="s">
         <v>41</v>
       </c>
       <c r="N24" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B25" t="s">
         <v>38</v>
@@ -1584,16 +1555,16 @@
         <v>40</v>
       </c>
       <c r="E25" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="F25" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="G25" t="n">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="H25" t="n">
-        <v>19.8</v>
+        <v>23.3</v>
       </c>
       <c r="I25" t="s">
         <v>21</v>
@@ -1602,16 +1573,16 @@
         <v>20</v>
       </c>
       <c r="K25" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="L25" t="n">
-        <v>43.5</v>
+        <v>50</v>
       </c>
       <c r="M25" t="s">
         <v>41</v>
       </c>
       <c r="N25" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1628,16 +1599,16 @@
         <v>44</v>
       </c>
       <c r="E26" t="n">
-        <v>10.1</v>
+        <v>-20.5</v>
       </c>
       <c r="F26" t="n">
-        <v>10.1</v>
+        <v>-20.5</v>
       </c>
       <c r="G26" t="n">
-        <v>12.1</v>
+        <v>-22.7</v>
       </c>
       <c r="H26" t="n">
-        <v>47</v>
+        <v>45.1</v>
       </c>
       <c r="I26" t="s">
         <v>17</v>
@@ -1646,16 +1617,16 @@
         <v>18</v>
       </c>
       <c r="K26" t="n">
-        <v>6.5</v>
+        <v>-23.5</v>
       </c>
       <c r="L26" t="n">
-        <v>49.5</v>
+        <v>52.5</v>
       </c>
       <c r="M26" t="s">
         <v>45</v>
       </c>
       <c r="N26" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="27">
@@ -1672,16 +1643,16 @@
         <v>44</v>
       </c>
       <c r="E27" t="n">
-        <v>10.1</v>
+        <v>-20.5</v>
       </c>
       <c r="F27" t="n">
-        <v>10.1</v>
+        <v>-20.5</v>
       </c>
       <c r="G27" t="n">
-        <v>12.1</v>
+        <v>-22.7</v>
       </c>
       <c r="H27" t="n">
-        <v>46.1</v>
+        <v>44.7</v>
       </c>
       <c r="I27" t="s">
         <v>17</v>
@@ -1690,16 +1661,16 @@
         <v>20</v>
       </c>
       <c r="K27" t="n">
-        <v>6.5</v>
+        <v>-23.5</v>
       </c>
       <c r="L27" t="n">
-        <v>49.5</v>
+        <v>52.5</v>
       </c>
       <c r="M27" t="s">
         <v>45</v>
       </c>
       <c r="N27" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="28">
@@ -1716,16 +1687,16 @@
         <v>44</v>
       </c>
       <c r="E28" t="n">
-        <v>5</v>
+        <v>-10.2</v>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>-10.2</v>
       </c>
       <c r="G28" t="n">
-        <v>6</v>
+        <v>-11.4</v>
       </c>
       <c r="H28" t="n">
-        <v>23.5</v>
+        <v>22.6</v>
       </c>
       <c r="I28" t="s">
         <v>21</v>
@@ -1734,16 +1705,16 @@
         <v>18</v>
       </c>
       <c r="K28" t="n">
-        <v>6.5</v>
+        <v>-23.5</v>
       </c>
       <c r="L28" t="n">
-        <v>49.5</v>
+        <v>52.5</v>
       </c>
       <c r="M28" t="s">
         <v>45</v>
       </c>
       <c r="N28" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="29">
@@ -1760,16 +1731,16 @@
         <v>44</v>
       </c>
       <c r="E29" t="n">
-        <v>5</v>
+        <v>-10.2</v>
       </c>
       <c r="F29" t="n">
-        <v>5</v>
+        <v>-10.2</v>
       </c>
       <c r="G29" t="n">
-        <v>6</v>
+        <v>-11.4</v>
       </c>
       <c r="H29" t="n">
-        <v>23</v>
+        <v>22.3</v>
       </c>
       <c r="I29" t="s">
         <v>21</v>
@@ -1778,42 +1749,42 @@
         <v>20</v>
       </c>
       <c r="K29" t="n">
-        <v>6.5</v>
+        <v>-23.5</v>
       </c>
       <c r="L29" t="n">
-        <v>49.5</v>
+        <v>52.5</v>
       </c>
       <c r="M29" t="s">
         <v>45</v>
       </c>
       <c r="N29" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46257</v>
+        <v>46261</v>
       </c>
       <c r="B30" t="s">
         <v>46</v>
       </c>
       <c r="C30" t="s">
+        <v>16</v>
+      </c>
+      <c r="D30" t="s">
         <v>47</v>
       </c>
-      <c r="D30" t="s">
-        <v>48</v>
-      </c>
       <c r="E30" t="n">
-        <v>-20.5</v>
+        <v>4.9</v>
       </c>
       <c r="F30" t="n">
-        <v>-20.5</v>
+        <v>4.9</v>
       </c>
       <c r="G30" t="n">
-        <v>-22.7</v>
+        <v>-1.6</v>
       </c>
       <c r="H30" t="n">
-        <v>45.1</v>
+        <v>46.3</v>
       </c>
       <c r="I30" t="s">
         <v>17</v>
@@ -1822,42 +1793,42 @@
         <v>18</v>
       </c>
       <c r="K30" t="n">
-        <v>-24.5</v>
+        <v>-1.5</v>
       </c>
       <c r="L30" t="n">
-        <v>52</v>
+        <v>47.5</v>
       </c>
       <c r="M30" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="N30" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46257</v>
+        <v>46261</v>
       </c>
       <c r="B31" t="s">
         <v>46</v>
       </c>
       <c r="C31" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31" t="s">
         <v>47</v>
       </c>
-      <c r="D31" t="s">
-        <v>48</v>
-      </c>
       <c r="E31" t="n">
-        <v>-20.5</v>
+        <v>4.9</v>
       </c>
       <c r="F31" t="n">
-        <v>-20.5</v>
+        <v>4.9</v>
       </c>
       <c r="G31" t="n">
-        <v>-22.7</v>
+        <v>-1.6</v>
       </c>
       <c r="H31" t="n">
-        <v>44.8</v>
+        <v>46.3</v>
       </c>
       <c r="I31" t="s">
         <v>17</v>
@@ -1866,42 +1837,42 @@
         <v>20</v>
       </c>
       <c r="K31" t="n">
-        <v>-24.5</v>
+        <v>-1.5</v>
       </c>
       <c r="L31" t="n">
-        <v>52</v>
+        <v>47.5</v>
       </c>
       <c r="M31" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="N31" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46257</v>
+        <v>46261</v>
       </c>
       <c r="B32" t="s">
         <v>46</v>
       </c>
       <c r="C32" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32" t="s">
         <v>47</v>
       </c>
-      <c r="D32" t="s">
-        <v>48</v>
-      </c>
       <c r="E32" t="n">
-        <v>-10.2</v>
+        <v>2.5</v>
       </c>
       <c r="F32" t="n">
-        <v>-10.2</v>
+        <v>2.5</v>
       </c>
       <c r="G32" t="n">
-        <v>-11.4</v>
+        <v>-0.8</v>
       </c>
       <c r="H32" t="n">
-        <v>22.6</v>
+        <v>23.1</v>
       </c>
       <c r="I32" t="s">
         <v>21</v>
@@ -1910,42 +1881,42 @@
         <v>18</v>
       </c>
       <c r="K32" t="n">
-        <v>-24.5</v>
+        <v>-1.5</v>
       </c>
       <c r="L32" t="n">
-        <v>52</v>
+        <v>47.5</v>
       </c>
       <c r="M32" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="N32" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46257</v>
+        <v>46261</v>
       </c>
       <c r="B33" t="s">
         <v>46</v>
       </c>
       <c r="C33" t="s">
+        <v>16</v>
+      </c>
+      <c r="D33" t="s">
         <v>47</v>
       </c>
-      <c r="D33" t="s">
-        <v>48</v>
-      </c>
       <c r="E33" t="n">
-        <v>-10.2</v>
+        <v>2.5</v>
       </c>
       <c r="F33" t="n">
-        <v>-10.2</v>
+        <v>2.5</v>
       </c>
       <c r="G33" t="n">
-        <v>-11.4</v>
+        <v>-0.8</v>
       </c>
       <c r="H33" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="I33" t="s">
         <v>21</v>
@@ -1954,16 +1925,368 @@
         <v>20</v>
       </c>
       <c r="K33" t="n">
-        <v>-24.5</v>
+        <v>-1.5</v>
       </c>
       <c r="L33" t="n">
-        <v>52</v>
+        <v>47.5</v>
       </c>
       <c r="M33" t="s">
+        <v>25</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B34" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" t="s">
+        <v>28</v>
+      </c>
+      <c r="D34" t="s">
+        <v>35</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H34" t="n">
+        <v>43</v>
+      </c>
+      <c r="I34" t="s">
+        <v>17</v>
+      </c>
+      <c r="J34" t="s">
+        <v>18</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="L34" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="M34" t="s">
+        <v>48</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B35" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" t="s">
+        <v>28</v>
+      </c>
+      <c r="D35" t="s">
+        <v>35</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H35" t="n">
+        <v>43</v>
+      </c>
+      <c r="I35" t="s">
+        <v>17</v>
+      </c>
+      <c r="J35" t="s">
+        <v>20</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="L35" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="M35" t="s">
+        <v>48</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B36" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" t="s">
+        <v>28</v>
+      </c>
+      <c r="D36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="H36" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="I36" t="s">
+        <v>21</v>
+      </c>
+      <c r="J36" t="s">
+        <v>18</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="L36" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="M36" t="s">
+        <v>48</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B37" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" t="s">
+        <v>28</v>
+      </c>
+      <c r="D37" t="s">
+        <v>35</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="H37" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="I37" t="s">
+        <v>21</v>
+      </c>
+      <c r="J37" t="s">
+        <v>20</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="L37" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="M37" t="s">
+        <v>48</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B38" t="s">
+        <v>22</v>
+      </c>
+      <c r="C38" t="s">
         <v>49</v>
       </c>
-      <c r="N33" t="n">
-        <v>0.9</v>
+      <c r="D38" t="s">
+        <v>36</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="H38" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="I38" t="s">
+        <v>17</v>
+      </c>
+      <c r="J38" t="s">
+        <v>18</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="L38" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="M38" t="s">
+        <v>50</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B39" t="s">
+        <v>22</v>
+      </c>
+      <c r="C39" t="s">
+        <v>49</v>
+      </c>
+      <c r="D39" t="s">
+        <v>36</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="H39" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="I39" t="s">
+        <v>17</v>
+      </c>
+      <c r="J39" t="s">
+        <v>20</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="L39" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="M39" t="s">
+        <v>50</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B40" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" t="s">
+        <v>49</v>
+      </c>
+      <c r="D40" t="s">
+        <v>36</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="H40" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="I40" t="s">
+        <v>21</v>
+      </c>
+      <c r="J40" t="s">
+        <v>18</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="L40" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="M40" t="s">
+        <v>50</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B41" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" t="s">
+        <v>49</v>
+      </c>
+      <c r="D41" t="s">
+        <v>36</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="H41" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="I41" t="s">
+        <v>21</v>
+      </c>
+      <c r="J41" t="s">
+        <v>20</v>
+      </c>
+      <c r="K41" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="L41" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="M41" t="s">
+        <v>50</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_upcoming_projections.xlsx
+++ b/files/NRL_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -56,115 +56,112 @@
     <t xml:space="preserve">Forecast Rain mm</t>
   </si>
   <si>
+    <t xml:space="preserve">19:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melbourne storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Rain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suncorp Stadium, Brisbane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1H</t>
+  </si>
+  <si>
     <t xml:space="preserve">18:00</t>
   </si>
   <si>
-    <t xml:space="preserve">canberra raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Rain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GIO Stadium, Canberra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1H</t>
+    <t xml:space="preserve">manly-warringah sea eagles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st george-illawarra dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Pines Park, Sydney</t>
   </si>
   <si>
     <t xml:space="preserve">20:00</t>
   </si>
   <si>
+    <t xml:space="preserve">penrith panthers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlueBet Stadium, Penrith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">south sydney rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cbus Super Stadium, Gold Coast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
     <t xml:space="preserve">dolphins</t>
   </si>
   <si>
+    <t xml:space="preserve">Allianz Stadium, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north queensland cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wests tigers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Queensland Country Bank Stadium, Townsville</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Go Media Stadium, Auckland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:05</t>
+  </si>
+  <si>
     <t xml:space="preserve">parramatta eels</t>
   </si>
   <si>
-    <t xml:space="preserve">Suncorp Stadium, Brisbane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">newcastle knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manly-warringah sea eagles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">McDonald Jones Stadium, Newcastle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">south sydney rabbitohs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accor Stadium, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st george-illawarra dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WIN Stadium, Wollongong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
     <t xml:space="preserve">cronulla-sutherland sharks</t>
   </si>
   <si>
-    <t xml:space="preserve">Cbus Super Stadium, Gold Coast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wests tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allianz Stadium, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">melbourne storm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 Pines Park, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penrith panthers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BlueBet Stadium, Penrith</t>
+    <t xml:space="preserve">CommBank Stadium, Sydney</t>
   </si>
 </sst>
 </file>
@@ -503,7 +500,7 @@
   <cols>
     <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="5.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="27.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="26.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="29.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="27.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
@@ -513,7 +510,7 @@
     <col min="10" max="10" width="16.71" hidden="0" customWidth="1"/>
     <col min="11" max="11" width="11.71" hidden="0" customWidth="1"/>
     <col min="12" max="12" width="12.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="33.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="43.71" hidden="0" customWidth="1"/>
     <col min="14" max="14" width="16.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
@@ -563,7 +560,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46255</v>
+        <v>46261</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -575,16 +572,16 @@
         <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>-8.7</v>
+        <v>4.4</v>
       </c>
       <c r="F2" t="n">
-        <v>-8.7</v>
+        <v>4.4</v>
       </c>
       <c r="G2" t="n">
-        <v>-4.6</v>
+        <v>3.7</v>
       </c>
       <c r="H2" t="n">
-        <v>47.7</v>
+        <v>48.8</v>
       </c>
       <c r="I2" t="s">
         <v>17</v>
@@ -592,18 +589,22 @@
       <c r="J2" t="s">
         <v>18</v>
       </c>
-      <c r="K2"/>
-      <c r="L2"/>
+      <c r="K2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L2" t="n">
+        <v>49.5</v>
+      </c>
       <c r="M2" t="s">
         <v>19</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46255</v>
+        <v>46261</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -615,16 +616,16 @@
         <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>-8.7</v>
+        <v>4.4</v>
       </c>
       <c r="F3" t="n">
-        <v>-8.7</v>
+        <v>4.4</v>
       </c>
       <c r="G3" t="n">
-        <v>-4.6</v>
+        <v>3.7</v>
       </c>
       <c r="H3" t="n">
-        <v>47.3</v>
+        <v>48.5</v>
       </c>
       <c r="I3" t="s">
         <v>17</v>
@@ -632,18 +633,22 @@
       <c r="J3" t="s">
         <v>20</v>
       </c>
-      <c r="K3"/>
-      <c r="L3"/>
+      <c r="K3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>49.5</v>
+      </c>
       <c r="M3" t="s">
         <v>19</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46255</v>
+        <v>46261</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -655,16 +660,16 @@
         <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>-4.3</v>
+        <v>2.2</v>
       </c>
       <c r="F4" t="n">
-        <v>-4.3</v>
+        <v>2.2</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.3</v>
+        <v>1.8</v>
       </c>
       <c r="H4" t="n">
-        <v>23.9</v>
+        <v>24.4</v>
       </c>
       <c r="I4" t="s">
         <v>21</v>
@@ -672,18 +677,22 @@
       <c r="J4" t="s">
         <v>18</v>
       </c>
-      <c r="K4"/>
-      <c r="L4"/>
+      <c r="K4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>49.5</v>
+      </c>
       <c r="M4" t="s">
         <v>19</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46255</v>
+        <v>46261</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -695,16 +704,16 @@
         <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>-4.3</v>
+        <v>2.2</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.3</v>
+        <v>2.2</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.3</v>
+        <v>1.8</v>
       </c>
       <c r="H5" t="n">
-        <v>23.7</v>
+        <v>24.2</v>
       </c>
       <c r="I5" t="s">
         <v>21</v>
@@ -712,18 +721,22 @@
       <c r="J5" t="s">
         <v>20</v>
       </c>
-      <c r="K5"/>
-      <c r="L5"/>
+      <c r="K5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>49.5</v>
+      </c>
       <c r="M5" t="s">
         <v>19</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46255</v>
+        <v>46262</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
@@ -735,16 +748,16 @@
         <v>24</v>
       </c>
       <c r="E6" t="n">
-        <v>-11.8</v>
+        <v>-9.8</v>
       </c>
       <c r="F6" t="n">
-        <v>-11.8</v>
+        <v>-9.8</v>
       </c>
       <c r="G6" t="n">
-        <v>-14.5</v>
+        <v>-2.5</v>
       </c>
       <c r="H6" t="n">
-        <v>49.1</v>
+        <v>47</v>
       </c>
       <c r="I6" t="s">
         <v>17</v>
@@ -752,8 +765,12 @@
       <c r="J6" t="s">
         <v>18</v>
       </c>
-      <c r="K6"/>
-      <c r="L6"/>
+      <c r="K6" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L6" t="n">
+        <v>48.5</v>
+      </c>
       <c r="M6" t="s">
         <v>25</v>
       </c>
@@ -763,7 +780,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46255</v>
+        <v>46262</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
@@ -775,16 +792,16 @@
         <v>24</v>
       </c>
       <c r="E7" t="n">
-        <v>-11.8</v>
+        <v>-9.8</v>
       </c>
       <c r="F7" t="n">
-        <v>-11.8</v>
+        <v>-9.8</v>
       </c>
       <c r="G7" t="n">
-        <v>-14.5</v>
+        <v>-2.5</v>
       </c>
       <c r="H7" t="n">
-        <v>49.1</v>
+        <v>47</v>
       </c>
       <c r="I7" t="s">
         <v>17</v>
@@ -792,8 +809,12 @@
       <c r="J7" t="s">
         <v>20</v>
       </c>
-      <c r="K7"/>
-      <c r="L7"/>
+      <c r="K7" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L7" t="n">
+        <v>48.5</v>
+      </c>
       <c r="M7" t="s">
         <v>25</v>
       </c>
@@ -803,7 +824,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46255</v>
+        <v>46262</v>
       </c>
       <c r="B8" t="s">
         <v>22</v>
@@ -815,16 +836,16 @@
         <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.9</v>
+        <v>-4.9</v>
       </c>
       <c r="F8" t="n">
-        <v>-5.9</v>
+        <v>-4.9</v>
       </c>
       <c r="G8" t="n">
-        <v>-7.2</v>
+        <v>-1.3</v>
       </c>
       <c r="H8" t="n">
-        <v>24.6</v>
+        <v>23.5</v>
       </c>
       <c r="I8" t="s">
         <v>21</v>
@@ -832,8 +853,12 @@
       <c r="J8" t="s">
         <v>18</v>
       </c>
-      <c r="K8"/>
-      <c r="L8"/>
+      <c r="K8" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L8" t="n">
+        <v>48.5</v>
+      </c>
       <c r="M8" t="s">
         <v>25</v>
       </c>
@@ -843,7 +868,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46255</v>
+        <v>46262</v>
       </c>
       <c r="B9" t="s">
         <v>22</v>
@@ -855,16 +880,16 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.9</v>
+        <v>-4.9</v>
       </c>
       <c r="F9" t="n">
-        <v>-5.9</v>
+        <v>-4.9</v>
       </c>
       <c r="G9" t="n">
-        <v>-7.2</v>
+        <v>-1.3</v>
       </c>
       <c r="H9" t="n">
-        <v>24.6</v>
+        <v>23.5</v>
       </c>
       <c r="I9" t="s">
         <v>21</v>
@@ -872,8 +897,12 @@
       <c r="J9" t="s">
         <v>20</v>
       </c>
-      <c r="K9"/>
-      <c r="L9"/>
+      <c r="K9" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L9" t="n">
+        <v>48.5</v>
+      </c>
       <c r="M9" t="s">
         <v>25</v>
       </c>
@@ -883,7 +912,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46256</v>
+        <v>46262</v>
       </c>
       <c r="B10" t="s">
         <v>26</v>
@@ -895,16 +924,16 @@
         <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6</v>
+        <v>-8.1</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6</v>
+        <v>-8.1</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3</v>
+        <v>-8.1</v>
       </c>
       <c r="H10" t="n">
-        <v>44.7</v>
+        <v>39.8</v>
       </c>
       <c r="I10" t="s">
         <v>17</v>
@@ -913,10 +942,10 @@
         <v>18</v>
       </c>
       <c r="K10" t="n">
-        <v>-8.5</v>
+        <v>-9</v>
       </c>
       <c r="L10" t="n">
-        <v>50.5</v>
+        <v>40.5</v>
       </c>
       <c r="M10" t="s">
         <v>29</v>
@@ -927,7 +956,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46256</v>
+        <v>46262</v>
       </c>
       <c r="B11" t="s">
         <v>26</v>
@@ -939,16 +968,16 @@
         <v>28</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6</v>
+        <v>-8.1</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6</v>
+        <v>-8.1</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3</v>
+        <v>-8.1</v>
       </c>
       <c r="H11" t="n">
-        <v>44.7</v>
+        <v>39.8</v>
       </c>
       <c r="I11" t="s">
         <v>17</v>
@@ -957,10 +986,10 @@
         <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>-8.5</v>
+        <v>-9</v>
       </c>
       <c r="L11" t="n">
-        <v>50.5</v>
+        <v>40.5</v>
       </c>
       <c r="M11" t="s">
         <v>29</v>
@@ -971,7 +1000,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46256</v>
+        <v>46262</v>
       </c>
       <c r="B12" t="s">
         <v>26</v>
@@ -983,16 +1012,16 @@
         <v>28</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8</v>
+        <v>-4</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8</v>
+        <v>-4</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2</v>
+        <v>-4.1</v>
       </c>
       <c r="H12" t="n">
-        <v>22.3</v>
+        <v>19.9</v>
       </c>
       <c r="I12" t="s">
         <v>21</v>
@@ -1001,10 +1030,10 @@
         <v>18</v>
       </c>
       <c r="K12" t="n">
-        <v>-8.5</v>
+        <v>-9</v>
       </c>
       <c r="L12" t="n">
-        <v>50.5</v>
+        <v>40.5</v>
       </c>
       <c r="M12" t="s">
         <v>29</v>
@@ -1015,7 +1044,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46256</v>
+        <v>46262</v>
       </c>
       <c r="B13" t="s">
         <v>26</v>
@@ -1027,16 +1056,16 @@
         <v>28</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.8</v>
+        <v>-4</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8</v>
+        <v>-4</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2</v>
+        <v>-4.1</v>
       </c>
       <c r="H13" t="n">
-        <v>22.3</v>
+        <v>19.9</v>
       </c>
       <c r="I13" t="s">
         <v>21</v>
@@ -1045,10 +1074,10 @@
         <v>20</v>
       </c>
       <c r="K13" t="n">
-        <v>-8.5</v>
+        <v>-9</v>
       </c>
       <c r="L13" t="n">
-        <v>50.5</v>
+        <v>40.5</v>
       </c>
       <c r="M13" t="s">
         <v>29</v>
@@ -1059,7 +1088,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46256</v>
+        <v>46263</v>
       </c>
       <c r="B14" t="s">
         <v>30</v>
@@ -1071,16 +1100,16 @@
         <v>32</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1</v>
+        <v>5.6</v>
       </c>
       <c r="F14" t="n">
-        <v>3.1</v>
+        <v>5.6</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8</v>
+        <v>5.3</v>
       </c>
       <c r="H14" t="n">
-        <v>44.8</v>
+        <v>51.7</v>
       </c>
       <c r="I14" t="s">
         <v>17</v>
@@ -1089,21 +1118,21 @@
         <v>18</v>
       </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L14" t="n">
-        <v>46</v>
+        <v>53.5</v>
       </c>
       <c r="M14" t="s">
         <v>33</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46256</v>
+        <v>46263</v>
       </c>
       <c r="B15" t="s">
         <v>30</v>
@@ -1115,16 +1144,16 @@
         <v>32</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1</v>
+        <v>5.6</v>
       </c>
       <c r="F15" t="n">
-        <v>3.1</v>
+        <v>5.6</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8</v>
+        <v>5.3</v>
       </c>
       <c r="H15" t="n">
-        <v>44.8</v>
+        <v>51.3</v>
       </c>
       <c r="I15" t="s">
         <v>17</v>
@@ -1133,21 +1162,21 @@
         <v>20</v>
       </c>
       <c r="K15" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L15" t="n">
-        <v>46</v>
+        <v>53.5</v>
       </c>
       <c r="M15" t="s">
         <v>33</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46256</v>
+        <v>46263</v>
       </c>
       <c r="B16" t="s">
         <v>30</v>
@@ -1159,16 +1188,16 @@
         <v>32</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="H16" t="n">
-        <v>22.4</v>
+        <v>25.9</v>
       </c>
       <c r="I16" t="s">
         <v>21</v>
@@ -1177,21 +1206,21 @@
         <v>18</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L16" t="n">
-        <v>46</v>
+        <v>53.5</v>
       </c>
       <c r="M16" t="s">
         <v>33</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46256</v>
+        <v>46263</v>
       </c>
       <c r="B17" t="s">
         <v>30</v>
@@ -1203,16 +1232,16 @@
         <v>32</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="H17" t="n">
-        <v>22.4</v>
+        <v>25.6</v>
       </c>
       <c r="I17" t="s">
         <v>21</v>
@@ -1221,21 +1250,21 @@
         <v>20</v>
       </c>
       <c r="K17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L17" t="n">
-        <v>46</v>
+        <v>53.5</v>
       </c>
       <c r="M17" t="s">
         <v>33</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46256</v>
+        <v>46263</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
@@ -1247,16 +1276,16 @@
         <v>36</v>
       </c>
       <c r="E18" t="n">
-        <v>6.7</v>
+        <v>-4.4</v>
       </c>
       <c r="F18" t="n">
-        <v>6.7</v>
+        <v>-4.4</v>
       </c>
       <c r="G18" t="n">
-        <v>3.8</v>
+        <v>-6.3</v>
       </c>
       <c r="H18" t="n">
-        <v>40.1</v>
+        <v>50</v>
       </c>
       <c r="I18" t="s">
         <v>17</v>
@@ -1265,10 +1294,10 @@
         <v>18</v>
       </c>
       <c r="K18" t="n">
-        <v>6</v>
+        <v>-5.5</v>
       </c>
       <c r="L18" t="n">
-        <v>43</v>
+        <v>47.5</v>
       </c>
       <c r="M18" t="s">
         <v>37</v>
@@ -1279,7 +1308,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46256</v>
+        <v>46263</v>
       </c>
       <c r="B19" t="s">
         <v>34</v>
@@ -1291,16 +1320,16 @@
         <v>36</v>
       </c>
       <c r="E19" t="n">
-        <v>6.7</v>
+        <v>-4.4</v>
       </c>
       <c r="F19" t="n">
-        <v>6.7</v>
+        <v>-4.4</v>
       </c>
       <c r="G19" t="n">
-        <v>3.8</v>
+        <v>-6.3</v>
       </c>
       <c r="H19" t="n">
-        <v>40.1</v>
+        <v>50</v>
       </c>
       <c r="I19" t="s">
         <v>17</v>
@@ -1309,10 +1338,10 @@
         <v>20</v>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>-5.5</v>
       </c>
       <c r="L19" t="n">
-        <v>43</v>
+        <v>47.5</v>
       </c>
       <c r="M19" t="s">
         <v>37</v>
@@ -1323,7 +1352,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46256</v>
+        <v>46263</v>
       </c>
       <c r="B20" t="s">
         <v>34</v>
@@ -1335,16 +1364,16 @@
         <v>36</v>
       </c>
       <c r="E20" t="n">
-        <v>3.4</v>
+        <v>-2.2</v>
       </c>
       <c r="F20" t="n">
-        <v>3.4</v>
+        <v>-2.2</v>
       </c>
       <c r="G20" t="n">
-        <v>1.9</v>
+        <v>-3.1</v>
       </c>
       <c r="H20" t="n">
-        <v>20.1</v>
+        <v>25</v>
       </c>
       <c r="I20" t="s">
         <v>21</v>
@@ -1353,10 +1382,10 @@
         <v>18</v>
       </c>
       <c r="K20" t="n">
-        <v>6</v>
+        <v>-5.5</v>
       </c>
       <c r="L20" t="n">
-        <v>43</v>
+        <v>47.5</v>
       </c>
       <c r="M20" t="s">
         <v>37</v>
@@ -1367,7 +1396,7 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46256</v>
+        <v>46263</v>
       </c>
       <c r="B21" t="s">
         <v>34</v>
@@ -1379,16 +1408,16 @@
         <v>36</v>
       </c>
       <c r="E21" t="n">
-        <v>3.4</v>
+        <v>-2.2</v>
       </c>
       <c r="F21" t="n">
-        <v>3.4</v>
+        <v>-2.2</v>
       </c>
       <c r="G21" t="n">
-        <v>1.9</v>
+        <v>-3.1</v>
       </c>
       <c r="H21" t="n">
-        <v>20.1</v>
+        <v>25</v>
       </c>
       <c r="I21" t="s">
         <v>21</v>
@@ -1397,10 +1426,10 @@
         <v>20</v>
       </c>
       <c r="K21" t="n">
-        <v>6</v>
+        <v>-5.5</v>
       </c>
       <c r="L21" t="n">
-        <v>43</v>
+        <v>47.5</v>
       </c>
       <c r="M21" t="s">
         <v>37</v>
@@ -1411,7 +1440,7 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46257</v>
+        <v>46263</v>
       </c>
       <c r="B22" t="s">
         <v>38</v>
@@ -1423,16 +1452,16 @@
         <v>40</v>
       </c>
       <c r="E22" t="n">
-        <v>10.1</v>
+        <v>-10.7</v>
       </c>
       <c r="F22" t="n">
-        <v>10.1</v>
+        <v>-10.7</v>
       </c>
       <c r="G22" t="n">
-        <v>12.1</v>
+        <v>-9.5</v>
       </c>
       <c r="H22" t="n">
-        <v>47</v>
+        <v>50.3</v>
       </c>
       <c r="I22" t="s">
         <v>17</v>
@@ -1441,21 +1470,21 @@
         <v>18</v>
       </c>
       <c r="K22" t="n">
-        <v>7.5</v>
+        <v>-13</v>
       </c>
       <c r="L22" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M22" t="s">
         <v>41</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46257</v>
+        <v>46263</v>
       </c>
       <c r="B23" t="s">
         <v>38</v>
@@ -1467,16 +1496,16 @@
         <v>40</v>
       </c>
       <c r="E23" t="n">
-        <v>10.1</v>
+        <v>-10.7</v>
       </c>
       <c r="F23" t="n">
-        <v>10.1</v>
+        <v>-10.7</v>
       </c>
       <c r="G23" t="n">
-        <v>12.1</v>
+        <v>-9.5</v>
       </c>
       <c r="H23" t="n">
-        <v>46.7</v>
+        <v>50.3</v>
       </c>
       <c r="I23" t="s">
         <v>17</v>
@@ -1485,21 +1514,21 @@
         <v>20</v>
       </c>
       <c r="K23" t="n">
-        <v>7.5</v>
+        <v>-13</v>
       </c>
       <c r="L23" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M23" t="s">
         <v>41</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46257</v>
+        <v>46263</v>
       </c>
       <c r="B24" t="s">
         <v>38</v>
@@ -1511,16 +1540,16 @@
         <v>40</v>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>-5.4</v>
       </c>
       <c r="F24" t="n">
-        <v>5</v>
+        <v>-5.4</v>
       </c>
       <c r="G24" t="n">
-        <v>6</v>
+        <v>-4.8</v>
       </c>
       <c r="H24" t="n">
-        <v>23.5</v>
+        <v>25.2</v>
       </c>
       <c r="I24" t="s">
         <v>21</v>
@@ -1529,21 +1558,21 @@
         <v>18</v>
       </c>
       <c r="K24" t="n">
-        <v>7.5</v>
+        <v>-13</v>
       </c>
       <c r="L24" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M24" t="s">
         <v>41</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46257</v>
+        <v>46263</v>
       </c>
       <c r="B25" t="s">
         <v>38</v>
@@ -1555,16 +1584,16 @@
         <v>40</v>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>-5.4</v>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>-5.4</v>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>-4.8</v>
       </c>
       <c r="H25" t="n">
-        <v>23.3</v>
+        <v>25.2</v>
       </c>
       <c r="I25" t="s">
         <v>21</v>
@@ -1573,21 +1602,21 @@
         <v>20</v>
       </c>
       <c r="K25" t="n">
-        <v>7.5</v>
+        <v>-13</v>
       </c>
       <c r="L25" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M25" t="s">
         <v>41</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46257</v>
+        <v>46264</v>
       </c>
       <c r="B26" t="s">
         <v>42</v>
@@ -1599,16 +1628,16 @@
         <v>44</v>
       </c>
       <c r="E26" t="n">
-        <v>-20.5</v>
+        <v>-8.7</v>
       </c>
       <c r="F26" t="n">
-        <v>-20.5</v>
+        <v>-8.7</v>
       </c>
       <c r="G26" t="n">
-        <v>-22.7</v>
+        <v>-12.4</v>
       </c>
       <c r="H26" t="n">
-        <v>45.1</v>
+        <v>47.9</v>
       </c>
       <c r="I26" t="s">
         <v>17</v>
@@ -1617,21 +1646,21 @@
         <v>18</v>
       </c>
       <c r="K26" t="n">
-        <v>-23.5</v>
+        <v>-11.5</v>
       </c>
       <c r="L26" t="n">
-        <v>52.5</v>
+        <v>48.5</v>
       </c>
       <c r="M26" t="s">
         <v>45</v>
       </c>
       <c r="N26" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46257</v>
+        <v>46264</v>
       </c>
       <c r="B27" t="s">
         <v>42</v>
@@ -1643,16 +1672,16 @@
         <v>44</v>
       </c>
       <c r="E27" t="n">
-        <v>-20.5</v>
+        <v>-8.7</v>
       </c>
       <c r="F27" t="n">
-        <v>-20.5</v>
+        <v>-8.7</v>
       </c>
       <c r="G27" t="n">
-        <v>-22.7</v>
+        <v>-12.4</v>
       </c>
       <c r="H27" t="n">
-        <v>44.7</v>
+        <v>47.5</v>
       </c>
       <c r="I27" t="s">
         <v>17</v>
@@ -1661,21 +1690,21 @@
         <v>20</v>
       </c>
       <c r="K27" t="n">
-        <v>-23.5</v>
+        <v>-11.5</v>
       </c>
       <c r="L27" t="n">
-        <v>52.5</v>
+        <v>48.5</v>
       </c>
       <c r="M27" t="s">
         <v>45</v>
       </c>
       <c r="N27" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46257</v>
+        <v>46264</v>
       </c>
       <c r="B28" t="s">
         <v>42</v>
@@ -1687,16 +1716,16 @@
         <v>44</v>
       </c>
       <c r="E28" t="n">
-        <v>-10.2</v>
+        <v>-4.3</v>
       </c>
       <c r="F28" t="n">
-        <v>-10.2</v>
+        <v>-4.3</v>
       </c>
       <c r="G28" t="n">
-        <v>-11.4</v>
+        <v>-6.2</v>
       </c>
       <c r="H28" t="n">
-        <v>22.6</v>
+        <v>24</v>
       </c>
       <c r="I28" t="s">
         <v>21</v>
@@ -1705,21 +1734,21 @@
         <v>18</v>
       </c>
       <c r="K28" t="n">
-        <v>-23.5</v>
+        <v>-11.5</v>
       </c>
       <c r="L28" t="n">
-        <v>52.5</v>
+        <v>48.5</v>
       </c>
       <c r="M28" t="s">
         <v>45</v>
       </c>
       <c r="N28" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46257</v>
+        <v>46264</v>
       </c>
       <c r="B29" t="s">
         <v>42</v>
@@ -1731,16 +1760,16 @@
         <v>44</v>
       </c>
       <c r="E29" t="n">
-        <v>-10.2</v>
+        <v>-4.3</v>
       </c>
       <c r="F29" t="n">
-        <v>-10.2</v>
+        <v>-4.3</v>
       </c>
       <c r="G29" t="n">
-        <v>-11.4</v>
+        <v>-6.2</v>
       </c>
       <c r="H29" t="n">
-        <v>22.3</v>
+        <v>23.8</v>
       </c>
       <c r="I29" t="s">
         <v>21</v>
@@ -1749,42 +1778,42 @@
         <v>20</v>
       </c>
       <c r="K29" t="n">
-        <v>-23.5</v>
+        <v>-11.5</v>
       </c>
       <c r="L29" t="n">
-        <v>52.5</v>
+        <v>48.5</v>
       </c>
       <c r="M29" t="s">
         <v>45</v>
       </c>
       <c r="N29" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46261</v>
+        <v>46264</v>
       </c>
       <c r="B30" t="s">
         <v>46</v>
       </c>
       <c r="C30" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="D30" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E30" t="n">
-        <v>4.9</v>
+        <v>10.7</v>
       </c>
       <c r="F30" t="n">
-        <v>4.9</v>
+        <v>10.7</v>
       </c>
       <c r="G30" t="n">
-        <v>-1.6</v>
+        <v>11.9</v>
       </c>
       <c r="H30" t="n">
-        <v>46.3</v>
+        <v>48.6</v>
       </c>
       <c r="I30" t="s">
         <v>17</v>
@@ -1793,13 +1822,13 @@
         <v>18</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.5</v>
+        <v>6</v>
       </c>
       <c r="L30" t="n">
-        <v>47.5</v>
+        <v>52.5</v>
       </c>
       <c r="M30" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -1807,28 +1836,28 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46261</v>
+        <v>46264</v>
       </c>
       <c r="B31" t="s">
         <v>46</v>
       </c>
       <c r="C31" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="D31" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E31" t="n">
-        <v>4.9</v>
+        <v>10.7</v>
       </c>
       <c r="F31" t="n">
-        <v>4.9</v>
+        <v>10.7</v>
       </c>
       <c r="G31" t="n">
-        <v>-1.6</v>
+        <v>11.9</v>
       </c>
       <c r="H31" t="n">
-        <v>46.3</v>
+        <v>48.6</v>
       </c>
       <c r="I31" t="s">
         <v>17</v>
@@ -1837,13 +1866,13 @@
         <v>20</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.5</v>
+        <v>6</v>
       </c>
       <c r="L31" t="n">
-        <v>47.5</v>
+        <v>52.5</v>
       </c>
       <c r="M31" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -1851,28 +1880,28 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46261</v>
+        <v>46264</v>
       </c>
       <c r="B32" t="s">
         <v>46</v>
       </c>
       <c r="C32" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="D32" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E32" t="n">
-        <v>2.5</v>
+        <v>5.4</v>
       </c>
       <c r="F32" t="n">
-        <v>2.5</v>
+        <v>5.4</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.8</v>
+        <v>5.9</v>
       </c>
       <c r="H32" t="n">
-        <v>23.1</v>
+        <v>24.3</v>
       </c>
       <c r="I32" t="s">
         <v>21</v>
@@ -1881,13 +1910,13 @@
         <v>18</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.5</v>
+        <v>6</v>
       </c>
       <c r="L32" t="n">
-        <v>47.5</v>
+        <v>52.5</v>
       </c>
       <c r="M32" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -1895,28 +1924,28 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46261</v>
+        <v>46264</v>
       </c>
       <c r="B33" t="s">
         <v>46</v>
       </c>
       <c r="C33" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="D33" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E33" t="n">
-        <v>2.5</v>
+        <v>5.4</v>
       </c>
       <c r="F33" t="n">
-        <v>2.5</v>
+        <v>5.4</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.8</v>
+        <v>5.9</v>
       </c>
       <c r="H33" t="n">
-        <v>23.1</v>
+        <v>24.3</v>
       </c>
       <c r="I33" t="s">
         <v>21</v>
@@ -1925,367 +1954,15 @@
         <v>20</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.5</v>
+        <v>6</v>
       </c>
       <c r="L33" t="n">
-        <v>47.5</v>
+        <v>52.5</v>
       </c>
       <c r="M33" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>46262</v>
-      </c>
-      <c r="B34" t="s">
-        <v>14</v>
-      </c>
-      <c r="C34" t="s">
-        <v>28</v>
-      </c>
-      <c r="D34" t="s">
-        <v>35</v>
-      </c>
-      <c r="E34" t="n">
-        <v>-10.4</v>
-      </c>
-      <c r="F34" t="n">
-        <v>-10.4</v>
-      </c>
-      <c r="G34" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="H34" t="n">
-        <v>43</v>
-      </c>
-      <c r="I34" t="s">
-        <v>17</v>
-      </c>
-      <c r="J34" t="s">
-        <v>18</v>
-      </c>
-      <c r="K34" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="L34" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="M34" t="s">
-        <v>48</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>46262</v>
-      </c>
-      <c r="B35" t="s">
-        <v>14</v>
-      </c>
-      <c r="C35" t="s">
-        <v>28</v>
-      </c>
-      <c r="D35" t="s">
-        <v>35</v>
-      </c>
-      <c r="E35" t="n">
-        <v>-10.4</v>
-      </c>
-      <c r="F35" t="n">
-        <v>-10.4</v>
-      </c>
-      <c r="G35" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="H35" t="n">
-        <v>43</v>
-      </c>
-      <c r="I35" t="s">
-        <v>17</v>
-      </c>
-      <c r="J35" t="s">
-        <v>20</v>
-      </c>
-      <c r="K35" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="L35" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="M35" t="s">
-        <v>48</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>46262</v>
-      </c>
-      <c r="B36" t="s">
-        <v>14</v>
-      </c>
-      <c r="C36" t="s">
-        <v>28</v>
-      </c>
-      <c r="D36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E36" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="F36" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="G36" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="H36" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="I36" t="s">
-        <v>21</v>
-      </c>
-      <c r="J36" t="s">
-        <v>18</v>
-      </c>
-      <c r="K36" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="L36" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="M36" t="s">
-        <v>48</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>46262</v>
-      </c>
-      <c r="B37" t="s">
-        <v>14</v>
-      </c>
-      <c r="C37" t="s">
-        <v>28</v>
-      </c>
-      <c r="D37" t="s">
-        <v>35</v>
-      </c>
-      <c r="E37" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="F37" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="G37" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="H37" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="I37" t="s">
-        <v>21</v>
-      </c>
-      <c r="J37" t="s">
-        <v>20</v>
-      </c>
-      <c r="K37" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="L37" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="M37" t="s">
-        <v>48</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>46262</v>
-      </c>
-      <c r="B38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C38" t="s">
-        <v>49</v>
-      </c>
-      <c r="D38" t="s">
-        <v>36</v>
-      </c>
-      <c r="E38" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="F38" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="G38" t="n">
-        <v>-10.7</v>
-      </c>
-      <c r="H38" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="I38" t="s">
-        <v>17</v>
-      </c>
-      <c r="J38" t="s">
-        <v>18</v>
-      </c>
-      <c r="K38" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="L38" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="M38" t="s">
-        <v>50</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>46262</v>
-      </c>
-      <c r="B39" t="s">
-        <v>22</v>
-      </c>
-      <c r="C39" t="s">
-        <v>49</v>
-      </c>
-      <c r="D39" t="s">
-        <v>36</v>
-      </c>
-      <c r="E39" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="F39" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="G39" t="n">
-        <v>-10.7</v>
-      </c>
-      <c r="H39" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="I39" t="s">
-        <v>17</v>
-      </c>
-      <c r="J39" t="s">
-        <v>20</v>
-      </c>
-      <c r="K39" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="L39" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="M39" t="s">
-        <v>50</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>46262</v>
-      </c>
-      <c r="B40" t="s">
-        <v>22</v>
-      </c>
-      <c r="C40" t="s">
-        <v>49</v>
-      </c>
-      <c r="D40" t="s">
-        <v>36</v>
-      </c>
-      <c r="E40" t="n">
-        <v>-4.8</v>
-      </c>
-      <c r="F40" t="n">
-        <v>-4.8</v>
-      </c>
-      <c r="G40" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="H40" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="I40" t="s">
-        <v>21</v>
-      </c>
-      <c r="J40" t="s">
-        <v>18</v>
-      </c>
-      <c r="K40" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="L40" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="M40" t="s">
-        <v>50</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>46262</v>
-      </c>
-      <c r="B41" t="s">
-        <v>22</v>
-      </c>
-      <c r="C41" t="s">
-        <v>49</v>
-      </c>
-      <c r="D41" t="s">
-        <v>36</v>
-      </c>
-      <c r="E41" t="n">
-        <v>-4.8</v>
-      </c>
-      <c r="F41" t="n">
-        <v>-4.8</v>
-      </c>
-      <c r="G41" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="H41" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="I41" t="s">
-        <v>21</v>
-      </c>
-      <c r="J41" t="s">
-        <v>20</v>
-      </c>
-      <c r="K41" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="L41" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="M41" t="s">
-        <v>50</v>
-      </c>
-      <c r="N41" t="n">
         <v>0</v>
       </c>
     </row>

--- a/files/NRL_upcoming_projections.xlsx
+++ b/files/NRL_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -59,109 +59,106 @@
     <t xml:space="preserve">19:50</t>
   </si>
   <si>
+    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
+  </si>
+  <si>
     <t xml:space="preserve">brisbane broncos</t>
   </si>
   <si>
+    <t xml:space="preserve">FT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Rain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accor Stadium, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dolphins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cbus Super Stadium, Gold Coast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">south sydney rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manly-warringah sea eagles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Go Media Stadium, Auckland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north queensland cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Queensland Country Bank Stadium, Townsville</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
     <t xml:space="preserve">melbourne storm</t>
   </si>
   <si>
-    <t xml:space="preserve">FT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Rain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suncorp Stadium, Brisbane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manly-warringah sea eagles</t>
+    <t xml:space="preserve">Sharks Stadium, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:00</t>
   </si>
   <si>
     <t xml:space="preserve">st george-illawarra dragons</t>
   </si>
   <si>
-    <t xml:space="preserve">4 Pines Park, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:00</t>
+    <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WIN Stadium, Wollongong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:05</t>
   </si>
   <si>
     <t xml:space="preserve">penrith panthers</t>
   </si>
   <si>
-    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
+    <t xml:space="preserve">wests tigers</t>
   </si>
   <si>
     <t xml:space="preserve">BlueBet Stadium, Penrith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">south sydney rabbitohs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cbus Super Stadium, Gold Coast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allianz Stadium, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north queensland cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wests tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Queensland Country Bank Stadium, Townsville</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">newcastle knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Go Media Stadium, Auckland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CommBank Stadium, Sydney</t>
   </si>
 </sst>
 </file>
@@ -500,8 +497,8 @@
   <cols>
     <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="5.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="26.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="29.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="29.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="26.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="27.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="16.71" hidden="0" customWidth="1"/>
@@ -560,7 +557,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46261</v>
+        <v>46268</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -572,16 +569,16 @@
         <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4</v>
+        <v>-5.6</v>
       </c>
       <c r="F2" t="n">
-        <v>4.4</v>
+        <v>-5.6</v>
       </c>
       <c r="G2" t="n">
-        <v>3.7</v>
+        <v>-8.9</v>
       </c>
       <c r="H2" t="n">
-        <v>48.8</v>
+        <v>46.7</v>
       </c>
       <c r="I2" t="s">
         <v>17</v>
@@ -590,21 +587,21 @@
         <v>18</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5</v>
+        <v>-10.5</v>
       </c>
       <c r="L2" t="n">
-        <v>49.5</v>
+        <v>52.5</v>
       </c>
       <c r="M2" t="s">
         <v>19</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46261</v>
+        <v>46268</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -616,16 +613,16 @@
         <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4</v>
+        <v>-5.6</v>
       </c>
       <c r="F3" t="n">
-        <v>4.4</v>
+        <v>-5.6</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7</v>
+        <v>-8.9</v>
       </c>
       <c r="H3" t="n">
-        <v>48.5</v>
+        <v>46.7</v>
       </c>
       <c r="I3" t="s">
         <v>17</v>
@@ -634,21 +631,21 @@
         <v>20</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5</v>
+        <v>-10.5</v>
       </c>
       <c r="L3" t="n">
-        <v>49.5</v>
+        <v>52.5</v>
       </c>
       <c r="M3" t="s">
         <v>19</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46261</v>
+        <v>46268</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -660,16 +657,16 @@
         <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2</v>
+        <v>-2.8</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2</v>
+        <v>-2.8</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8</v>
+        <v>-4.4</v>
       </c>
       <c r="H4" t="n">
-        <v>24.4</v>
+        <v>23.4</v>
       </c>
       <c r="I4" t="s">
         <v>21</v>
@@ -678,21 +675,21 @@
         <v>18</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5</v>
+        <v>-10.5</v>
       </c>
       <c r="L4" t="n">
-        <v>49.5</v>
+        <v>52.5</v>
       </c>
       <c r="M4" t="s">
         <v>19</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46261</v>
+        <v>46268</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -704,16 +701,16 @@
         <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2</v>
+        <v>-2.8</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2</v>
+        <v>-2.8</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8</v>
+        <v>-4.4</v>
       </c>
       <c r="H5" t="n">
-        <v>24.2</v>
+        <v>23.4</v>
       </c>
       <c r="I5" t="s">
         <v>21</v>
@@ -722,21 +719,21 @@
         <v>20</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5</v>
+        <v>-10.5</v>
       </c>
       <c r="L5" t="n">
-        <v>49.5</v>
+        <v>52.5</v>
       </c>
       <c r="M5" t="s">
         <v>19</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
@@ -748,16 +745,16 @@
         <v>24</v>
       </c>
       <c r="E6" t="n">
-        <v>-9.8</v>
+        <v>8.9</v>
       </c>
       <c r="F6" t="n">
-        <v>-9.8</v>
+        <v>8.9</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.5</v>
+        <v>11.9</v>
       </c>
       <c r="H6" t="n">
-        <v>47</v>
+        <v>52.8</v>
       </c>
       <c r="I6" t="s">
         <v>17</v>
@@ -766,10 +763,10 @@
         <v>18</v>
       </c>
       <c r="K6" t="n">
-        <v>-8</v>
+        <v>13</v>
       </c>
       <c r="L6" t="n">
-        <v>48.5</v>
+        <v>57</v>
       </c>
       <c r="M6" t="s">
         <v>25</v>
@@ -780,7 +777,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
@@ -792,16 +789,16 @@
         <v>24</v>
       </c>
       <c r="E7" t="n">
-        <v>-9.8</v>
+        <v>8.9</v>
       </c>
       <c r="F7" t="n">
-        <v>-9.8</v>
+        <v>8.9</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.5</v>
+        <v>11.9</v>
       </c>
       <c r="H7" t="n">
-        <v>47</v>
+        <v>52.8</v>
       </c>
       <c r="I7" t="s">
         <v>17</v>
@@ -810,10 +807,10 @@
         <v>20</v>
       </c>
       <c r="K7" t="n">
-        <v>-8</v>
+        <v>13</v>
       </c>
       <c r="L7" t="n">
-        <v>48.5</v>
+        <v>57</v>
       </c>
       <c r="M7" t="s">
         <v>25</v>
@@ -824,7 +821,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="B8" t="s">
         <v>22</v>
@@ -836,16 +833,16 @@
         <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.9</v>
+        <v>4.4</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.9</v>
+        <v>4.4</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3</v>
+        <v>5.9</v>
       </c>
       <c r="H8" t="n">
-        <v>23.5</v>
+        <v>26.4</v>
       </c>
       <c r="I8" t="s">
         <v>21</v>
@@ -854,10 +851,10 @@
         <v>18</v>
       </c>
       <c r="K8" t="n">
-        <v>-8</v>
+        <v>13</v>
       </c>
       <c r="L8" t="n">
-        <v>48.5</v>
+        <v>57</v>
       </c>
       <c r="M8" t="s">
         <v>25</v>
@@ -868,7 +865,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="B9" t="s">
         <v>22</v>
@@ -880,16 +877,16 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.9</v>
+        <v>4.4</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.9</v>
+        <v>4.4</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3</v>
+        <v>5.9</v>
       </c>
       <c r="H9" t="n">
-        <v>23.5</v>
+        <v>26.4</v>
       </c>
       <c r="I9" t="s">
         <v>21</v>
@@ -898,10 +895,10 @@
         <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>-8</v>
+        <v>13</v>
       </c>
       <c r="L9" t="n">
-        <v>48.5</v>
+        <v>57</v>
       </c>
       <c r="M9" t="s">
         <v>25</v>
@@ -912,7 +909,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="B10" t="s">
         <v>26</v>
@@ -924,16 +921,16 @@
         <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>-8.1</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>-8.1</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>-8.1</v>
+        <v>-0.5</v>
       </c>
       <c r="H10" t="n">
-        <v>39.8</v>
+        <v>50.9</v>
       </c>
       <c r="I10" t="s">
         <v>17</v>
@@ -942,13 +939,13 @@
         <v>18</v>
       </c>
       <c r="K10" t="n">
-        <v>-9</v>
+        <v>-21.5</v>
       </c>
       <c r="L10" t="n">
-        <v>40.5</v>
+        <v>54.5</v>
       </c>
       <c r="M10" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -956,7 +953,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="B11" t="s">
         <v>26</v>
@@ -968,16 +965,16 @@
         <v>28</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.1</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>-8.1</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>-8.1</v>
+        <v>-0.5</v>
       </c>
       <c r="H11" t="n">
-        <v>39.8</v>
+        <v>50.9</v>
       </c>
       <c r="I11" t="s">
         <v>17</v>
@@ -986,13 +983,13 @@
         <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>-9</v>
+        <v>-21.5</v>
       </c>
       <c r="L11" t="n">
-        <v>40.5</v>
+        <v>54.5</v>
       </c>
       <c r="M11" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1000,7 +997,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="B12" t="s">
         <v>26</v>
@@ -1012,16 +1009,16 @@
         <v>28</v>
       </c>
       <c r="E12" t="n">
-        <v>-4</v>
+        <v>0.5</v>
       </c>
       <c r="F12" t="n">
-        <v>-4</v>
+        <v>0.5</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.1</v>
+        <v>-0.2</v>
       </c>
       <c r="H12" t="n">
-        <v>19.9</v>
+        <v>25.4</v>
       </c>
       <c r="I12" t="s">
         <v>21</v>
@@ -1030,13 +1027,13 @@
         <v>18</v>
       </c>
       <c r="K12" t="n">
-        <v>-9</v>
+        <v>-21.5</v>
       </c>
       <c r="L12" t="n">
-        <v>40.5</v>
+        <v>54.5</v>
       </c>
       <c r="M12" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1044,7 +1041,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="B13" t="s">
         <v>26</v>
@@ -1056,16 +1053,16 @@
         <v>28</v>
       </c>
       <c r="E13" t="n">
-        <v>-4</v>
+        <v>0.5</v>
       </c>
       <c r="F13" t="n">
-        <v>-4</v>
+        <v>0.5</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.1</v>
+        <v>-0.2</v>
       </c>
       <c r="H13" t="n">
-        <v>19.9</v>
+        <v>25.4</v>
       </c>
       <c r="I13" t="s">
         <v>21</v>
@@ -1074,13 +1071,13 @@
         <v>20</v>
       </c>
       <c r="K13" t="n">
-        <v>-9</v>
+        <v>-21.5</v>
       </c>
       <c r="L13" t="n">
-        <v>40.5</v>
+        <v>54.5</v>
       </c>
       <c r="M13" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1088,28 +1085,28 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46263</v>
+        <v>46270</v>
       </c>
       <c r="B14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" t="s">
         <v>30</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>31</v>
       </c>
-      <c r="D14" t="s">
-        <v>32</v>
-      </c>
       <c r="E14" t="n">
-        <v>5.6</v>
+        <v>-8.8</v>
       </c>
       <c r="F14" t="n">
-        <v>5.6</v>
+        <v>-8.8</v>
       </c>
       <c r="G14" t="n">
-        <v>5.3</v>
+        <v>-13.6</v>
       </c>
       <c r="H14" t="n">
-        <v>51.7</v>
+        <v>48.8</v>
       </c>
       <c r="I14" t="s">
         <v>17</v>
@@ -1118,42 +1115,42 @@
         <v>18</v>
       </c>
       <c r="K14" t="n">
-        <v>10</v>
+        <v>-11</v>
       </c>
       <c r="L14" t="n">
-        <v>53.5</v>
+        <v>49</v>
       </c>
       <c r="M14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N14" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46263</v>
+        <v>46270</v>
       </c>
       <c r="B15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" t="s">
         <v>30</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>31</v>
       </c>
-      <c r="D15" t="s">
-        <v>32</v>
-      </c>
       <c r="E15" t="n">
-        <v>5.6</v>
+        <v>-8.8</v>
       </c>
       <c r="F15" t="n">
-        <v>5.6</v>
+        <v>-8.8</v>
       </c>
       <c r="G15" t="n">
-        <v>5.3</v>
+        <v>-13.6</v>
       </c>
       <c r="H15" t="n">
-        <v>51.3</v>
+        <v>48.6</v>
       </c>
       <c r="I15" t="s">
         <v>17</v>
@@ -1162,42 +1159,42 @@
         <v>20</v>
       </c>
       <c r="K15" t="n">
-        <v>10</v>
+        <v>-11</v>
       </c>
       <c r="L15" t="n">
-        <v>53.5</v>
+        <v>49</v>
       </c>
       <c r="M15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46263</v>
+        <v>46270</v>
       </c>
       <c r="B16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" t="s">
         <v>30</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>31</v>
       </c>
-      <c r="D16" t="s">
-        <v>32</v>
-      </c>
       <c r="E16" t="n">
-        <v>2.8</v>
+        <v>-4.4</v>
       </c>
       <c r="F16" t="n">
-        <v>2.8</v>
+        <v>-4.4</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7</v>
+        <v>-6.8</v>
       </c>
       <c r="H16" t="n">
-        <v>25.9</v>
+        <v>24.4</v>
       </c>
       <c r="I16" t="s">
         <v>21</v>
@@ -1206,42 +1203,42 @@
         <v>18</v>
       </c>
       <c r="K16" t="n">
-        <v>10</v>
+        <v>-11</v>
       </c>
       <c r="L16" t="n">
-        <v>53.5</v>
+        <v>49</v>
       </c>
       <c r="M16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46263</v>
+        <v>46270</v>
       </c>
       <c r="B17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" t="s">
         <v>30</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>31</v>
       </c>
-      <c r="D17" t="s">
-        <v>32</v>
-      </c>
       <c r="E17" t="n">
-        <v>2.8</v>
+        <v>-4.4</v>
       </c>
       <c r="F17" t="n">
-        <v>2.8</v>
+        <v>-4.4</v>
       </c>
       <c r="G17" t="n">
-        <v>2.7</v>
+        <v>-6.8</v>
       </c>
       <c r="H17" t="n">
-        <v>25.6</v>
+        <v>24.3</v>
       </c>
       <c r="I17" t="s">
         <v>21</v>
@@ -1250,42 +1247,42 @@
         <v>20</v>
       </c>
       <c r="K17" t="n">
-        <v>10</v>
+        <v>-11</v>
       </c>
       <c r="L17" t="n">
-        <v>53.5</v>
+        <v>49</v>
       </c>
       <c r="M17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N17" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46263</v>
+        <v>46270</v>
       </c>
       <c r="B18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" t="s">
         <v>34</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>35</v>
       </c>
-      <c r="D18" t="s">
-        <v>36</v>
-      </c>
       <c r="E18" t="n">
-        <v>-4.4</v>
+        <v>-0.2</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.4</v>
+        <v>-0.2</v>
       </c>
       <c r="G18" t="n">
-        <v>-6.3</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>50</v>
+        <v>53.3</v>
       </c>
       <c r="I18" t="s">
         <v>17</v>
@@ -1294,13 +1291,13 @@
         <v>18</v>
       </c>
       <c r="K18" t="n">
-        <v>-5.5</v>
+        <v>-5</v>
       </c>
       <c r="L18" t="n">
-        <v>47.5</v>
+        <v>54</v>
       </c>
       <c r="M18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1308,28 +1305,28 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46263</v>
+        <v>46270</v>
       </c>
       <c r="B19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" t="s">
         <v>34</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>35</v>
       </c>
-      <c r="D19" t="s">
-        <v>36</v>
-      </c>
       <c r="E19" t="n">
-        <v>-4.4</v>
+        <v>-0.2</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.4</v>
+        <v>-0.2</v>
       </c>
       <c r="G19" t="n">
-        <v>-6.3</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>50</v>
+        <v>53.3</v>
       </c>
       <c r="I19" t="s">
         <v>17</v>
@@ -1338,13 +1335,13 @@
         <v>20</v>
       </c>
       <c r="K19" t="n">
-        <v>-5.5</v>
+        <v>-5</v>
       </c>
       <c r="L19" t="n">
-        <v>47.5</v>
+        <v>54</v>
       </c>
       <c r="M19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -1352,28 +1349,28 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46263</v>
+        <v>46270</v>
       </c>
       <c r="B20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" t="s">
         <v>34</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>35</v>
       </c>
-      <c r="D20" t="s">
-        <v>36</v>
-      </c>
       <c r="E20" t="n">
-        <v>-2.2</v>
+        <v>-0.1</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.2</v>
+        <v>-0.1</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.1</v>
+        <v>0.5</v>
       </c>
       <c r="H20" t="n">
-        <v>25</v>
+        <v>26.6</v>
       </c>
       <c r="I20" t="s">
         <v>21</v>
@@ -1382,13 +1379,13 @@
         <v>18</v>
       </c>
       <c r="K20" t="n">
-        <v>-5.5</v>
+        <v>-5</v>
       </c>
       <c r="L20" t="n">
-        <v>47.5</v>
+        <v>54</v>
       </c>
       <c r="M20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -1396,28 +1393,28 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46263</v>
+        <v>46270</v>
       </c>
       <c r="B21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" t="s">
         <v>34</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>35</v>
       </c>
-      <c r="D21" t="s">
-        <v>36</v>
-      </c>
       <c r="E21" t="n">
-        <v>-2.2</v>
+        <v>-0.1</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2</v>
+        <v>-0.1</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.1</v>
+        <v>0.5</v>
       </c>
       <c r="H21" t="n">
-        <v>25</v>
+        <v>26.6</v>
       </c>
       <c r="I21" t="s">
         <v>21</v>
@@ -1426,13 +1423,13 @@
         <v>20</v>
       </c>
       <c r="K21" t="n">
-        <v>-5.5</v>
+        <v>-5</v>
       </c>
       <c r="L21" t="n">
-        <v>47.5</v>
+        <v>54</v>
       </c>
       <c r="M21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -1440,28 +1437,28 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46263</v>
+        <v>46270</v>
       </c>
       <c r="B22" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" t="s">
         <v>38</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>39</v>
       </c>
-      <c r="D22" t="s">
-        <v>40</v>
-      </c>
       <c r="E22" t="n">
-        <v>-10.7</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>-10.7</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>-9.5</v>
+        <v>-0.2</v>
       </c>
       <c r="H22" t="n">
-        <v>50.3</v>
+        <v>50.6</v>
       </c>
       <c r="I22" t="s">
         <v>17</v>
@@ -1470,42 +1467,42 @@
         <v>18</v>
       </c>
       <c r="K22" t="n">
-        <v>-13</v>
+        <v>8.5</v>
       </c>
       <c r="L22" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46263</v>
+        <v>46270</v>
       </c>
       <c r="B23" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" t="s">
         <v>38</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>39</v>
       </c>
-      <c r="D23" t="s">
-        <v>40</v>
-      </c>
       <c r="E23" t="n">
-        <v>-10.7</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>-10.7</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>-9.5</v>
+        <v>-0.2</v>
       </c>
       <c r="H23" t="n">
-        <v>50.3</v>
+        <v>50.5</v>
       </c>
       <c r="I23" t="s">
         <v>17</v>
@@ -1514,42 +1511,42 @@
         <v>20</v>
       </c>
       <c r="K23" t="n">
-        <v>-13</v>
+        <v>8.5</v>
       </c>
       <c r="L23" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46263</v>
+        <v>46270</v>
       </c>
       <c r="B24" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" t="s">
         <v>38</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>39</v>
       </c>
-      <c r="D24" t="s">
-        <v>40</v>
-      </c>
       <c r="E24" t="n">
-        <v>-5.4</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.4</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.8</v>
+        <v>-0.1</v>
       </c>
       <c r="H24" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="I24" t="s">
         <v>21</v>
@@ -1558,42 +1555,42 @@
         <v>18</v>
       </c>
       <c r="K24" t="n">
-        <v>-13</v>
+        <v>8.5</v>
       </c>
       <c r="L24" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46263</v>
+        <v>46270</v>
       </c>
       <c r="B25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" t="s">
         <v>38</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>39</v>
       </c>
-      <c r="D25" t="s">
-        <v>40</v>
-      </c>
       <c r="E25" t="n">
-        <v>-5.4</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.4</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.8</v>
+        <v>-0.1</v>
       </c>
       <c r="H25" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="I25" t="s">
         <v>21</v>
@@ -1602,42 +1599,42 @@
         <v>20</v>
       </c>
       <c r="K25" t="n">
-        <v>-13</v>
+        <v>8.5</v>
       </c>
       <c r="L25" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46264</v>
+        <v>46271</v>
       </c>
       <c r="B26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" t="s">
         <v>42</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>43</v>
       </c>
-      <c r="D26" t="s">
-        <v>44</v>
-      </c>
       <c r="E26" t="n">
-        <v>-8.7</v>
+        <v>5.6</v>
       </c>
       <c r="F26" t="n">
-        <v>-8.7</v>
+        <v>5.6</v>
       </c>
       <c r="G26" t="n">
-        <v>-12.4</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>47.9</v>
+        <v>49.2</v>
       </c>
       <c r="I26" t="s">
         <v>17</v>
@@ -1646,42 +1643,42 @@
         <v>18</v>
       </c>
       <c r="K26" t="n">
-        <v>-11.5</v>
+        <v>2.5</v>
       </c>
       <c r="L26" t="n">
-        <v>48.5</v>
+        <v>56</v>
       </c>
       <c r="M26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N26" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46264</v>
+        <v>46271</v>
       </c>
       <c r="B27" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" t="s">
         <v>42</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>43</v>
       </c>
-      <c r="D27" t="s">
-        <v>44</v>
-      </c>
       <c r="E27" t="n">
-        <v>-8.7</v>
+        <v>5.6</v>
       </c>
       <c r="F27" t="n">
-        <v>-8.7</v>
+        <v>5.6</v>
       </c>
       <c r="G27" t="n">
-        <v>-12.4</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>47.5</v>
+        <v>49.2</v>
       </c>
       <c r="I27" t="s">
         <v>17</v>
@@ -1690,42 +1687,42 @@
         <v>20</v>
       </c>
       <c r="K27" t="n">
-        <v>-11.5</v>
+        <v>2.5</v>
       </c>
       <c r="L27" t="n">
-        <v>48.5</v>
+        <v>56</v>
       </c>
       <c r="M27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N27" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46264</v>
+        <v>46271</v>
       </c>
       <c r="B28" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" t="s">
         <v>42</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>43</v>
       </c>
-      <c r="D28" t="s">
-        <v>44</v>
-      </c>
       <c r="E28" t="n">
-        <v>-4.3</v>
+        <v>2.8</v>
       </c>
       <c r="F28" t="n">
-        <v>-4.3</v>
+        <v>2.8</v>
       </c>
       <c r="G28" t="n">
-        <v>-6.2</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>24</v>
+        <v>24.6</v>
       </c>
       <c r="I28" t="s">
         <v>21</v>
@@ -1734,42 +1731,42 @@
         <v>18</v>
       </c>
       <c r="K28" t="n">
-        <v>-11.5</v>
+        <v>2.5</v>
       </c>
       <c r="L28" t="n">
-        <v>48.5</v>
+        <v>56</v>
       </c>
       <c r="M28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N28" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46264</v>
+        <v>46271</v>
       </c>
       <c r="B29" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" t="s">
         <v>42</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>43</v>
       </c>
-      <c r="D29" t="s">
-        <v>44</v>
-      </c>
       <c r="E29" t="n">
-        <v>-4.3</v>
+        <v>2.8</v>
       </c>
       <c r="F29" t="n">
-        <v>-4.3</v>
+        <v>2.8</v>
       </c>
       <c r="G29" t="n">
-        <v>-6.2</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>23.8</v>
+        <v>24.6</v>
       </c>
       <c r="I29" t="s">
         <v>21</v>
@@ -1778,42 +1775,42 @@
         <v>20</v>
       </c>
       <c r="K29" t="n">
-        <v>-11.5</v>
+        <v>2.5</v>
       </c>
       <c r="L29" t="n">
-        <v>48.5</v>
+        <v>56</v>
       </c>
       <c r="M29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N29" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46264</v>
+        <v>46271</v>
       </c>
       <c r="B30" t="s">
+        <v>45</v>
+      </c>
+      <c r="C30" t="s">
         <v>46</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>47</v>
       </c>
-      <c r="D30" t="s">
-        <v>48</v>
-      </c>
       <c r="E30" t="n">
-        <v>10.7</v>
+        <v>-19.4</v>
       </c>
       <c r="F30" t="n">
-        <v>10.7</v>
+        <v>-19.4</v>
       </c>
       <c r="G30" t="n">
-        <v>11.9</v>
+        <v>-20.6</v>
       </c>
       <c r="H30" t="n">
-        <v>48.6</v>
+        <v>43.8</v>
       </c>
       <c r="I30" t="s">
         <v>17</v>
@@ -1822,13 +1819,13 @@
         <v>18</v>
       </c>
       <c r="K30" t="n">
-        <v>6</v>
+        <v>-19.5</v>
       </c>
       <c r="L30" t="n">
-        <v>52.5</v>
+        <v>48</v>
       </c>
       <c r="M30" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -1836,28 +1833,28 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46264</v>
+        <v>46271</v>
       </c>
       <c r="B31" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" t="s">
         <v>46</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>47</v>
       </c>
-      <c r="D31" t="s">
-        <v>48</v>
-      </c>
       <c r="E31" t="n">
-        <v>10.7</v>
+        <v>-19.4</v>
       </c>
       <c r="F31" t="n">
-        <v>10.7</v>
+        <v>-19.4</v>
       </c>
       <c r="G31" t="n">
-        <v>11.9</v>
+        <v>-20.6</v>
       </c>
       <c r="H31" t="n">
-        <v>48.6</v>
+        <v>43.8</v>
       </c>
       <c r="I31" t="s">
         <v>17</v>
@@ -1866,13 +1863,13 @@
         <v>20</v>
       </c>
       <c r="K31" t="n">
-        <v>6</v>
+        <v>-19.5</v>
       </c>
       <c r="L31" t="n">
-        <v>52.5</v>
+        <v>48</v>
       </c>
       <c r="M31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -1880,28 +1877,28 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46264</v>
+        <v>46271</v>
       </c>
       <c r="B32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C32" t="s">
         <v>46</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>47</v>
       </c>
-      <c r="D32" t="s">
-        <v>48</v>
-      </c>
       <c r="E32" t="n">
-        <v>5.4</v>
+        <v>-9.7</v>
       </c>
       <c r="F32" t="n">
-        <v>5.4</v>
+        <v>-9.7</v>
       </c>
       <c r="G32" t="n">
-        <v>5.9</v>
+        <v>-10.3</v>
       </c>
       <c r="H32" t="n">
-        <v>24.3</v>
+        <v>21.9</v>
       </c>
       <c r="I32" t="s">
         <v>21</v>
@@ -1910,13 +1907,13 @@
         <v>18</v>
       </c>
       <c r="K32" t="n">
-        <v>6</v>
+        <v>-19.5</v>
       </c>
       <c r="L32" t="n">
-        <v>52.5</v>
+        <v>48</v>
       </c>
       <c r="M32" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -1924,28 +1921,28 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46264</v>
+        <v>46271</v>
       </c>
       <c r="B33" t="s">
+        <v>45</v>
+      </c>
+      <c r="C33" t="s">
         <v>46</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>47</v>
       </c>
-      <c r="D33" t="s">
-        <v>48</v>
-      </c>
       <c r="E33" t="n">
-        <v>5.4</v>
+        <v>-9.7</v>
       </c>
       <c r="F33" t="n">
-        <v>5.4</v>
+        <v>-9.7</v>
       </c>
       <c r="G33" t="n">
-        <v>5.9</v>
+        <v>-10.3</v>
       </c>
       <c r="H33" t="n">
-        <v>24.3</v>
+        <v>21.9</v>
       </c>
       <c r="I33" t="s">
         <v>21</v>
@@ -1954,13 +1951,13 @@
         <v>20</v>
       </c>
       <c r="K33" t="n">
-        <v>6</v>
+        <v>-19.5</v>
       </c>
       <c r="L33" t="n">
-        <v>52.5</v>
+        <v>48</v>
       </c>
       <c r="M33" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>

--- a/files/NRL_upcoming_projections.xlsx
+++ b/files/NRL_upcoming_projections.xlsx
@@ -1819,7 +1819,7 @@
         <v>18</v>
       </c>
       <c r="K30" t="n">
-        <v>-19.5</v>
+        <v>-19</v>
       </c>
       <c r="L30" t="n">
         <v>48</v>
@@ -1863,7 +1863,7 @@
         <v>20</v>
       </c>
       <c r="K31" t="n">
-        <v>-19.5</v>
+        <v>-19</v>
       </c>
       <c r="L31" t="n">
         <v>48</v>
@@ -1907,7 +1907,7 @@
         <v>18</v>
       </c>
       <c r="K32" t="n">
-        <v>-19.5</v>
+        <v>-19</v>
       </c>
       <c r="L32" t="n">
         <v>48</v>
@@ -1951,7 +1951,7 @@
         <v>20</v>
       </c>
       <c r="K33" t="n">
-        <v>-19.5</v>
+        <v>-19</v>
       </c>
       <c r="L33" t="n">
         <v>48</v>

--- a/files/NRL_upcoming_projections.xlsx
+++ b/files/NRL_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -56,13 +56,13 @@
     <t xml:space="preserve">Forecast Rain mm</t>
   </si>
   <si>
-    <t xml:space="preserve">19:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
+    <t xml:space="preserve">18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dolphins</t>
   </si>
   <si>
     <t xml:space="preserve">FT</t>
@@ -71,34 +71,25 @@
     <t xml:space="preserve">No Rain</t>
   </si>
   <si>
+    <t xml:space="preserve">Cbus Super Stadium, Gold Coast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">south sydney rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
     <t xml:space="preserve">Accor Stadium, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cbus Super Stadium, Gold Coast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">south sydney rabbitohs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney roosters</t>
   </si>
   <si>
     <t xml:space="preserve">17:00</t>
@@ -497,7 +488,7 @@
   <cols>
     <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="5.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="29.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="27.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="26.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="27.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
@@ -557,7 +548,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -569,16 +560,16 @@
         <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>-5.6</v>
+        <v>9.6</v>
       </c>
       <c r="F2" t="n">
-        <v>-5.6</v>
+        <v>9.6</v>
       </c>
       <c r="G2" t="n">
-        <v>-8.9</v>
+        <v>12.2</v>
       </c>
       <c r="H2" t="n">
-        <v>46.7</v>
+        <v>52.8</v>
       </c>
       <c r="I2" t="s">
         <v>17</v>
@@ -587,10 +578,10 @@
         <v>18</v>
       </c>
       <c r="K2" t="n">
-        <v>-10.5</v>
+        <v>13</v>
       </c>
       <c r="L2" t="n">
-        <v>52.5</v>
+        <v>57</v>
       </c>
       <c r="M2" t="s">
         <v>19</v>
@@ -601,7 +592,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -613,16 +604,16 @@
         <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>-5.6</v>
+        <v>9.6</v>
       </c>
       <c r="F3" t="n">
-        <v>-5.6</v>
+        <v>9.6</v>
       </c>
       <c r="G3" t="n">
-        <v>-8.9</v>
+        <v>12.2</v>
       </c>
       <c r="H3" t="n">
-        <v>46.7</v>
+        <v>52.8</v>
       </c>
       <c r="I3" t="s">
         <v>17</v>
@@ -631,10 +622,10 @@
         <v>20</v>
       </c>
       <c r="K3" t="n">
-        <v>-10.5</v>
+        <v>13</v>
       </c>
       <c r="L3" t="n">
-        <v>52.5</v>
+        <v>57</v>
       </c>
       <c r="M3" t="s">
         <v>19</v>
@@ -645,7 +636,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -657,16 +648,16 @@
         <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.8</v>
+        <v>4.8</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.8</v>
+        <v>4.8</v>
       </c>
       <c r="G4" t="n">
-        <v>-4.4</v>
+        <v>6.1</v>
       </c>
       <c r="H4" t="n">
-        <v>23.4</v>
+        <v>26.4</v>
       </c>
       <c r="I4" t="s">
         <v>21</v>
@@ -675,10 +666,10 @@
         <v>18</v>
       </c>
       <c r="K4" t="n">
-        <v>-10.5</v>
+        <v>13</v>
       </c>
       <c r="L4" t="n">
-        <v>52.5</v>
+        <v>57</v>
       </c>
       <c r="M4" t="s">
         <v>19</v>
@@ -689,7 +680,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -701,16 +692,16 @@
         <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.8</v>
+        <v>4.8</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.8</v>
+        <v>4.8</v>
       </c>
       <c r="G5" t="n">
-        <v>-4.4</v>
+        <v>6.1</v>
       </c>
       <c r="H5" t="n">
-        <v>23.4</v>
+        <v>26.4</v>
       </c>
       <c r="I5" t="s">
         <v>21</v>
@@ -719,10 +710,10 @@
         <v>20</v>
       </c>
       <c r="K5" t="n">
-        <v>-10.5</v>
+        <v>13</v>
       </c>
       <c r="L5" t="n">
-        <v>52.5</v>
+        <v>57</v>
       </c>
       <c r="M5" t="s">
         <v>19</v>
@@ -745,16 +736,16 @@
         <v>24</v>
       </c>
       <c r="E6" t="n">
-        <v>8.9</v>
+        <v>1.7</v>
       </c>
       <c r="F6" t="n">
-        <v>8.9</v>
+        <v>1.7</v>
       </c>
       <c r="G6" t="n">
-        <v>11.9</v>
+        <v>1.5</v>
       </c>
       <c r="H6" t="n">
-        <v>52.8</v>
+        <v>50.9</v>
       </c>
       <c r="I6" t="s">
         <v>17</v>
@@ -763,10 +754,10 @@
         <v>18</v>
       </c>
       <c r="K6" t="n">
-        <v>13</v>
+        <v>-21.5</v>
       </c>
       <c r="L6" t="n">
-        <v>57</v>
+        <v>54.5</v>
       </c>
       <c r="M6" t="s">
         <v>25</v>
@@ -789,16 +780,16 @@
         <v>24</v>
       </c>
       <c r="E7" t="n">
-        <v>8.9</v>
+        <v>1.7</v>
       </c>
       <c r="F7" t="n">
-        <v>8.9</v>
+        <v>1.7</v>
       </c>
       <c r="G7" t="n">
-        <v>11.9</v>
+        <v>1.5</v>
       </c>
       <c r="H7" t="n">
-        <v>52.8</v>
+        <v>50.9</v>
       </c>
       <c r="I7" t="s">
         <v>17</v>
@@ -807,10 +798,10 @@
         <v>20</v>
       </c>
       <c r="K7" t="n">
-        <v>13</v>
+        <v>-21.5</v>
       </c>
       <c r="L7" t="n">
-        <v>57</v>
+        <v>54.5</v>
       </c>
       <c r="M7" t="s">
         <v>25</v>
@@ -833,16 +824,16 @@
         <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="F8" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="G8" t="n">
-        <v>5.9</v>
+        <v>0.8</v>
       </c>
       <c r="H8" t="n">
-        <v>26.4</v>
+        <v>25.4</v>
       </c>
       <c r="I8" t="s">
         <v>21</v>
@@ -851,10 +842,10 @@
         <v>18</v>
       </c>
       <c r="K8" t="n">
-        <v>13</v>
+        <v>-21.5</v>
       </c>
       <c r="L8" t="n">
-        <v>57</v>
+        <v>54.5</v>
       </c>
       <c r="M8" t="s">
         <v>25</v>
@@ -877,16 +868,16 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="F9" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="G9" t="n">
-        <v>5.9</v>
+        <v>0.8</v>
       </c>
       <c r="H9" t="n">
-        <v>26.4</v>
+        <v>25.4</v>
       </c>
       <c r="I9" t="s">
         <v>21</v>
@@ -895,10 +886,10 @@
         <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>13</v>
+        <v>-21.5</v>
       </c>
       <c r="L9" t="n">
-        <v>57</v>
+        <v>54.5</v>
       </c>
       <c r="M9" t="s">
         <v>25</v>
@@ -909,7 +900,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B10" t="s">
         <v>26</v>
@@ -921,16 +912,16 @@
         <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>-10.2</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>-10.2</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5</v>
+        <v>-14.9</v>
       </c>
       <c r="H10" t="n">
-        <v>50.9</v>
+        <v>48.8</v>
       </c>
       <c r="I10" t="s">
         <v>17</v>
@@ -939,13 +930,13 @@
         <v>18</v>
       </c>
       <c r="K10" t="n">
-        <v>-21.5</v>
+        <v>-11</v>
       </c>
       <c r="L10" t="n">
-        <v>54.5</v>
+        <v>49</v>
       </c>
       <c r="M10" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -953,7 +944,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B11" t="s">
         <v>26</v>
@@ -965,16 +956,16 @@
         <v>28</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>-10.2</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>-10.2</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5</v>
+        <v>-14.9</v>
       </c>
       <c r="H11" t="n">
-        <v>50.9</v>
+        <v>48.8</v>
       </c>
       <c r="I11" t="s">
         <v>17</v>
@@ -983,13 +974,13 @@
         <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>-21.5</v>
+        <v>-11</v>
       </c>
       <c r="L11" t="n">
-        <v>54.5</v>
+        <v>49</v>
       </c>
       <c r="M11" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -997,7 +988,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B12" t="s">
         <v>26</v>
@@ -1009,16 +1000,16 @@
         <v>28</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5</v>
+        <v>-5.1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5</v>
+        <v>-5.1</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2</v>
+        <v>-7.4</v>
       </c>
       <c r="H12" t="n">
-        <v>25.4</v>
+        <v>24.4</v>
       </c>
       <c r="I12" t="s">
         <v>21</v>
@@ -1027,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="K12" t="n">
-        <v>-21.5</v>
+        <v>-11</v>
       </c>
       <c r="L12" t="n">
-        <v>54.5</v>
+        <v>49</v>
       </c>
       <c r="M12" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1041,7 +1032,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B13" t="s">
         <v>26</v>
@@ -1053,16 +1044,16 @@
         <v>28</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5</v>
+        <v>-5.1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5</v>
+        <v>-5.1</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2</v>
+        <v>-7.4</v>
       </c>
       <c r="H13" t="n">
-        <v>25.4</v>
+        <v>24.4</v>
       </c>
       <c r="I13" t="s">
         <v>21</v>
@@ -1071,13 +1062,13 @@
         <v>20</v>
       </c>
       <c r="K13" t="n">
-        <v>-21.5</v>
+        <v>-11</v>
       </c>
       <c r="L13" t="n">
-        <v>54.5</v>
+        <v>49</v>
       </c>
       <c r="M13" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1088,25 +1079,25 @@
         <v>46270</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E14" t="n">
-        <v>-8.8</v>
+        <v>-0.2</v>
       </c>
       <c r="F14" t="n">
-        <v>-8.8</v>
+        <v>-0.2</v>
       </c>
       <c r="G14" t="n">
-        <v>-13.6</v>
+        <v>1.1</v>
       </c>
       <c r="H14" t="n">
-        <v>48.8</v>
+        <v>53.3</v>
       </c>
       <c r="I14" t="s">
         <v>17</v>
@@ -1115,16 +1106,16 @@
         <v>18</v>
       </c>
       <c r="K14" t="n">
-        <v>-11</v>
+        <v>-5</v>
       </c>
       <c r="L14" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="M14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1132,25 +1123,25 @@
         <v>46270</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E15" t="n">
-        <v>-8.8</v>
+        <v>-0.2</v>
       </c>
       <c r="F15" t="n">
-        <v>-8.8</v>
+        <v>-0.2</v>
       </c>
       <c r="G15" t="n">
-        <v>-13.6</v>
+        <v>1.1</v>
       </c>
       <c r="H15" t="n">
-        <v>48.6</v>
+        <v>53.3</v>
       </c>
       <c r="I15" t="s">
         <v>17</v>
@@ -1159,16 +1150,16 @@
         <v>20</v>
       </c>
       <c r="K15" t="n">
-        <v>-11</v>
+        <v>-5</v>
       </c>
       <c r="L15" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="M15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1176,25 +1167,25 @@
         <v>46270</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.4</v>
+        <v>-0.1</v>
       </c>
       <c r="F16" t="n">
-        <v>-4.4</v>
+        <v>-0.1</v>
       </c>
       <c r="G16" t="n">
-        <v>-6.8</v>
+        <v>0.6</v>
       </c>
       <c r="H16" t="n">
-        <v>24.4</v>
+        <v>26.6</v>
       </c>
       <c r="I16" t="s">
         <v>21</v>
@@ -1203,16 +1194,16 @@
         <v>18</v>
       </c>
       <c r="K16" t="n">
-        <v>-11</v>
+        <v>-5</v>
       </c>
       <c r="L16" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="M16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1220,25 +1211,25 @@
         <v>46270</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E17" t="n">
-        <v>-4.4</v>
+        <v>-0.1</v>
       </c>
       <c r="F17" t="n">
-        <v>-4.4</v>
+        <v>-0.1</v>
       </c>
       <c r="G17" t="n">
-        <v>-6.8</v>
+        <v>0.6</v>
       </c>
       <c r="H17" t="n">
-        <v>24.3</v>
+        <v>26.6</v>
       </c>
       <c r="I17" t="s">
         <v>21</v>
@@ -1247,16 +1238,16 @@
         <v>20</v>
       </c>
       <c r="K17" t="n">
-        <v>-11</v>
+        <v>-5</v>
       </c>
       <c r="L17" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="M17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1264,25 +1255,25 @@
         <v>46270</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>-0.3</v>
       </c>
       <c r="H18" t="n">
-        <v>53.3</v>
+        <v>50.6</v>
       </c>
       <c r="I18" t="s">
         <v>17</v>
@@ -1291,13 +1282,13 @@
         <v>18</v>
       </c>
       <c r="K18" t="n">
-        <v>-5</v>
+        <v>8.5</v>
       </c>
       <c r="L18" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="M18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1308,25 +1299,25 @@
         <v>46270</v>
       </c>
       <c r="B19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>-0.3</v>
       </c>
       <c r="H19" t="n">
-        <v>53.3</v>
+        <v>50.6</v>
       </c>
       <c r="I19" t="s">
         <v>17</v>
@@ -1335,13 +1326,13 @@
         <v>20</v>
       </c>
       <c r="K19" t="n">
-        <v>-5</v>
+        <v>8.5</v>
       </c>
       <c r="L19" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="M19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -1352,25 +1343,25 @@
         <v>46270</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
         <v>-0.1</v>
       </c>
-      <c r="F20" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.5</v>
-      </c>
       <c r="H20" t="n">
-        <v>26.6</v>
+        <v>25.3</v>
       </c>
       <c r="I20" t="s">
         <v>21</v>
@@ -1379,13 +1370,13 @@
         <v>18</v>
       </c>
       <c r="K20" t="n">
-        <v>-5</v>
+        <v>8.5</v>
       </c>
       <c r="L20" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="M20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -1396,25 +1387,25 @@
         <v>46270</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
         <v>-0.1</v>
       </c>
-      <c r="F21" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.5</v>
-      </c>
       <c r="H21" t="n">
-        <v>26.6</v>
+        <v>25.3</v>
       </c>
       <c r="I21" t="s">
         <v>21</v>
@@ -1423,13 +1414,13 @@
         <v>20</v>
       </c>
       <c r="K21" t="n">
-        <v>-5</v>
+        <v>8.5</v>
       </c>
       <c r="L21" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="M21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -1437,28 +1428,28 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B22" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D22" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2</v>
+        <v>2.1</v>
       </c>
       <c r="H22" t="n">
-        <v>50.6</v>
+        <v>49.2</v>
       </c>
       <c r="I22" t="s">
         <v>17</v>
@@ -1467,42 +1458,42 @@
         <v>18</v>
       </c>
       <c r="K22" t="n">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="L22" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="M22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B23" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D23" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.2</v>
+        <v>2.1</v>
       </c>
       <c r="H23" t="n">
-        <v>50.5</v>
+        <v>49.2</v>
       </c>
       <c r="I23" t="s">
         <v>17</v>
@@ -1511,42 +1502,42 @@
         <v>20</v>
       </c>
       <c r="K23" t="n">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="L23" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="M23" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D24" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>25.3</v>
+        <v>24.6</v>
       </c>
       <c r="I24" t="s">
         <v>21</v>
@@ -1555,42 +1546,42 @@
         <v>18</v>
       </c>
       <c r="K24" t="n">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="L24" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="M24" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B25" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C25" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D25" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.1</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>25.3</v>
+        <v>24.6</v>
       </c>
       <c r="I25" t="s">
         <v>21</v>
@@ -1599,16 +1590,16 @@
         <v>20</v>
       </c>
       <c r="K25" t="n">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="L25" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="M25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N25" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1616,25 +1607,25 @@
         <v>46271</v>
       </c>
       <c r="B26" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C26" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D26" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E26" t="n">
-        <v>5.6</v>
+        <v>-19.4</v>
       </c>
       <c r="F26" t="n">
-        <v>5.6</v>
+        <v>-19.4</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>-20.6</v>
       </c>
       <c r="H26" t="n">
-        <v>49.2</v>
+        <v>43.8</v>
       </c>
       <c r="I26" t="s">
         <v>17</v>
@@ -1643,13 +1634,13 @@
         <v>18</v>
       </c>
       <c r="K26" t="n">
-        <v>2.5</v>
+        <v>-19</v>
       </c>
       <c r="L26" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="M26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -1660,25 +1651,25 @@
         <v>46271</v>
       </c>
       <c r="B27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E27" t="n">
-        <v>5.6</v>
+        <v>-19.4</v>
       </c>
       <c r="F27" t="n">
-        <v>5.6</v>
+        <v>-19.4</v>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>-20.6</v>
       </c>
       <c r="H27" t="n">
-        <v>49.2</v>
+        <v>43.8</v>
       </c>
       <c r="I27" t="s">
         <v>17</v>
@@ -1687,13 +1678,13 @@
         <v>20</v>
       </c>
       <c r="K27" t="n">
-        <v>2.5</v>
+        <v>-19</v>
       </c>
       <c r="L27" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="M27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -1704,25 +1695,25 @@
         <v>46271</v>
       </c>
       <c r="B28" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C28" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E28" t="n">
-        <v>2.8</v>
+        <v>-9.7</v>
       </c>
       <c r="F28" t="n">
-        <v>2.8</v>
+        <v>-9.7</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>-10.3</v>
       </c>
       <c r="H28" t="n">
-        <v>24.6</v>
+        <v>21.9</v>
       </c>
       <c r="I28" t="s">
         <v>21</v>
@@ -1731,13 +1722,13 @@
         <v>18</v>
       </c>
       <c r="K28" t="n">
-        <v>2.5</v>
+        <v>-19</v>
       </c>
       <c r="L28" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="M28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -1748,25 +1739,25 @@
         <v>46271</v>
       </c>
       <c r="B29" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C29" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D29" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E29" t="n">
-        <v>2.8</v>
+        <v>-9.7</v>
       </c>
       <c r="F29" t="n">
-        <v>2.8</v>
+        <v>-9.7</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>-10.3</v>
       </c>
       <c r="H29" t="n">
-        <v>24.6</v>
+        <v>21.9</v>
       </c>
       <c r="I29" t="s">
         <v>21</v>
@@ -1775,191 +1766,15 @@
         <v>20</v>
       </c>
       <c r="K29" t="n">
-        <v>2.5</v>
+        <v>-19</v>
       </c>
       <c r="L29" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="M29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>46271</v>
-      </c>
-      <c r="B30" t="s">
-        <v>45</v>
-      </c>
-      <c r="C30" t="s">
-        <v>46</v>
-      </c>
-      <c r="D30" t="s">
-        <v>47</v>
-      </c>
-      <c r="E30" t="n">
-        <v>-19.4</v>
-      </c>
-      <c r="F30" t="n">
-        <v>-19.4</v>
-      </c>
-      <c r="G30" t="n">
-        <v>-20.6</v>
-      </c>
-      <c r="H30" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="I30" t="s">
-        <v>17</v>
-      </c>
-      <c r="J30" t="s">
-        <v>18</v>
-      </c>
-      <c r="K30" t="n">
-        <v>-19</v>
-      </c>
-      <c r="L30" t="n">
-        <v>48</v>
-      </c>
-      <c r="M30" t="s">
-        <v>48</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>46271</v>
-      </c>
-      <c r="B31" t="s">
-        <v>45</v>
-      </c>
-      <c r="C31" t="s">
-        <v>46</v>
-      </c>
-      <c r="D31" t="s">
-        <v>47</v>
-      </c>
-      <c r="E31" t="n">
-        <v>-19.4</v>
-      </c>
-      <c r="F31" t="n">
-        <v>-19.4</v>
-      </c>
-      <c r="G31" t="n">
-        <v>-20.6</v>
-      </c>
-      <c r="H31" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="I31" t="s">
-        <v>17</v>
-      </c>
-      <c r="J31" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" t="n">
-        <v>-19</v>
-      </c>
-      <c r="L31" t="n">
-        <v>48</v>
-      </c>
-      <c r="M31" t="s">
-        <v>48</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>46271</v>
-      </c>
-      <c r="B32" t="s">
-        <v>45</v>
-      </c>
-      <c r="C32" t="s">
-        <v>46</v>
-      </c>
-      <c r="D32" t="s">
-        <v>47</v>
-      </c>
-      <c r="E32" t="n">
-        <v>-9.7</v>
-      </c>
-      <c r="F32" t="n">
-        <v>-9.7</v>
-      </c>
-      <c r="G32" t="n">
-        <v>-10.3</v>
-      </c>
-      <c r="H32" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="I32" t="s">
-        <v>21</v>
-      </c>
-      <c r="J32" t="s">
-        <v>18</v>
-      </c>
-      <c r="K32" t="n">
-        <v>-19</v>
-      </c>
-      <c r="L32" t="n">
-        <v>48</v>
-      </c>
-      <c r="M32" t="s">
-        <v>48</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>46271</v>
-      </c>
-      <c r="B33" t="s">
-        <v>45</v>
-      </c>
-      <c r="C33" t="s">
-        <v>46</v>
-      </c>
-      <c r="D33" t="s">
-        <v>47</v>
-      </c>
-      <c r="E33" t="n">
-        <v>-9.7</v>
-      </c>
-      <c r="F33" t="n">
-        <v>-9.7</v>
-      </c>
-      <c r="G33" t="n">
-        <v>-10.3</v>
-      </c>
-      <c r="H33" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="I33" t="s">
-        <v>21</v>
-      </c>
-      <c r="J33" t="s">
-        <v>20</v>
-      </c>
-      <c r="K33" t="n">
-        <v>-19</v>
-      </c>
-      <c r="L33" t="n">
-        <v>48</v>
-      </c>
-      <c r="M33" t="s">
-        <v>48</v>
-      </c>
-      <c r="N33" t="n">
         <v>0</v>
       </c>
     </row>

--- a/files/NRL_upcoming_projections.xlsx
+++ b/files/NRL_upcoming_projections.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -56,100 +56,58 @@
     <t xml:space="preserve">Forecast Rain mm</t>
   </si>
   <si>
-    <t xml:space="preserve">18:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans</t>
+    <t xml:space="preserve">19:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">south sydney rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Rain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allianz Stadium, Sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weather Adjusted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
   </si>
   <si>
     <t xml:space="preserve">dolphins</t>
   </si>
   <si>
-    <t xml:space="preserve">FT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Rain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cbus Super Stadium, Gold Coast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weather Adjusted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">south sydney rabbitohs</t>
+    <t xml:space="preserve">Go Media Stadium, Auckland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north queensland cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penrith panthers</t>
   </si>
   <si>
     <t xml:space="preserve">sydney roosters</t>
   </si>
   <si>
-    <t xml:space="preserve">Accor Stadium, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manly-warringah sea eagles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Go Media Stadium, Auckland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north queensland cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberra raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Queensland Country Bank Stadium, Townsville</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">melbourne storm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sharks Stadium, Sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st george-illawarra dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WIN Stadium, Wollongong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penrith panthers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wests tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BlueBet Stadium, Penrith</t>
+    <t xml:space="preserve">CommBank Stadium, Sydney</t>
   </si>
 </sst>
 </file>
@@ -488,8 +446,8 @@
   <cols>
     <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="5.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="27.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="26.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="26.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="24.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="27.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="16.71" hidden="0" customWidth="1"/>
@@ -498,7 +456,7 @@
     <col min="10" max="10" width="16.71" hidden="0" customWidth="1"/>
     <col min="11" max="11" width="11.71" hidden="0" customWidth="1"/>
     <col min="12" max="12" width="12.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="43.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="26.71" hidden="0" customWidth="1"/>
     <col min="14" max="14" width="16.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
@@ -548,7 +506,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46269</v>
+        <v>46276</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -560,16 +518,16 @@
         <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>9.6</v>
+        <v>-0.1</v>
       </c>
       <c r="F2" t="n">
-        <v>9.6</v>
+        <v>-0.1</v>
       </c>
       <c r="G2" t="n">
-        <v>12.2</v>
+        <v>-4.5</v>
       </c>
       <c r="H2" t="n">
-        <v>52.8</v>
+        <v>55.1</v>
       </c>
       <c r="I2" t="s">
         <v>17</v>
@@ -578,21 +536,21 @@
         <v>18</v>
       </c>
       <c r="K2" t="n">
-        <v>13</v>
+        <v>-7.5</v>
       </c>
       <c r="L2" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="M2" t="s">
         <v>19</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46269</v>
+        <v>46276</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -604,16 +562,16 @@
         <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>9.6</v>
+        <v>-0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>9.6</v>
+        <v>-0.1</v>
       </c>
       <c r="G3" t="n">
-        <v>12.2</v>
+        <v>-4.5</v>
       </c>
       <c r="H3" t="n">
-        <v>52.8</v>
+        <v>55</v>
       </c>
       <c r="I3" t="s">
         <v>17</v>
@@ -622,21 +580,21 @@
         <v>20</v>
       </c>
       <c r="K3" t="n">
-        <v>13</v>
+        <v>-7.5</v>
       </c>
       <c r="L3" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="M3" t="s">
         <v>19</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46269</v>
+        <v>46276</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -648,16 +606,16 @@
         <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>6.1</v>
+        <v>-2.3</v>
       </c>
       <c r="H4" t="n">
-        <v>26.4</v>
+        <v>27.5</v>
       </c>
       <c r="I4" t="s">
         <v>21</v>
@@ -666,21 +624,21 @@
         <v>18</v>
       </c>
       <c r="K4" t="n">
-        <v>13</v>
+        <v>-7.5</v>
       </c>
       <c r="L4" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="M4" t="s">
         <v>19</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46269</v>
+        <v>46276</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -692,16 +650,16 @@
         <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>6.1</v>
+        <v>-2.3</v>
       </c>
       <c r="H5" t="n">
-        <v>26.4</v>
+        <v>27.5</v>
       </c>
       <c r="I5" t="s">
         <v>21</v>
@@ -710,21 +668,21 @@
         <v>20</v>
       </c>
       <c r="K5" t="n">
-        <v>13</v>
+        <v>-7.5</v>
       </c>
       <c r="L5" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="M5" t="s">
         <v>19</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46269</v>
+        <v>46277</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
@@ -736,16 +694,16 @@
         <v>24</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7</v>
+        <v>-6.3</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7</v>
+        <v>-6.3</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5</v>
+        <v>-5.7</v>
       </c>
       <c r="H6" t="n">
-        <v>50.9</v>
+        <v>51.2</v>
       </c>
       <c r="I6" t="s">
         <v>17</v>
@@ -754,21 +712,21 @@
         <v>18</v>
       </c>
       <c r="K6" t="n">
-        <v>-21.5</v>
+        <v>-4</v>
       </c>
       <c r="L6" t="n">
-        <v>54.5</v>
+        <v>46.5</v>
       </c>
       <c r="M6" t="s">
         <v>25</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46269</v>
+        <v>46277</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
@@ -780,16 +738,16 @@
         <v>24</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7</v>
+        <v>-6.3</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7</v>
+        <v>-6.3</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5</v>
+        <v>-5.7</v>
       </c>
       <c r="H7" t="n">
-        <v>50.9</v>
+        <v>50.6</v>
       </c>
       <c r="I7" t="s">
         <v>17</v>
@@ -798,21 +756,21 @@
         <v>20</v>
       </c>
       <c r="K7" t="n">
-        <v>-21.5</v>
+        <v>-4</v>
       </c>
       <c r="L7" t="n">
-        <v>54.5</v>
+        <v>46.5</v>
       </c>
       <c r="M7" t="s">
         <v>25</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46269</v>
+        <v>46277</v>
       </c>
       <c r="B8" t="s">
         <v>22</v>
@@ -824,16 +782,16 @@
         <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9</v>
+        <v>-3.1</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9</v>
+        <v>-3.1</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8</v>
+        <v>-2.8</v>
       </c>
       <c r="H8" t="n">
-        <v>25.4</v>
+        <v>25.6</v>
       </c>
       <c r="I8" t="s">
         <v>21</v>
@@ -842,21 +800,21 @@
         <v>18</v>
       </c>
       <c r="K8" t="n">
-        <v>-21.5</v>
+        <v>-4</v>
       </c>
       <c r="L8" t="n">
-        <v>54.5</v>
+        <v>46.5</v>
       </c>
       <c r="M8" t="s">
         <v>25</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46269</v>
+        <v>46277</v>
       </c>
       <c r="B9" t="s">
         <v>22</v>
@@ -868,16 +826,16 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9</v>
+        <v>-3.1</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9</v>
+        <v>-3.1</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8</v>
+        <v>-2.8</v>
       </c>
       <c r="H9" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="I9" t="s">
         <v>21</v>
@@ -886,42 +844,42 @@
         <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>-21.5</v>
+        <v>-4</v>
       </c>
       <c r="L9" t="n">
-        <v>54.5</v>
+        <v>46.5</v>
       </c>
       <c r="M9" t="s">
         <v>25</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
         <v>26</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>27</v>
       </c>
-      <c r="D10" t="s">
-        <v>28</v>
-      </c>
       <c r="E10" t="n">
-        <v>-10.2</v>
+        <v>-9</v>
       </c>
       <c r="F10" t="n">
-        <v>-10.2</v>
+        <v>-9</v>
       </c>
       <c r="G10" t="n">
-        <v>-14.9</v>
+        <v>-12.2</v>
       </c>
       <c r="H10" t="n">
-        <v>48.8</v>
+        <v>51.3</v>
       </c>
       <c r="I10" t="s">
         <v>17</v>
@@ -930,42 +888,42 @@
         <v>18</v>
       </c>
       <c r="K10" t="n">
-        <v>-11</v>
+        <v>-7</v>
       </c>
       <c r="L10" t="n">
-        <v>49</v>
+        <v>47.5</v>
       </c>
       <c r="M10" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
         <v>26</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>27</v>
       </c>
-      <c r="D11" t="s">
-        <v>28</v>
-      </c>
       <c r="E11" t="n">
-        <v>-10.2</v>
+        <v>-9</v>
       </c>
       <c r="F11" t="n">
-        <v>-10.2</v>
+        <v>-9</v>
       </c>
       <c r="G11" t="n">
-        <v>-14.9</v>
+        <v>-12.2</v>
       </c>
       <c r="H11" t="n">
-        <v>48.8</v>
+        <v>51.2</v>
       </c>
       <c r="I11" t="s">
         <v>17</v>
@@ -974,42 +932,42 @@
         <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>-11</v>
+        <v>-7</v>
       </c>
       <c r="L11" t="n">
-        <v>49</v>
+        <v>47.5</v>
       </c>
       <c r="M11" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" t="s">
         <v>26</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>27</v>
       </c>
-      <c r="D12" t="s">
-        <v>28</v>
-      </c>
       <c r="E12" t="n">
-        <v>-5.1</v>
+        <v>-4.5</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.1</v>
+        <v>-4.5</v>
       </c>
       <c r="G12" t="n">
-        <v>-7.4</v>
+        <v>-6.1</v>
       </c>
       <c r="H12" t="n">
-        <v>24.4</v>
+        <v>25.7</v>
       </c>
       <c r="I12" t="s">
         <v>21</v>
@@ -1018,42 +976,42 @@
         <v>18</v>
       </c>
       <c r="K12" t="n">
-        <v>-11</v>
+        <v>-7</v>
       </c>
       <c r="L12" t="n">
-        <v>49</v>
+        <v>47.5</v>
       </c>
       <c r="M12" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" t="s">
         <v>26</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>27</v>
       </c>
-      <c r="D13" t="s">
-        <v>28</v>
-      </c>
       <c r="E13" t="n">
-        <v>-5.1</v>
+        <v>-4.5</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.1</v>
+        <v>-4.5</v>
       </c>
       <c r="G13" t="n">
-        <v>-7.4</v>
+        <v>-6.1</v>
       </c>
       <c r="H13" t="n">
-        <v>24.4</v>
+        <v>25.6</v>
       </c>
       <c r="I13" t="s">
         <v>21</v>
@@ -1062,42 +1020,42 @@
         <v>20</v>
       </c>
       <c r="K13" t="n">
-        <v>-11</v>
+        <v>-7</v>
       </c>
       <c r="L13" t="n">
-        <v>49</v>
+        <v>47.5</v>
       </c>
       <c r="M13" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46270</v>
+        <v>46278</v>
       </c>
       <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" t="s">
         <v>30</v>
       </c>
-      <c r="C14" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" t="s">
-        <v>32</v>
-      </c>
       <c r="E14" t="n">
-        <v>-0.2</v>
+        <v>-4</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2</v>
+        <v>-4</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1</v>
+        <v>-3.5</v>
       </c>
       <c r="H14" t="n">
-        <v>53.3</v>
+        <v>43.2</v>
       </c>
       <c r="I14" t="s">
         <v>17</v>
@@ -1106,13 +1064,13 @@
         <v>18</v>
       </c>
       <c r="K14" t="n">
-        <v>-5</v>
+        <v>-9</v>
       </c>
       <c r="L14" t="n">
-        <v>54</v>
+        <v>42.5</v>
       </c>
       <c r="M14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1120,28 +1078,28 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46270</v>
+        <v>46278</v>
       </c>
       <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" t="s">
         <v>30</v>
       </c>
-      <c r="C15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" t="s">
-        <v>32</v>
-      </c>
       <c r="E15" t="n">
-        <v>-0.2</v>
+        <v>-4</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2</v>
+        <v>-4</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1</v>
+        <v>-3.5</v>
       </c>
       <c r="H15" t="n">
-        <v>53.3</v>
+        <v>43.2</v>
       </c>
       <c r="I15" t="s">
         <v>17</v>
@@ -1150,13 +1108,13 @@
         <v>20</v>
       </c>
       <c r="K15" t="n">
-        <v>-5</v>
+        <v>-9</v>
       </c>
       <c r="L15" t="n">
-        <v>54</v>
+        <v>42.5</v>
       </c>
       <c r="M15" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1164,28 +1122,28 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46270</v>
+        <v>46278</v>
       </c>
       <c r="B16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" t="s">
         <v>30</v>
       </c>
-      <c r="C16" t="s">
-        <v>31</v>
-      </c>
-      <c r="D16" t="s">
-        <v>32</v>
-      </c>
       <c r="E16" t="n">
-        <v>-0.1</v>
+        <v>-2</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1</v>
+        <v>-2</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6</v>
+        <v>-1.8</v>
       </c>
       <c r="H16" t="n">
-        <v>26.6</v>
+        <v>21.6</v>
       </c>
       <c r="I16" t="s">
         <v>21</v>
@@ -1194,13 +1152,13 @@
         <v>18</v>
       </c>
       <c r="K16" t="n">
-        <v>-5</v>
+        <v>-9</v>
       </c>
       <c r="L16" t="n">
-        <v>54</v>
+        <v>42.5</v>
       </c>
       <c r="M16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1208,28 +1166,28 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46270</v>
+        <v>46278</v>
       </c>
       <c r="B17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" t="s">
         <v>30</v>
       </c>
-      <c r="C17" t="s">
-        <v>31</v>
-      </c>
-      <c r="D17" t="s">
-        <v>32</v>
-      </c>
       <c r="E17" t="n">
-        <v>-0.1</v>
+        <v>-2</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1</v>
+        <v>-2</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6</v>
+        <v>-1.8</v>
       </c>
       <c r="H17" t="n">
-        <v>26.6</v>
+        <v>21.6</v>
       </c>
       <c r="I17" t="s">
         <v>21</v>
@@ -1238,543 +1196,15 @@
         <v>20</v>
       </c>
       <c r="K17" t="n">
-        <v>-5</v>
+        <v>-9</v>
       </c>
       <c r="L17" t="n">
-        <v>54</v>
+        <v>42.5</v>
       </c>
       <c r="M17" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>46270</v>
-      </c>
-      <c r="B18" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" t="s">
-        <v>35</v>
-      </c>
-      <c r="D18" t="s">
-        <v>36</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="H18" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="I18" t="s">
-        <v>17</v>
-      </c>
-      <c r="J18" t="s">
-        <v>18</v>
-      </c>
-      <c r="K18" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="L18" t="n">
-        <v>51</v>
-      </c>
-      <c r="M18" t="s">
-        <v>37</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>46270</v>
-      </c>
-      <c r="B19" t="s">
-        <v>34</v>
-      </c>
-      <c r="C19" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19" t="s">
-        <v>36</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="H19" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="I19" t="s">
-        <v>17</v>
-      </c>
-      <c r="J19" t="s">
-        <v>20</v>
-      </c>
-      <c r="K19" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="L19" t="n">
-        <v>51</v>
-      </c>
-      <c r="M19" t="s">
-        <v>37</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>46270</v>
-      </c>
-      <c r="B20" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" t="s">
-        <v>35</v>
-      </c>
-      <c r="D20" t="s">
-        <v>36</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="H20" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="I20" t="s">
-        <v>21</v>
-      </c>
-      <c r="J20" t="s">
-        <v>18</v>
-      </c>
-      <c r="K20" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="L20" t="n">
-        <v>51</v>
-      </c>
-      <c r="M20" t="s">
-        <v>37</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>46270</v>
-      </c>
-      <c r="B21" t="s">
-        <v>34</v>
-      </c>
-      <c r="C21" t="s">
-        <v>35</v>
-      </c>
-      <c r="D21" t="s">
-        <v>36</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="H21" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="I21" t="s">
-        <v>21</v>
-      </c>
-      <c r="J21" t="s">
-        <v>20</v>
-      </c>
-      <c r="K21" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="L21" t="n">
-        <v>51</v>
-      </c>
-      <c r="M21" t="s">
-        <v>37</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>46271</v>
-      </c>
-      <c r="B22" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" t="s">
-        <v>39</v>
-      </c>
-      <c r="D22" t="s">
-        <v>40</v>
-      </c>
-      <c r="E22" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="F22" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="G22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H22" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="I22" t="s">
-        <v>17</v>
-      </c>
-      <c r="J22" t="s">
-        <v>18</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L22" t="n">
-        <v>56</v>
-      </c>
-      <c r="M22" t="s">
-        <v>41</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>46271</v>
-      </c>
-      <c r="B23" t="s">
-        <v>38</v>
-      </c>
-      <c r="C23" t="s">
-        <v>39</v>
-      </c>
-      <c r="D23" t="s">
-        <v>40</v>
-      </c>
-      <c r="E23" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="F23" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="G23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H23" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="I23" t="s">
-        <v>17</v>
-      </c>
-      <c r="J23" t="s">
-        <v>20</v>
-      </c>
-      <c r="K23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L23" t="n">
-        <v>56</v>
-      </c>
-      <c r="M23" t="s">
-        <v>41</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>46271</v>
-      </c>
-      <c r="B24" t="s">
-        <v>38</v>
-      </c>
-      <c r="C24" t="s">
-        <v>39</v>
-      </c>
-      <c r="D24" t="s">
-        <v>40</v>
-      </c>
-      <c r="E24" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F24" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="I24" t="s">
-        <v>21</v>
-      </c>
-      <c r="J24" t="s">
-        <v>18</v>
-      </c>
-      <c r="K24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L24" t="n">
-        <v>56</v>
-      </c>
-      <c r="M24" t="s">
-        <v>41</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>46271</v>
-      </c>
-      <c r="B25" t="s">
-        <v>38</v>
-      </c>
-      <c r="C25" t="s">
-        <v>39</v>
-      </c>
-      <c r="D25" t="s">
-        <v>40</v>
-      </c>
-      <c r="E25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="I25" t="s">
-        <v>21</v>
-      </c>
-      <c r="J25" t="s">
-        <v>20</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L25" t="n">
-        <v>56</v>
-      </c>
-      <c r="M25" t="s">
-        <v>41</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>46271</v>
-      </c>
-      <c r="B26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C26" t="s">
-        <v>43</v>
-      </c>
-      <c r="D26" t="s">
-        <v>44</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-19.4</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-19.4</v>
-      </c>
-      <c r="G26" t="n">
-        <v>-20.6</v>
-      </c>
-      <c r="H26" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="I26" t="s">
-        <v>17</v>
-      </c>
-      <c r="J26" t="s">
-        <v>18</v>
-      </c>
-      <c r="K26" t="n">
-        <v>-19</v>
-      </c>
-      <c r="L26" t="n">
-        <v>48</v>
-      </c>
-      <c r="M26" t="s">
-        <v>45</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>46271</v>
-      </c>
-      <c r="B27" t="s">
-        <v>42</v>
-      </c>
-      <c r="C27" t="s">
-        <v>43</v>
-      </c>
-      <c r="D27" t="s">
-        <v>44</v>
-      </c>
-      <c r="E27" t="n">
-        <v>-19.4</v>
-      </c>
-      <c r="F27" t="n">
-        <v>-19.4</v>
-      </c>
-      <c r="G27" t="n">
-        <v>-20.6</v>
-      </c>
-      <c r="H27" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="I27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J27" t="s">
-        <v>20</v>
-      </c>
-      <c r="K27" t="n">
-        <v>-19</v>
-      </c>
-      <c r="L27" t="n">
-        <v>48</v>
-      </c>
-      <c r="M27" t="s">
-        <v>45</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>46271</v>
-      </c>
-      <c r="B28" t="s">
-        <v>42</v>
-      </c>
-      <c r="C28" t="s">
-        <v>43</v>
-      </c>
-      <c r="D28" t="s">
-        <v>44</v>
-      </c>
-      <c r="E28" t="n">
-        <v>-9.7</v>
-      </c>
-      <c r="F28" t="n">
-        <v>-9.7</v>
-      </c>
-      <c r="G28" t="n">
-        <v>-10.3</v>
-      </c>
-      <c r="H28" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="I28" t="s">
-        <v>21</v>
-      </c>
-      <c r="J28" t="s">
-        <v>18</v>
-      </c>
-      <c r="K28" t="n">
-        <v>-19</v>
-      </c>
-      <c r="L28" t="n">
-        <v>48</v>
-      </c>
-      <c r="M28" t="s">
-        <v>45</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>46271</v>
-      </c>
-      <c r="B29" t="s">
-        <v>42</v>
-      </c>
-      <c r="C29" t="s">
-        <v>43</v>
-      </c>
-      <c r="D29" t="s">
-        <v>44</v>
-      </c>
-      <c r="E29" t="n">
-        <v>-9.7</v>
-      </c>
-      <c r="F29" t="n">
-        <v>-9.7</v>
-      </c>
-      <c r="G29" t="n">
-        <v>-10.3</v>
-      </c>
-      <c r="H29" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="I29" t="s">
-        <v>21</v>
-      </c>
-      <c r="J29" t="s">
-        <v>20</v>
-      </c>
-      <c r="K29" t="n">
-        <v>-19</v>
-      </c>
-      <c r="L29" t="n">
-        <v>48</v>
-      </c>
-      <c r="M29" t="s">
-        <v>45</v>
-      </c>
-      <c r="N29" t="n">
         <v>0</v>
       </c>
     </row>

--- a/files/NRL_upcoming_projections.xlsx
+++ b/files/NRL_upcoming_projections.xlsx
@@ -518,16 +518,16 @@
         <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1</v>
+        <v>-2.7</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1</v>
+        <v>-2.7</v>
       </c>
       <c r="G2" t="n">
-        <v>-4.5</v>
+        <v>-7.7</v>
       </c>
       <c r="H2" t="n">
-        <v>55.1</v>
+        <v>57.3</v>
       </c>
       <c r="I2" t="s">
         <v>17</v>
@@ -562,16 +562,16 @@
         <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1</v>
+        <v>-2.7</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1</v>
+        <v>-2.7</v>
       </c>
       <c r="G3" t="n">
-        <v>-4.5</v>
+        <v>-7.7</v>
       </c>
       <c r="H3" t="n">
-        <v>55</v>
+        <v>57.2</v>
       </c>
       <c r="I3" t="s">
         <v>17</v>
@@ -606,16 +606,16 @@
         <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>-1.4</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-1.4</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.3</v>
+        <v>-3.8</v>
       </c>
       <c r="H4" t="n">
-        <v>27.5</v>
+        <v>28.6</v>
       </c>
       <c r="I4" t="s">
         <v>21</v>
@@ -650,16 +650,16 @@
         <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>-1.4</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-1.4</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.3</v>
+        <v>-3.8</v>
       </c>
       <c r="H5" t="n">
-        <v>27.5</v>
+        <v>28.6</v>
       </c>
       <c r="I5" t="s">
         <v>21</v>
@@ -694,16 +694,16 @@
         <v>24</v>
       </c>
       <c r="E6" t="n">
-        <v>-6.3</v>
+        <v>-4.7</v>
       </c>
       <c r="F6" t="n">
-        <v>-6.3</v>
+        <v>-4.7</v>
       </c>
       <c r="G6" t="n">
-        <v>-5.7</v>
+        <v>-5</v>
       </c>
       <c r="H6" t="n">
-        <v>51.2</v>
+        <v>53</v>
       </c>
       <c r="I6" t="s">
         <v>17</v>
@@ -738,16 +738,16 @@
         <v>24</v>
       </c>
       <c r="E7" t="n">
-        <v>-6.3</v>
+        <v>-4.7</v>
       </c>
       <c r="F7" t="n">
-        <v>-6.3</v>
+        <v>-4.7</v>
       </c>
       <c r="G7" t="n">
-        <v>-5.7</v>
+        <v>-5</v>
       </c>
       <c r="H7" t="n">
-        <v>50.6</v>
+        <v>52.3</v>
       </c>
       <c r="I7" t="s">
         <v>17</v>
@@ -782,16 +782,16 @@
         <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.1</v>
+        <v>-2.4</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.1</v>
+        <v>-2.4</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.8</v>
+        <v>-2.5</v>
       </c>
       <c r="H8" t="n">
-        <v>25.6</v>
+        <v>26.5</v>
       </c>
       <c r="I8" t="s">
         <v>21</v>
@@ -826,16 +826,16 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.1</v>
+        <v>-2.4</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.1</v>
+        <v>-2.4</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.8</v>
+        <v>-2.5</v>
       </c>
       <c r="H9" t="n">
-        <v>25.3</v>
+        <v>26.2</v>
       </c>
       <c r="I9" t="s">
         <v>21</v>
@@ -870,16 +870,16 @@
         <v>27</v>
       </c>
       <c r="E10" t="n">
-        <v>-9</v>
+        <v>-11.5</v>
       </c>
       <c r="F10" t="n">
-        <v>-9</v>
+        <v>-11.5</v>
       </c>
       <c r="G10" t="n">
-        <v>-12.2</v>
+        <v>-13</v>
       </c>
       <c r="H10" t="n">
-        <v>51.3</v>
+        <v>54</v>
       </c>
       <c r="I10" t="s">
         <v>17</v>
@@ -914,16 +914,16 @@
         <v>27</v>
       </c>
       <c r="E11" t="n">
-        <v>-9</v>
+        <v>-11.5</v>
       </c>
       <c r="F11" t="n">
-        <v>-9</v>
+        <v>-11.5</v>
       </c>
       <c r="G11" t="n">
-        <v>-12.2</v>
+        <v>-13</v>
       </c>
       <c r="H11" t="n">
-        <v>51.2</v>
+        <v>53.9</v>
       </c>
       <c r="I11" t="s">
         <v>17</v>
@@ -958,16 +958,16 @@
         <v>27</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.5</v>
+        <v>-5.7</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.5</v>
+        <v>-5.7</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.1</v>
+        <v>-6.5</v>
       </c>
       <c r="H12" t="n">
-        <v>25.7</v>
+        <v>27</v>
       </c>
       <c r="I12" t="s">
         <v>21</v>
@@ -1002,16 +1002,16 @@
         <v>27</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.5</v>
+        <v>-5.7</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.5</v>
+        <v>-5.7</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.1</v>
+        <v>-6.5</v>
       </c>
       <c r="H13" t="n">
-        <v>25.6</v>
+        <v>26.9</v>
       </c>
       <c r="I13" t="s">
         <v>21</v>
@@ -1046,16 +1046,16 @@
         <v>30</v>
       </c>
       <c r="E14" t="n">
-        <v>-4</v>
+        <v>-1.8</v>
       </c>
       <c r="F14" t="n">
-        <v>-4</v>
+        <v>-1.8</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.5</v>
+        <v>-5.2</v>
       </c>
       <c r="H14" t="n">
-        <v>43.2</v>
+        <v>45.6</v>
       </c>
       <c r="I14" t="s">
         <v>17</v>
@@ -1090,16 +1090,16 @@
         <v>30</v>
       </c>
       <c r="E15" t="n">
-        <v>-4</v>
+        <v>-1.8</v>
       </c>
       <c r="F15" t="n">
-        <v>-4</v>
+        <v>-1.8</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.5</v>
+        <v>-5.2</v>
       </c>
       <c r="H15" t="n">
-        <v>43.2</v>
+        <v>45.6</v>
       </c>
       <c r="I15" t="s">
         <v>17</v>
@@ -1134,16 +1134,16 @@
         <v>30</v>
       </c>
       <c r="E16" t="n">
-        <v>-2</v>
+        <v>-0.9</v>
       </c>
       <c r="F16" t="n">
-        <v>-2</v>
+        <v>-0.9</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.8</v>
+        <v>-2.6</v>
       </c>
       <c r="H16" t="n">
-        <v>21.6</v>
+        <v>22.8</v>
       </c>
       <c r="I16" t="s">
         <v>21</v>
@@ -1178,16 +1178,16 @@
         <v>30</v>
       </c>
       <c r="E17" t="n">
-        <v>-2</v>
+        <v>-0.9</v>
       </c>
       <c r="F17" t="n">
-        <v>-2</v>
+        <v>-0.9</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.8</v>
+        <v>-2.6</v>
       </c>
       <c r="H17" t="n">
-        <v>21.6</v>
+        <v>22.8</v>
       </c>
       <c r="I17" t="s">
         <v>21</v>
